--- a/Document/IDD.xlsx
+++ b/Document/IDD.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\SoC_Design\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CA7864-7285-4199-9EB1-1FE21F65683E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F16341D-7116-49B5-8A12-6FA89759AD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
   </bookViews>
   <sheets>
     <sheet name="CPU" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CPU!$C$17:$G$17</definedName>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="337">
   <si>
     <t>top_cpu</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -284,14 +283,6 @@
   </si>
   <si>
     <t>Decoded rs Register</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded rt Register</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded rd Register</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1319,6 +1310,106 @@
   </si>
   <si>
     <t>w_ex_ctr_branch</t>
+  </si>
+  <si>
+    <t>w_ex_regwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_regwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_regwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegWrite Flag (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegWrite Flag (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegWrite Flag (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rd Register (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rt Register (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_dec_rt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_dec_rd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_dec_rt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_dec_rd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_dec_rt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_dec_rd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rd Register (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rt Register (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rd Register (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rt Register (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rd Register (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_ctr_regdst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_ctr_regdst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_ctr_regdst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegDst Flag (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegDst Flag (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegDst Flag (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2256,9 +2347,6 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2274,9 +2362,6 @@
     <xf numFmtId="176" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2310,16 +2395,58 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2337,52 +2464,16 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2745,32 +2836,32 @@
   <sheetData>
     <row r="1" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="144" t="s">
+      <c r="B2" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="145"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="145"/>
-      <c r="F2" s="145"/>
-      <c r="G2" s="146"/>
-      <c r="I2" s="123" t="s">
-        <v>108</v>
-      </c>
-      <c r="J2" s="124"/>
-      <c r="K2" s="123" t="s">
-        <v>102</v>
-      </c>
-      <c r="L2" s="125"/>
-      <c r="M2" s="124"/>
-      <c r="O2" s="123" t="s">
-        <v>108</v>
-      </c>
-      <c r="P2" s="124"/>
-      <c r="Q2" s="123" t="s">
-        <v>155</v>
-      </c>
-      <c r="R2" s="125"/>
-      <c r="S2" s="124"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="136"/>
+      <c r="I2" s="120" t="s">
+        <v>106</v>
+      </c>
+      <c r="J2" s="122"/>
+      <c r="K2" s="120" t="s">
+        <v>100</v>
+      </c>
+      <c r="L2" s="121"/>
+      <c r="M2" s="122"/>
+      <c r="O2" s="120" t="s">
+        <v>106</v>
+      </c>
+      <c r="P2" s="122"/>
+      <c r="Q2" s="120" t="s">
+        <v>153</v>
+      </c>
+      <c r="R2" s="121"/>
+      <c r="S2" s="122"/>
     </row>
     <row r="3" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="34" t="s">
@@ -2791,24 +2882,24 @@
       <c r="G3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="133" t="s">
-        <v>114</v>
-      </c>
-      <c r="J3" s="134"/>
-      <c r="K3" s="135" t="s">
-        <v>115</v>
-      </c>
-      <c r="L3" s="136"/>
-      <c r="M3" s="137"/>
-      <c r="O3" s="133" t="s">
-        <v>114</v>
-      </c>
-      <c r="P3" s="134"/>
-      <c r="Q3" s="135" t="s">
-        <v>243</v>
-      </c>
-      <c r="R3" s="136"/>
-      <c r="S3" s="137"/>
+      <c r="I3" s="129" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" s="130"/>
+      <c r="K3" s="131" t="s">
+        <v>113</v>
+      </c>
+      <c r="L3" s="132"/>
+      <c r="M3" s="133"/>
+      <c r="O3" s="129" t="s">
+        <v>112</v>
+      </c>
+      <c r="P3" s="130"/>
+      <c r="Q3" s="131" t="s">
+        <v>241</v>
+      </c>
+      <c r="R3" s="132"/>
+      <c r="S3" s="133"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B4" s="35">
@@ -2829,24 +2920,24 @@
       <c r="G4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="133" t="s">
-        <v>112</v>
-      </c>
-      <c r="J4" s="134"/>
-      <c r="K4" s="133" t="s">
-        <v>68</v>
-      </c>
-      <c r="L4" s="138"/>
-      <c r="M4" s="134"/>
-      <c r="O4" s="133" t="s">
-        <v>112</v>
-      </c>
-      <c r="P4" s="134"/>
-      <c r="Q4" s="133" t="s">
-        <v>68</v>
-      </c>
-      <c r="R4" s="138"/>
-      <c r="S4" s="134"/>
+      <c r="I4" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="J4" s="130"/>
+      <c r="K4" s="129" t="s">
+        <v>66</v>
+      </c>
+      <c r="L4" s="143"/>
+      <c r="M4" s="130"/>
+      <c r="O4" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="P4" s="130"/>
+      <c r="Q4" s="129" t="s">
+        <v>66</v>
+      </c>
+      <c r="R4" s="143"/>
+      <c r="S4" s="130"/>
     </row>
     <row r="5" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="54">
@@ -2867,24 +2958,24 @@
       <c r="G5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="139" t="s">
+      <c r="I5" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="140"/>
-      <c r="K5" s="141" t="s">
-        <v>107</v>
-      </c>
-      <c r="L5" s="122"/>
-      <c r="M5" s="142"/>
-      <c r="O5" s="139" t="s">
+      <c r="J5" s="124"/>
+      <c r="K5" s="125" t="s">
+        <v>105</v>
+      </c>
+      <c r="L5" s="126"/>
+      <c r="M5" s="127"/>
+      <c r="O5" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="140"/>
-      <c r="Q5" s="141" t="s">
-        <v>156</v>
-      </c>
-      <c r="R5" s="122"/>
-      <c r="S5" s="142"/>
+      <c r="P5" s="124"/>
+      <c r="Q5" s="125" t="s">
+        <v>154</v>
+      </c>
+      <c r="R5" s="126"/>
+      <c r="S5" s="127"/>
     </row>
     <row r="6" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="55">
@@ -2908,22 +2999,22 @@
       <c r="I6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="131" t="s">
-        <v>103</v>
-      </c>
-      <c r="K6" s="131"/>
-      <c r="L6" s="131"/>
+      <c r="J6" s="128" t="s">
+        <v>101</v>
+      </c>
+      <c r="K6" s="128"/>
+      <c r="L6" s="128"/>
       <c r="M6" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="131" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q6" s="131"/>
-      <c r="R6" s="131"/>
+      <c r="P6" s="128" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q6" s="128"/>
+      <c r="R6" s="128"/>
       <c r="S6" s="69" t="s">
         <v>8</v>
       </c>
@@ -2950,24 +3041,24 @@
       <c r="I7" s="70">
         <v>1</v>
       </c>
-      <c r="J7" s="143" t="s">
+      <c r="J7" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="143"/>
-      <c r="L7" s="143"/>
+      <c r="K7" s="137"/>
+      <c r="L7" s="137"/>
       <c r="M7" s="71" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="O7" s="87">
         <v>1</v>
       </c>
-      <c r="P7" s="132" t="s">
+      <c r="P7" s="144" t="s">
         <v>21</v>
       </c>
-      <c r="Q7" s="132"/>
-      <c r="R7" s="132"/>
+      <c r="Q7" s="144"/>
+      <c r="R7" s="144"/>
       <c r="S7" s="88" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2993,7 +3084,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="68" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K8" s="68" t="s">
         <v>1</v>
@@ -3007,13 +3098,13 @@
       <c r="O8" s="80">
         <v>2</v>
       </c>
-      <c r="P8" s="122" t="s">
+      <c r="P8" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="122"/>
-      <c r="R8" s="122"/>
+      <c r="Q8" s="126"/>
+      <c r="R8" s="126"/>
       <c r="S8" s="82" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3039,22 +3130,22 @@
         <v>1</v>
       </c>
       <c r="J9" s="73" t="s">
+        <v>95</v>
+      </c>
+      <c r="K9" s="73" t="s">
         <v>97</v>
-      </c>
-      <c r="K9" s="73" t="s">
-        <v>99</v>
       </c>
       <c r="L9" s="74" t="s">
         <v>21</v>
       </c>
       <c r="M9" s="75" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="O9" s="67" t="s">
         <v>41</v>
       </c>
       <c r="P9" s="68" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q9" s="68" t="s">
         <v>1</v>
@@ -3089,22 +3180,22 @@
         <v>2</v>
       </c>
       <c r="J10" s="77" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K10" s="77" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L10" s="78" t="s">
         <v>21</v>
       </c>
       <c r="M10" s="79" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="O10" s="72">
         <v>1</v>
       </c>
       <c r="P10" s="73" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q10" s="73" t="s">
         <v>5</v>
@@ -3113,7 +3204,7 @@
         <v>1</v>
       </c>
       <c r="S10" s="75" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3139,22 +3230,22 @@
         <v>3</v>
       </c>
       <c r="J11" s="66" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K11" s="66" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L11" s="81" t="s">
         <v>21</v>
       </c>
       <c r="M11" s="82" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="O11" s="72">
         <v>2</v>
       </c>
       <c r="P11" s="73" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q11" s="73" t="s">
         <v>6</v>
@@ -3163,7 +3254,7 @@
         <v>1</v>
       </c>
       <c r="S11" s="75" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3185,29 +3276,29 @@
       <c r="G12" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="126" t="s">
-        <v>110</v>
-      </c>
-      <c r="J12" s="127"/>
-      <c r="K12" s="128" t="s">
-        <v>111</v>
-      </c>
-      <c r="L12" s="129"/>
-      <c r="M12" s="130"/>
+      <c r="I12" s="138" t="s">
+        <v>108</v>
+      </c>
+      <c r="J12" s="139"/>
+      <c r="K12" s="140" t="s">
+        <v>109</v>
+      </c>
+      <c r="L12" s="141"/>
+      <c r="M12" s="142"/>
       <c r="O12" s="72">
         <v>3</v>
       </c>
       <c r="P12" s="73" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q12" s="73" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R12" s="74" t="s">
         <v>21</v>
       </c>
       <c r="S12" s="75" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3233,7 +3324,7 @@
         <v>4</v>
       </c>
       <c r="P13" s="73" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q13" s="73" t="s">
         <v>10</v>
@@ -3268,16 +3359,16 @@
         <v>5</v>
       </c>
       <c r="P14" s="77" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q14" s="73" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="R14" s="74" t="s">
         <v>21</v>
       </c>
       <c r="S14" s="79" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3303,28 +3394,28 @@
         <v>6</v>
       </c>
       <c r="P15" s="66" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q15" s="73" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="R15" s="74" t="s">
         <v>20</v>
       </c>
       <c r="S15" s="82" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="O16" s="126" t="s">
-        <v>110</v>
-      </c>
-      <c r="P16" s="127"/>
-      <c r="Q16" s="128" t="s">
-        <v>246</v>
-      </c>
-      <c r="R16" s="129"/>
-      <c r="S16" s="130"/>
+      <c r="O16" s="138" t="s">
+        <v>108</v>
+      </c>
+      <c r="P16" s="139"/>
+      <c r="Q16" s="140" t="s">
+        <v>244</v>
+      </c>
+      <c r="R16" s="141"/>
+      <c r="S16" s="142"/>
     </row>
     <row r="17" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="90" t="s">
@@ -3347,272 +3438,272 @@
       </c>
     </row>
     <row r="18" spans="2:19" ht="33" x14ac:dyDescent="0.3">
-      <c r="B18" s="92">
+      <c r="B18" s="145">
         <f>IF(C18="","",1)</f>
         <v>1</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D18" s="90" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F18" s="103" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G18" s="99" t="s">
-        <v>203</v>
-      </c>
-      <c r="I18" s="123" t="s">
-        <v>108</v>
-      </c>
-      <c r="J18" s="124"/>
-      <c r="K18" s="123" t="s">
-        <v>109</v>
-      </c>
-      <c r="L18" s="125"/>
-      <c r="M18" s="124"/>
-      <c r="O18" s="123" t="s">
-        <v>108</v>
-      </c>
-      <c r="P18" s="124"/>
-      <c r="Q18" s="123" t="s">
-        <v>165</v>
-      </c>
-      <c r="R18" s="125"/>
-      <c r="S18" s="124"/>
+        <v>201</v>
+      </c>
+      <c r="I18" s="120" t="s">
+        <v>106</v>
+      </c>
+      <c r="J18" s="122"/>
+      <c r="K18" s="120" t="s">
+        <v>107</v>
+      </c>
+      <c r="L18" s="121"/>
+      <c r="M18" s="122"/>
+      <c r="O18" s="120" t="s">
+        <v>106</v>
+      </c>
+      <c r="P18" s="122"/>
+      <c r="Q18" s="120" t="s">
+        <v>163</v>
+      </c>
+      <c r="R18" s="121"/>
+      <c r="S18" s="122"/>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B19" s="33">
-        <f>IF(C19="","",B18+1)</f>
+      <c r="B19" s="145">
+        <f t="shared" ref="B19:B50" si="0">IF(C19="","",B18+1)</f>
         <v>2</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D19" s="1">
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I19" s="133" t="s">
+        <v>87</v>
+      </c>
+      <c r="I19" s="129" t="s">
+        <v>112</v>
+      </c>
+      <c r="J19" s="130"/>
+      <c r="K19" s="131" t="s">
         <v>114</v>
       </c>
-      <c r="J19" s="134"/>
-      <c r="K19" s="135" t="s">
-        <v>116</v>
-      </c>
-      <c r="L19" s="136"/>
-      <c r="M19" s="137"/>
-      <c r="O19" s="133" t="s">
-        <v>114</v>
-      </c>
-      <c r="P19" s="134"/>
-      <c r="Q19" s="135" t="s">
-        <v>243</v>
-      </c>
-      <c r="R19" s="136"/>
-      <c r="S19" s="137"/>
+      <c r="L19" s="132"/>
+      <c r="M19" s="133"/>
+      <c r="O19" s="129" t="s">
+        <v>112</v>
+      </c>
+      <c r="P19" s="130"/>
+      <c r="Q19" s="131" t="s">
+        <v>241</v>
+      </c>
+      <c r="R19" s="132"/>
+      <c r="S19" s="133"/>
     </row>
     <row r="20" spans="2:19" ht="33" x14ac:dyDescent="0.3">
-      <c r="B20" s="92">
-        <f>IF(C20="","",B19+1)</f>
+      <c r="B20" s="145">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D20" s="1">
         <v>4</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="103" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="F20" s="103" t="s">
-        <v>80</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="I20" s="133" t="s">
-        <v>112</v>
-      </c>
-      <c r="J20" s="134"/>
-      <c r="K20" s="135" t="s">
-        <v>113</v>
-      </c>
-      <c r="L20" s="136"/>
-      <c r="M20" s="137"/>
-      <c r="O20" s="133" t="s">
-        <v>112</v>
-      </c>
-      <c r="P20" s="134"/>
-      <c r="Q20" s="133" t="s">
-        <v>68</v>
-      </c>
-      <c r="R20" s="138"/>
-      <c r="S20" s="134"/>
+      <c r="I20" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="J20" s="130"/>
+      <c r="K20" s="131" t="s">
+        <v>111</v>
+      </c>
+      <c r="L20" s="132"/>
+      <c r="M20" s="133"/>
+      <c r="O20" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="P20" s="130"/>
+      <c r="Q20" s="129" t="s">
+        <v>66</v>
+      </c>
+      <c r="R20" s="143"/>
+      <c r="S20" s="130"/>
     </row>
     <row r="21" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="33">
-        <f>IF(C21="","",B20+1)</f>
+      <c r="B21" s="145">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D21" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F21" s="103" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="I21" s="139" t="s">
+        <v>266</v>
+      </c>
+      <c r="I21" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="140"/>
-      <c r="K21" s="141" t="s">
-        <v>130</v>
-      </c>
-      <c r="L21" s="122"/>
-      <c r="M21" s="142"/>
-      <c r="O21" s="139" t="s">
+      <c r="J21" s="124"/>
+      <c r="K21" s="125" t="s">
+        <v>128</v>
+      </c>
+      <c r="L21" s="126"/>
+      <c r="M21" s="127"/>
+      <c r="O21" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="140"/>
-      <c r="Q21" s="141" t="s">
-        <v>166</v>
-      </c>
-      <c r="R21" s="122"/>
-      <c r="S21" s="142"/>
+      <c r="P21" s="124"/>
+      <c r="Q21" s="125" t="s">
+        <v>164</v>
+      </c>
+      <c r="R21" s="126"/>
+      <c r="S21" s="127"/>
     </row>
     <row r="22" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="33">
-        <f>IF(C22="","",B21+1)</f>
+      <c r="B22" s="145">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J22" s="131" t="s">
-        <v>103</v>
-      </c>
-      <c r="K22" s="131"/>
-      <c r="L22" s="131"/>
+      <c r="J22" s="128" t="s">
+        <v>101</v>
+      </c>
+      <c r="K22" s="128"/>
+      <c r="L22" s="128"/>
       <c r="M22" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P22" s="131" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q22" s="131"/>
-      <c r="R22" s="131"/>
+      <c r="P22" s="128" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q22" s="128"/>
+      <c r="R22" s="128"/>
       <c r="S22" s="69" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="23" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="33">
-        <f>IF(C23="","",B22+1)</f>
+      <c r="B23" s="145">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D23" s="1">
         <v>3</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="I23" s="70">
         <v>1</v>
       </c>
-      <c r="J23" s="143" t="s">
+      <c r="J23" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="K23" s="143"/>
-      <c r="L23" s="143"/>
+      <c r="K23" s="137"/>
+      <c r="L23" s="137"/>
       <c r="M23" s="71" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O23" s="87">
         <v>1</v>
       </c>
-      <c r="P23" s="132" t="s">
+      <c r="P23" s="144" t="s">
         <v>21</v>
       </c>
-      <c r="Q23" s="132"/>
-      <c r="R23" s="132"/>
+      <c r="Q23" s="144"/>
+      <c r="R23" s="144"/>
       <c r="S23" s="88" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="33">
-        <f>IF(C24="","",B23+1)</f>
+      <c r="B24" s="145">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D24" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" s="103" t="s">
+        <v>78</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="F24" s="103" t="s">
-        <v>80</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>87</v>
       </c>
       <c r="I24" s="67" t="s">
         <v>41</v>
       </c>
       <c r="J24" s="68" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K24" s="68" t="s">
         <v>1</v>
@@ -3626,55 +3717,55 @@
       <c r="O24" s="80">
         <v>2</v>
       </c>
-      <c r="P24" s="122" t="s">
+      <c r="P24" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="Q24" s="122"/>
-      <c r="R24" s="122"/>
+      <c r="Q24" s="126"/>
+      <c r="R24" s="126"/>
       <c r="S24" s="82" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="33">
-        <f>IF(C25="","",B24+1)</f>
+      <c r="B25" s="145">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D25" s="1">
         <v>1</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="I25" s="72">
         <v>1</v>
       </c>
       <c r="J25" s="73" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K25" s="73" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="L25" s="74" t="s">
         <v>20</v>
       </c>
       <c r="M25" s="75" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="O25" s="67" t="s">
         <v>41</v>
       </c>
       <c r="P25" s="68" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q25" s="68" t="s">
         <v>1</v>
@@ -3687,12 +3778,12 @@
       </c>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B26" s="33">
-        <f>IF(C26="","",B25+1)</f>
+      <c r="B26" s="145">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D26" s="90" t="s">
         <v>20</v>
@@ -3704,28 +3795,28 @@
         <v>53</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I26" s="76">
         <v>2</v>
       </c>
       <c r="J26" s="77" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K26" s="77" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L26" s="78" t="s">
         <v>20</v>
       </c>
       <c r="M26" s="79" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="O26" s="72">
         <v>1</v>
       </c>
       <c r="P26" s="73" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q26" s="73" t="s">
         <v>5</v>
@@ -3734,16 +3825,16 @@
         <v>1</v>
       </c>
       <c r="S26" s="75" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B27" s="33">
-        <f>IF(C27="","",B26+1)</f>
+      <c r="B27" s="145">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D27" s="90" t="s">
         <v>21</v>
@@ -3755,28 +3846,28 @@
         <v>36</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I27" s="83">
         <v>3</v>
       </c>
       <c r="J27" s="77" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K27" s="84" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L27" s="84">
         <v>1</v>
       </c>
       <c r="M27" s="85" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="O27" s="72">
         <v>2</v>
       </c>
       <c r="P27" s="73" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q27" s="73" t="s">
         <v>6</v>
@@ -3785,684 +3876,684 @@
         <v>1</v>
       </c>
       <c r="S27" s="75" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B28" s="33">
-        <f>IF(C28="","",B27+1)</f>
+      <c r="B28" s="145">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D28" s="1">
         <v>1</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I28" s="83">
         <v>4</v>
       </c>
       <c r="J28" s="84" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K28" s="84" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L28" s="84">
         <v>4</v>
       </c>
       <c r="M28" s="85" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O28" s="83">
         <v>3</v>
       </c>
       <c r="P28" s="73" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q28" s="73" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R28" s="74" t="s">
         <v>21</v>
       </c>
       <c r="S28" s="75" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="2:19" ht="33" x14ac:dyDescent="0.3">
-      <c r="B29" s="33">
-        <f>IF(C29="","",B28+1)</f>
+      <c r="B29" s="145">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
       </c>
       <c r="E29" s="102" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>53</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I29" s="83">
         <v>5</v>
       </c>
       <c r="J29" s="84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K29" s="84" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L29" s="86" t="s">
         <v>20</v>
       </c>
       <c r="M29" s="85" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="O29" s="83">
         <v>4</v>
       </c>
       <c r="P29" s="77" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q29" s="84" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="R29" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S29" s="85" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B30" s="33">
-        <f>IF(C30="","",B29+1)</f>
+      <c r="B30" s="145">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D30" s="1">
         <v>1</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>36</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I30" s="83">
         <v>6</v>
       </c>
       <c r="J30" s="84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K30" s="84" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="L30" s="84">
         <v>1</v>
       </c>
       <c r="M30" s="85" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O30" s="83">
         <v>5</v>
       </c>
       <c r="P30" s="77" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q30" s="84" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="R30" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S30" s="85" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="33">
-        <f>IF(C31="","",B30+1)</f>
+      <c r="B31" s="145">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>252</v>
+        <v>331</v>
       </c>
       <c r="D31" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>69</v>
+        <v>245</v>
+      </c>
+      <c r="F31" s="103" t="s">
+        <v>246</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>253</v>
+        <v>334</v>
       </c>
       <c r="I31" s="80">
         <v>7</v>
       </c>
       <c r="J31" s="66" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K31" s="66" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L31" s="66">
         <v>1</v>
       </c>
       <c r="M31" s="82" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O31" s="83">
         <v>6</v>
       </c>
       <c r="P31" s="77" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q31" s="84" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="R31" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S31" s="85" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="33">
-        <f>IF(C32="","",B31+1)</f>
+      <c r="B32" s="145">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="D32" s="90" t="s">
-        <v>20</v>
+        <v>250</v>
+      </c>
+      <c r="D32" s="1">
+        <v>6</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>91</v>
+        <v>242</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="I32" s="126" t="s">
-        <v>110</v>
-      </c>
-      <c r="J32" s="127"/>
-      <c r="K32" s="128" t="s">
-        <v>84</v>
-      </c>
-      <c r="L32" s="129"/>
-      <c r="M32" s="130"/>
+        <v>251</v>
+      </c>
+      <c r="I32" s="138" t="s">
+        <v>108</v>
+      </c>
+      <c r="J32" s="139"/>
+      <c r="K32" s="140" t="s">
+        <v>82</v>
+      </c>
+      <c r="L32" s="141"/>
+      <c r="M32" s="142"/>
       <c r="O32" s="83">
         <v>7</v>
       </c>
       <c r="P32" s="77" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q32" s="77" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="R32" s="78" t="s">
         <v>21</v>
       </c>
       <c r="S32" s="79" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B33" s="33">
-        <f>IF(C33="","",B32+1)</f>
+      <c r="B33" s="145">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="D33" s="101" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="102" t="s">
-        <v>244</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>36</v>
+        <v>321</v>
+      </c>
+      <c r="D33" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="F33" s="103" t="s">
+        <v>246</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>241</v>
+        <v>326</v>
       </c>
       <c r="O33" s="83">
         <v>8</v>
       </c>
       <c r="P33" s="84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q33" s="84" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R33" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S33" s="85" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B34" s="33">
-        <f>IF(C34="","",B33+1)</f>
+      <c r="B34" s="145">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C34" s="97" t="s">
-        <v>286</v>
+      <c r="C34" s="3" t="s">
+        <v>320</v>
       </c>
       <c r="D34" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F34" s="98" t="s">
-        <v>35</v>
-      </c>
-      <c r="G34" s="99" t="s">
-        <v>287</v>
+        <v>56</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="F34" s="103" t="s">
+        <v>246</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>319</v>
       </c>
       <c r="O34" s="83">
         <v>9</v>
       </c>
       <c r="P34" s="84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q34" s="84" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="R34" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S34" s="85" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="33">
-        <f>IF(C35="","",B34+1)</f>
+      <c r="B35" s="145">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D35" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O35" s="80">
         <v>10</v>
       </c>
       <c r="P35" s="66" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q35" s="66" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="R35" s="81" t="s">
         <v>20</v>
       </c>
       <c r="S35" s="82" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="36" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="145">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D36" s="101" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="102" t="s">
+        <v>242</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="O36" s="138" t="s">
+        <v>108</v>
+      </c>
+      <c r="P36" s="139"/>
+      <c r="Q36" s="140" t="s">
+        <v>245</v>
+      </c>
+      <c r="R36" s="141"/>
+      <c r="S36" s="142"/>
+    </row>
+    <row r="37" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="145">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C37" s="97" t="s">
+        <v>284</v>
+      </c>
+      <c r="D37" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F37" s="98" t="s">
+        <v>35</v>
+      </c>
+      <c r="G37" s="99" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="38" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B38" s="145">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D38" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I38" s="120" t="s">
+        <v>106</v>
+      </c>
+      <c r="J38" s="122"/>
+      <c r="K38" s="120" t="s">
+        <v>126</v>
+      </c>
+      <c r="L38" s="121"/>
+      <c r="M38" s="122"/>
+      <c r="O38" s="120" t="s">
+        <v>106</v>
+      </c>
+      <c r="P38" s="122"/>
+      <c r="Q38" s="120" t="s">
+        <v>177</v>
+      </c>
+      <c r="R38" s="121"/>
+      <c r="S38" s="122"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B39" s="145">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1</v>
+      </c>
+      <c r="E39" s="118" t="s">
+        <v>245</v>
+      </c>
+      <c r="F39" s="118" t="s">
+        <v>246</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="I39" s="129" t="s">
+        <v>112</v>
+      </c>
+      <c r="J39" s="130"/>
+      <c r="K39" s="131" t="s">
+        <v>127</v>
+      </c>
+      <c r="L39" s="132"/>
+      <c r="M39" s="133"/>
+      <c r="O39" s="129" t="s">
+        <v>112</v>
+      </c>
+      <c r="P39" s="130"/>
+      <c r="Q39" s="131" t="s">
+        <v>241</v>
+      </c>
+      <c r="R39" s="132"/>
+      <c r="S39" s="133"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B40" s="145">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F40" s="103" t="s">
+        <v>246</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="I40" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="J40" s="130"/>
+      <c r="K40" s="131" t="s">
+        <v>111</v>
+      </c>
+      <c r="L40" s="132"/>
+      <c r="M40" s="133"/>
+      <c r="O40" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="P40" s="130"/>
+      <c r="Q40" s="129" t="s">
+        <v>66</v>
+      </c>
+      <c r="R40" s="143"/>
+      <c r="S40" s="130"/>
+    </row>
+    <row r="41" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="145">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1</v>
+      </c>
+      <c r="E41" s="118" t="s">
+        <v>245</v>
+      </c>
+      <c r="F41" s="118" t="s">
+        <v>246</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="I41" s="123" t="s">
+        <v>8</v>
+      </c>
+      <c r="J41" s="124"/>
+      <c r="K41" s="125" t="s">
+        <v>129</v>
+      </c>
+      <c r="L41" s="126"/>
+      <c r="M41" s="127"/>
+      <c r="O41" s="123" t="s">
+        <v>8</v>
+      </c>
+      <c r="P41" s="124"/>
+      <c r="Q41" s="125" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="36" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="33">
-        <f>IF(C36="","",B35+1)</f>
-        <v>19</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="D36" s="1">
-        <v>1</v>
-      </c>
-      <c r="E36" s="120" t="s">
-        <v>247</v>
-      </c>
-      <c r="F36" s="120" t="s">
-        <v>248</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="O36" s="126" t="s">
-        <v>110</v>
-      </c>
-      <c r="P36" s="127"/>
-      <c r="Q36" s="128" t="s">
-        <v>247</v>
-      </c>
-      <c r="R36" s="129"/>
-      <c r="S36" s="130"/>
-    </row>
-    <row r="37" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="33">
-        <f>IF(C37="","",B36+1)</f>
-        <v>20</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="D37" s="1">
-        <v>1</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F37" s="103" t="s">
-        <v>248</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B38" s="33">
-        <f>IF(C38="","",B37+1)</f>
-        <v>21</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="D38" s="1">
-        <v>1</v>
-      </c>
-      <c r="E38" s="120" t="s">
-        <v>247</v>
-      </c>
-      <c r="F38" s="120" t="s">
-        <v>248</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="I38" s="123" t="s">
-        <v>108</v>
-      </c>
-      <c r="J38" s="124"/>
-      <c r="K38" s="123" t="s">
-        <v>128</v>
-      </c>
-      <c r="L38" s="125"/>
-      <c r="M38" s="124"/>
-      <c r="O38" s="123" t="s">
-        <v>108</v>
-      </c>
-      <c r="P38" s="124"/>
-      <c r="Q38" s="123" t="s">
-        <v>179</v>
-      </c>
-      <c r="R38" s="125"/>
-      <c r="S38" s="124"/>
-    </row>
-    <row r="39" spans="2:19" ht="33" x14ac:dyDescent="0.3">
-      <c r="B39" s="33">
-        <f>IF(C39="","",B38+1)</f>
-        <v>22</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D39" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="F39" s="103" t="s">
-        <v>80</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="I39" s="133" t="s">
-        <v>114</v>
-      </c>
-      <c r="J39" s="134"/>
-      <c r="K39" s="135" t="s">
-        <v>129</v>
-      </c>
-      <c r="L39" s="136"/>
-      <c r="M39" s="137"/>
-      <c r="O39" s="133" t="s">
-        <v>114</v>
-      </c>
-      <c r="P39" s="134"/>
-      <c r="Q39" s="135" t="s">
-        <v>243</v>
-      </c>
-      <c r="R39" s="136"/>
-      <c r="S39" s="137"/>
-    </row>
-    <row r="40" spans="2:19" ht="33" x14ac:dyDescent="0.3">
-      <c r="B40" s="33">
-        <f>IF(C40="","",B39+1)</f>
-        <v>23</v>
-      </c>
-      <c r="C40" s="118" t="s">
-        <v>229</v>
-      </c>
-      <c r="D40" s="119" t="s">
-        <v>20</v>
-      </c>
-      <c r="E40" s="117" t="s">
-        <v>244</v>
-      </c>
-      <c r="F40" s="121" t="s">
-        <v>270</v>
-      </c>
-      <c r="G40" s="118" t="s">
-        <v>231</v>
-      </c>
-      <c r="I40" s="133" t="s">
-        <v>112</v>
-      </c>
-      <c r="J40" s="134"/>
-      <c r="K40" s="135" t="s">
-        <v>113</v>
-      </c>
-      <c r="L40" s="136"/>
-      <c r="M40" s="137"/>
-      <c r="O40" s="133" t="s">
-        <v>112</v>
-      </c>
-      <c r="P40" s="134"/>
-      <c r="Q40" s="133" t="s">
-        <v>68</v>
-      </c>
-      <c r="R40" s="138"/>
-      <c r="S40" s="134"/>
-    </row>
-    <row r="41" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="104">
-        <f>IF(C41="","",B40+1)</f>
-        <v>24</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="D41" s="90" t="s">
-        <v>49</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="I41" s="139" t="s">
-        <v>8</v>
-      </c>
-      <c r="J41" s="140"/>
-      <c r="K41" s="141" t="s">
-        <v>131</v>
-      </c>
-      <c r="L41" s="122"/>
-      <c r="M41" s="142"/>
-      <c r="O41" s="139" t="s">
-        <v>8</v>
-      </c>
-      <c r="P41" s="140"/>
-      <c r="Q41" s="141" t="s">
-        <v>180</v>
-      </c>
-      <c r="R41" s="122"/>
-      <c r="S41" s="142"/>
-    </row>
-    <row r="42" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="104">
-        <f>IF(C42="","",B41+1)</f>
+      <c r="R41" s="126"/>
+      <c r="S41" s="127"/>
+    </row>
+    <row r="42" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="145">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>294</v>
+        <v>226</v>
       </c>
       <c r="D42" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>40</v>
+        <v>242</v>
+      </c>
+      <c r="F42" s="103" t="s">
+        <v>78</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>52</v>
+        <v>228</v>
       </c>
       <c r="I42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J42" s="131" t="s">
-        <v>103</v>
-      </c>
-      <c r="K42" s="131"/>
-      <c r="L42" s="131"/>
+      <c r="J42" s="128" t="s">
+        <v>101</v>
+      </c>
+      <c r="K42" s="128"/>
+      <c r="L42" s="128"/>
       <c r="M42" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P42" s="131" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q42" s="131"/>
-      <c r="R42" s="131"/>
+      <c r="P42" s="128" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q42" s="128"/>
+      <c r="R42" s="128"/>
       <c r="S42" s="69" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="43" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="33">
-        <f>IF(C43="","",B42+1)</f>
+      <c r="B43" s="145">
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="D43" s="90" t="s">
+      <c r="C43" s="116" t="s">
+        <v>227</v>
+      </c>
+      <c r="D43" s="117" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="F43" s="103" t="s">
-        <v>48</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>234</v>
+      <c r="E43" s="115" t="s">
+        <v>242</v>
+      </c>
+      <c r="F43" s="119" t="s">
+        <v>268</v>
+      </c>
+      <c r="G43" s="116" t="s">
+        <v>229</v>
       </c>
       <c r="I43" s="70">
         <v>1</v>
       </c>
-      <c r="J43" s="143" t="s">
+      <c r="J43" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="K43" s="143"/>
-      <c r="L43" s="143"/>
+      <c r="K43" s="137"/>
+      <c r="L43" s="137"/>
       <c r="M43" s="71" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O43" s="87">
         <v>1</v>
       </c>
-      <c r="P43" s="132" t="s">
+      <c r="P43" s="144" t="s">
         <v>21</v>
       </c>
-      <c r="Q43" s="132"/>
-      <c r="R43" s="132"/>
+      <c r="Q43" s="144"/>
+      <c r="R43" s="144"/>
       <c r="S43" s="88" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="33">
-        <f>IF(C44="","",B43+1)</f>
+      <c r="B44" s="145">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D44" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E44" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>245</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>68</v>
+        <v>246</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>199</v>
+        <v>315</v>
       </c>
       <c r="I44" s="67" t="s">
         <v>41</v>
       </c>
       <c r="J44" s="68" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K44" s="68" t="s">
         <v>1</v>
@@ -4476,55 +4567,55 @@
       <c r="O44" s="80">
         <v>2</v>
       </c>
-      <c r="P44" s="122" t="s">
+      <c r="P44" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="Q44" s="122"/>
-      <c r="R44" s="122"/>
+      <c r="Q44" s="126"/>
+      <c r="R44" s="126"/>
       <c r="S44" s="82" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="45" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="33">
-        <f>IF(C45="","",B44+1)</f>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="145">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>202</v>
+        <v>291</v>
       </c>
       <c r="D45" s="90" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="F45" s="103" t="s">
-        <v>264</v>
-      </c>
-      <c r="G45" s="99" t="s">
-        <v>200</v>
+        <v>47</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="I45" s="72">
         <v>1</v>
       </c>
       <c r="J45" s="73" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K45" s="73" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L45" s="73">
         <v>6</v>
       </c>
       <c r="M45" s="75" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="O45" s="67" t="s">
         <v>41</v>
       </c>
       <c r="P45" s="68" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q45" s="68" t="s">
         <v>1</v>
@@ -4537,45 +4628,45 @@
       </c>
     </row>
     <row r="46" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B46" s="33">
-        <f>IF(C46="","",B45+1)</f>
+      <c r="B46" s="145">
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D46" s="1">
-        <v>3</v>
+        <v>292</v>
+      </c>
+      <c r="D46" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>58</v>
+        <v>291</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>247</v>
+        <v>40</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>218</v>
+        <v>52</v>
       </c>
       <c r="I46" s="76">
         <v>2</v>
       </c>
       <c r="J46" s="77" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K46" s="77" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L46" s="77">
         <v>3</v>
       </c>
       <c r="M46" s="79" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="O46" s="72">
         <v>1</v>
       </c>
       <c r="P46" s="73" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q46" s="73" t="s">
         <v>5</v>
@@ -4584,49 +4675,49 @@
         <v>1</v>
       </c>
       <c r="S46" s="75" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="47" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="33">
-        <f>IF(C47="","",B46+1)</f>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="145">
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D47" s="1">
-        <v>1</v>
+        <v>230</v>
+      </c>
+      <c r="D47" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
+      </c>
+      <c r="F47" s="103" t="s">
+        <v>48</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="I47" s="80">
         <v>3</v>
       </c>
       <c r="J47" s="66" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K47" s="66" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L47" s="66">
         <v>4</v>
       </c>
       <c r="M47" s="82" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O47" s="72">
         <v>2</v>
       </c>
       <c r="P47" s="73" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q47" s="73" t="s">
         <v>6</v>
@@ -4635,298 +4726,298 @@
         <v>1</v>
       </c>
       <c r="S47" s="75" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="33">
-        <f>IF(C48="","",B47+1)</f>
+      <c r="B48" s="145">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D48" s="1">
-        <v>1</v>
+        <v>196</v>
+      </c>
+      <c r="D48" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>58</v>
+        <v>243</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>244</v>
+        <v>66</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="I48" s="126" t="s">
-        <v>110</v>
-      </c>
-      <c r="J48" s="127"/>
-      <c r="K48" s="128" t="s">
-        <v>69</v>
-      </c>
-      <c r="L48" s="129"/>
-      <c r="M48" s="130"/>
+        <v>197</v>
+      </c>
+      <c r="I48" s="138" t="s">
+        <v>108</v>
+      </c>
+      <c r="J48" s="139"/>
+      <c r="K48" s="140" t="s">
+        <v>67</v>
+      </c>
+      <c r="L48" s="141"/>
+      <c r="M48" s="142"/>
       <c r="O48" s="83">
         <v>3</v>
       </c>
       <c r="P48" s="73" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q48" s="73" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="R48" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S48" s="75" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="49" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B49" s="33">
-        <f>IF(C49="","",B48+1)</f>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="49" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+      <c r="B49" s="145">
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D49" s="1">
-        <v>1</v>
+        <v>200</v>
+      </c>
+      <c r="D49" s="90" t="s">
+        <v>21</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>226</v>
+        <v>243</v>
+      </c>
+      <c r="F49" s="103" t="s">
+        <v>262</v>
+      </c>
+      <c r="G49" s="99" t="s">
+        <v>198</v>
       </c>
       <c r="O49" s="83">
         <v>4</v>
       </c>
       <c r="P49" s="77" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q49" s="84" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="R49" s="84">
         <v>1</v>
       </c>
       <c r="S49" s="85" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="50" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="110">
-        <f>IF(C50="","",B49+1)</f>
+      <c r="B50" s="146">
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D50" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>67</v>
+        <v>245</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="O50" s="83">
         <v>5</v>
       </c>
       <c r="P50" s="77" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q50" s="84" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="R50" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S50" s="85" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="51" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B51" s="33">
-        <f>IF(C51="","",B50+1)</f>
+      <c r="B51" s="145">
+        <f t="shared" ref="B51:B82" si="1">IF(C51="","",B50+1)</f>
         <v>34</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="D51" s="90" t="s">
-        <v>57</v>
+        <v>209</v>
+      </c>
+      <c r="D51" s="1">
+        <v>1</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>43</v>
+        <v>245</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I51" s="123" t="s">
-        <v>108</v>
-      </c>
-      <c r="J51" s="124"/>
-      <c r="K51" s="123" t="s">
-        <v>135</v>
-      </c>
-      <c r="L51" s="125"/>
-      <c r="M51" s="124"/>
+        <v>223</v>
+      </c>
+      <c r="I51" s="120" t="s">
+        <v>106</v>
+      </c>
+      <c r="J51" s="122"/>
+      <c r="K51" s="120" t="s">
+        <v>133</v>
+      </c>
+      <c r="L51" s="121"/>
+      <c r="M51" s="122"/>
       <c r="O51" s="83">
         <v>6</v>
       </c>
       <c r="P51" s="77" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q51" s="84" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="R51" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S51" s="85" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B52" s="33">
-        <f>IF(C52="","",B51+1)</f>
+      <c r="B52" s="145">
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>250</v>
+        <v>204</v>
       </c>
       <c r="D52" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="I52" s="133" t="s">
-        <v>114</v>
-      </c>
-      <c r="J52" s="134"/>
-      <c r="K52" s="135" t="s">
-        <v>136</v>
-      </c>
-      <c r="L52" s="136"/>
-      <c r="M52" s="137"/>
+        <v>218</v>
+      </c>
+      <c r="I52" s="129" t="s">
+        <v>112</v>
+      </c>
+      <c r="J52" s="130"/>
+      <c r="K52" s="131" t="s">
+        <v>134</v>
+      </c>
+      <c r="L52" s="132"/>
+      <c r="M52" s="133"/>
       <c r="O52" s="83">
         <v>7</v>
       </c>
       <c r="P52" s="77" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q52" s="77" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="R52" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S52" s="79" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="53" spans="2:19" ht="33" x14ac:dyDescent="0.3">
-      <c r="B53" s="104">
-        <f>IF(C53="","",B52+1)</f>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="53" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B53" s="145">
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="C53" s="97" t="s">
-        <v>288</v>
-      </c>
-      <c r="D53" s="101" t="s">
-        <v>45</v>
-      </c>
-      <c r="E53" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="F53" s="98" t="s">
-        <v>42</v>
-      </c>
-      <c r="G53" s="99" t="s">
-        <v>50</v>
-      </c>
-      <c r="I53" s="133" t="s">
-        <v>112</v>
-      </c>
-      <c r="J53" s="134"/>
-      <c r="K53" s="135" t="s">
-        <v>113</v>
-      </c>
-      <c r="L53" s="136"/>
-      <c r="M53" s="137"/>
+      <c r="C53" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D53" s="1">
+        <v>1</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="I53" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="J53" s="130"/>
+      <c r="K53" s="131" t="s">
+        <v>111</v>
+      </c>
+      <c r="L53" s="132"/>
+      <c r="M53" s="133"/>
       <c r="O53" s="83">
         <v>8</v>
       </c>
       <c r="P53" s="84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q53" s="84" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="R53" s="84">
         <v>1</v>
       </c>
       <c r="S53" s="85" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="33">
-        <f>IF(C54="","",B53+1)</f>
+      <c r="B54" s="145">
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="D54" s="90" t="s">
-        <v>55</v>
+        <v>203</v>
+      </c>
+      <c r="D54" s="1">
+        <v>1</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F54" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="F54" s="1" t="s">
+        <v>245</v>
+      </c>
       <c r="G54" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="I54" s="139" t="s">
+        <v>217</v>
+      </c>
+      <c r="I54" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="140"/>
-      <c r="K54" s="141" t="s">
-        <v>137</v>
-      </c>
-      <c r="L54" s="122"/>
-      <c r="M54" s="142"/>
+      <c r="J54" s="124"/>
+      <c r="K54" s="125" t="s">
+        <v>135</v>
+      </c>
+      <c r="L54" s="126"/>
+      <c r="M54" s="127"/>
       <c r="O54" s="83">
         <v>9</v>
       </c>
       <c r="P54" s="84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q54" s="84" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R54" s="86" t="s">
         <v>20</v>
@@ -4936,21 +5027,21 @@
       </c>
     </row>
     <row r="55" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="33">
-        <f>IF(C55="","",B54+1)</f>
+      <c r="B55" s="145">
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>299</v>
       </c>
       <c r="D55" s="90" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>62</v>
@@ -4958,11 +5049,11 @@
       <c r="I55" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J55" s="131" t="s">
-        <v>103</v>
-      </c>
-      <c r="K55" s="131"/>
-      <c r="L55" s="131"/>
+      <c r="J55" s="128" t="s">
+        <v>101</v>
+      </c>
+      <c r="K55" s="128"/>
+      <c r="L55" s="128"/>
       <c r="M55" s="69" t="s">
         <v>8</v>
       </c>
@@ -4970,10 +5061,10 @@
         <v>10</v>
       </c>
       <c r="P55" s="66" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q55" s="66" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="R55" s="81" t="s">
         <v>20</v>
@@ -4984,102 +5075,102 @@
     </row>
     <row r="56" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="33">
-        <f>IF(C56="","",B55+1)</f>
+        <f t="shared" si="1"/>
         <v>39</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="D56" s="90" t="s">
-        <v>56</v>
+        <v>248</v>
+      </c>
+      <c r="D56" s="1">
+        <v>6</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>65</v>
+        <v>245</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>60</v>
+        <v>249</v>
       </c>
       <c r="I56" s="87">
         <v>1</v>
       </c>
-      <c r="J56" s="132" t="s">
+      <c r="J56" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="K56" s="132"/>
-      <c r="L56" s="132"/>
+      <c r="K56" s="144"/>
+      <c r="L56" s="144"/>
       <c r="M56" s="88" t="s">
-        <v>139</v>
-      </c>
-      <c r="O56" s="126" t="s">
-        <v>110</v>
-      </c>
-      <c r="P56" s="127"/>
-      <c r="Q56" s="128" t="s">
-        <v>248</v>
-      </c>
-      <c r="R56" s="129"/>
-      <c r="S56" s="130"/>
+        <v>137</v>
+      </c>
+      <c r="O56" s="138" t="s">
+        <v>108</v>
+      </c>
+      <c r="P56" s="139"/>
+      <c r="Q56" s="140" t="s">
+        <v>246</v>
+      </c>
+      <c r="R56" s="141"/>
+      <c r="S56" s="142"/>
     </row>
     <row r="57" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="33">
-        <f>IF(C57="","",B56+1)</f>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D57" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E57" s="1" t="s">
+      <c r="C57" s="97" t="s">
+        <v>286</v>
+      </c>
+      <c r="D57" s="101" t="s">
+        <v>45</v>
+      </c>
+      <c r="E57" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="103" t="s">
-        <v>66</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>61</v>
+      <c r="F57" s="98" t="s">
+        <v>42</v>
+      </c>
+      <c r="G57" s="99" t="s">
+        <v>50</v>
       </c>
       <c r="I57" s="80">
         <v>2</v>
       </c>
-      <c r="J57" s="122" t="s">
+      <c r="J57" s="126" t="s">
         <v>55</v>
       </c>
-      <c r="K57" s="122"/>
-      <c r="L57" s="122"/>
+      <c r="K57" s="126"/>
+      <c r="L57" s="126"/>
       <c r="M57" s="89" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="58" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B58" s="33">
-        <f>IF(C58="","",B57+1)</f>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="D58" s="1">
-        <v>5</v>
+        <v>294</v>
+      </c>
+      <c r="D58" s="90" t="s">
+        <v>55</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="I58" s="67" t="s">
         <v>41</v>
       </c>
       <c r="J58" s="68" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K58" s="68" t="s">
         <v>1</v>
@@ -5090,44 +5181,44 @@
       <c r="M58" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="123" t="s">
-        <v>108</v>
-      </c>
-      <c r="P58" s="124"/>
-      <c r="Q58" s="123" t="s">
-        <v>190</v>
-      </c>
-      <c r="R58" s="125"/>
-      <c r="S58" s="124"/>
-    </row>
-    <row r="59" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+      <c r="O58" s="120" t="s">
+        <v>106</v>
+      </c>
+      <c r="P58" s="122"/>
+      <c r="Q58" s="120" t="s">
+        <v>188</v>
+      </c>
+      <c r="R58" s="121"/>
+      <c r="S58" s="122"/>
+    </row>
+    <row r="59" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B59" s="33">
-        <f>IF(C59="","",B58+1)</f>
+        <f t="shared" si="1"/>
         <v>42</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D59" s="101" t="s">
-        <v>20</v>
-      </c>
-      <c r="E59" s="102" t="s">
-        <v>292</v>
+        <v>297</v>
+      </c>
+      <c r="D59" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>239</v>
+        <v>318</v>
       </c>
       <c r="I59" s="72">
         <v>1</v>
       </c>
       <c r="J59" s="73" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K59" s="73" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L59" s="74" t="s">
         <v>55</v>
@@ -5135,287 +5226,287 @@
       <c r="M59" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="O59" s="133" t="s">
-        <v>114</v>
-      </c>
-      <c r="P59" s="134"/>
-      <c r="Q59" s="135" t="s">
-        <v>243</v>
-      </c>
-      <c r="R59" s="136"/>
-      <c r="S59" s="137"/>
+      <c r="O59" s="129" t="s">
+        <v>112</v>
+      </c>
+      <c r="P59" s="130"/>
+      <c r="Q59" s="131" t="s">
+        <v>241</v>
+      </c>
+      <c r="R59" s="132"/>
+      <c r="S59" s="133"/>
     </row>
     <row r="60" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B60" s="33">
-        <f>IF(C60="","",B59+1)</f>
+        <f t="shared" si="1"/>
         <v>43</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D60" s="1">
-        <v>1</v>
+        <v>295</v>
+      </c>
+      <c r="D60" s="90" t="s">
+        <v>56</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F60" s="120" t="s">
-        <v>247</v>
+        <v>44</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>223</v>
+        <v>60</v>
       </c>
       <c r="I60" s="76">
         <v>2</v>
       </c>
       <c r="J60" s="84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K60" s="77" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="L60" s="77">
         <v>1</v>
       </c>
       <c r="M60" s="79" t="s">
-        <v>70</v>
-      </c>
-      <c r="O60" s="133" t="s">
-        <v>112</v>
-      </c>
-      <c r="P60" s="134"/>
-      <c r="Q60" s="133" t="s">
         <v>68</v>
       </c>
-      <c r="R60" s="138"/>
-      <c r="S60" s="134"/>
+      <c r="O60" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="P60" s="130"/>
+      <c r="Q60" s="129" t="s">
+        <v>66</v>
+      </c>
+      <c r="R60" s="143"/>
+      <c r="S60" s="130"/>
     </row>
     <row r="61" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="33">
-        <f>IF(C61="","",B60+1)</f>
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D61" s="1">
-        <v>1</v>
+        <v>296</v>
+      </c>
+      <c r="D61" s="90" t="s">
+        <v>56</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>244</v>
+        <v>63</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>221</v>
+        <v>319</v>
       </c>
       <c r="I61" s="83">
         <v>3</v>
       </c>
       <c r="J61" s="84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K61" s="84" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L61" s="84">
         <v>1</v>
       </c>
       <c r="M61" s="85" t="s">
-        <v>151</v>
-      </c>
-      <c r="O61" s="139" t="s">
+        <v>149</v>
+      </c>
+      <c r="O61" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="P61" s="140"/>
-      <c r="Q61" s="141" t="s">
-        <v>191</v>
-      </c>
-      <c r="R61" s="122"/>
-      <c r="S61" s="142"/>
+      <c r="P61" s="124"/>
+      <c r="Q61" s="125" t="s">
+        <v>189</v>
+      </c>
+      <c r="R61" s="126"/>
+      <c r="S61" s="127"/>
     </row>
     <row r="62" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B62" s="33">
-        <f>IF(C62="","",B61+1)</f>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>210</v>
+        <v>298</v>
       </c>
       <c r="D62" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F62" s="120" t="s">
-        <v>247</v>
+        <v>44</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>224</v>
+        <v>61</v>
       </c>
       <c r="I62" s="83">
         <v>4</v>
       </c>
       <c r="J62" s="84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K62" s="84" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L62" s="84">
         <v>1</v>
       </c>
       <c r="M62" s="85" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O62" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P62" s="131" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q62" s="131"/>
-      <c r="R62" s="131"/>
+      <c r="P62" s="128" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q62" s="128"/>
+      <c r="R62" s="128"/>
       <c r="S62" s="69" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B63" s="33">
-        <f>IF(C63="","",B62+1)</f>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="D63" s="90" t="s">
+        <v>236</v>
+      </c>
+      <c r="D63" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="E63" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F63" s="117" t="s">
-        <v>244</v>
+      <c r="E63" s="102" t="s">
+        <v>290</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="I63" s="83">
         <v>5</v>
       </c>
       <c r="J63" s="84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K63" s="84" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L63" s="84">
         <v>1</v>
       </c>
       <c r="M63" s="85" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O63" s="87">
         <v>1</v>
       </c>
-      <c r="P63" s="132" t="s">
+      <c r="P63" s="144" t="s">
         <v>21</v>
       </c>
-      <c r="Q63" s="132"/>
-      <c r="R63" s="132"/>
+      <c r="Q63" s="144"/>
+      <c r="R63" s="144"/>
       <c r="S63" s="88" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="64" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B64" s="33">
-        <f>IF(C64="","",B63+1)</f>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
-      <c r="C64" s="118" t="s">
-        <v>215</v>
-      </c>
-      <c r="D64" s="119" t="s">
-        <v>20</v>
+      <c r="C64" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D64" s="1">
+        <v>1</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F64" s="117" t="s">
-        <v>244</v>
-      </c>
-      <c r="G64" s="118" t="s">
-        <v>217</v>
+        <v>58</v>
+      </c>
+      <c r="F64" s="118" t="s">
+        <v>245</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>221</v>
       </c>
       <c r="I64" s="83">
         <v>6</v>
       </c>
       <c r="J64" s="84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K64" s="84" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L64" s="84">
         <v>1</v>
       </c>
       <c r="M64" s="85" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O64" s="80">
         <v>2</v>
       </c>
-      <c r="P64" s="122" t="s">
+      <c r="P64" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="Q64" s="122"/>
-      <c r="R64" s="122"/>
+      <c r="Q64" s="126"/>
+      <c r="R64" s="126"/>
       <c r="S64" s="82" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="65" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="33">
-        <f>IF(C65="","",B64+1)</f>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="D65" s="90" t="s">
-        <v>56</v>
+        <v>205</v>
+      </c>
+      <c r="D65" s="1">
+        <v>1</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F65" s="103" t="s">
-        <v>65</v>
+        <v>58</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>242</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>83</v>
+        <v>219</v>
       </c>
       <c r="I65" s="83">
         <v>7</v>
       </c>
       <c r="J65" s="84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K65" s="84" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L65" s="84">
         <v>1</v>
       </c>
       <c r="M65" s="85" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="O65" s="67" t="s">
         <v>41</v>
       </c>
       <c r="P65" s="68" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q65" s="68" t="s">
         <v>1</v>
@@ -5429,7 +5520,7 @@
     </row>
     <row r="66" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B66" s="33">
-        <f>IF(C66="","",B65+1)</f>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="C66" s="3" t="s">
@@ -5441,8 +5532,8 @@
       <c r="E66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F66" s="2" t="s">
-        <v>65</v>
+      <c r="F66" s="118" t="s">
+        <v>245</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>222</v>
@@ -5451,22 +5542,22 @@
         <v>8</v>
       </c>
       <c r="J66" s="84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K66" s="84" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L66" s="84">
         <v>1</v>
       </c>
       <c r="M66" s="85" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O66" s="72">
         <v>1</v>
       </c>
       <c r="P66" s="73" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q66" s="73" t="s">
         <v>5</v>
@@ -5475,49 +5566,49 @@
         <v>1</v>
       </c>
       <c r="S66" s="75" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="67" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B67" s="33">
-        <f>IF(C67="","",B66+1)</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D67" s="101" t="s">
-        <v>46</v>
+        <v>212</v>
+      </c>
+      <c r="D67" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>238</v>
+        <v>63</v>
+      </c>
+      <c r="F67" s="115" t="s">
+        <v>242</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>51</v>
+        <v>214</v>
       </c>
       <c r="I67" s="83">
         <v>9</v>
       </c>
       <c r="J67" s="84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K67" s="84" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L67" s="84">
         <v>3</v>
       </c>
       <c r="M67" s="85" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="O67" s="72">
         <v>2</v>
       </c>
       <c r="P67" s="73" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q67" s="73" t="s">
         <v>6</v>
@@ -5526,52 +5617,52 @@
         <v>1</v>
       </c>
       <c r="S67" s="75" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B68" s="33">
-        <f>IF(C68="","",B67+1)</f>
+        <f t="shared" si="1"/>
         <v>51</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="116" t="s">
         <v>213</v>
       </c>
-      <c r="D68" s="1">
-        <v>1</v>
+      <c r="D68" s="117" t="s">
+        <v>20</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>227</v>
+        <v>63</v>
+      </c>
+      <c r="F68" s="115" t="s">
+        <v>242</v>
+      </c>
+      <c r="G68" s="116" t="s">
+        <v>215</v>
       </c>
       <c r="I68" s="83">
         <v>10</v>
       </c>
       <c r="J68" s="84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K68" s="84" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L68" s="84">
         <v>1</v>
       </c>
       <c r="M68" s="85" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O68" s="83">
         <v>3</v>
       </c>
       <c r="P68" s="84" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q68" s="84" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="R68" s="86" t="s">
         <v>20</v>
@@ -5582,80 +5673,80 @@
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B69" s="33">
-        <f>IF(C69="","",B68+1)</f>
+        <f t="shared" si="1"/>
         <v>52</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>235</v>
+        <v>301</v>
       </c>
       <c r="D69" s="90" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="F69" s="103" t="s">
-        <v>244</v>
+        <v>63</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>233</v>
+        <v>81</v>
       </c>
       <c r="I69" s="83">
         <v>11</v>
       </c>
       <c r="J69" s="84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K69" s="84" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="L69" s="84">
         <v>1</v>
       </c>
       <c r="M69" s="85" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O69" s="83">
         <v>4</v>
       </c>
       <c r="P69" s="84" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q69" s="84" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="R69" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S69" s="85" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B70" s="33">
-        <f>IF(C70="","",B69+1)</f>
+        <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="C70" s="97" t="s">
-        <v>196</v>
-      </c>
-      <c r="D70" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E70" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="F70" s="98" t="s">
-        <v>246</v>
-      </c>
-      <c r="G70" s="99" t="s">
-        <v>197</v>
+      <c r="C70" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D70" s="1">
+        <v>1</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="I70" s="83">
         <v>12</v>
       </c>
       <c r="J70" s="84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K70" s="84" t="s">
         <v>18</v>
@@ -5664,49 +5755,49 @@
         <v>1</v>
       </c>
       <c r="M70" s="85" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O70" s="83">
         <v>5</v>
       </c>
       <c r="P70" s="84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q70" s="84" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="R70" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S70" s="85" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="71" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B71" s="33">
-        <f>IF(C71="","",B70+1)</f>
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="C71" s="93" t="s">
+      <c r="C71" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="D71" s="94" t="s">
-        <v>21</v>
-      </c>
-      <c r="E71" s="92" t="s">
-        <v>35</v>
-      </c>
-      <c r="F71" s="95" t="s">
-        <v>78</v>
-      </c>
-      <c r="G71" s="96" t="s">
-        <v>37</v>
+      <c r="D71" s="101" t="s">
+        <v>46</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="I71" s="80">
         <v>13</v>
       </c>
       <c r="J71" s="66" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K71" s="66" t="s">
         <v>19</v>
@@ -5715,592 +5806,768 @@
         <v>1</v>
       </c>
       <c r="M71" s="82" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O71" s="83">
         <v>6</v>
       </c>
       <c r="P71" s="84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q71" s="84" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R71" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S71" s="85" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="72" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B72" s="33">
-        <f>IF(C72="","",B71+1)</f>
+        <f t="shared" si="1"/>
         <v>55</v>
       </c>
-      <c r="C72" s="93" t="s">
-        <v>290</v>
-      </c>
-      <c r="D72" s="92">
-        <v>1</v>
-      </c>
-      <c r="E72" s="92" t="s">
-        <v>35</v>
-      </c>
-      <c r="F72" s="100" t="s">
-        <v>11</v>
-      </c>
-      <c r="G72" s="96" t="s">
-        <v>38</v>
-      </c>
-      <c r="I72" s="126" t="s">
-        <v>110</v>
-      </c>
-      <c r="J72" s="127"/>
-      <c r="K72" s="128" t="s">
+      <c r="C72" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D72" s="1">
+        <v>1</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="L72" s="129"/>
-      <c r="M72" s="130"/>
-      <c r="O72" s="126" t="s">
-        <v>110</v>
-      </c>
-      <c r="P72" s="127"/>
-      <c r="Q72" s="128" t="s">
-        <v>249</v>
-      </c>
-      <c r="R72" s="129"/>
-      <c r="S72" s="130"/>
-    </row>
-    <row r="73" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+      <c r="F72" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="I72" s="138" t="s">
+        <v>108</v>
+      </c>
+      <c r="J72" s="139"/>
+      <c r="K72" s="140" t="s">
+        <v>58</v>
+      </c>
+      <c r="L72" s="141"/>
+      <c r="M72" s="142"/>
+      <c r="O72" s="138" t="s">
+        <v>108</v>
+      </c>
+      <c r="P72" s="139"/>
+      <c r="Q72" s="140" t="s">
+        <v>247</v>
+      </c>
+      <c r="R72" s="141"/>
+      <c r="S72" s="142"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B73" s="33">
-        <f>IF(C73="","",B72+1)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
-      <c r="C73" s="105" t="s">
-        <v>266</v>
-      </c>
-      <c r="D73" s="115" t="s">
+      <c r="C73" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D73" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="106" t="s">
-        <v>248</v>
-      </c>
-      <c r="F73" s="116" t="s">
-        <v>284</v>
-      </c>
-      <c r="G73" s="108" t="s">
-        <v>269</v>
+      <c r="E73" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F73" s="103" t="s">
+        <v>242</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B74" s="33">
-        <f>IF(C74="","",B73+1)</f>
+        <f t="shared" si="1"/>
         <v>57</v>
       </c>
-      <c r="C74" s="105" t="s">
-        <v>260</v>
-      </c>
-      <c r="D74" s="106">
-        <v>1</v>
-      </c>
-      <c r="E74" s="106" t="s">
-        <v>248</v>
-      </c>
-      <c r="F74" s="107" t="s">
-        <v>14</v>
-      </c>
-      <c r="G74" s="108" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="C74" s="97" t="s">
+        <v>194</v>
+      </c>
+      <c r="D74" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E74" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="F74" s="98" t="s">
+        <v>244</v>
+      </c>
+      <c r="G74" s="99" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B75" s="33">
-        <f>IF(C75="","",B74+1)</f>
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="D75" s="1">
-        <v>1</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="G75" s="5" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="76" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+      <c r="C75" s="93" t="s">
+        <v>287</v>
+      </c>
+      <c r="D75" s="94" t="s">
+        <v>21</v>
+      </c>
+      <c r="E75" s="92" t="s">
+        <v>35</v>
+      </c>
+      <c r="F75" s="95" t="s">
+        <v>76</v>
+      </c>
+      <c r="G75" s="96" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B76" s="33">
-        <f>IF(C76="","",B75+1)</f>
+        <f t="shared" si="1"/>
         <v>59</v>
       </c>
-      <c r="C76" s="105" t="s">
-        <v>261</v>
-      </c>
-      <c r="D76" s="106">
-        <v>1</v>
-      </c>
-      <c r="E76" s="106" t="s">
-        <v>248</v>
-      </c>
-      <c r="F76" s="109" t="s">
-        <v>77</v>
-      </c>
-      <c r="G76" s="108" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="C76" s="93" t="s">
+        <v>288</v>
+      </c>
+      <c r="D76" s="92">
+        <v>1</v>
+      </c>
+      <c r="E76" s="92" t="s">
+        <v>35</v>
+      </c>
+      <c r="F76" s="100" t="s">
+        <v>11</v>
+      </c>
+      <c r="G76" s="96" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B77" s="33">
-        <f>IF(C77="","",B76+1)</f>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="C77" s="111" t="s">
-        <v>271</v>
-      </c>
-      <c r="D77" s="112" t="s">
+      <c r="C77" s="104" t="s">
+        <v>264</v>
+      </c>
+      <c r="D77" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="113" t="s">
-        <v>248</v>
+      <c r="E77" s="105" t="s">
+        <v>246</v>
       </c>
       <c r="F77" s="114" t="s">
-        <v>17</v>
-      </c>
-      <c r="G77" s="111" t="s">
-        <v>272</v>
+        <v>282</v>
+      </c>
+      <c r="G77" s="107" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B78" s="33">
-        <f>IF(C78="","",B77+1)</f>
+        <f t="shared" si="1"/>
         <v>61</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="D78" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>249</v>
+        <v>332</v>
+      </c>
+      <c r="D78" s="1">
+        <v>1</v>
+      </c>
+      <c r="E78" s="103" t="s">
+        <v>246</v>
       </c>
       <c r="F78" s="103" t="s">
-        <v>86</v>
+        <v>247</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>285</v>
+        <v>335</v>
       </c>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B79" s="33">
-        <f>IF(C79="","",B78+1)</f>
+        <f t="shared" si="1"/>
         <v>62</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="D79" s="1">
-        <v>1</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>86</v>
+        <v>323</v>
+      </c>
+      <c r="D79" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E79" s="103" t="s">
+        <v>246</v>
+      </c>
+      <c r="F79" s="103" t="s">
+        <v>247</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>282</v>
+        <v>328</v>
       </c>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B80" s="33">
-        <f>IF(C80="","",B79+1)</f>
+        <f t="shared" si="1"/>
         <v>63</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="D80" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E80" s="103" t="s">
+        <v>246</v>
+      </c>
+      <c r="F80" s="103" t="s">
+        <v>247</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B81" s="33">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
+      <c r="C81" s="104" t="s">
+        <v>258</v>
+      </c>
+      <c r="D81" s="105">
+        <v>1</v>
+      </c>
+      <c r="E81" s="105" t="s">
+        <v>246</v>
+      </c>
+      <c r="F81" s="106" t="s">
+        <v>14</v>
+      </c>
+      <c r="G81" s="107" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B82" s="33">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D82" s="1">
+        <v>1</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B83" s="33">
+        <f t="shared" ref="B83:B114" si="2">IF(C83="","",B82+1)</f>
+        <v>66</v>
+      </c>
+      <c r="C83" s="104" t="s">
+        <v>259</v>
+      </c>
+      <c r="D83" s="105">
+        <v>1</v>
+      </c>
+      <c r="E83" s="105" t="s">
+        <v>246</v>
+      </c>
+      <c r="F83" s="108" t="s">
+        <v>75</v>
+      </c>
+      <c r="G83" s="107" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B84" s="33">
+        <f t="shared" si="2"/>
+        <v>67</v>
+      </c>
+      <c r="C84" s="109" t="s">
+        <v>269</v>
+      </c>
+      <c r="D84" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F80" s="2" t="s">
+      <c r="E84" s="111" t="s">
+        <v>246</v>
+      </c>
+      <c r="F84" s="112" t="s">
+        <v>17</v>
+      </c>
+      <c r="G84" s="109" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B85" s="33">
+        <f t="shared" si="2"/>
+        <v>68</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D85" s="1">
+        <v>1</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B86" s="33">
+        <f t="shared" si="2"/>
+        <v>69</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D86" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F86" s="103" t="s">
+        <v>84</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B87" s="33">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D87" s="1">
+        <v>1</v>
+      </c>
+      <c r="E87" s="103" t="s">
+        <v>247</v>
+      </c>
+      <c r="F87" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G80" s="5" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B81" s="33" t="str">
-        <f>IF(C81="","",B80+1)</f>
+      <c r="G87" s="5" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B88" s="33">
+        <f t="shared" si="2"/>
+        <v>71</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D88" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E88" s="103" t="s">
+        <v>247</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B89" s="33">
+        <f t="shared" si="2"/>
+        <v>72</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="D89" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E89" s="103" t="s">
+        <v>247</v>
+      </c>
+      <c r="F89" s="103" t="s">
+        <v>64</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B90" s="33">
+        <f t="shared" si="2"/>
+        <v>73</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D90" s="1">
+        <v>1</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B91" s="33">
+        <f t="shared" si="2"/>
+        <v>74</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D91" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="92" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B92" s="33">
+        <f t="shared" si="2"/>
+        <v>75</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D92" s="1">
+        <v>1</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B93" s="33" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="E81" s="2"/>
-    </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B82" s="33" t="str">
-        <f>IF(C82="","",B81+1)</f>
+    </row>
+    <row r="94" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B94" s="33" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B83" s="33" t="str">
-        <f>IF(C83="","",B82+1)</f>
+    <row r="95" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B95" s="33" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="E83" s="2"/>
-    </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B84" s="33" t="str">
-        <f>IF(C84="","",B83+1)</f>
-        <v/>
-      </c>
-      <c r="D84" s="90"/>
-      <c r="F84" s="103"/>
-    </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B85" s="33" t="str">
-        <f>IF(C85="","",B84+1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B86" s="33" t="str">
-        <f>IF(C86="","",B85+1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B87" s="33" t="str">
-        <f>IF(C87="","",B86+1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B88" s="33" t="str">
-        <f>IF(C88="","",B87+1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B89" s="33" t="str">
-        <f>IF(C89="","",B88+1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B90" s="33" t="str">
-        <f>IF(C90="","",B89+1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B91" s="33" t="str">
-        <f>IF(C91="","",B90+1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B92" s="33" t="str">
-        <f>IF(C92="","",B91+1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B93" s="33" t="str">
-        <f>IF(C93="","",B92+1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B94" s="33" t="str">
-        <f>IF(C94="","",B93+1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B95" s="33" t="str">
-        <f>IF(C95="","",B94+1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B96" s="33" t="str">
-        <f>IF(C96="","",B95+1)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="97" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B97" s="33" t="str">
-        <f>IF(C97="","",B96+1)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="98" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B98" s="33" t="str">
-        <f>IF(C98="","",B97+1)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B99" s="33" t="str">
-        <f>IF(C99="","",B98+1)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B100" s="33" t="str">
-        <f>IF(C100="","",B99+1)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="101" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B101" s="33" t="str">
-        <f>IF(C101="","",B100+1)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="102" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B102" s="33" t="str">
-        <f>IF(C102="","",B101+1)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="103" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B103" s="33" t="str">
-        <f>IF(C103="","",B102+1)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="104" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B104" s="33" t="str">
-        <f>IF(C104="","",B103+1)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="105" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B105" s="33" t="str">
-        <f>IF(C105="","",B104+1)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="106" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B106" s="33" t="str">
-        <f>IF(C106="","",B105+1)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="107" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B107" s="33" t="str">
-        <f>IF(C107="","",B106+1)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="108" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B108" s="33" t="str">
-        <f>IF(C108="","",B107+1)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="109" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B109" s="33" t="str">
-        <f>IF(C109="","",B108+1)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="110" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B110" s="33" t="str">
-        <f>IF(C110="","",B109+1)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="111" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B111" s="33" t="str">
-        <f>IF(C111="","",B110+1)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="112" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B112" s="33" t="str">
-        <f>IF(C112="","",B111+1)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="113" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B113" s="33" t="str">
-        <f>IF(C113="","",B112+1)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="114" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B114" s="33" t="str">
-        <f>IF(C114="","",B113+1)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="115" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B115" s="33" t="str">
-        <f>IF(C115="","",B114+1)</f>
+        <f t="shared" ref="B115:B146" si="3">IF(C115="","",B114+1)</f>
         <v/>
       </c>
     </row>
     <row r="116" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B116" s="33" t="str">
-        <f>IF(C116="","",B115+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="117" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B117" s="33" t="str">
-        <f>IF(C117="","",B116+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="118" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B118" s="33" t="str">
-        <f>IF(C118="","",B117+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="119" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B119" s="33" t="str">
-        <f>IF(C119="","",B118+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="120" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B120" s="33" t="str">
-        <f>IF(C120="","",B119+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="121" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B121" s="33" t="str">
-        <f>IF(C121="","",B120+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="122" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B122" s="33" t="str">
-        <f>IF(C122="","",B121+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="123" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B123" s="33" t="str">
-        <f>IF(C123="","",B122+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="124" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B124" s="33" t="str">
-        <f>IF(C124="","",B123+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="125" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B125" s="33" t="str">
-        <f>IF(C125="","",B124+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="126" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B126" s="33" t="str">
-        <f>IF(C126="","",B125+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="127" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B127" s="33" t="str">
-        <f>IF(C127="","",B126+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="128" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B128" s="33" t="str">
-        <f>IF(C128="","",B127+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="129" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B129" s="33" t="str">
-        <f>IF(C129="","",B128+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="130" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B130" s="33" t="str">
-        <f>IF(C130="","",B129+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="131" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B131" s="33" t="str">
-        <f>IF(C131="","",B130+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="132" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B132" s="33" t="str">
-        <f>IF(C132="","",B131+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="133" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B133" s="33" t="str">
-        <f>IF(C133="","",B132+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="134" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B134" s="33" t="str">
-        <f>IF(C134="","",B133+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="135" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B135" s="33" t="str">
-        <f>IF(C135="","",B134+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="136" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B136" s="33" t="str">
-        <f>IF(C136="","",B135+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="137" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B137" s="33" t="str">
-        <f>IF(C137="","",B136+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="138" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B138" s="33" t="str">
-        <f>IF(C138="","",B137+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="139" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B139" s="33" t="str">
-        <f>IF(C139="","",B138+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="140" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B140" s="33" t="str">
-        <f>IF(C140="","",B139+1)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -6311,39 +6578,51 @@
     </sortState>
   </autoFilter>
   <mergeCells count="102">
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="P44:R44"/>
+    <mergeCell ref="O56:P56"/>
+    <mergeCell ref="Q56:S56"/>
+    <mergeCell ref="P62:R62"/>
+    <mergeCell ref="P63:R63"/>
+    <mergeCell ref="P64:R64"/>
+    <mergeCell ref="O72:P72"/>
+    <mergeCell ref="Q72:S72"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="O59:P59"/>
+    <mergeCell ref="Q59:S59"/>
+    <mergeCell ref="O60:P60"/>
+    <mergeCell ref="Q60:S60"/>
+    <mergeCell ref="O61:P61"/>
+    <mergeCell ref="Q61:S61"/>
+    <mergeCell ref="P42:R42"/>
+    <mergeCell ref="P43:R43"/>
+    <mergeCell ref="O58:P58"/>
+    <mergeCell ref="Q58:S58"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="P22:R22"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:S18"/>
     <mergeCell ref="I72:J72"/>
     <mergeCell ref="K72:M72"/>
     <mergeCell ref="J57:L57"/>
@@ -6368,1110 +6647,41 @@
     <mergeCell ref="K52:M52"/>
     <mergeCell ref="I40:J40"/>
     <mergeCell ref="K40:M40"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:S20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="O72:P72"/>
-    <mergeCell ref="Q72:S72"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="O59:P59"/>
-    <mergeCell ref="Q59:S59"/>
-    <mergeCell ref="O60:P60"/>
-    <mergeCell ref="Q60:S60"/>
-    <mergeCell ref="O61:P61"/>
-    <mergeCell ref="Q61:S61"/>
-    <mergeCell ref="P42:R42"/>
-    <mergeCell ref="P43:R43"/>
-    <mergeCell ref="O58:P58"/>
-    <mergeCell ref="Q58:S58"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="Q39:S39"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="Q41:S41"/>
-    <mergeCell ref="P22:R22"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="Q36:S36"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="P44:R44"/>
-    <mergeCell ref="O56:P56"/>
-    <mergeCell ref="Q56:S56"/>
-    <mergeCell ref="P62:R62"/>
-    <mergeCell ref="P63:R63"/>
-    <mergeCell ref="P64:R64"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF92D3D8-0345-4AD6-BEE9-F1C90AED6963}">
-  <dimension ref="A1:H73"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1">
-        <v>32</v>
-      </c>
-      <c r="B1" s="93" t="s">
-        <v>290</v>
-      </c>
-      <c r="F1">
-        <f>COUNTIF($H$1:$H$62,B1)</f>
-        <v>1</v>
-      </c>
-      <c r="H1" s="93" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>33</v>
-      </c>
-      <c r="B2" s="93" t="s">
-        <v>289</v>
-      </c>
-      <c r="F2">
-        <f t="shared" ref="F2:F65" si="0">COUNTIF($H$1:$H$62,B2)</f>
-        <v>1</v>
-      </c>
-      <c r="H2" s="97" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>34</v>
-      </c>
-      <c r="B3" s="97" t="s">
-        <v>286</v>
-      </c>
-      <c r="F3">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H3" s="93" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>35</v>
-      </c>
-      <c r="B4" s="97" t="s">
-        <v>196</v>
-      </c>
-      <c r="F4">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H4" s="97" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <f>A4+1</f>
-        <v>36</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H5" s="97" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <f t="shared" ref="A6:A67" si="1">A5+1</f>
-        <v>37</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F6">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <f t="shared" si="1"/>
-        <v>38</v>
-      </c>
-      <c r="B7" s="97" t="s">
-        <v>288</v>
-      </c>
-      <c r="F7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <f t="shared" si="1"/>
-        <v>39</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="F9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="F10">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <f t="shared" si="1"/>
-        <v>42</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <f t="shared" si="1"/>
-        <v>43</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="F12">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <f t="shared" si="1"/>
-        <v>44</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="F13">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <f t="shared" si="1"/>
-        <v>45</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="F14">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <f t="shared" si="1"/>
-        <v>46</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <f t="shared" si="1"/>
-        <v>47</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <f t="shared" si="1"/>
-        <v>48</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <f t="shared" si="1"/>
-        <v>49</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="F19">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <f t="shared" si="1"/>
-        <v>51</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <f t="shared" si="1"/>
-        <v>52</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <f t="shared" si="1"/>
-        <v>53</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <f t="shared" si="1"/>
-        <v>54</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <f t="shared" si="1"/>
-        <v>55</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F24">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H24" s="105" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <f t="shared" si="1"/>
-        <v>56</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="F25">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H25" s="105" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <f t="shared" si="1"/>
-        <v>57</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F26">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <f t="shared" si="1"/>
-        <v>58</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="F27">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <f t="shared" si="1"/>
-        <v>59</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="F28">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="F29">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <f t="shared" si="1"/>
-        <v>61</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="F30">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <f t="shared" si="1"/>
-        <v>62</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="F31">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <f t="shared" si="1"/>
-        <v>63</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F32">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <f t="shared" si="1"/>
-        <v>64</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="F33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H33" s="111" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <f t="shared" si="1"/>
-        <v>65</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="F34">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <f t="shared" si="1"/>
-        <v>66</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="F35">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <f t="shared" si="1"/>
-        <v>67</v>
-      </c>
-      <c r="B36" s="105" t="s">
-        <v>260</v>
-      </c>
-      <c r="F36">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H36" s="105" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <f t="shared" si="1"/>
-        <v>68</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="F37">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <f t="shared" si="1"/>
-        <v>69</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="F38">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <f t="shared" si="1"/>
-        <v>70</v>
-      </c>
-      <c r="B39" s="105" t="s">
-        <v>261</v>
-      </c>
-      <c r="F39">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <f t="shared" si="1"/>
-        <v>71</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="F40">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <f t="shared" si="1"/>
-        <v>72</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="F41">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <f t="shared" si="1"/>
-        <v>73</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F42">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43">
-        <f t="shared" si="1"/>
-        <v>74</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="F43">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44">
-        <f t="shared" si="1"/>
-        <v>75</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="F44">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45">
-        <f t="shared" si="1"/>
-        <v>76</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="F45">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46">
-        <f t="shared" si="1"/>
-        <v>77</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="F46">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47">
-        <f t="shared" si="1"/>
-        <v>78</v>
-      </c>
-      <c r="B47" s="3"/>
-      <c r="F47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48">
-        <f t="shared" si="1"/>
-        <v>79</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F48">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49">
-        <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="F49">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H49" s="118" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <f t="shared" si="1"/>
-        <v>81</v>
-      </c>
-      <c r="B50" s="118" t="s">
-        <v>215</v>
-      </c>
-      <c r="F50">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <f t="shared" si="1"/>
-        <v>82</v>
-      </c>
-      <c r="B51" s="118" t="s">
-        <v>229</v>
-      </c>
-      <c r="F51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <f t="shared" si="1"/>
-        <v>83</v>
-      </c>
-      <c r="B52" s="111" t="s">
-        <v>271</v>
-      </c>
-      <c r="F52">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <f t="shared" si="1"/>
-        <v>84</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="F53">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <f t="shared" si="1"/>
-        <v>85</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="F54">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <f t="shared" si="1"/>
-        <v>86</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="F55">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <f t="shared" si="1"/>
-        <v>87</v>
-      </c>
-      <c r="B56" s="105" t="s">
-        <v>266</v>
-      </c>
-      <c r="F56">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <f t="shared" si="1"/>
-        <v>88</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="F57">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <f t="shared" si="1"/>
-        <v>89</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="F58">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <f t="shared" si="1"/>
-        <v>90</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="F59">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="F60">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <f t="shared" si="1"/>
-        <v>92</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="F61">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H61" s="118" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <f t="shared" si="1"/>
-        <v>93</v>
-      </c>
-      <c r="F62">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <f t="shared" si="1"/>
-        <v>94</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="F63">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <f t="shared" si="1"/>
-        <v>95</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="F64">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <f t="shared" si="1"/>
-        <v>96</v>
-      </c>
-      <c r="B65" s="3"/>
-      <c r="F65">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66">
-        <f t="shared" si="1"/>
-        <v>97</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="F66">
-        <f t="shared" ref="F66:F67" si="2">COUNTIF($H$1:$H$62,B66)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67">
-        <f t="shared" si="1"/>
-        <v>98</v>
-      </c>
-      <c r="F67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B73" s="3"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Document/IDD.xlsx
+++ b/Document/IDD.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\SoC_Design\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F16341D-7116-49B5-8A12-6FA89759AD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9644CE-B4C7-46A8-9CB2-BE0B6BEBB16E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
   </bookViews>
   <sheets>
     <sheet name="CPU" sheetId="1" r:id="rId1"/>
+    <sheet name="정리용" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CPU!$C$17:$G$17</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="366">
   <si>
     <t>top_cpu</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -279,10 +280,6 @@
   </si>
   <si>
     <t>Decoded OPCODE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded rs Register</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -381,10 +378,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>rt or rd Register</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>u_alu</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1182,6 +1175,339 @@
   </si>
   <si>
     <t>w_wb_alu_out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU Output (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_jump_mux_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Branch ADDR or Jump ADDR ([Warning] Hazard)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_dec_jaddr</t>
+  </si>
+  <si>
+    <t>w_if_i_mem_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_if_i_mem_en</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_shift_left2_dec_jaddr</t>
+  </si>
+  <si>
+    <t>w_id_add4_addr
+w_id_shift_left2_dec_jaddr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_shift_left2_sign_extend_const</t>
+  </si>
+  <si>
+    <t>w_ex_sign_extend_branch_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_branch_addr</t>
+  </si>
+  <si>
+    <t>w_id_dec_opcode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_dec_rs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_dec_rt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_dec_rd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_dec_shamt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_dec_const</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_alu_ctr</t>
+  </si>
+  <si>
+    <t>w_wb_memtoreg_mux_data</t>
+  </si>
+  <si>
+    <t>ALU Output or D-MEM RDATA ([Warning] Hazard)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_alusrc_mux_data</t>
+  </si>
+  <si>
+    <t>w_ex_alu_carry_out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_alu_zero</t>
+  </si>
+  <si>
+    <t>w_ex_hi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_lo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_branch_mux_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_branch
+w_ex_alu_zero</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_ctr_branch</t>
+  </si>
+  <si>
+    <t>w_ex_regwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_regwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegWrite Flag (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegWrite Flag (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegWrite Flag (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rd Register (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rt Register (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_dec_rt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_dec_rd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_dec_rt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_dec_rd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_dec_rt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_dec_rd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rd Register (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rt Register (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rd Register (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rt Register (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rd Register (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_ctr_regdst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_ctr_regdst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_ctr_regdst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegDst Flag (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegDst Flag (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegDst Flag (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_regdst_mux_reg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rt or rd Register (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>top파일 복붙용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시작위치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>끝위치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>추출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>엑셀 복붙용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_ctr_regwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_mem_wb_bridge
+u_forward_regdst_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름
+바뀐거
+찾기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안적은거
+찾기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_dec_rs</t>
+  </si>
+  <si>
+    <t>Decoded rs Register (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rs Register (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_registers
+u_id_ex_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_forward_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_regdst_mux_reg</t>
+  </si>
+  <si>
+    <t>u_forward_regdst_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rt or rd Register (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_if_pc_mux_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_pc_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I-MEM RADDR (Next)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ctr_forward_a</t>
+  </si>
+  <si>
+    <t>w_ctr_forward_b</t>
+  </si>
+  <si>
+    <t>w_ex_forward_mux_data_a</t>
+  </si>
+  <si>
+    <t>w_ex_forward_mux_data_b</t>
+  </si>
+  <si>
+    <t>ForwardA Output</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ForwardB Output</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_forward_a_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_forward_b_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ForwardA MUX Data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ForwardB MUX Data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_ex_mem_bridge
+u_forward_unit</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1199,216 +1525,21 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>o_d_mem_addr</t>
+      <t xml:space="preserve">o_d_mem_addr
+</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU Output (WB)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_jump_mux_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Branch ADDR or Jump ADDR ([Warning] Hazard)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_dec_jaddr</t>
-  </si>
-  <si>
-    <t>w_if_i_mem_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_if_i_mem_en</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_shift_left2_dec_jaddr</t>
-  </si>
-  <si>
-    <t>w_id_add4_addr
-w_id_shift_left2_dec_jaddr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_shift_left2_sign_extend_const</t>
-  </si>
-  <si>
-    <t>w_ex_sign_extend_branch_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_branch_addr</t>
-  </si>
-  <si>
-    <t>w_id_dec_opcode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_dec_rs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_dec_rt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_dec_rd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_dec_shamt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_dec_const</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_alu_ctr</t>
-  </si>
-  <si>
-    <t>w_id_regdst_mux_reg</t>
-  </si>
-  <si>
-    <t>w_wb_memtoreg_mux_data</t>
-  </si>
-  <si>
-    <t>ALU Output or D-MEM RDATA ([Warning] Hazard)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_alusrc_mux_data</t>
-  </si>
-  <si>
-    <t>w_ex_alu_carry_out</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_alu_zero</t>
-  </si>
-  <si>
-    <t>w_ex_hi</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_lo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_branch_mux_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_branch
-w_ex_alu_zero</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_ctr_branch</t>
-  </si>
-  <si>
-    <t>w_ex_regwrite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_regwrite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_regwrite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RegWrite Flag (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RegWrite Flag (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RegWrite Flag (WB)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded rd Register (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded rt Register (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_dec_rt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_dec_rd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_dec_rt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_dec_rd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_dec_rt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_dec_rd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded rd Register (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded rt Register (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded rd Register (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded rt Register (WB)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded rd Register (WB)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_ctr_regdst</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_ctr_regdst</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_ctr_regdst</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RegDst Flag (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RegDst Flag (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RegDst Flag (WB)</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>u_forward_a_mux
+u_forward_b_mux</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2034,7 +2165,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2395,13 +2526,58 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2413,28 +2589,10 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2446,34 +2604,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2836,32 +2973,32 @@
   <sheetData>
     <row r="1" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="134" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="136"/>
-      <c r="I2" s="120" t="s">
-        <v>106</v>
-      </c>
-      <c r="J2" s="122"/>
-      <c r="K2" s="120" t="s">
-        <v>100</v>
-      </c>
-      <c r="L2" s="121"/>
-      <c r="M2" s="122"/>
-      <c r="O2" s="120" t="s">
-        <v>106</v>
-      </c>
-      <c r="P2" s="122"/>
-      <c r="Q2" s="120" t="s">
-        <v>153</v>
-      </c>
-      <c r="R2" s="121"/>
-      <c r="S2" s="122"/>
+      <c r="B2" s="143" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="144"/>
+      <c r="D2" s="144"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="145"/>
+      <c r="I2" s="122" t="s">
+        <v>104</v>
+      </c>
+      <c r="J2" s="123"/>
+      <c r="K2" s="122" t="s">
+        <v>98</v>
+      </c>
+      <c r="L2" s="124"/>
+      <c r="M2" s="123"/>
+      <c r="O2" s="122" t="s">
+        <v>104</v>
+      </c>
+      <c r="P2" s="123"/>
+      <c r="Q2" s="122" t="s">
+        <v>151</v>
+      </c>
+      <c r="R2" s="124"/>
+      <c r="S2" s="123"/>
     </row>
     <row r="3" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="34" t="s">
@@ -2882,24 +3019,24 @@
       <c r="G3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="129" t="s">
-        <v>112</v>
-      </c>
-      <c r="J3" s="130"/>
-      <c r="K3" s="131" t="s">
-        <v>113</v>
-      </c>
-      <c r="L3" s="132"/>
-      <c r="M3" s="133"/>
-      <c r="O3" s="129" t="s">
-        <v>112</v>
-      </c>
-      <c r="P3" s="130"/>
-      <c r="Q3" s="131" t="s">
-        <v>241</v>
-      </c>
-      <c r="R3" s="132"/>
-      <c r="S3" s="133"/>
+      <c r="I3" s="132" t="s">
+        <v>110</v>
+      </c>
+      <c r="J3" s="133"/>
+      <c r="K3" s="134" t="s">
+        <v>111</v>
+      </c>
+      <c r="L3" s="135"/>
+      <c r="M3" s="136"/>
+      <c r="O3" s="132" t="s">
+        <v>110</v>
+      </c>
+      <c r="P3" s="133"/>
+      <c r="Q3" s="134" t="s">
+        <v>239</v>
+      </c>
+      <c r="R3" s="135"/>
+      <c r="S3" s="136"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B4" s="35">
@@ -2920,24 +3057,24 @@
       <c r="G4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="129" t="s">
-        <v>110</v>
-      </c>
-      <c r="J4" s="130"/>
-      <c r="K4" s="129" t="s">
-        <v>66</v>
-      </c>
-      <c r="L4" s="143"/>
-      <c r="M4" s="130"/>
-      <c r="O4" s="129" t="s">
-        <v>110</v>
-      </c>
-      <c r="P4" s="130"/>
-      <c r="Q4" s="129" t="s">
-        <v>66</v>
-      </c>
-      <c r="R4" s="143"/>
-      <c r="S4" s="130"/>
+      <c r="I4" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="J4" s="133"/>
+      <c r="K4" s="132" t="s">
+        <v>65</v>
+      </c>
+      <c r="L4" s="137"/>
+      <c r="M4" s="133"/>
+      <c r="O4" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="P4" s="133"/>
+      <c r="Q4" s="132" t="s">
+        <v>65</v>
+      </c>
+      <c r="R4" s="137"/>
+      <c r="S4" s="133"/>
     </row>
     <row r="5" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="54">
@@ -2958,24 +3095,24 @@
       <c r="G5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="123" t="s">
+      <c r="I5" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="124"/>
-      <c r="K5" s="125" t="s">
-        <v>105</v>
-      </c>
-      <c r="L5" s="126"/>
-      <c r="M5" s="127"/>
-      <c r="O5" s="123" t="s">
+      <c r="J5" s="139"/>
+      <c r="K5" s="140" t="s">
+        <v>103</v>
+      </c>
+      <c r="L5" s="121"/>
+      <c r="M5" s="141"/>
+      <c r="O5" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="124"/>
-      <c r="Q5" s="125" t="s">
-        <v>154</v>
-      </c>
-      <c r="R5" s="126"/>
-      <c r="S5" s="127"/>
+      <c r="P5" s="139"/>
+      <c r="Q5" s="140" t="s">
+        <v>152</v>
+      </c>
+      <c r="R5" s="121"/>
+      <c r="S5" s="141"/>
     </row>
     <row r="6" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="55">
@@ -2999,22 +3136,22 @@
       <c r="I6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="128" t="s">
-        <v>101</v>
-      </c>
-      <c r="K6" s="128"/>
-      <c r="L6" s="128"/>
+      <c r="J6" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="K6" s="130"/>
+      <c r="L6" s="130"/>
       <c r="M6" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="128" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q6" s="128"/>
-      <c r="R6" s="128"/>
+      <c r="P6" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q6" s="130"/>
+      <c r="R6" s="130"/>
       <c r="S6" s="69" t="s">
         <v>8</v>
       </c>
@@ -3041,24 +3178,24 @@
       <c r="I7" s="70">
         <v>1</v>
       </c>
-      <c r="J7" s="137" t="s">
+      <c r="J7" s="142" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="137"/>
-      <c r="L7" s="137"/>
+      <c r="K7" s="142"/>
+      <c r="L7" s="142"/>
       <c r="M7" s="71" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O7" s="87">
         <v>1</v>
       </c>
-      <c r="P7" s="144" t="s">
+      <c r="P7" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="Q7" s="144"/>
-      <c r="R7" s="144"/>
+      <c r="Q7" s="131"/>
+      <c r="R7" s="131"/>
       <c r="S7" s="88" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3084,7 +3221,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="68" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K8" s="68" t="s">
         <v>1</v>
@@ -3098,13 +3235,13 @@
       <c r="O8" s="80">
         <v>2</v>
       </c>
-      <c r="P8" s="126" t="s">
+      <c r="P8" s="121" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="126"/>
-      <c r="R8" s="126"/>
+      <c r="Q8" s="121"/>
+      <c r="R8" s="121"/>
       <c r="S8" s="82" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3130,22 +3267,22 @@
         <v>1</v>
       </c>
       <c r="J9" s="73" t="s">
+        <v>93</v>
+      </c>
+      <c r="K9" s="73" t="s">
         <v>95</v>
-      </c>
-      <c r="K9" s="73" t="s">
-        <v>97</v>
       </c>
       <c r="L9" s="74" t="s">
         <v>21</v>
       </c>
       <c r="M9" s="75" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="O9" s="67" t="s">
         <v>41</v>
       </c>
       <c r="P9" s="68" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Q9" s="68" t="s">
         <v>1</v>
@@ -3180,22 +3317,22 @@
         <v>2</v>
       </c>
       <c r="J10" s="77" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K10" s="77" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L10" s="78" t="s">
         <v>21</v>
       </c>
       <c r="M10" s="79" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O10" s="72">
         <v>1</v>
       </c>
       <c r="P10" s="73" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q10" s="73" t="s">
         <v>5</v>
@@ -3204,7 +3341,7 @@
         <v>1</v>
       </c>
       <c r="S10" s="75" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3230,22 +3367,22 @@
         <v>3</v>
       </c>
       <c r="J11" s="66" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K11" s="66" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L11" s="81" t="s">
         <v>21</v>
       </c>
       <c r="M11" s="82" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="O11" s="72">
         <v>2</v>
       </c>
       <c r="P11" s="73" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q11" s="73" t="s">
         <v>6</v>
@@ -3254,7 +3391,7 @@
         <v>1</v>
       </c>
       <c r="S11" s="75" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3276,29 +3413,29 @@
       <c r="G12" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="138" t="s">
-        <v>108</v>
-      </c>
-      <c r="J12" s="139"/>
-      <c r="K12" s="140" t="s">
-        <v>109</v>
-      </c>
-      <c r="L12" s="141"/>
-      <c r="M12" s="142"/>
+      <c r="I12" s="125" t="s">
+        <v>106</v>
+      </c>
+      <c r="J12" s="126"/>
+      <c r="K12" s="127" t="s">
+        <v>107</v>
+      </c>
+      <c r="L12" s="128"/>
+      <c r="M12" s="129"/>
       <c r="O12" s="72">
         <v>3</v>
       </c>
       <c r="P12" s="73" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q12" s="73" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R12" s="74" t="s">
         <v>21</v>
       </c>
       <c r="S12" s="75" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3324,7 +3461,7 @@
         <v>4</v>
       </c>
       <c r="P13" s="73" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q13" s="73" t="s">
         <v>10</v>
@@ -3359,16 +3496,16 @@
         <v>5</v>
       </c>
       <c r="P14" s="77" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q14" s="73" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R14" s="74" t="s">
         <v>21</v>
       </c>
       <c r="S14" s="79" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3394,28 +3531,28 @@
         <v>6</v>
       </c>
       <c r="P15" s="66" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q15" s="73" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R15" s="74" t="s">
         <v>20</v>
       </c>
       <c r="S15" s="82" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="O16" s="138" t="s">
-        <v>108</v>
-      </c>
-      <c r="P16" s="139"/>
-      <c r="Q16" s="140" t="s">
-        <v>244</v>
-      </c>
-      <c r="R16" s="141"/>
-      <c r="S16" s="142"/>
+      <c r="O16" s="125" t="s">
+        <v>106</v>
+      </c>
+      <c r="P16" s="126"/>
+      <c r="Q16" s="127" t="s">
+        <v>242</v>
+      </c>
+      <c r="R16" s="128"/>
+      <c r="S16" s="129"/>
     </row>
     <row r="17" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="90" t="s">
@@ -3437,273 +3574,273 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="2:19" ht="33" x14ac:dyDescent="0.3">
-      <c r="B18" s="145">
+    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B18" s="33">
         <f>IF(C18="","",1)</f>
         <v>1</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D18" s="90" t="s">
-        <v>21</v>
+        <v>354</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="F18" s="103" t="s">
-        <v>263</v>
-      </c>
-      <c r="G18" s="99" t="s">
-        <v>201</v>
-      </c>
-      <c r="I18" s="120" t="s">
-        <v>106</v>
-      </c>
-      <c r="J18" s="122"/>
-      <c r="K18" s="120" t="s">
-        <v>107</v>
-      </c>
-      <c r="L18" s="121"/>
-      <c r="M18" s="122"/>
-      <c r="O18" s="120" t="s">
-        <v>106</v>
-      </c>
-      <c r="P18" s="122"/>
-      <c r="Q18" s="120" t="s">
-        <v>163</v>
-      </c>
-      <c r="R18" s="121"/>
-      <c r="S18" s="122"/>
+        <v>347</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="I18" s="122" t="s">
+        <v>104</v>
+      </c>
+      <c r="J18" s="123"/>
+      <c r="K18" s="122" t="s">
+        <v>105</v>
+      </c>
+      <c r="L18" s="124"/>
+      <c r="M18" s="123"/>
+      <c r="O18" s="122" t="s">
+        <v>104</v>
+      </c>
+      <c r="P18" s="123"/>
+      <c r="Q18" s="122" t="s">
+        <v>161</v>
+      </c>
+      <c r="R18" s="124"/>
+      <c r="S18" s="123"/>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B19" s="145">
+      <c r="B19" s="33">
         <f t="shared" ref="B19:B50" si="0">IF(C19="","",B18+1)</f>
         <v>2</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>305</v>
+        <v>355</v>
       </c>
       <c r="D19" s="1">
         <v>1</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>82</v>
+      <c r="E19" s="2" t="s">
+        <v>347</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>66</v>
+        <v>361</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="I19" s="129" t="s">
+        <v>359</v>
+      </c>
+      <c r="I19" s="132" t="s">
+        <v>110</v>
+      </c>
+      <c r="J19" s="133"/>
+      <c r="K19" s="134" t="s">
         <v>112</v>
       </c>
-      <c r="J19" s="130"/>
-      <c r="K19" s="131" t="s">
-        <v>114</v>
-      </c>
-      <c r="L19" s="132"/>
-      <c r="M19" s="133"/>
-      <c r="O19" s="129" t="s">
-        <v>112</v>
-      </c>
-      <c r="P19" s="130"/>
-      <c r="Q19" s="131" t="s">
-        <v>241</v>
-      </c>
-      <c r="R19" s="132"/>
-      <c r="S19" s="133"/>
+      <c r="L19" s="135"/>
+      <c r="M19" s="136"/>
+      <c r="O19" s="132" t="s">
+        <v>110</v>
+      </c>
+      <c r="P19" s="133"/>
+      <c r="Q19" s="134" t="s">
+        <v>239</v>
+      </c>
+      <c r="R19" s="135"/>
+      <c r="S19" s="136"/>
     </row>
     <row r="20" spans="2:19" ht="33" x14ac:dyDescent="0.3">
-      <c r="B20" s="145">
+      <c r="B20" s="33">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="D20" s="1">
+        <v>197</v>
+      </c>
+      <c r="D20" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F20" s="103" t="s">
+        <v>261</v>
+      </c>
+      <c r="G20" s="99" t="s">
+        <v>199</v>
+      </c>
+      <c r="I20" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="J20" s="133"/>
+      <c r="K20" s="134" t="s">
+        <v>109</v>
+      </c>
+      <c r="L20" s="135"/>
+      <c r="M20" s="136"/>
+      <c r="O20" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="P20" s="133"/>
+      <c r="Q20" s="132" t="s">
+        <v>65</v>
+      </c>
+      <c r="R20" s="137"/>
+      <c r="S20" s="133"/>
+    </row>
+    <row r="21" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="33">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="C21" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I21" s="138" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="139"/>
+      <c r="K21" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="L21" s="121"/>
+      <c r="M21" s="141"/>
+      <c r="O21" s="138" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="139"/>
+      <c r="Q21" s="140" t="s">
+        <v>162</v>
+      </c>
+      <c r="R21" s="121"/>
+      <c r="S21" s="141"/>
+    </row>
+    <row r="22" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="33">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D22" s="1">
+        <v>4</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" s="103" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="103" t="s">
+      <c r="G22" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="I20" s="129" t="s">
-        <v>110</v>
-      </c>
-      <c r="J20" s="130"/>
-      <c r="K20" s="131" t="s">
-        <v>111</v>
-      </c>
-      <c r="L20" s="132"/>
-      <c r="M20" s="133"/>
-      <c r="O20" s="129" t="s">
-        <v>110</v>
-      </c>
-      <c r="P20" s="130"/>
-      <c r="Q20" s="129" t="s">
-        <v>66</v>
-      </c>
-      <c r="R20" s="143"/>
-      <c r="S20" s="130"/>
-    </row>
-    <row r="21" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="145">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="D21" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F21" s="103" t="s">
-        <v>246</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="I21" s="123" t="s">
-        <v>8</v>
-      </c>
-      <c r="J21" s="124"/>
-      <c r="K21" s="125" t="s">
-        <v>128</v>
-      </c>
-      <c r="L21" s="126"/>
-      <c r="M21" s="127"/>
-      <c r="O21" s="123" t="s">
-        <v>8</v>
-      </c>
-      <c r="P21" s="124"/>
-      <c r="Q21" s="125" t="s">
-        <v>164</v>
-      </c>
-      <c r="R21" s="126"/>
-      <c r="S21" s="127"/>
-    </row>
-    <row r="22" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="145">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="D22" s="1">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>88</v>
       </c>
       <c r="I22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J22" s="128" t="s">
-        <v>101</v>
-      </c>
-      <c r="K22" s="128"/>
-      <c r="L22" s="128"/>
+      <c r="J22" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="K22" s="130"/>
+      <c r="L22" s="130"/>
       <c r="M22" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P22" s="128" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q22" s="128"/>
-      <c r="R22" s="128"/>
+      <c r="P22" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q22" s="130"/>
+      <c r="R22" s="130"/>
       <c r="S22" s="69" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="23" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="145">
+      <c r="B23" s="33">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="D23" s="1">
-        <v>3</v>
+        <v>263</v>
+      </c>
+      <c r="D23" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>67</v>
+        <v>80</v>
+      </c>
+      <c r="F23" s="103" t="s">
+        <v>244</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="I23" s="70">
         <v>1</v>
       </c>
-      <c r="J23" s="137" t="s">
+      <c r="J23" s="142" t="s">
         <v>20</v>
       </c>
-      <c r="K23" s="137"/>
-      <c r="L23" s="137"/>
+      <c r="K23" s="142"/>
+      <c r="L23" s="142"/>
       <c r="M23" s="71" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="O23" s="87">
         <v>1</v>
       </c>
-      <c r="P23" s="144" t="s">
+      <c r="P23" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="Q23" s="144"/>
-      <c r="R23" s="144"/>
+      <c r="Q23" s="131"/>
+      <c r="R23" s="131"/>
       <c r="S23" s="88" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="24" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="145">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="33">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="D24" s="90" t="s">
-        <v>20</v>
+        <v>302</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F24" s="103" t="s">
-        <v>78</v>
+        <v>80</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>307</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I24" s="67" t="s">
         <v>41</v>
       </c>
       <c r="J24" s="68" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K24" s="68" t="s">
         <v>1</v>
@@ -3717,55 +3854,55 @@
       <c r="O24" s="80">
         <v>2</v>
       </c>
-      <c r="P24" s="126" t="s">
+      <c r="P24" s="121" t="s">
         <v>20</v>
       </c>
-      <c r="Q24" s="126"/>
-      <c r="R24" s="126"/>
+      <c r="Q24" s="121"/>
+      <c r="R24" s="121"/>
       <c r="S24" s="82" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="145">
+      <c r="B25" s="33">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D25" s="1">
-        <v>1</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>245</v>
+        <v>3</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>311</v>
+        <v>66</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="I25" s="72">
         <v>1</v>
       </c>
       <c r="J25" s="73" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K25" s="73" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="L25" s="74" t="s">
         <v>20</v>
       </c>
       <c r="M25" s="75" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="O25" s="67" t="s">
         <v>41</v>
       </c>
       <c r="P25" s="68" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Q25" s="68" t="s">
         <v>1</v>
@@ -3778,45 +3915,45 @@
       </c>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B26" s="145">
+      <c r="B26" s="33">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="D26" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>53</v>
+        <v>81</v>
+      </c>
+      <c r="F26" s="103" t="s">
+        <v>361</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>240</v>
+        <v>83</v>
       </c>
       <c r="I26" s="76">
         <v>2</v>
       </c>
       <c r="J26" s="77" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K26" s="77" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L26" s="78" t="s">
         <v>20</v>
       </c>
       <c r="M26" s="79" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O26" s="72">
         <v>1</v>
       </c>
       <c r="P26" s="73" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q26" s="73" t="s">
         <v>5</v>
@@ -3825,49 +3962,49 @@
         <v>1</v>
       </c>
       <c r="S26" s="75" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B27" s="145">
+      <c r="B27" s="33">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="D27" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>53</v>
+        <v>269</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>36</v>
+        <v>307</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>92</v>
+        <v>270</v>
       </c>
       <c r="I27" s="83">
         <v>3</v>
       </c>
       <c r="J27" s="77" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K27" s="84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="L27" s="84">
         <v>1</v>
       </c>
       <c r="M27" s="85" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="O27" s="72">
         <v>2</v>
       </c>
       <c r="P27" s="73" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q27" s="73" t="s">
         <v>6</v>
@@ -3876,684 +4013,684 @@
         <v>1</v>
       </c>
       <c r="S27" s="75" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B28" s="145">
+      <c r="B28" s="33">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="D28" s="1">
-        <v>1</v>
+        <v>290</v>
+      </c>
+      <c r="D28" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>242</v>
+        <v>40</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="I28" s="83">
         <v>4</v>
       </c>
       <c r="J28" s="84" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K28" s="84" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L28" s="84">
         <v>4</v>
       </c>
       <c r="M28" s="85" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O28" s="83">
         <v>3</v>
       </c>
       <c r="P28" s="73" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q28" s="73" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R28" s="74" t="s">
         <v>21</v>
       </c>
       <c r="S28" s="75" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="29" spans="2:19" ht="33" x14ac:dyDescent="0.3">
-      <c r="B29" s="145">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B29" s="33">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="D29" s="1">
-        <v>1</v>
-      </c>
-      <c r="E29" s="102" t="s">
-        <v>310</v>
+        <v>305</v>
+      </c>
+      <c r="D29" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I29" s="83">
         <v>5</v>
       </c>
       <c r="J29" s="84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K29" s="84" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L29" s="86" t="s">
         <v>20</v>
       </c>
       <c r="M29" s="85" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="O29" s="83">
         <v>4</v>
       </c>
       <c r="P29" s="77" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q29" s="84" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="R29" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S29" s="85" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B30" s="145">
+      <c r="B30" s="33">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>273</v>
+        <v>232</v>
       </c>
       <c r="D30" s="1">
         <v>1</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>245</v>
+      <c r="E30" s="1" t="s">
+        <v>240</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>274</v>
+        <v>233</v>
       </c>
       <c r="I30" s="83">
         <v>6</v>
       </c>
       <c r="J30" s="84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K30" s="84" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L30" s="84">
         <v>1</v>
       </c>
       <c r="M30" s="85" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="O30" s="83">
         <v>5</v>
       </c>
       <c r="P30" s="77" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q30" s="84" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="R30" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S30" s="85" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="31" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="145">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="31" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="33">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>331</v>
+        <v>307</v>
       </c>
       <c r="D31" s="1">
         <v>1</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="F31" s="103" t="s">
-        <v>246</v>
+      <c r="E31" s="102" t="s">
+        <v>306</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>334</v>
+        <v>91</v>
       </c>
       <c r="I31" s="80">
         <v>7</v>
       </c>
       <c r="J31" s="66" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K31" s="66" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L31" s="66">
         <v>1</v>
       </c>
       <c r="M31" s="82" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="O31" s="83">
         <v>6</v>
       </c>
       <c r="P31" s="77" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q31" s="84" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="R31" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S31" s="85" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="145">
+      <c r="B32" s="33">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="D32" s="1">
-        <v>6</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>242</v>
+        <v>1</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="I32" s="138" t="s">
-        <v>108</v>
-      </c>
-      <c r="J32" s="139"/>
-      <c r="K32" s="140" t="s">
-        <v>82</v>
-      </c>
-      <c r="L32" s="141"/>
-      <c r="M32" s="142"/>
+        <v>272</v>
+      </c>
+      <c r="I32" s="125" t="s">
+        <v>106</v>
+      </c>
+      <c r="J32" s="126"/>
+      <c r="K32" s="127" t="s">
+        <v>80</v>
+      </c>
+      <c r="L32" s="128"/>
+      <c r="M32" s="129"/>
       <c r="O32" s="83">
         <v>7</v>
       </c>
       <c r="P32" s="77" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q32" s="77" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R32" s="78" t="s">
         <v>21</v>
       </c>
       <c r="S32" s="79" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B33" s="145">
+      <c r="B33" s="33">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="D33" s="90" t="s">
-        <v>56</v>
+        <v>326</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F33" s="103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="O33" s="83">
         <v>8</v>
       </c>
       <c r="P33" s="84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q33" s="84" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="R33" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S33" s="85" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B34" s="145">
+      <c r="B34" s="33">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="D34" s="90" t="s">
-        <v>56</v>
+        <v>248</v>
+      </c>
+      <c r="D34" s="1">
+        <v>6</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="F34" s="103" t="s">
-        <v>246</v>
+        <v>240</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>319</v>
+        <v>249</v>
       </c>
       <c r="O34" s="83">
         <v>9</v>
       </c>
       <c r="P34" s="84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q34" s="84" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="R34" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S34" s="85" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="145">
+      <c r="B35" s="33">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="D35" s="90" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>66</v>
+        <v>243</v>
+      </c>
+      <c r="F35" s="103" t="s">
+        <v>244</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>90</v>
+        <v>321</v>
       </c>
       <c r="O35" s="80">
         <v>10</v>
       </c>
       <c r="P35" s="66" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q35" s="66" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="R35" s="81" t="s">
         <v>20</v>
       </c>
       <c r="S35" s="82" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="145">
+      <c r="B36" s="33">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D36" s="101" t="s">
+        <v>343</v>
+      </c>
+      <c r="D36" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="O36" s="125" t="s">
+        <v>106</v>
+      </c>
+      <c r="P36" s="126"/>
+      <c r="Q36" s="127" t="s">
+        <v>243</v>
+      </c>
+      <c r="R36" s="128"/>
+      <c r="S36" s="129"/>
+    </row>
+    <row r="37" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="33">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="E36" s="102" t="s">
-        <v>242</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="O36" s="138" t="s">
-        <v>108</v>
-      </c>
-      <c r="P36" s="139"/>
-      <c r="Q36" s="140" t="s">
-        <v>245</v>
-      </c>
-      <c r="R36" s="141"/>
-      <c r="S36" s="142"/>
-    </row>
-    <row r="37" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="145">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="C37" s="97" t="s">
-        <v>284</v>
+      <c r="C37" s="3" t="s">
+        <v>315</v>
       </c>
       <c r="D37" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="F37" s="103" t="s">
+        <v>364</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="38" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+      <c r="B38" s="33">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="E37" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F37" s="98" t="s">
-        <v>35</v>
-      </c>
-      <c r="G37" s="99" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B38" s="145">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
       <c r="C38" s="3" t="s">
-        <v>308</v>
+        <v>356</v>
       </c>
       <c r="D38" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>66</v>
+        <v>360</v>
+      </c>
+      <c r="F38" s="103" t="s">
+        <v>77</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="I38" s="120" t="s">
-        <v>106</v>
-      </c>
-      <c r="J38" s="122"/>
-      <c r="K38" s="120" t="s">
-        <v>126</v>
-      </c>
-      <c r="L38" s="121"/>
-      <c r="M38" s="122"/>
-      <c r="O38" s="120" t="s">
-        <v>106</v>
-      </c>
-      <c r="P38" s="122"/>
-      <c r="Q38" s="120" t="s">
-        <v>177</v>
-      </c>
-      <c r="R38" s="121"/>
-      <c r="S38" s="122"/>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B39" s="145">
+        <v>362</v>
+      </c>
+      <c r="I38" s="122" t="s">
+        <v>104</v>
+      </c>
+      <c r="J38" s="123"/>
+      <c r="K38" s="122" t="s">
+        <v>124</v>
+      </c>
+      <c r="L38" s="124"/>
+      <c r="M38" s="123"/>
+      <c r="O38" s="122" t="s">
+        <v>104</v>
+      </c>
+      <c r="P38" s="123"/>
+      <c r="Q38" s="122" t="s">
+        <v>175</v>
+      </c>
+      <c r="R38" s="124"/>
+      <c r="S38" s="123"/>
+    </row>
+    <row r="39" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+      <c r="B39" s="33">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="D39" s="1">
-        <v>1</v>
-      </c>
-      <c r="E39" s="118" t="s">
-        <v>245</v>
-      </c>
-      <c r="F39" s="118" t="s">
-        <v>246</v>
+        <v>357</v>
+      </c>
+      <c r="D39" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="F39" s="103" t="s">
+        <v>77</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="I39" s="129" t="s">
-        <v>112</v>
-      </c>
-      <c r="J39" s="130"/>
-      <c r="K39" s="131" t="s">
+        <v>363</v>
+      </c>
+      <c r="I39" s="132" t="s">
+        <v>110</v>
+      </c>
+      <c r="J39" s="133"/>
+      <c r="K39" s="134" t="s">
+        <v>125</v>
+      </c>
+      <c r="L39" s="135"/>
+      <c r="M39" s="136"/>
+      <c r="O39" s="132" t="s">
+        <v>110</v>
+      </c>
+      <c r="P39" s="133"/>
+      <c r="Q39" s="134" t="s">
+        <v>239</v>
+      </c>
+      <c r="R39" s="135"/>
+      <c r="S39" s="136"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B40" s="33">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D40" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="I40" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="J40" s="133"/>
+      <c r="K40" s="134" t="s">
+        <v>109</v>
+      </c>
+      <c r="L40" s="135"/>
+      <c r="M40" s="136"/>
+      <c r="O40" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="P40" s="133"/>
+      <c r="Q40" s="132" t="s">
+        <v>65</v>
+      </c>
+      <c r="R40" s="137"/>
+      <c r="S40" s="133"/>
+    </row>
+    <row r="41" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="33">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D41" s="101" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" s="102" t="s">
+        <v>240</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="I41" s="138" t="s">
+        <v>8</v>
+      </c>
+      <c r="J41" s="139"/>
+      <c r="K41" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="L39" s="132"/>
-      <c r="M39" s="133"/>
-      <c r="O39" s="129" t="s">
-        <v>112</v>
-      </c>
-      <c r="P39" s="130"/>
-      <c r="Q39" s="131" t="s">
-        <v>241</v>
-      </c>
-      <c r="R39" s="132"/>
-      <c r="S39" s="133"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B40" s="145">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D40" s="1">
-        <v>1</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="F40" s="103" t="s">
-        <v>246</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="I40" s="129" t="s">
-        <v>110</v>
-      </c>
-      <c r="J40" s="130"/>
-      <c r="K40" s="131" t="s">
-        <v>111</v>
-      </c>
-      <c r="L40" s="132"/>
-      <c r="M40" s="133"/>
-      <c r="O40" s="129" t="s">
-        <v>110</v>
-      </c>
-      <c r="P40" s="130"/>
-      <c r="Q40" s="129" t="s">
-        <v>66</v>
-      </c>
-      <c r="R40" s="143"/>
-      <c r="S40" s="130"/>
-    </row>
-    <row r="41" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="145">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="D41" s="1">
-        <v>1</v>
-      </c>
-      <c r="E41" s="118" t="s">
-        <v>245</v>
-      </c>
-      <c r="F41" s="118" t="s">
-        <v>246</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="I41" s="123" t="s">
+      <c r="L41" s="121"/>
+      <c r="M41" s="141"/>
+      <c r="O41" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="124"/>
-      <c r="K41" s="125" t="s">
-        <v>129</v>
-      </c>
-      <c r="L41" s="126"/>
-      <c r="M41" s="127"/>
-      <c r="O41" s="123" t="s">
-        <v>8</v>
-      </c>
-      <c r="P41" s="124"/>
-      <c r="Q41" s="125" t="s">
-        <v>178</v>
-      </c>
-      <c r="R41" s="126"/>
-      <c r="S41" s="127"/>
-    </row>
-    <row r="42" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="145">
+      <c r="P41" s="139"/>
+      <c r="Q41" s="140" t="s">
+        <v>176</v>
+      </c>
+      <c r="R41" s="121"/>
+      <c r="S41" s="141"/>
+    </row>
+    <row r="42" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="33">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>226</v>
+      <c r="C42" s="97" t="s">
+        <v>281</v>
       </c>
       <c r="D42" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="F42" s="103" t="s">
-        <v>78</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>228</v>
+        <v>21</v>
+      </c>
+      <c r="E42" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F42" s="98" t="s">
+        <v>35</v>
+      </c>
+      <c r="G42" s="99" t="s">
+        <v>282</v>
       </c>
       <c r="I42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J42" s="128" t="s">
-        <v>101</v>
-      </c>
-      <c r="K42" s="128"/>
-      <c r="L42" s="128"/>
+      <c r="J42" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="K42" s="130"/>
+      <c r="L42" s="130"/>
       <c r="M42" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P42" s="128" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q42" s="128"/>
-      <c r="R42" s="128"/>
+      <c r="P42" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q42" s="130"/>
+      <c r="R42" s="130"/>
       <c r="S42" s="69" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="145">
+    <row r="43" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="33">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C43" s="116" t="s">
-        <v>227</v>
-      </c>
-      <c r="D43" s="117" t="s">
+      <c r="C43" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D43" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="115" t="s">
-        <v>242</v>
-      </c>
-      <c r="F43" s="119" t="s">
-        <v>268</v>
-      </c>
-      <c r="G43" s="116" t="s">
-        <v>229</v>
+      <c r="E43" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="I43" s="70">
         <v>1</v>
       </c>
-      <c r="J43" s="137" t="s">
+      <c r="J43" s="142" t="s">
         <v>20</v>
       </c>
-      <c r="K43" s="137"/>
-      <c r="L43" s="137"/>
+      <c r="K43" s="142"/>
+      <c r="L43" s="142"/>
       <c r="M43" s="71" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="O43" s="87">
         <v>1</v>
       </c>
-      <c r="P43" s="144" t="s">
+      <c r="P43" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="Q43" s="144"/>
-      <c r="R43" s="144"/>
+      <c r="Q43" s="131"/>
+      <c r="R43" s="131"/>
       <c r="S43" s="88" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="44" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="145">
+      <c r="B44" s="33">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>312</v>
+        <v>252</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>246</v>
+      <c r="E44" s="118" t="s">
+        <v>243</v>
+      </c>
+      <c r="F44" s="118" t="s">
+        <v>244</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>315</v>
+        <v>254</v>
       </c>
       <c r="I44" s="67" t="s">
         <v>41</v>
       </c>
       <c r="J44" s="68" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K44" s="68" t="s">
         <v>1</v>
@@ -4567,55 +4704,55 @@
       <c r="O44" s="80">
         <v>2</v>
       </c>
-      <c r="P44" s="126" t="s">
+      <c r="P44" s="121" t="s">
         <v>20</v>
       </c>
-      <c r="Q44" s="126"/>
-      <c r="R44" s="126"/>
+      <c r="Q44" s="121"/>
+      <c r="R44" s="121"/>
       <c r="S44" s="82" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="145">
+      <c r="B45" s="33">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D45" s="90" t="s">
-        <v>49</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>292</v>
+        <v>273</v>
+      </c>
+      <c r="D45" s="1">
+        <v>1</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F45" s="103" t="s">
+        <v>244</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>54</v>
+        <v>276</v>
       </c>
       <c r="I45" s="72">
         <v>1</v>
       </c>
       <c r="J45" s="73" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K45" s="73" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L45" s="73">
         <v>6</v>
       </c>
       <c r="M45" s="75" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="O45" s="67" t="s">
         <v>41</v>
       </c>
       <c r="P45" s="68" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Q45" s="68" t="s">
         <v>1</v>
@@ -4628,45 +4765,45 @@
       </c>
     </row>
     <row r="46" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B46" s="145">
+      <c r="B46" s="33">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="D46" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>40</v>
+        <v>253</v>
+      </c>
+      <c r="D46" s="1">
+        <v>1</v>
+      </c>
+      <c r="E46" s="118" t="s">
+        <v>243</v>
+      </c>
+      <c r="F46" s="118" t="s">
+        <v>244</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>52</v>
+        <v>255</v>
       </c>
       <c r="I46" s="76">
         <v>2</v>
       </c>
       <c r="J46" s="77" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K46" s="77" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L46" s="77">
         <v>3</v>
       </c>
       <c r="M46" s="79" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O46" s="72">
         <v>1</v>
       </c>
       <c r="P46" s="73" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q46" s="73" t="s">
         <v>5</v>
@@ -4675,49 +4812,49 @@
         <v>1</v>
       </c>
       <c r="S46" s="75" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="47" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="145">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="33">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D47" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F47" s="103" t="s">
-        <v>48</v>
+        <v>360</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="I47" s="80">
         <v>3</v>
       </c>
       <c r="J47" s="66" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K47" s="66" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L47" s="66">
         <v>4</v>
       </c>
       <c r="M47" s="82" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O47" s="72">
         <v>2</v>
       </c>
       <c r="P47" s="73" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q47" s="73" t="s">
         <v>6</v>
@@ -4726,298 +4863,298 @@
         <v>1</v>
       </c>
       <c r="S47" s="75" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="48" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="145">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="33">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D48" s="90" t="s">
+      <c r="C48" s="116" t="s">
+        <v>225</v>
+      </c>
+      <c r="D48" s="117" t="s">
         <v>20</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="F48" s="2" t="s">
+      <c r="E48" s="115" t="s">
+        <v>240</v>
+      </c>
+      <c r="F48" s="119" t="s">
+        <v>266</v>
+      </c>
+      <c r="G48" s="116" t="s">
+        <v>227</v>
+      </c>
+      <c r="I48" s="125" t="s">
+        <v>106</v>
+      </c>
+      <c r="J48" s="126"/>
+      <c r="K48" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="G48" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="I48" s="138" t="s">
-        <v>108</v>
-      </c>
-      <c r="J48" s="139"/>
-      <c r="K48" s="140" t="s">
-        <v>67</v>
-      </c>
-      <c r="L48" s="141"/>
-      <c r="M48" s="142"/>
+      <c r="L48" s="128"/>
+      <c r="M48" s="129"/>
       <c r="O48" s="83">
         <v>3</v>
       </c>
       <c r="P48" s="73" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q48" s="73" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="R48" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S48" s="75" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="49" spans="2:19" ht="33" x14ac:dyDescent="0.3">
-      <c r="B49" s="145">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="49" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B49" s="33">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D49" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E49" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D49" s="1">
+        <v>1</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F49" s="103" t="s">
-        <v>262</v>
-      </c>
-      <c r="G49" s="99" t="s">
-        <v>198</v>
+      <c r="F49" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>310</v>
       </c>
       <c r="O49" s="83">
         <v>4</v>
       </c>
       <c r="P49" s="77" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q49" s="84" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="R49" s="84">
         <v>1</v>
       </c>
       <c r="S49" s="85" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="50" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="146">
+      <c r="B50" s="120">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D50" s="1">
-        <v>3</v>
+        <v>288</v>
+      </c>
+      <c r="D50" s="90" t="s">
+        <v>49</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>245</v>
+        <v>47</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>289</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>216</v>
+        <v>54</v>
       </c>
       <c r="O50" s="83">
         <v>5</v>
       </c>
       <c r="P50" s="77" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q50" s="84" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="R50" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S50" s="85" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="51" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B51" s="145">
+      <c r="B51" s="33">
         <f t="shared" ref="B51:B82" si="1">IF(C51="","",B50+1)</f>
         <v>34</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D51" s="1">
-        <v>1</v>
+        <v>289</v>
+      </c>
+      <c r="D51" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>58</v>
+        <v>288</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>245</v>
+        <v>40</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="I51" s="120" t="s">
-        <v>106</v>
-      </c>
-      <c r="J51" s="122"/>
-      <c r="K51" s="120" t="s">
-        <v>133</v>
-      </c>
-      <c r="L51" s="121"/>
-      <c r="M51" s="122"/>
+        <v>52</v>
+      </c>
+      <c r="I51" s="122" t="s">
+        <v>104</v>
+      </c>
+      <c r="J51" s="123"/>
+      <c r="K51" s="122" t="s">
+        <v>131</v>
+      </c>
+      <c r="L51" s="124"/>
+      <c r="M51" s="123"/>
       <c r="O51" s="83">
         <v>6</v>
       </c>
       <c r="P51" s="77" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q51" s="84" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="R51" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S51" s="85" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="52" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B52" s="145">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="52" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+      <c r="B52" s="33">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D52" s="1">
-        <v>1</v>
+        <v>228</v>
+      </c>
+      <c r="D52" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
+      </c>
+      <c r="F52" s="103" t="s">
+        <v>48</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="I52" s="129" t="s">
-        <v>112</v>
-      </c>
-      <c r="J52" s="130"/>
-      <c r="K52" s="131" t="s">
-        <v>134</v>
-      </c>
-      <c r="L52" s="132"/>
-      <c r="M52" s="133"/>
+        <v>230</v>
+      </c>
+      <c r="I52" s="132" t="s">
+        <v>110</v>
+      </c>
+      <c r="J52" s="133"/>
+      <c r="K52" s="134" t="s">
+        <v>132</v>
+      </c>
+      <c r="L52" s="135"/>
+      <c r="M52" s="136"/>
       <c r="O52" s="83">
         <v>7</v>
       </c>
       <c r="P52" s="77" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q52" s="77" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="R52" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S52" s="79" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="53" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B53" s="145">
+      <c r="B53" s="33">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D53" s="1">
-        <v>1</v>
+        <v>194</v>
+      </c>
+      <c r="D53" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>58</v>
+        <v>241</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>245</v>
+        <v>65</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="I53" s="129" t="s">
-        <v>110</v>
-      </c>
-      <c r="J53" s="130"/>
-      <c r="K53" s="131" t="s">
-        <v>111</v>
-      </c>
-      <c r="L53" s="132"/>
-      <c r="M53" s="133"/>
+        <v>195</v>
+      </c>
+      <c r="I53" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="J53" s="133"/>
+      <c r="K53" s="134" t="s">
+        <v>109</v>
+      </c>
+      <c r="L53" s="135"/>
+      <c r="M53" s="136"/>
       <c r="O53" s="83">
         <v>8</v>
       </c>
       <c r="P53" s="84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q53" s="84" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="R53" s="84">
         <v>1</v>
       </c>
       <c r="S53" s="85" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="54" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="145">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="54" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="33">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D54" s="1">
-        <v>1</v>
+        <v>198</v>
+      </c>
+      <c r="D54" s="90" t="s">
+        <v>21</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="I54" s="123" t="s">
+        <v>241</v>
+      </c>
+      <c r="F54" s="103" t="s">
+        <v>260</v>
+      </c>
+      <c r="G54" s="99" t="s">
+        <v>196</v>
+      </c>
+      <c r="I54" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="124"/>
-      <c r="K54" s="125" t="s">
-        <v>135</v>
-      </c>
-      <c r="L54" s="126"/>
-      <c r="M54" s="127"/>
+      <c r="J54" s="139"/>
+      <c r="K54" s="140" t="s">
+        <v>133</v>
+      </c>
+      <c r="L54" s="121"/>
+      <c r="M54" s="141"/>
       <c r="O54" s="83">
         <v>9</v>
       </c>
       <c r="P54" s="84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q54" s="84" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="R54" s="86" t="s">
         <v>20</v>
@@ -5027,33 +5164,33 @@
       </c>
     </row>
     <row r="55" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="145">
+      <c r="B55" s="33">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="D55" s="90" t="s">
-        <v>57</v>
+        <v>200</v>
+      </c>
+      <c r="D55" s="1">
+        <v>3</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>43</v>
+        <v>243</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>62</v>
+        <v>214</v>
       </c>
       <c r="I55" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J55" s="128" t="s">
-        <v>101</v>
-      </c>
-      <c r="K55" s="128"/>
-      <c r="L55" s="128"/>
+      <c r="J55" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="K55" s="130"/>
+      <c r="L55" s="130"/>
       <c r="M55" s="69" t="s">
         <v>8</v>
       </c>
@@ -5061,10 +5198,10 @@
         <v>10</v>
       </c>
       <c r="P55" s="66" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q55" s="66" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="R55" s="81" t="s">
         <v>20</v>
@@ -5079,71 +5216,71 @@
         <v>39</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>248</v>
+        <v>207</v>
       </c>
       <c r="D56" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>249</v>
+        <v>221</v>
       </c>
       <c r="I56" s="87">
         <v>1</v>
       </c>
-      <c r="J56" s="144" t="s">
+      <c r="J56" s="131" t="s">
         <v>20</v>
       </c>
-      <c r="K56" s="144"/>
-      <c r="L56" s="144"/>
+      <c r="K56" s="131"/>
+      <c r="L56" s="131"/>
       <c r="M56" s="88" t="s">
-        <v>137</v>
-      </c>
-      <c r="O56" s="138" t="s">
-        <v>108</v>
-      </c>
-      <c r="P56" s="139"/>
-      <c r="Q56" s="140" t="s">
-        <v>246</v>
-      </c>
-      <c r="R56" s="141"/>
-      <c r="S56" s="142"/>
+        <v>135</v>
+      </c>
+      <c r="O56" s="125" t="s">
+        <v>106</v>
+      </c>
+      <c r="P56" s="126"/>
+      <c r="Q56" s="127" t="s">
+        <v>244</v>
+      </c>
+      <c r="R56" s="128"/>
+      <c r="S56" s="129"/>
     </row>
     <row r="57" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="33">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="C57" s="97" t="s">
-        <v>286</v>
-      </c>
-      <c r="D57" s="101" t="s">
-        <v>45</v>
-      </c>
-      <c r="E57" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="F57" s="98" t="s">
-        <v>42</v>
-      </c>
-      <c r="G57" s="99" t="s">
-        <v>50</v>
+      <c r="C57" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D57" s="1">
+        <v>1</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="I57" s="80">
         <v>2</v>
       </c>
-      <c r="J57" s="126" t="s">
+      <c r="J57" s="121" t="s">
         <v>55</v>
       </c>
-      <c r="K57" s="126"/>
-      <c r="L57" s="126"/>
+      <c r="K57" s="121"/>
+      <c r="L57" s="121"/>
       <c r="M57" s="89" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="58" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5152,25 +5289,25 @@
         <v>41</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D58" s="90" t="s">
-        <v>55</v>
+        <v>208</v>
+      </c>
+      <c r="D58" s="1">
+        <v>1</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>58</v>
+        <v>243</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>59</v>
+        <v>222</v>
       </c>
       <c r="I58" s="67" t="s">
         <v>41</v>
       </c>
       <c r="J58" s="68" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K58" s="68" t="s">
         <v>1</v>
@@ -5181,15 +5318,15 @@
       <c r="M58" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="120" t="s">
-        <v>106</v>
-      </c>
-      <c r="P58" s="122"/>
-      <c r="Q58" s="120" t="s">
-        <v>188</v>
-      </c>
-      <c r="R58" s="121"/>
-      <c r="S58" s="122"/>
+      <c r="O58" s="122" t="s">
+        <v>104</v>
+      </c>
+      <c r="P58" s="123"/>
+      <c r="Q58" s="122" t="s">
+        <v>186</v>
+      </c>
+      <c r="R58" s="124"/>
+      <c r="S58" s="123"/>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B59" s="33">
@@ -5197,28 +5334,28 @@
         <v>42</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="D59" s="90" t="s">
-        <v>56</v>
+        <v>201</v>
+      </c>
+      <c r="D59" s="1">
+        <v>1</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>245</v>
+        <v>58</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>318</v>
+        <v>215</v>
       </c>
       <c r="I59" s="72">
         <v>1</v>
       </c>
       <c r="J59" s="73" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K59" s="73" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L59" s="74" t="s">
         <v>55</v>
@@ -5226,15 +5363,15 @@
       <c r="M59" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="O59" s="129" t="s">
-        <v>112</v>
-      </c>
-      <c r="P59" s="130"/>
-      <c r="Q59" s="131" t="s">
-        <v>241</v>
-      </c>
-      <c r="R59" s="132"/>
-      <c r="S59" s="133"/>
+      <c r="O59" s="132" t="s">
+        <v>110</v>
+      </c>
+      <c r="P59" s="133"/>
+      <c r="Q59" s="134" t="s">
+        <v>239</v>
+      </c>
+      <c r="R59" s="135"/>
+      <c r="S59" s="136"/>
     </row>
     <row r="60" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B60" s="33">
@@ -5242,44 +5379,44 @@
         <v>43</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D60" s="90" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I60" s="76">
         <v>2</v>
       </c>
       <c r="J60" s="84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K60" s="77" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L60" s="77">
         <v>1</v>
       </c>
       <c r="M60" s="79" t="s">
-        <v>68</v>
-      </c>
-      <c r="O60" s="129" t="s">
-        <v>110</v>
-      </c>
-      <c r="P60" s="130"/>
-      <c r="Q60" s="129" t="s">
-        <v>66</v>
-      </c>
-      <c r="R60" s="143"/>
-      <c r="S60" s="130"/>
+        <v>67</v>
+      </c>
+      <c r="O60" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="P60" s="133"/>
+      <c r="Q60" s="132" t="s">
+        <v>65</v>
+      </c>
+      <c r="R60" s="137"/>
+      <c r="S60" s="133"/>
     </row>
     <row r="61" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="33">
@@ -5287,137 +5424,137 @@
         <v>44</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="D61" s="90" t="s">
-        <v>56</v>
+        <v>246</v>
+      </c>
+      <c r="D61" s="1">
+        <v>6</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>63</v>
+        <v>243</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>319</v>
+        <v>247</v>
       </c>
       <c r="I61" s="83">
         <v>3</v>
       </c>
       <c r="J61" s="84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K61" s="84" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L61" s="84">
         <v>1</v>
       </c>
       <c r="M61" s="85" t="s">
-        <v>149</v>
-      </c>
-      <c r="O61" s="123" t="s">
+        <v>147</v>
+      </c>
+      <c r="O61" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="P61" s="124"/>
-      <c r="Q61" s="125" t="s">
-        <v>189</v>
-      </c>
-      <c r="R61" s="126"/>
-      <c r="S61" s="127"/>
-    </row>
-    <row r="62" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P61" s="139"/>
+      <c r="Q61" s="140" t="s">
+        <v>187</v>
+      </c>
+      <c r="R61" s="121"/>
+      <c r="S61" s="141"/>
+    </row>
+    <row r="62" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B62" s="33">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D62" s="1">
-        <v>5</v>
-      </c>
-      <c r="E62" s="1" t="s">
+      <c r="C62" s="97" t="s">
+        <v>283</v>
+      </c>
+      <c r="D62" s="101" t="s">
+        <v>45</v>
+      </c>
+      <c r="E62" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="F62" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>61</v>
+      <c r="F62" s="98" t="s">
+        <v>42</v>
+      </c>
+      <c r="G62" s="99" t="s">
+        <v>50</v>
       </c>
       <c r="I62" s="83">
         <v>4</v>
       </c>
       <c r="J62" s="84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K62" s="84" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="L62" s="84">
         <v>1</v>
       </c>
       <c r="M62" s="85" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="O62" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P62" s="128" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q62" s="128"/>
-      <c r="R62" s="128"/>
+      <c r="P62" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q62" s="130"/>
+      <c r="R62" s="130"/>
       <c r="S62" s="69" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B63" s="33">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="D63" s="101" t="s">
-        <v>20</v>
-      </c>
-      <c r="E63" s="102" t="s">
-        <v>290</v>
+        <v>291</v>
+      </c>
+      <c r="D63" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>245</v>
+        <v>58</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>237</v>
+        <v>59</v>
       </c>
       <c r="I63" s="83">
         <v>5</v>
       </c>
       <c r="J63" s="84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K63" s="84" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L63" s="84">
         <v>1</v>
       </c>
       <c r="M63" s="85" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O63" s="87">
         <v>1</v>
       </c>
-      <c r="P63" s="144" t="s">
+      <c r="P63" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="Q63" s="144"/>
-      <c r="R63" s="144"/>
+      <c r="Q63" s="131"/>
+      <c r="R63" s="131"/>
       <c r="S63" s="88" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="64" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5426,87 +5563,87 @@
         <v>47</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D64" s="1">
-        <v>1</v>
+        <v>294</v>
+      </c>
+      <c r="D64" s="90" t="s">
+        <v>56</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F64" s="118" t="s">
-        <v>245</v>
+        <v>44</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>221</v>
+        <v>313</v>
       </c>
       <c r="I64" s="83">
         <v>6</v>
       </c>
       <c r="J64" s="84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K64" s="84" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L64" s="84">
         <v>1</v>
       </c>
       <c r="M64" s="85" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O64" s="80">
         <v>2</v>
       </c>
-      <c r="P64" s="126" t="s">
+      <c r="P64" s="121" t="s">
         <v>20</v>
       </c>
-      <c r="Q64" s="126"/>
-      <c r="R64" s="126"/>
+      <c r="Q64" s="121"/>
+      <c r="R64" s="121"/>
       <c r="S64" s="82" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="65" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="33">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D65" s="1">
-        <v>1</v>
+        <v>292</v>
+      </c>
+      <c r="D65" s="90" t="s">
+        <v>56</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>242</v>
+        <v>44</v>
+      </c>
+      <c r="F65" s="103" t="s">
+        <v>346</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>219</v>
+        <v>345</v>
       </c>
       <c r="I65" s="83">
         <v>7</v>
       </c>
       <c r="J65" s="84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K65" s="84" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L65" s="84">
         <v>1</v>
       </c>
       <c r="M65" s="85" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O65" s="67" t="s">
         <v>41</v>
       </c>
       <c r="P65" s="68" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Q65" s="68" t="s">
         <v>1</v>
@@ -5524,40 +5661,40 @@
         <v>49</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D66" s="1">
-        <v>1</v>
+        <v>293</v>
+      </c>
+      <c r="D66" s="90" t="s">
+        <v>56</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F66" s="118" t="s">
-        <v>245</v>
+        <v>44</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>222</v>
+        <v>314</v>
       </c>
       <c r="I66" s="83">
         <v>8</v>
       </c>
       <c r="J66" s="84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K66" s="84" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L66" s="84">
         <v>1</v>
       </c>
       <c r="M66" s="85" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O66" s="72">
         <v>1</v>
       </c>
       <c r="P66" s="73" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q66" s="73" t="s">
         <v>5</v>
@@ -5566,7 +5703,7 @@
         <v>1</v>
       </c>
       <c r="S66" s="75" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.3">
@@ -5575,40 +5712,40 @@
         <v>50</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D67" s="90" t="s">
-        <v>20</v>
+        <v>295</v>
+      </c>
+      <c r="D67" s="1">
+        <v>5</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F67" s="115" t="s">
-        <v>242</v>
+        <v>44</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>214</v>
+        <v>60</v>
       </c>
       <c r="I67" s="83">
         <v>9</v>
       </c>
       <c r="J67" s="84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K67" s="84" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L67" s="84">
         <v>3</v>
       </c>
       <c r="M67" s="85" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O67" s="72">
         <v>2</v>
       </c>
       <c r="P67" s="73" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q67" s="73" t="s">
         <v>6</v>
@@ -5617,52 +5754,52 @@
         <v>1</v>
       </c>
       <c r="S67" s="75" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="68" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B68" s="33">
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
-      <c r="C68" s="116" t="s">
-        <v>213</v>
-      </c>
-      <c r="D68" s="117" t="s">
+      <c r="C68" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D68" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F68" s="115" t="s">
-        <v>242</v>
-      </c>
-      <c r="G68" s="116" t="s">
-        <v>215</v>
+      <c r="E68" s="102" t="s">
+        <v>287</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="I68" s="83">
         <v>10</v>
       </c>
       <c r="J68" s="84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K68" s="84" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L68" s="84">
         <v>1</v>
       </c>
       <c r="M68" s="85" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O68" s="83">
         <v>3</v>
       </c>
       <c r="P68" s="84" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q68" s="84" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="R68" s="86" t="s">
         <v>20</v>
@@ -5677,49 +5814,49 @@
         <v>52</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="D69" s="90" t="s">
-        <v>56</v>
+        <v>205</v>
+      </c>
+      <c r="D69" s="1">
+        <v>1</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F69" s="103" t="s">
-        <v>63</v>
+        <v>58</v>
+      </c>
+      <c r="F69" s="118" t="s">
+        <v>243</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>81</v>
+        <v>219</v>
       </c>
       <c r="I69" s="83">
         <v>11</v>
       </c>
       <c r="J69" s="84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K69" s="84" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L69" s="84">
         <v>1</v>
       </c>
       <c r="M69" s="85" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O69" s="83">
         <v>4</v>
       </c>
       <c r="P69" s="84" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q69" s="84" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="R69" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S69" s="85" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.3">
@@ -5728,7 +5865,7 @@
         <v>53</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D70" s="1">
         <v>1</v>
@@ -5737,16 +5874,16 @@
         <v>58</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I70" s="83">
         <v>12</v>
       </c>
       <c r="J70" s="84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K70" s="84" t="s">
         <v>18</v>
@@ -5755,49 +5892,49 @@
         <v>1</v>
       </c>
       <c r="M70" s="85" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O70" s="83">
         <v>5</v>
       </c>
       <c r="P70" s="84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q70" s="84" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="R70" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S70" s="85" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="71" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B71" s="33">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="D71" s="101" t="s">
-        <v>46</v>
+        <v>206</v>
+      </c>
+      <c r="D71" s="1">
+        <v>1</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>236</v>
+        <v>58</v>
+      </c>
+      <c r="F71" s="118" t="s">
+        <v>243</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>51</v>
+        <v>220</v>
       </c>
       <c r="I71" s="80">
         <v>13</v>
       </c>
       <c r="J71" s="66" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K71" s="66" t="s">
         <v>19</v>
@@ -5806,22 +5943,22 @@
         <v>1</v>
       </c>
       <c r="M71" s="82" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O71" s="83">
         <v>6</v>
       </c>
       <c r="P71" s="84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q71" s="84" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="R71" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S71" s="85" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="72" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5830,58 +5967,58 @@
         <v>55</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D72" s="1">
-        <v>1</v>
+        <v>210</v>
+      </c>
+      <c r="D72" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E72" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F72" s="115" t="s">
+        <v>240</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="I72" s="125" t="s">
+        <v>106</v>
+      </c>
+      <c r="J72" s="126"/>
+      <c r="K72" s="127" t="s">
         <v>58</v>
       </c>
-      <c r="F72" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G72" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="I72" s="138" t="s">
-        <v>108</v>
-      </c>
-      <c r="J72" s="139"/>
-      <c r="K72" s="140" t="s">
-        <v>58</v>
-      </c>
-      <c r="L72" s="141"/>
-      <c r="M72" s="142"/>
-      <c r="O72" s="138" t="s">
-        <v>108</v>
-      </c>
-      <c r="P72" s="139"/>
-      <c r="Q72" s="140" t="s">
-        <v>247</v>
-      </c>
-      <c r="R72" s="141"/>
-      <c r="S72" s="142"/>
+      <c r="L72" s="128"/>
+      <c r="M72" s="129"/>
+      <c r="O72" s="125" t="s">
+        <v>106</v>
+      </c>
+      <c r="P72" s="126"/>
+      <c r="Q72" s="127" t="s">
+        <v>245</v>
+      </c>
+      <c r="R72" s="128"/>
+      <c r="S72" s="129"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B73" s="33">
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
-      <c r="C73" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D73" s="90" t="s">
+      <c r="C73" s="116" t="s">
+        <v>211</v>
+      </c>
+      <c r="D73" s="117" t="s">
         <v>20</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F73" s="103" t="s">
-        <v>242</v>
-      </c>
-      <c r="G73" s="5" t="s">
-        <v>231</v>
+        <v>62</v>
+      </c>
+      <c r="F73" s="115" t="s">
+        <v>240</v>
+      </c>
+      <c r="G73" s="116" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.3">
@@ -5889,41 +6026,41 @@
         <f t="shared" si="1"/>
         <v>57</v>
       </c>
-      <c r="C74" s="97" t="s">
-        <v>194</v>
-      </c>
-      <c r="D74" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E74" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="F74" s="98" t="s">
-        <v>244</v>
-      </c>
-      <c r="G74" s="99" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="75" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+      <c r="C74" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D74" s="1">
+        <v>1</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B75" s="33">
         <f t="shared" si="1"/>
         <v>58</v>
       </c>
-      <c r="C75" s="93" t="s">
-        <v>287</v>
-      </c>
-      <c r="D75" s="94" t="s">
-        <v>21</v>
-      </c>
-      <c r="E75" s="92" t="s">
-        <v>35</v>
-      </c>
-      <c r="F75" s="95" t="s">
-        <v>76</v>
-      </c>
-      <c r="G75" s="96" t="s">
-        <v>37</v>
+      <c r="C75" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D75" s="101" t="s">
+        <v>46</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.3">
@@ -5931,41 +6068,41 @@
         <f t="shared" si="1"/>
         <v>59</v>
       </c>
-      <c r="C76" s="93" t="s">
-        <v>288</v>
-      </c>
-      <c r="D76" s="92">
+      <c r="C76" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D76" s="1">
         <v>1</v>
       </c>
-      <c r="E76" s="92" t="s">
-        <v>35</v>
-      </c>
-      <c r="F76" s="100" t="s">
-        <v>11</v>
-      </c>
-      <c r="G76" s="96" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="77" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+      <c r="E76" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B77" s="33">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="C77" s="104" t="s">
-        <v>264</v>
-      </c>
-      <c r="D77" s="113" t="s">
+      <c r="C77" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D77" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="105" t="s">
-        <v>246</v>
-      </c>
-      <c r="F77" s="114" t="s">
-        <v>282</v>
-      </c>
-      <c r="G77" s="107" t="s">
-        <v>267</v>
+      <c r="E77" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F77" s="103" t="s">
+        <v>240</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.3">
@@ -5973,41 +6110,41 @@
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
-      <c r="C78" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="D78" s="1">
-        <v>1</v>
-      </c>
-      <c r="E78" s="103" t="s">
-        <v>246</v>
-      </c>
-      <c r="F78" s="103" t="s">
-        <v>247</v>
-      </c>
-      <c r="G78" s="5" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="C78" s="97" t="s">
+        <v>192</v>
+      </c>
+      <c r="D78" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E78" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="F78" s="98" t="s">
+        <v>242</v>
+      </c>
+      <c r="G78" s="99" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B79" s="33">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D79" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E79" s="103" t="s">
-        <v>246</v>
-      </c>
-      <c r="F79" s="103" t="s">
-        <v>247</v>
-      </c>
-      <c r="G79" s="5" t="s">
-        <v>328</v>
+      <c r="C79" s="93" t="s">
+        <v>284</v>
+      </c>
+      <c r="D79" s="94" t="s">
+        <v>21</v>
+      </c>
+      <c r="E79" s="92" t="s">
+        <v>35</v>
+      </c>
+      <c r="F79" s="95" t="s">
+        <v>75</v>
+      </c>
+      <c r="G79" s="96" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.3">
@@ -6015,20 +6152,20 @@
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D80" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E80" s="103" t="s">
-        <v>246</v>
-      </c>
-      <c r="F80" s="103" t="s">
-        <v>247</v>
-      </c>
-      <c r="G80" s="5" t="s">
-        <v>327</v>
+      <c r="C80" s="93" t="s">
+        <v>285</v>
+      </c>
+      <c r="D80" s="92">
+        <v>1</v>
+      </c>
+      <c r="E80" s="92" t="s">
+        <v>35</v>
+      </c>
+      <c r="F80" s="100" t="s">
+        <v>11</v>
+      </c>
+      <c r="G80" s="96" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.3">
@@ -6036,41 +6173,41 @@
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
-      <c r="C81" s="104" t="s">
-        <v>258</v>
-      </c>
-      <c r="D81" s="105">
-        <v>1</v>
-      </c>
-      <c r="E81" s="105" t="s">
-        <v>246</v>
-      </c>
-      <c r="F81" s="106" t="s">
-        <v>14</v>
-      </c>
-      <c r="G81" s="107" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C81" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="D81" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" ht="66" x14ac:dyDescent="0.3">
       <c r="B82" s="33">
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
-      <c r="C82" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="D82" s="1">
-        <v>1</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="G82" s="5" t="s">
-        <v>279</v>
+      <c r="C82" s="104" t="s">
+        <v>262</v>
+      </c>
+      <c r="D82" s="113" t="s">
+        <v>20</v>
+      </c>
+      <c r="E82" s="105" t="s">
+        <v>244</v>
+      </c>
+      <c r="F82" s="114" t="s">
+        <v>365</v>
+      </c>
+      <c r="G82" s="107" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="83" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6078,83 +6215,83 @@
         <f t="shared" ref="B83:B114" si="2">IF(C83="","",B82+1)</f>
         <v>66</v>
       </c>
-      <c r="C83" s="104" t="s">
-        <v>259</v>
-      </c>
-      <c r="D83" s="105">
+      <c r="C83" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D83" s="1">
         <v>1</v>
       </c>
-      <c r="E83" s="105" t="s">
-        <v>246</v>
-      </c>
-      <c r="F83" s="108" t="s">
-        <v>75</v>
-      </c>
-      <c r="G83" s="107" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E83" s="103" t="s">
+        <v>244</v>
+      </c>
+      <c r="F83" s="103" t="s">
+        <v>340</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B84" s="33">
         <f t="shared" si="2"/>
         <v>67</v>
       </c>
-      <c r="C84" s="109" t="s">
-        <v>269</v>
-      </c>
-      <c r="D84" s="110" t="s">
-        <v>20</v>
-      </c>
-      <c r="E84" s="111" t="s">
-        <v>246</v>
-      </c>
-      <c r="F84" s="112" t="s">
-        <v>17</v>
-      </c>
-      <c r="G84" s="109" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C84" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D84" s="1">
+        <v>1</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="F84" s="103" t="s">
+        <v>340</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B85" s="33">
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="D85" s="1">
-        <v>1</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>247</v>
+        <v>318</v>
+      </c>
+      <c r="D85" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E85" s="103" t="s">
+        <v>244</v>
+      </c>
+      <c r="F85" s="103" t="s">
+        <v>340</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.3">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B86" s="33">
         <f t="shared" si="2"/>
         <v>69</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="D86" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>247</v>
+        <v>56</v>
+      </c>
+      <c r="E86" s="103" t="s">
+        <v>244</v>
       </c>
       <c r="F86" s="103" t="s">
-        <v>84</v>
+        <v>340</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>283</v>
+        <v>322</v>
       </c>
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.3">
@@ -6162,20 +6299,20 @@
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="C87" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="D87" s="1">
+      <c r="C87" s="104" t="s">
+        <v>256</v>
+      </c>
+      <c r="D87" s="105">
         <v>1</v>
       </c>
-      <c r="E87" s="103" t="s">
-        <v>247</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G87" s="5" t="s">
-        <v>336</v>
+      <c r="E87" s="105" t="s">
+        <v>244</v>
+      </c>
+      <c r="F87" s="106" t="s">
+        <v>14</v>
+      </c>
+      <c r="G87" s="107" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.3">
@@ -6184,19 +6321,19 @@
         <v>71</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="D88" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E88" s="103" t="s">
-        <v>247</v>
+        <v>274</v>
+      </c>
+      <c r="D88" s="1">
+        <v>1</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>244</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>65</v>
+        <v>245</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>330</v>
+        <v>277</v>
       </c>
     </row>
     <row r="89" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6204,20 +6341,20 @@
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="C89" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="D89" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E89" s="103" t="s">
-        <v>247</v>
-      </c>
-      <c r="F89" s="103" t="s">
-        <v>64</v>
-      </c>
-      <c r="G89" s="5" t="s">
-        <v>329</v>
+      <c r="C89" s="104" t="s">
+        <v>257</v>
+      </c>
+      <c r="D89" s="105">
+        <v>1</v>
+      </c>
+      <c r="E89" s="105" t="s">
+        <v>244</v>
+      </c>
+      <c r="F89" s="108" t="s">
+        <v>74</v>
+      </c>
+      <c r="G89" s="107" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.3">
@@ -6225,20 +6362,20 @@
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
-      <c r="C90" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="D90" s="1">
-        <v>1</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G90" s="5" t="s">
-        <v>280</v>
+      <c r="C90" s="109" t="s">
+        <v>267</v>
+      </c>
+      <c r="D90" s="110" t="s">
+        <v>20</v>
+      </c>
+      <c r="E90" s="111" t="s">
+        <v>244</v>
+      </c>
+      <c r="F90" s="112" t="s">
+        <v>17</v>
+      </c>
+      <c r="G90" s="109" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.3">
@@ -6247,19 +6384,19 @@
         <v>74</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>302</v>
+        <v>348</v>
       </c>
       <c r="D91" s="90" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>84</v>
+        <v>349</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>63</v>
+        <v>347</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>303</v>
+        <v>350</v>
       </c>
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.3">
@@ -6268,136 +6405,241 @@
         <v>75</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="D92" s="1">
+        <v>279</v>
+      </c>
+      <c r="D92" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="F92" s="103" t="s">
+        <v>82</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B93" s="33">
+        <f t="shared" si="2"/>
+        <v>76</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D93" s="1">
         <v>1</v>
       </c>
-      <c r="E92" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F92" s="2" t="s">
+      <c r="E93" s="103" t="s">
+        <v>245</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B94" s="33">
+        <f t="shared" si="2"/>
+        <v>77</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D94" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E94" s="103" t="s">
+        <v>245</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B95" s="33">
+        <f t="shared" si="2"/>
+        <v>78</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D95" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E95" s="103" t="s">
+        <v>245</v>
+      </c>
+      <c r="F95" s="103" t="s">
         <v>63</v>
       </c>
-      <c r="G92" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="93" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B93" s="33" t="str">
+      <c r="G95" s="5" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B96" s="33">
+        <f t="shared" si="2"/>
+        <v>79</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D96" s="1">
+        <v>1</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B97" s="33">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D97" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B98" s="33">
+        <f t="shared" si="2"/>
+        <v>81</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D98" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F98" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B99" s="33">
+        <f t="shared" si="2"/>
+        <v>82</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D99" s="1">
+        <v>1</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="100" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B100" s="33" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="94" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B94" s="33" t="str">
+    <row r="101" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B101" s="33" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="95" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B95" s="33" t="str">
+    <row r="102" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B102" s="33" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="96" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B96" s="33" t="str">
+    <row r="103" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B103" s="33" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B97" s="33" t="str">
+    <row r="104" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B104" s="33" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B98" s="33" t="str">
+    <row r="105" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B105" s="33" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B99" s="33" t="str">
+    <row r="106" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B106" s="33" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B100" s="33" t="str">
+    <row r="107" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B107" s="33" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B101" s="33" t="str">
+    <row r="108" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B108" s="33" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B102" s="33" t="str">
+    <row r="109" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B109" s="33" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B103" s="33" t="str">
+    <row r="110" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B110" s="33" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B104" s="33" t="str">
+    <row r="111" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B111" s="33" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B105" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B106" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B107" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B108" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B109" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B110" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B111" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B112" s="33" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -6417,7 +6659,7 @@
     </row>
     <row r="115" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B115" s="33" t="str">
-        <f t="shared" ref="B115:B146" si="3">IF(C115="","",B114+1)</f>
+        <f t="shared" ref="B115:B140" si="3">IF(C115="","",B114+1)</f>
         <v/>
       </c>
     </row>
@@ -6578,15 +6820,75 @@
     </sortState>
   </autoFilter>
   <mergeCells count="102">
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="P44:R44"/>
-    <mergeCell ref="O56:P56"/>
-    <mergeCell ref="Q56:S56"/>
-    <mergeCell ref="P62:R62"/>
-    <mergeCell ref="P63:R63"/>
-    <mergeCell ref="P64:R64"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="K72:M72"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="K53:M53"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="K54:M54"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="K48:M48"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="K51:M51"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="K52:M52"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:S18"/>
     <mergeCell ref="O72:P72"/>
     <mergeCell ref="Q72:S72"/>
     <mergeCell ref="P8:R8"/>
@@ -6611,77 +6913,1938 @@
     <mergeCell ref="O36:P36"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:S20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="I72:J72"/>
-    <mergeCell ref="K72:M72"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="K53:M53"/>
-    <mergeCell ref="I54:J54"/>
-    <mergeCell ref="K54:M54"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="K48:M48"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="K51:M51"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="K52:M52"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:M40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:M39"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="P44:R44"/>
+    <mergeCell ref="O56:P56"/>
+    <mergeCell ref="Q56:S56"/>
+    <mergeCell ref="P62:R62"/>
+    <mergeCell ref="P63:R63"/>
+    <mergeCell ref="P64:R64"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3AACD3-19B9-4F27-A163-F65AFD95CDAE}">
+  <dimension ref="B2:H84"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.25" style="3" customWidth="1"/>
+    <col min="3" max="4" width="9" style="1"/>
+    <col min="5" max="6" width="30.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="G2" s="102" t="s">
+        <v>341</v>
+      </c>
+      <c r="H2" s="102" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C3" s="1" t="e">
+        <f>FIND("w_",B3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D3" s="1" t="e">
+        <f>FIND(";",B3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E3" s="1" t="e">
+        <f>MID(B3,C3,D3-C3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F3" s="146"/>
+      <c r="G3" s="1">
+        <f>COUNTIF($E$3:$E$100,F3)</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <f>COUNTIF($F$3:$F$100,E3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C4" s="1" t="e">
+        <f t="shared" ref="C4:C67" si="0">FIND("w_",B4)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D4" s="1" t="e">
+        <f t="shared" ref="D4:D67" si="1">FIND(";",B4)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E4" s="1" t="e">
+        <f t="shared" ref="E4:E67" si="2">MID(B4,C4,D4-C4)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F4" s="146"/>
+      <c r="G4" s="1">
+        <f t="shared" ref="G4:G67" si="3">COUNTIF($E$3:$E$100,F4)</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <f t="shared" ref="H4:H67" si="4">COUNTIF($F$3:$F$100,E4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C5" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D5" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E5" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F5" s="146"/>
+      <c r="G5" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C6" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D6" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E6" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F6" s="146"/>
+      <c r="G6" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C7" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D7" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E7" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F7" s="146"/>
+      <c r="G7" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C8" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D8" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E8" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F8" s="146"/>
+      <c r="G8" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C9" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D9" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E9" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F9" s="146"/>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C10" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D10" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E10" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F10" s="146"/>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C11" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D11" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E11" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F11" s="146"/>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C12" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D12" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E12" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F12" s="146"/>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C13" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D13" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E13" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F13" s="146"/>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C14" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D14" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E14" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F14" s="146"/>
+      <c r="G14" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C15" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D15" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E15" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F15" s="146"/>
+      <c r="G15" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C16" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D16" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E16" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F16" s="146"/>
+      <c r="G16" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C17" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D17" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E17" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F17" s="146"/>
+      <c r="G17" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C18" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D18" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E18" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F18" s="146"/>
+      <c r="G18" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C19" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D19" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E19" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F19" s="146"/>
+      <c r="G19" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C20" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D20" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E20" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F20" s="146"/>
+      <c r="G20" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C21" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D21" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E21" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F21" s="146"/>
+      <c r="G21" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C22" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D22" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E22" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F22" s="147"/>
+      <c r="G22" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C23" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D23" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E23" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F23" s="146"/>
+      <c r="G23" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C24" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D24" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E24" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F24" s="146"/>
+      <c r="G24" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C25" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D25" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E25" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F25" s="146"/>
+      <c r="G25" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C26" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D26" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E26" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F26" s="146"/>
+      <c r="G26" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C27" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D27" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E27" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F27" s="146"/>
+      <c r="G27" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C28" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D28" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E28" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F28" s="148"/>
+      <c r="G28" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C29" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D29" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E29" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F29" s="146"/>
+      <c r="G29" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C30" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D30" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E30" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F30" s="146"/>
+      <c r="G30" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C31" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D31" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E31" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F31" s="146"/>
+      <c r="G31" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C32" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D32" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E32" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F32" s="146"/>
+      <c r="G32" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C33" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D33" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E33" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F33" s="146"/>
+      <c r="G33" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C34" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D34" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E34" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F34" s="146"/>
+      <c r="G34" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C35" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D35" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E35" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F35" s="146"/>
+      <c r="G35" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C36" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D36" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E36" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F36" s="146"/>
+      <c r="G36" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C37" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D37" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E37" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F37" s="146"/>
+      <c r="G37" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C38" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D38" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E38" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F38" s="146"/>
+      <c r="G38" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C39" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D39" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E39" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F39" s="146"/>
+      <c r="G39" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C40" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D40" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E40" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F40" s="146"/>
+      <c r="G40" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C41" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D41" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E41" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F41" s="146"/>
+      <c r="G41" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C42" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D42" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E42" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F42" s="147"/>
+      <c r="G42" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C43" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D43" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E43" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F43" s="146"/>
+      <c r="G43" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C44" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D44" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E44" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F44" s="146"/>
+      <c r="G44" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C45" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D45" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E45" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F45" s="146"/>
+      <c r="G45" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C46" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D46" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E46" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F46" s="146"/>
+      <c r="G46" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C47" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D47" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E47" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F47" s="146"/>
+      <c r="G47" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C48" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D48" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E48" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F48" s="146"/>
+      <c r="G48" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C49" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D49" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E49" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F49" s="146"/>
+      <c r="G49" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C50" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D50" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E50" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F50" s="146"/>
+      <c r="G50" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H50" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C51" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D51" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E51" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F51" s="146"/>
+      <c r="G51" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H51" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C52" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D52" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E52" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F52" s="146"/>
+      <c r="G52" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C53" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D53" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E53" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F53" s="148"/>
+      <c r="G53" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C54" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D54" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E54" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F54" s="146"/>
+      <c r="G54" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H54" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C55" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D55" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E55" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F55" s="146"/>
+      <c r="G55" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H55" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C56" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D56" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E56" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F56" s="146"/>
+      <c r="G56" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H56" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C57" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D57" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E57" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F57" s="146"/>
+      <c r="G57" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H57" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C58" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D58" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E58" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F58" s="147"/>
+      <c r="G58" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C59" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D59" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E59" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F59" s="147"/>
+      <c r="G59" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H59" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C60" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D60" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E60" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F60" s="147"/>
+      <c r="G60" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C61" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D61" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E61" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F61" s="146"/>
+      <c r="G61" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H61" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C62" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D62" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E62" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F62" s="146"/>
+      <c r="G62" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H62" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C63" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D63" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E63" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F63" s="146"/>
+      <c r="G63" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H63" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C64" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D64" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E64" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F64" s="146"/>
+      <c r="G64" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H64" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C65" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D65" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E65" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F65" s="146"/>
+      <c r="G65" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H65" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C66" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D66" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E66" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F66" s="146"/>
+      <c r="G66" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H66" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C67" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D67" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E67" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F67" s="146"/>
+      <c r="G67" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H67" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C68" s="1" t="e">
+        <f t="shared" ref="C68:C84" si="5">FIND("w_",B68)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D68" s="1" t="e">
+        <f t="shared" ref="D68:D84" si="6">FIND(";",B68)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E68" s="1" t="e">
+        <f t="shared" ref="E68:E84" si="7">MID(B68,C68,D68-C68)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F68" s="148"/>
+      <c r="G68" s="1">
+        <f t="shared" ref="G68:G84" si="8">COUNTIF($E$3:$E$100,F68)</f>
+        <v>0</v>
+      </c>
+      <c r="H68" s="1">
+        <f t="shared" ref="H68:H84" si="9">COUNTIF($F$3:$F$100,E68)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C69" s="1" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D69" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E69" s="1" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F69" s="146"/>
+      <c r="G69" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H69" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C70" s="1" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D70" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E70" s="1" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F70" s="146"/>
+      <c r="G70" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H70" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C71" s="1" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D71" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E71" s="1" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F71" s="146"/>
+      <c r="G71" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H71" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C72" s="1" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D72" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E72" s="1" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F72" s="146"/>
+      <c r="G72" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H72" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C73" s="1" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D73" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E73" s="1" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F73" s="146"/>
+      <c r="G73" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H73" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C74" s="1" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D74" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E74" s="1" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F74" s="146"/>
+      <c r="G74" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H74" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C75" s="1" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D75" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E75" s="1" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F75" s="146"/>
+      <c r="G75" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H75" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C76" s="1" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D76" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E76" s="1" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F76" s="146"/>
+      <c r="G76" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H76" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C77" s="1" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D77" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E77" s="1" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F77" s="146"/>
+      <c r="G77" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H77" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C78" s="1" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D78" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E78" s="1" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G78" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H78" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C79" s="1" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D79" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E79" s="1" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G79" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H79" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C80" s="1" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D80" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E80" s="1" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G80" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H80" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C81" s="1" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D81" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E81" s="1" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G81" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H81" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C82" s="1" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D82" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E82" s="1" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G82" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H82" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C83" s="1" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D83" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E83" s="1" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G83" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H83" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C84" s="1" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D84" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E84" s="1" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G84" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H84" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Document/IDD.xlsx
+++ b/Document/IDD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\SoC_Design\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9644CE-B4C7-46A8-9CB2-BE0B6BEBB16E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC941B3F-7F6D-47C9-B9E9-D04C64D437AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
   </bookViews>
   <sheets>
     <sheet name="CPU" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="377">
   <si>
     <t>top_cpu</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1121,11 +1121,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>u_alusrc_mux
-u_ex_mem_bridge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>w_mem_reg_rdata2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1404,15 +1399,6 @@
   </si>
   <si>
     <t>엑셀 복붙용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_ctr_regwrite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_mem_wb_bridge
-u_forward_regdst_mux</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1443,17 +1429,9 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>u_forward_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>w_mem_regdst_mux_reg</t>
   </si>
   <si>
-    <t>u_forward_regdst_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rt or rd Register (MEM)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1470,34 +1448,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>w_ctr_forward_a</t>
-  </si>
-  <si>
-    <t>w_ctr_forward_b</t>
-  </si>
-  <si>
-    <t>w_ex_forward_mux_data_a</t>
-  </si>
-  <si>
-    <t>w_ex_forward_mux_data_b</t>
-  </si>
-  <si>
-    <t>ForwardA Output</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ForwardB Output</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_forward_a_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_forward_b_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ForwardA MUX Data</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1506,40 +1456,106 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>u_alu_forwarding_unit</t>
+  </si>
+  <si>
+    <t>u_mem_wb_bridge
+u_alu_forward_mem_regdst_mux</t>
+  </si>
+  <si>
+    <t>u_alu_forward_mem_regdst_mux</t>
+  </si>
+  <si>
+    <t>w_ctr_alu_forward_a</t>
+  </si>
+  <si>
+    <t>w_ctr_alu_forward_b</t>
+  </si>
+  <si>
+    <t>ALU ForwardA Output</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU ForwardB Output</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alu_forward_a_mux</t>
+  </si>
+  <si>
+    <t>u_alu_forward_b_mux</t>
+  </si>
+  <si>
+    <t>u_mem_wb_bridge
+o_d_mem_addr
+u_alu_forward_a_mux
+u_alu_forward_b_mux</t>
+  </si>
+  <si>
     <t>u_ex_mem_bridge
-u_forward_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">u_mem_wb_bridge
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">o_d_mem_addr
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>u_forward_a_mux
-u_forward_b_mux</t>
-    </r>
+u_alu_forwarding_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alu_forward_b_mux
+u_ex_mem_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_regwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_mem_wb_bridge
+u_alu_forwarding_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WDATA Forward Output</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_mem_wb_bridge
+u_alu_forward_mem_regdst_mux
+u_wdata_forward_unit</t>
+  </si>
+  <si>
+    <t>u_registers
+u_wdata_forwarding_unit</t>
+  </si>
+  <si>
+    <t>w_ctr_wdata_forward</t>
+  </si>
+  <si>
+    <t>u_wdata_forwarding_unit</t>
+  </si>
+  <si>
+    <t>w_ex_alu_forward_mux_data_a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_alu_forward_mux_data_b</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alu_src_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_wdata_forward_mux_data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_wdata_forward_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WDATA Forward MUX Data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_memtoreg_mux
+u_wdata_forward_mux</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2165,7 +2181,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2493,18 +2509,6 @@
     <xf numFmtId="176" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2529,16 +2533,58 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2556,62 +2602,26 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2973,32 +2983,32 @@
   <sheetData>
     <row r="1" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="143" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="145"/>
-      <c r="I2" s="122" t="s">
+      <c r="B2" s="131" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="133"/>
+      <c r="I2" s="117" t="s">
         <v>104</v>
       </c>
-      <c r="J2" s="123"/>
-      <c r="K2" s="122" t="s">
+      <c r="J2" s="119"/>
+      <c r="K2" s="117" t="s">
         <v>98</v>
       </c>
-      <c r="L2" s="124"/>
-      <c r="M2" s="123"/>
-      <c r="O2" s="122" t="s">
+      <c r="L2" s="118"/>
+      <c r="M2" s="119"/>
+      <c r="O2" s="117" t="s">
         <v>104</v>
       </c>
-      <c r="P2" s="123"/>
-      <c r="Q2" s="122" t="s">
+      <c r="P2" s="119"/>
+      <c r="Q2" s="117" t="s">
         <v>151</v>
       </c>
-      <c r="R2" s="124"/>
-      <c r="S2" s="123"/>
+      <c r="R2" s="118"/>
+      <c r="S2" s="119"/>
     </row>
     <row r="3" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="34" t="s">
@@ -3019,24 +3029,24 @@
       <c r="G3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="132" t="s">
+      <c r="I3" s="126" t="s">
         <v>110</v>
       </c>
-      <c r="J3" s="133"/>
-      <c r="K3" s="134" t="s">
+      <c r="J3" s="127"/>
+      <c r="K3" s="128" t="s">
         <v>111</v>
       </c>
-      <c r="L3" s="135"/>
-      <c r="M3" s="136"/>
-      <c r="O3" s="132" t="s">
+      <c r="L3" s="129"/>
+      <c r="M3" s="130"/>
+      <c r="O3" s="126" t="s">
         <v>110</v>
       </c>
-      <c r="P3" s="133"/>
-      <c r="Q3" s="134" t="s">
+      <c r="P3" s="127"/>
+      <c r="Q3" s="128" t="s">
         <v>239</v>
       </c>
-      <c r="R3" s="135"/>
-      <c r="S3" s="136"/>
+      <c r="R3" s="129"/>
+      <c r="S3" s="130"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B4" s="35">
@@ -3057,24 +3067,24 @@
       <c r="G4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="132" t="s">
+      <c r="I4" s="126" t="s">
         <v>108</v>
       </c>
-      <c r="J4" s="133"/>
-      <c r="K4" s="132" t="s">
+      <c r="J4" s="127"/>
+      <c r="K4" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="L4" s="137"/>
-      <c r="M4" s="133"/>
-      <c r="O4" s="132" t="s">
+      <c r="L4" s="140"/>
+      <c r="M4" s="127"/>
+      <c r="O4" s="126" t="s">
         <v>108</v>
       </c>
-      <c r="P4" s="133"/>
-      <c r="Q4" s="132" t="s">
+      <c r="P4" s="127"/>
+      <c r="Q4" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="R4" s="137"/>
-      <c r="S4" s="133"/>
+      <c r="R4" s="140"/>
+      <c r="S4" s="127"/>
     </row>
     <row r="5" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="54">
@@ -3095,24 +3105,24 @@
       <c r="G5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="138" t="s">
+      <c r="I5" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="139"/>
-      <c r="K5" s="140" t="s">
+      <c r="J5" s="121"/>
+      <c r="K5" s="122" t="s">
         <v>103</v>
       </c>
-      <c r="L5" s="121"/>
-      <c r="M5" s="141"/>
-      <c r="O5" s="138" t="s">
+      <c r="L5" s="123"/>
+      <c r="M5" s="124"/>
+      <c r="O5" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="139"/>
-      <c r="Q5" s="140" t="s">
+      <c r="P5" s="121"/>
+      <c r="Q5" s="122" t="s">
         <v>152</v>
       </c>
-      <c r="R5" s="121"/>
-      <c r="S5" s="141"/>
+      <c r="R5" s="123"/>
+      <c r="S5" s="124"/>
     </row>
     <row r="6" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="55">
@@ -3136,22 +3146,22 @@
       <c r="I6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="130" t="s">
+      <c r="J6" s="125" t="s">
         <v>99</v>
       </c>
-      <c r="K6" s="130"/>
-      <c r="L6" s="130"/>
+      <c r="K6" s="125"/>
+      <c r="L6" s="125"/>
       <c r="M6" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="130" t="s">
+      <c r="P6" s="125" t="s">
         <v>99</v>
       </c>
-      <c r="Q6" s="130"/>
-      <c r="R6" s="130"/>
+      <c r="Q6" s="125"/>
+      <c r="R6" s="125"/>
       <c r="S6" s="69" t="s">
         <v>8</v>
       </c>
@@ -3178,22 +3188,22 @@
       <c r="I7" s="70">
         <v>1</v>
       </c>
-      <c r="J7" s="142" t="s">
+      <c r="J7" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="142"/>
-      <c r="L7" s="142"/>
+      <c r="K7" s="134"/>
+      <c r="L7" s="134"/>
       <c r="M7" s="71" t="s">
         <v>134</v>
       </c>
       <c r="O7" s="87">
         <v>1</v>
       </c>
-      <c r="P7" s="131" t="s">
+      <c r="P7" s="141" t="s">
         <v>21</v>
       </c>
-      <c r="Q7" s="131"/>
-      <c r="R7" s="131"/>
+      <c r="Q7" s="141"/>
+      <c r="R7" s="141"/>
       <c r="S7" s="88" t="s">
         <v>134</v>
       </c>
@@ -3235,11 +3245,11 @@
       <c r="O8" s="80">
         <v>2</v>
       </c>
-      <c r="P8" s="121" t="s">
+      <c r="P8" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="121"/>
-      <c r="R8" s="121"/>
+      <c r="Q8" s="123"/>
+      <c r="R8" s="123"/>
       <c r="S8" s="82" t="s">
         <v>135</v>
       </c>
@@ -3413,15 +3423,15 @@
       <c r="G12" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="125" t="s">
+      <c r="I12" s="135" t="s">
         <v>106</v>
       </c>
-      <c r="J12" s="126"/>
-      <c r="K12" s="127" t="s">
+      <c r="J12" s="136"/>
+      <c r="K12" s="137" t="s">
         <v>107</v>
       </c>
-      <c r="L12" s="128"/>
-      <c r="M12" s="129"/>
+      <c r="L12" s="138"/>
+      <c r="M12" s="139"/>
       <c r="O12" s="72">
         <v>3</v>
       </c>
@@ -3544,15 +3554,15 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="O16" s="125" t="s">
+      <c r="O16" s="135" t="s">
         <v>106</v>
       </c>
-      <c r="P16" s="126"/>
-      <c r="Q16" s="127" t="s">
+      <c r="P16" s="136"/>
+      <c r="Q16" s="137" t="s">
         <v>242</v>
       </c>
-      <c r="R16" s="128"/>
-      <c r="S16" s="129"/>
+      <c r="R16" s="138"/>
+      <c r="S16" s="139"/>
     </row>
     <row r="17" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="90" t="s">
@@ -3586,32 +3596,32 @@
         <v>1</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="I18" s="122" t="s">
+        <v>356</v>
+      </c>
+      <c r="I18" s="117" t="s">
         <v>104</v>
       </c>
-      <c r="J18" s="123"/>
-      <c r="K18" s="122" t="s">
+      <c r="J18" s="119"/>
+      <c r="K18" s="117" t="s">
         <v>105</v>
       </c>
-      <c r="L18" s="124"/>
-      <c r="M18" s="123"/>
-      <c r="O18" s="122" t="s">
+      <c r="L18" s="118"/>
+      <c r="M18" s="119"/>
+      <c r="O18" s="117" t="s">
         <v>104</v>
       </c>
-      <c r="P18" s="123"/>
-      <c r="Q18" s="122" t="s">
+      <c r="P18" s="119"/>
+      <c r="Q18" s="117" t="s">
         <v>161</v>
       </c>
-      <c r="R18" s="124"/>
-      <c r="S18" s="123"/>
+      <c r="R18" s="118"/>
+      <c r="S18" s="119"/>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B19" s="33">
@@ -3625,32 +3635,32 @@
         <v>1</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="I19" s="132" t="s">
+        <v>357</v>
+      </c>
+      <c r="I19" s="126" t="s">
         <v>110</v>
       </c>
-      <c r="J19" s="133"/>
-      <c r="K19" s="134" t="s">
+      <c r="J19" s="127"/>
+      <c r="K19" s="128" t="s">
         <v>112</v>
       </c>
-      <c r="L19" s="135"/>
-      <c r="M19" s="136"/>
-      <c r="O19" s="132" t="s">
+      <c r="L19" s="129"/>
+      <c r="M19" s="130"/>
+      <c r="O19" s="126" t="s">
         <v>110</v>
       </c>
-      <c r="P19" s="133"/>
-      <c r="Q19" s="134" t="s">
+      <c r="P19" s="127"/>
+      <c r="Q19" s="128" t="s">
         <v>239</v>
       </c>
-      <c r="R19" s="135"/>
-      <c r="S19" s="136"/>
+      <c r="R19" s="129"/>
+      <c r="S19" s="130"/>
     </row>
     <row r="20" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B20" s="33">
@@ -3672,24 +3682,24 @@
       <c r="G20" s="99" t="s">
         <v>199</v>
       </c>
-      <c r="I20" s="132" t="s">
+      <c r="I20" s="126" t="s">
         <v>108</v>
       </c>
-      <c r="J20" s="133"/>
-      <c r="K20" s="134" t="s">
+      <c r="J20" s="127"/>
+      <c r="K20" s="128" t="s">
         <v>109</v>
       </c>
-      <c r="L20" s="135"/>
-      <c r="M20" s="136"/>
-      <c r="O20" s="132" t="s">
+      <c r="L20" s="129"/>
+      <c r="M20" s="130"/>
+      <c r="O20" s="126" t="s">
         <v>108</v>
       </c>
-      <c r="P20" s="133"/>
-      <c r="Q20" s="132" t="s">
+      <c r="P20" s="127"/>
+      <c r="Q20" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="R20" s="137"/>
-      <c r="S20" s="133"/>
+      <c r="R20" s="140"/>
+      <c r="S20" s="127"/>
     </row>
     <row r="21" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="33">
@@ -3697,7 +3707,7 @@
         <v>4</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
@@ -3711,24 +3721,24 @@
       <c r="G21" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="I21" s="138" t="s">
+      <c r="I21" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="139"/>
-      <c r="K21" s="140" t="s">
+      <c r="J21" s="121"/>
+      <c r="K21" s="122" t="s">
         <v>126</v>
       </c>
-      <c r="L21" s="121"/>
-      <c r="M21" s="141"/>
-      <c r="O21" s="138" t="s">
+      <c r="L21" s="123"/>
+      <c r="M21" s="124"/>
+      <c r="O21" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="139"/>
-      <c r="Q21" s="140" t="s">
+      <c r="P21" s="121"/>
+      <c r="Q21" s="122" t="s">
         <v>162</v>
       </c>
-      <c r="R21" s="121"/>
-      <c r="S21" s="141"/>
+      <c r="R21" s="123"/>
+      <c r="S21" s="124"/>
     </row>
     <row r="22" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="33">
@@ -3736,7 +3746,7 @@
         <v>5</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D22" s="1">
         <v>4</v>
@@ -3753,22 +3763,22 @@
       <c r="I22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J22" s="130" t="s">
+      <c r="J22" s="125" t="s">
         <v>99</v>
       </c>
-      <c r="K22" s="130"/>
-      <c r="L22" s="130"/>
+      <c r="K22" s="125"/>
+      <c r="L22" s="125"/>
       <c r="M22" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P22" s="130" t="s">
+      <c r="P22" s="125" t="s">
         <v>99</v>
       </c>
-      <c r="Q22" s="130"/>
-      <c r="R22" s="130"/>
+      <c r="Q22" s="125"/>
+      <c r="R22" s="125"/>
       <c r="S22" s="69" t="s">
         <v>8</v>
       </c>
@@ -3796,22 +3806,22 @@
       <c r="I23" s="70">
         <v>1</v>
       </c>
-      <c r="J23" s="142" t="s">
+      <c r="J23" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="K23" s="142"/>
-      <c r="L23" s="142"/>
+      <c r="K23" s="134"/>
+      <c r="L23" s="134"/>
       <c r="M23" s="71" t="s">
         <v>135</v>
       </c>
       <c r="O23" s="87">
         <v>1</v>
       </c>
-      <c r="P23" s="131" t="s">
+      <c r="P23" s="141" t="s">
         <v>21</v>
       </c>
-      <c r="Q23" s="131"/>
-      <c r="R23" s="131"/>
+      <c r="Q23" s="141"/>
+      <c r="R23" s="141"/>
       <c r="S23" s="88" t="s">
         <v>134</v>
       </c>
@@ -3822,7 +3832,7 @@
         <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
@@ -3831,7 +3841,7 @@
         <v>80</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>86</v>
@@ -3854,11 +3864,11 @@
       <c r="O24" s="80">
         <v>2</v>
       </c>
-      <c r="P24" s="121" t="s">
+      <c r="P24" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="Q24" s="121"/>
-      <c r="R24" s="121"/>
+      <c r="Q24" s="123"/>
+      <c r="R24" s="123"/>
       <c r="S24" s="82" t="s">
         <v>135</v>
       </c>
@@ -3914,13 +3924,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B26" s="33">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D26" s="90" t="s">
         <v>20</v>
@@ -3929,7 +3939,7 @@
         <v>81</v>
       </c>
       <c r="F26" s="103" t="s">
-        <v>361</v>
+        <v>77</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>83</v>
@@ -3971,7 +3981,7 @@
         <v>10</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D27" s="1">
         <v>1</v>
@@ -3980,10 +3990,10 @@
         <v>243</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I27" s="83">
         <v>3</v>
@@ -4022,7 +4032,7 @@
         <v>11</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D28" s="90" t="s">
         <v>20</v>
@@ -4073,7 +4083,7 @@
         <v>12</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D29" s="90" t="s">
         <v>21</v>
@@ -4175,13 +4185,13 @@
         <v>14</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D31" s="1">
         <v>1</v>
       </c>
       <c r="E31" s="102" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>53</v>
@@ -4226,7 +4236,7 @@
         <v>15</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
@@ -4238,17 +4248,17 @@
         <v>36</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="I32" s="125" t="s">
+        <v>271</v>
+      </c>
+      <c r="I32" s="135" t="s">
         <v>106</v>
       </c>
-      <c r="J32" s="126"/>
-      <c r="K32" s="127" t="s">
+      <c r="J32" s="136"/>
+      <c r="K32" s="137" t="s">
         <v>80</v>
       </c>
-      <c r="L32" s="128"/>
-      <c r="M32" s="129"/>
+      <c r="L32" s="138"/>
+      <c r="M32" s="139"/>
       <c r="O32" s="83">
         <v>7</v>
       </c>
@@ -4271,7 +4281,7 @@
         <v>16</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D33" s="1">
         <v>1</v>
@@ -4283,7 +4293,7 @@
         <v>244</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O33" s="83">
         <v>8</v>
@@ -4343,7 +4353,7 @@
         <v>18</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D35" s="90" t="s">
         <v>56</v>
@@ -4355,7 +4365,7 @@
         <v>244</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O35" s="80">
         <v>10</v>
@@ -4379,7 +4389,7 @@
         <v>19</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D36" s="90" t="s">
         <v>56</v>
@@ -4388,20 +4398,20 @@
         <v>243</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="O36" s="125" t="s">
+        <v>341</v>
+      </c>
+      <c r="O36" s="135" t="s">
         <v>106</v>
       </c>
-      <c r="P36" s="126"/>
-      <c r="Q36" s="127" t="s">
+      <c r="P36" s="136"/>
+      <c r="Q36" s="137" t="s">
         <v>243</v>
       </c>
-      <c r="R36" s="128"/>
-      <c r="S36" s="129"/>
+      <c r="R36" s="138"/>
+      <c r="S36" s="139"/>
     </row>
     <row r="37" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="33">
@@ -4409,7 +4419,7 @@
         <v>20</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D37" s="90" t="s">
         <v>56</v>
@@ -4418,10 +4428,10 @@
         <v>243</v>
       </c>
       <c r="F37" s="103" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="38" spans="2:19" ht="33" x14ac:dyDescent="0.3">
@@ -4430,77 +4440,77 @@
         <v>21</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="D38" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F38" s="103" t="s">
         <v>77</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="I38" s="122" t="s">
+        <v>349</v>
+      </c>
+      <c r="I38" s="117" t="s">
         <v>104</v>
       </c>
-      <c r="J38" s="123"/>
-      <c r="K38" s="122" t="s">
+      <c r="J38" s="119"/>
+      <c r="K38" s="117" t="s">
         <v>124</v>
       </c>
-      <c r="L38" s="124"/>
-      <c r="M38" s="123"/>
-      <c r="O38" s="122" t="s">
+      <c r="L38" s="118"/>
+      <c r="M38" s="119"/>
+      <c r="O38" s="117" t="s">
         <v>104</v>
       </c>
-      <c r="P38" s="123"/>
-      <c r="Q38" s="122" t="s">
+      <c r="P38" s="119"/>
+      <c r="Q38" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="R38" s="124"/>
-      <c r="S38" s="123"/>
-    </row>
-    <row r="39" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+      <c r="R38" s="118"/>
+      <c r="S38" s="119"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B39" s="33">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="D39" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F39" s="103" t="s">
-        <v>77</v>
+        <v>372</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="I39" s="132" t="s">
+        <v>350</v>
+      </c>
+      <c r="I39" s="126" t="s">
         <v>110</v>
       </c>
-      <c r="J39" s="133"/>
-      <c r="K39" s="134" t="s">
+      <c r="J39" s="127"/>
+      <c r="K39" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="L39" s="135"/>
-      <c r="M39" s="136"/>
-      <c r="O39" s="132" t="s">
+      <c r="L39" s="129"/>
+      <c r="M39" s="130"/>
+      <c r="O39" s="126" t="s">
         <v>110</v>
       </c>
-      <c r="P39" s="133"/>
-      <c r="Q39" s="134" t="s">
+      <c r="P39" s="127"/>
+      <c r="Q39" s="128" t="s">
         <v>239</v>
       </c>
-      <c r="R39" s="135"/>
-      <c r="S39" s="136"/>
+      <c r="R39" s="129"/>
+      <c r="S39" s="130"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B40" s="33">
@@ -4508,7 +4518,7 @@
         <v>23</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D40" s="90" t="s">
         <v>20</v>
@@ -4522,24 +4532,24 @@
       <c r="G40" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="I40" s="132" t="s">
+      <c r="I40" s="126" t="s">
         <v>108</v>
       </c>
-      <c r="J40" s="133"/>
-      <c r="K40" s="134" t="s">
+      <c r="J40" s="127"/>
+      <c r="K40" s="128" t="s">
         <v>109</v>
       </c>
-      <c r="L40" s="135"/>
-      <c r="M40" s="136"/>
-      <c r="O40" s="132" t="s">
+      <c r="L40" s="129"/>
+      <c r="M40" s="130"/>
+      <c r="O40" s="126" t="s">
         <v>108</v>
       </c>
-      <c r="P40" s="133"/>
-      <c r="Q40" s="132" t="s">
+      <c r="P40" s="127"/>
+      <c r="Q40" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="R40" s="137"/>
-      <c r="S40" s="133"/>
+      <c r="R40" s="140"/>
+      <c r="S40" s="127"/>
     </row>
     <row r="41" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="33">
@@ -4561,24 +4571,24 @@
       <c r="G41" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="I41" s="138" t="s">
+      <c r="I41" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="139"/>
-      <c r="K41" s="140" t="s">
+      <c r="J41" s="121"/>
+      <c r="K41" s="122" t="s">
         <v>127</v>
       </c>
-      <c r="L41" s="121"/>
-      <c r="M41" s="141"/>
-      <c r="O41" s="138" t="s">
+      <c r="L41" s="123"/>
+      <c r="M41" s="124"/>
+      <c r="O41" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="P41" s="139"/>
-      <c r="Q41" s="140" t="s">
+      <c r="P41" s="121"/>
+      <c r="Q41" s="122" t="s">
         <v>176</v>
       </c>
-      <c r="R41" s="121"/>
-      <c r="S41" s="141"/>
+      <c r="R41" s="123"/>
+      <c r="S41" s="124"/>
     </row>
     <row r="42" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="33">
@@ -4586,7 +4596,7 @@
         <v>25</v>
       </c>
       <c r="C42" s="97" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D42" s="90" t="s">
         <v>21</v>
@@ -4598,27 +4608,27 @@
         <v>35</v>
       </c>
       <c r="G42" s="99" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J42" s="130" t="s">
+      <c r="J42" s="125" t="s">
         <v>99</v>
       </c>
-      <c r="K42" s="130"/>
-      <c r="L42" s="130"/>
+      <c r="K42" s="125"/>
+      <c r="L42" s="125"/>
       <c r="M42" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P42" s="130" t="s">
+      <c r="P42" s="125" t="s">
         <v>99</v>
       </c>
-      <c r="Q42" s="130"/>
-      <c r="R42" s="130"/>
+      <c r="Q42" s="125"/>
+      <c r="R42" s="125"/>
       <c r="S42" s="69" t="s">
         <v>8</v>
       </c>
@@ -4629,7 +4639,7 @@
         <v>26</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D43" s="90" t="s">
         <v>20</v>
@@ -4646,22 +4656,22 @@
       <c r="I43" s="70">
         <v>1</v>
       </c>
-      <c r="J43" s="142" t="s">
+      <c r="J43" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="K43" s="142"/>
-      <c r="L43" s="142"/>
+      <c r="K43" s="134"/>
+      <c r="L43" s="134"/>
       <c r="M43" s="71" t="s">
         <v>135</v>
       </c>
       <c r="O43" s="87">
         <v>1</v>
       </c>
-      <c r="P43" s="131" t="s">
+      <c r="P43" s="141" t="s">
         <v>21</v>
       </c>
-      <c r="Q43" s="131"/>
-      <c r="R43" s="131"/>
+      <c r="Q43" s="141"/>
+      <c r="R43" s="141"/>
       <c r="S43" s="88" t="s">
         <v>134</v>
       </c>
@@ -4677,10 +4687,10 @@
       <c r="D44" s="1">
         <v>1</v>
       </c>
-      <c r="E44" s="118" t="s">
+      <c r="E44" s="114" t="s">
         <v>243</v>
       </c>
-      <c r="F44" s="118" t="s">
+      <c r="F44" s="114" t="s">
         <v>244</v>
       </c>
       <c r="G44" s="5" t="s">
@@ -4704,11 +4714,11 @@
       <c r="O44" s="80">
         <v>2</v>
       </c>
-      <c r="P44" s="121" t="s">
+      <c r="P44" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="Q44" s="121"/>
-      <c r="R44" s="121"/>
+      <c r="Q44" s="123"/>
+      <c r="R44" s="123"/>
       <c r="S44" s="82" t="s">
         <v>135</v>
       </c>
@@ -4719,7 +4729,7 @@
         <v>28</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D45" s="1">
         <v>1</v>
@@ -4731,7 +4741,7 @@
         <v>244</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I45" s="72">
         <v>1</v>
@@ -4775,10 +4785,10 @@
       <c r="D46" s="1">
         <v>1</v>
       </c>
-      <c r="E46" s="118" t="s">
+      <c r="E46" s="114" t="s">
         <v>243</v>
       </c>
-      <c r="F46" s="118" t="s">
+      <c r="F46" s="114" t="s">
         <v>244</v>
       </c>
       <c r="G46" s="5" t="s">
@@ -4830,7 +4840,7 @@
         <v>240</v>
       </c>
       <c r="F47" s="103" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>226</v>
@@ -4871,30 +4881,30 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C48" s="116" t="s">
+      <c r="C48" s="112" t="s">
         <v>225</v>
       </c>
-      <c r="D48" s="117" t="s">
+      <c r="D48" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="E48" s="115" t="s">
+      <c r="E48" s="111" t="s">
         <v>240</v>
       </c>
-      <c r="F48" s="119" t="s">
-        <v>266</v>
-      </c>
-      <c r="G48" s="116" t="s">
+      <c r="F48" s="115" t="s">
+        <v>362</v>
+      </c>
+      <c r="G48" s="112" t="s">
         <v>227</v>
       </c>
-      <c r="I48" s="125" t="s">
+      <c r="I48" s="135" t="s">
         <v>106</v>
       </c>
-      <c r="J48" s="126"/>
-      <c r="K48" s="127" t="s">
+      <c r="J48" s="136"/>
+      <c r="K48" s="137" t="s">
         <v>66</v>
       </c>
-      <c r="L48" s="128"/>
-      <c r="M48" s="129"/>
+      <c r="L48" s="138"/>
+      <c r="M48" s="139"/>
       <c r="O48" s="83">
         <v>3</v>
       </c>
@@ -4917,7 +4927,7 @@
         <v>32</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D49" s="1">
         <v>1</v>
@@ -4925,11 +4935,11 @@
       <c r="E49" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="F49" s="103" t="s">
         <v>244</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O49" s="83">
         <v>4</v>
@@ -4948,12 +4958,12 @@
       </c>
     </row>
     <row r="50" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="120">
+      <c r="B50" s="116">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D50" s="90" t="s">
         <v>49</v>
@@ -4962,7 +4972,7 @@
         <v>47</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>54</v>
@@ -4989,13 +4999,13 @@
         <v>34</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D51" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>40</v>
@@ -5003,15 +5013,15 @@
       <c r="G51" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I51" s="122" t="s">
+      <c r="I51" s="117" t="s">
         <v>104</v>
       </c>
-      <c r="J51" s="123"/>
-      <c r="K51" s="122" t="s">
+      <c r="J51" s="119"/>
+      <c r="K51" s="117" t="s">
         <v>131</v>
       </c>
-      <c r="L51" s="124"/>
-      <c r="M51" s="123"/>
+      <c r="L51" s="118"/>
+      <c r="M51" s="119"/>
       <c r="O51" s="83">
         <v>6</v>
       </c>
@@ -5048,15 +5058,15 @@
       <c r="G52" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="I52" s="132" t="s">
+      <c r="I52" s="126" t="s">
         <v>110</v>
       </c>
-      <c r="J52" s="133"/>
-      <c r="K52" s="134" t="s">
+      <c r="J52" s="127"/>
+      <c r="K52" s="128" t="s">
         <v>132</v>
       </c>
-      <c r="L52" s="135"/>
-      <c r="M52" s="136"/>
+      <c r="L52" s="129"/>
+      <c r="M52" s="130"/>
       <c r="O52" s="83">
         <v>7</v>
       </c>
@@ -5093,15 +5103,15 @@
       <c r="G53" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="I53" s="132" t="s">
+      <c r="I53" s="126" t="s">
         <v>108</v>
       </c>
-      <c r="J53" s="133"/>
-      <c r="K53" s="134" t="s">
+      <c r="J53" s="127"/>
+      <c r="K53" s="128" t="s">
         <v>109</v>
       </c>
-      <c r="L53" s="135"/>
-      <c r="M53" s="136"/>
+      <c r="L53" s="129"/>
+      <c r="M53" s="130"/>
       <c r="O53" s="83">
         <v>8</v>
       </c>
@@ -5138,15 +5148,15 @@
       <c r="G54" s="99" t="s">
         <v>196</v>
       </c>
-      <c r="I54" s="138" t="s">
+      <c r="I54" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="139"/>
-      <c r="K54" s="140" t="s">
+      <c r="J54" s="121"/>
+      <c r="K54" s="122" t="s">
         <v>133</v>
       </c>
-      <c r="L54" s="121"/>
-      <c r="M54" s="141"/>
+      <c r="L54" s="123"/>
+      <c r="M54" s="124"/>
       <c r="O54" s="83">
         <v>9</v>
       </c>
@@ -5186,11 +5196,11 @@
       <c r="I55" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J55" s="130" t="s">
+      <c r="J55" s="125" t="s">
         <v>99</v>
       </c>
-      <c r="K55" s="130"/>
-      <c r="L55" s="130"/>
+      <c r="K55" s="125"/>
+      <c r="L55" s="125"/>
       <c r="M55" s="69" t="s">
         <v>8</v>
       </c>
@@ -5233,23 +5243,23 @@
       <c r="I56" s="87">
         <v>1</v>
       </c>
-      <c r="J56" s="131" t="s">
+      <c r="J56" s="141" t="s">
         <v>20</v>
       </c>
-      <c r="K56" s="131"/>
-      <c r="L56" s="131"/>
+      <c r="K56" s="141"/>
+      <c r="L56" s="141"/>
       <c r="M56" s="88" t="s">
         <v>135</v>
       </c>
-      <c r="O56" s="125" t="s">
+      <c r="O56" s="135" t="s">
         <v>106</v>
       </c>
-      <c r="P56" s="126"/>
-      <c r="Q56" s="127" t="s">
+      <c r="P56" s="136"/>
+      <c r="Q56" s="137" t="s">
         <v>244</v>
       </c>
-      <c r="R56" s="128"/>
-      <c r="S56" s="129"/>
+      <c r="R56" s="138"/>
+      <c r="S56" s="139"/>
     </row>
     <row r="57" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="33">
@@ -5274,11 +5284,11 @@
       <c r="I57" s="80">
         <v>2</v>
       </c>
-      <c r="J57" s="121" t="s">
+      <c r="J57" s="123" t="s">
         <v>55</v>
       </c>
-      <c r="K57" s="121"/>
-      <c r="L57" s="121"/>
+      <c r="K57" s="123"/>
+      <c r="L57" s="123"/>
       <c r="M57" s="89" t="s">
         <v>136</v>
       </c>
@@ -5318,15 +5328,15 @@
       <c r="M58" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="122" t="s">
+      <c r="O58" s="117" t="s">
         <v>104</v>
       </c>
-      <c r="P58" s="123"/>
-      <c r="Q58" s="122" t="s">
+      <c r="P58" s="119"/>
+      <c r="Q58" s="117" t="s">
         <v>186</v>
       </c>
-      <c r="R58" s="124"/>
-      <c r="S58" s="123"/>
+      <c r="R58" s="118"/>
+      <c r="S58" s="119"/>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B59" s="33">
@@ -5363,15 +5373,15 @@
       <c r="M59" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="O59" s="132" t="s">
+      <c r="O59" s="126" t="s">
         <v>110</v>
       </c>
-      <c r="P59" s="133"/>
-      <c r="Q59" s="134" t="s">
+      <c r="P59" s="127"/>
+      <c r="Q59" s="128" t="s">
         <v>239</v>
       </c>
-      <c r="R59" s="135"/>
-      <c r="S59" s="136"/>
+      <c r="R59" s="129"/>
+      <c r="S59" s="130"/>
     </row>
     <row r="60" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B60" s="33">
@@ -5379,7 +5389,7 @@
         <v>43</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D60" s="90" t="s">
         <v>57</v>
@@ -5408,15 +5418,15 @@
       <c r="M60" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="O60" s="132" t="s">
+      <c r="O60" s="126" t="s">
         <v>108</v>
       </c>
-      <c r="P60" s="133"/>
-      <c r="Q60" s="132" t="s">
+      <c r="P60" s="127"/>
+      <c r="Q60" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="R60" s="137"/>
-      <c r="S60" s="133"/>
+      <c r="R60" s="140"/>
+      <c r="S60" s="127"/>
     </row>
     <row r="61" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="33">
@@ -5453,15 +5463,15 @@
       <c r="M61" s="85" t="s">
         <v>147</v>
       </c>
-      <c r="O61" s="138" t="s">
+      <c r="O61" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="P61" s="139"/>
-      <c r="Q61" s="140" t="s">
+      <c r="P61" s="121"/>
+      <c r="Q61" s="122" t="s">
         <v>187</v>
       </c>
-      <c r="R61" s="121"/>
-      <c r="S61" s="141"/>
+      <c r="R61" s="123"/>
+      <c r="S61" s="124"/>
     </row>
     <row r="62" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B62" s="33">
@@ -5469,7 +5479,7 @@
         <v>45</v>
       </c>
       <c r="C62" s="97" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D62" s="101" t="s">
         <v>45</v>
@@ -5501,11 +5511,11 @@
       <c r="O62" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P62" s="130" t="s">
+      <c r="P62" s="125" t="s">
         <v>99</v>
       </c>
-      <c r="Q62" s="130"/>
-      <c r="R62" s="130"/>
+      <c r="Q62" s="125"/>
+      <c r="R62" s="125"/>
       <c r="S62" s="69" t="s">
         <v>8</v>
       </c>
@@ -5516,7 +5526,7 @@
         <v>46</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D63" s="90" t="s">
         <v>55</v>
@@ -5548,11 +5558,11 @@
       <c r="O63" s="87">
         <v>1</v>
       </c>
-      <c r="P63" s="131" t="s">
+      <c r="P63" s="141" t="s">
         <v>21</v>
       </c>
-      <c r="Q63" s="131"/>
-      <c r="R63" s="131"/>
+      <c r="Q63" s="141"/>
+      <c r="R63" s="141"/>
       <c r="S63" s="88" t="s">
         <v>134</v>
       </c>
@@ -5563,7 +5573,7 @@
         <v>47</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D64" s="90" t="s">
         <v>56</v>
@@ -5575,7 +5585,7 @@
         <v>243</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I64" s="83">
         <v>6</v>
@@ -5595,11 +5605,11 @@
       <c r="O64" s="80">
         <v>2</v>
       </c>
-      <c r="P64" s="121" t="s">
+      <c r="P64" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="Q64" s="121"/>
-      <c r="R64" s="121"/>
+      <c r="Q64" s="123"/>
+      <c r="R64" s="123"/>
       <c r="S64" s="82" t="s">
         <v>135</v>
       </c>
@@ -5610,7 +5620,7 @@
         <v>48</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D65" s="90" t="s">
         <v>56</v>
@@ -5619,10 +5629,10 @@
         <v>44</v>
       </c>
       <c r="F65" s="103" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="I65" s="83">
         <v>7</v>
@@ -5661,7 +5671,7 @@
         <v>49</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D66" s="90" t="s">
         <v>56</v>
@@ -5673,7 +5683,7 @@
         <v>62</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I66" s="83">
         <v>8</v>
@@ -5712,7 +5722,7 @@
         <v>50</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D67" s="1">
         <v>5</v>
@@ -5769,7 +5779,7 @@
         <v>20</v>
       </c>
       <c r="E68" s="102" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>243</v>
@@ -5822,7 +5832,7 @@
       <c r="E69" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F69" s="118" t="s">
+      <c r="F69" s="114" t="s">
         <v>243</v>
       </c>
       <c r="G69" s="5" t="s">
@@ -5924,7 +5934,7 @@
       <c r="E71" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F71" s="118" t="s">
+      <c r="F71" s="114" t="s">
         <v>243</v>
       </c>
       <c r="G71" s="5" t="s">
@@ -5975,49 +5985,49 @@
       <c r="E72" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F72" s="115" t="s">
+      <c r="F72" s="111" t="s">
         <v>240</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="I72" s="125" t="s">
+      <c r="I72" s="135" t="s">
         <v>106</v>
       </c>
-      <c r="J72" s="126"/>
-      <c r="K72" s="127" t="s">
+      <c r="J72" s="136"/>
+      <c r="K72" s="137" t="s">
         <v>58</v>
       </c>
-      <c r="L72" s="128"/>
-      <c r="M72" s="129"/>
-      <c r="O72" s="125" t="s">
+      <c r="L72" s="138"/>
+      <c r="M72" s="139"/>
+      <c r="O72" s="135" t="s">
         <v>106</v>
       </c>
-      <c r="P72" s="126"/>
-      <c r="Q72" s="127" t="s">
+      <c r="P72" s="136"/>
+      <c r="Q72" s="137" t="s">
         <v>245</v>
       </c>
-      <c r="R72" s="128"/>
-      <c r="S72" s="129"/>
+      <c r="R72" s="138"/>
+      <c r="S72" s="139"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B73" s="33">
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
-      <c r="C73" s="116" t="s">
+      <c r="C73" s="112" t="s">
         <v>211</v>
       </c>
-      <c r="D73" s="117" t="s">
+      <c r="D73" s="113" t="s">
         <v>20</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F73" s="115" t="s">
+      <c r="F73" s="111" t="s">
         <v>240</v>
       </c>
-      <c r="G73" s="116" t="s">
+      <c r="G73" s="112" t="s">
         <v>213</v>
       </c>
     </row>
@@ -6048,7 +6058,7 @@
         <v>58</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D75" s="101" t="s">
         <v>46</v>
@@ -6132,7 +6142,7 @@
         <v>62</v>
       </c>
       <c r="C79" s="93" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D79" s="94" t="s">
         <v>21</v>
@@ -6153,7 +6163,7 @@
         <v>63</v>
       </c>
       <c r="C80" s="93" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D80" s="92">
         <v>1</v>
@@ -6174,19 +6184,19 @@
         <v>64</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D81" s="90" t="s">
         <v>21</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="2:7" ht="66" x14ac:dyDescent="0.3">
@@ -6197,14 +6207,14 @@
       <c r="C82" s="104" t="s">
         <v>262</v>
       </c>
-      <c r="D82" s="113" t="s">
+      <c r="D82" s="109" t="s">
         <v>20</v>
       </c>
       <c r="E82" s="105" t="s">
         <v>244</v>
       </c>
-      <c r="F82" s="114" t="s">
-        <v>365</v>
+      <c r="F82" s="110" t="s">
+        <v>360</v>
       </c>
       <c r="G82" s="107" t="s">
         <v>265</v>
@@ -6216,7 +6226,7 @@
         <v>66</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D83" s="1">
         <v>1</v>
@@ -6225,10 +6235,10 @@
         <v>244</v>
       </c>
       <c r="F83" s="103" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="84" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6237,7 +6247,7 @@
         <v>67</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="D84" s="1">
         <v>1</v>
@@ -6246,10 +6256,10 @@
         <v>244</v>
       </c>
       <c r="F84" s="103" t="s">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="85" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6258,7 +6268,7 @@
         <v>68</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D85" s="90" t="s">
         <v>56</v>
@@ -6267,19 +6277,19 @@
         <v>244</v>
       </c>
       <c r="F85" s="103" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="86" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B86" s="33">
         <f t="shared" si="2"/>
         <v>69</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D86" s="90" t="s">
         <v>56</v>
@@ -6288,10 +6298,10 @@
         <v>244</v>
       </c>
       <c r="F86" s="103" t="s">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.3">
@@ -6321,7 +6331,7 @@
         <v>71</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D88" s="1">
         <v>1</v>
@@ -6333,7 +6343,7 @@
         <v>245</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="89" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6362,20 +6372,20 @@
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
-      <c r="C90" s="109" t="s">
+      <c r="C90" s="143" t="s">
+        <v>266</v>
+      </c>
+      <c r="D90" s="144" t="s">
+        <v>20</v>
+      </c>
+      <c r="E90" s="145" t="s">
+        <v>244</v>
+      </c>
+      <c r="F90" s="146" t="s">
+        <v>374</v>
+      </c>
+      <c r="G90" s="143" t="s">
         <v>267</v>
-      </c>
-      <c r="D90" s="110" t="s">
-        <v>20</v>
-      </c>
-      <c r="E90" s="111" t="s">
-        <v>244</v>
-      </c>
-      <c r="F90" s="112" t="s">
-        <v>17</v>
-      </c>
-      <c r="G90" s="109" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.3">
@@ -6384,28 +6394,28 @@
         <v>74</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D91" s="90" t="s">
         <v>56</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="92" spans="2:7" x14ac:dyDescent="0.3">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="92" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B92" s="33">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D92" s="90" t="s">
         <v>20</v>
@@ -6414,10 +6424,10 @@
         <v>245</v>
       </c>
       <c r="F92" s="103" t="s">
-        <v>82</v>
+        <v>376</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.3">
@@ -6426,7 +6436,7 @@
         <v>76</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D93" s="1">
         <v>1</v>
@@ -6438,7 +6448,7 @@
         <v>64</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.3">
@@ -6447,7 +6457,7 @@
         <v>77</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D94" s="90" t="s">
         <v>56</v>
@@ -6459,7 +6469,7 @@
         <v>64</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="95" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6468,7 +6478,7 @@
         <v>78</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D95" s="90" t="s">
         <v>56</v>
@@ -6480,7 +6490,7 @@
         <v>63</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.3">
@@ -6489,7 +6499,7 @@
         <v>79</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D96" s="1">
         <v>1</v>
@@ -6501,7 +6511,7 @@
         <v>82</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="97" spans="2:7" x14ac:dyDescent="0.3">
@@ -6510,7 +6520,7 @@
         <v>80</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D97" s="90" t="s">
         <v>20</v>
@@ -6522,16 +6532,16 @@
         <v>62</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.3">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B98" s="33">
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D98" s="90" t="s">
         <v>56</v>
@@ -6540,19 +6550,19 @@
         <v>64</v>
       </c>
       <c r="F98" s="103" t="s">
-        <v>62</v>
+        <v>367</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B99" s="33">
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D99" s="1">
         <v>1</v>
@@ -6560,23 +6570,53 @@
       <c r="E99" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="F99" s="2" t="s">
-        <v>62</v>
+      <c r="F99" s="103" t="s">
+        <v>367</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B100" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="B100" s="33">
+        <f t="shared" si="2"/>
+        <v>83</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D100" s="33">
+        <v>1</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B101" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="B101" s="33">
+        <f t="shared" si="2"/>
+        <v>84</v>
+      </c>
+      <c r="C101" s="104" t="s">
+        <v>373</v>
+      </c>
+      <c r="D101" s="109" t="s">
+        <v>20</v>
+      </c>
+      <c r="E101" s="142" t="s">
+        <v>374</v>
+      </c>
+      <c r="F101" s="106" t="s">
+        <v>17</v>
+      </c>
+      <c r="G101" s="107" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.3">
@@ -6820,39 +6860,51 @@
     </sortState>
   </autoFilter>
   <mergeCells count="102">
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="P44:R44"/>
+    <mergeCell ref="O56:P56"/>
+    <mergeCell ref="Q56:S56"/>
+    <mergeCell ref="P62:R62"/>
+    <mergeCell ref="P63:R63"/>
+    <mergeCell ref="P64:R64"/>
+    <mergeCell ref="O72:P72"/>
+    <mergeCell ref="Q72:S72"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="O59:P59"/>
+    <mergeCell ref="Q59:S59"/>
+    <mergeCell ref="O60:P60"/>
+    <mergeCell ref="Q60:S60"/>
+    <mergeCell ref="O61:P61"/>
+    <mergeCell ref="Q61:S61"/>
+    <mergeCell ref="P42:R42"/>
+    <mergeCell ref="P43:R43"/>
+    <mergeCell ref="O58:P58"/>
+    <mergeCell ref="Q58:S58"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="P22:R22"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:S18"/>
     <mergeCell ref="I72:J72"/>
     <mergeCell ref="K72:M72"/>
     <mergeCell ref="J57:L57"/>
@@ -6877,51 +6929,39 @@
     <mergeCell ref="K52:M52"/>
     <mergeCell ref="I40:J40"/>
     <mergeCell ref="K40:M40"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:S20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="O72:P72"/>
-    <mergeCell ref="Q72:S72"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="O59:P59"/>
-    <mergeCell ref="Q59:S59"/>
-    <mergeCell ref="O60:P60"/>
-    <mergeCell ref="Q60:S60"/>
-    <mergeCell ref="O61:P61"/>
-    <mergeCell ref="Q61:S61"/>
-    <mergeCell ref="P42:R42"/>
-    <mergeCell ref="P43:R43"/>
-    <mergeCell ref="O58:P58"/>
-    <mergeCell ref="Q58:S58"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="Q39:S39"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="Q41:S41"/>
-    <mergeCell ref="P22:R22"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="Q36:S36"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="P44:R44"/>
-    <mergeCell ref="O56:P56"/>
-    <mergeCell ref="Q56:S56"/>
-    <mergeCell ref="P62:R62"/>
-    <mergeCell ref="P63:R63"/>
-    <mergeCell ref="P64:R64"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6943,25 +6983,25 @@
   <sheetData>
     <row r="2" spans="2:8" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="102" t="s">
         <v>338</v>
       </c>
-      <c r="G2" s="102" t="s">
-        <v>341</v>
-      </c>
       <c r="H2" s="102" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
@@ -6977,7 +7017,6 @@
         <f>MID(B3,C3,D3-C3)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F3" s="146"/>
       <c r="G3" s="1">
         <f>COUNTIF($E$3:$E$100,F3)</f>
         <v>0</v>
@@ -7000,7 +7039,6 @@
         <f t="shared" ref="E4:E67" si="2">MID(B4,C4,D4-C4)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F4" s="146"/>
       <c r="G4" s="1">
         <f t="shared" ref="G4:G67" si="3">COUNTIF($E$3:$E$100,F4)</f>
         <v>0</v>
@@ -7023,7 +7061,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F5" s="146"/>
       <c r="G5" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7046,7 +7083,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F6" s="146"/>
       <c r="G6" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7069,7 +7105,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F7" s="146"/>
       <c r="G7" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7092,7 +7127,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F8" s="146"/>
       <c r="G8" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7115,7 +7149,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F9" s="146"/>
       <c r="G9" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7138,7 +7171,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F10" s="146"/>
       <c r="G10" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7161,7 +7193,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F11" s="146"/>
       <c r="G11" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7184,7 +7215,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F12" s="146"/>
       <c r="G12" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7207,7 +7237,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F13" s="146"/>
       <c r="G13" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7230,7 +7259,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F14" s="146"/>
       <c r="G14" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7253,7 +7281,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F15" s="146"/>
       <c r="G15" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7276,7 +7303,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F16" s="146"/>
       <c r="G16" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7299,7 +7325,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F17" s="146"/>
       <c r="G17" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7322,7 +7347,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F18" s="146"/>
       <c r="G18" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7345,7 +7369,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F19" s="146"/>
       <c r="G19" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7368,7 +7391,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F20" s="146"/>
       <c r="G20" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7391,7 +7413,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F21" s="146"/>
       <c r="G21" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7414,7 +7435,7 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F22" s="147"/>
+      <c r="F22" s="33"/>
       <c r="G22" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7437,7 +7458,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F23" s="146"/>
       <c r="G23" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7460,7 +7480,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F24" s="146"/>
       <c r="G24" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7483,7 +7502,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F25" s="146"/>
       <c r="G25" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7506,7 +7524,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F26" s="146"/>
       <c r="G26" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7529,7 +7546,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F27" s="146"/>
       <c r="G27" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7552,7 +7568,7 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F28" s="148"/>
+      <c r="F28" s="111"/>
       <c r="G28" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7575,7 +7591,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F29" s="146"/>
       <c r="G29" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7598,7 +7613,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F30" s="146"/>
       <c r="G30" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7621,7 +7635,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F31" s="146"/>
       <c r="G31" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7644,7 +7657,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F32" s="146"/>
       <c r="G32" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7667,7 +7679,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F33" s="146"/>
       <c r="G33" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7690,7 +7701,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F34" s="146"/>
       <c r="G34" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7713,7 +7723,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F35" s="146"/>
       <c r="G35" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7736,7 +7745,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F36" s="146"/>
       <c r="G36" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7759,7 +7767,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F37" s="146"/>
       <c r="G37" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7782,7 +7789,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F38" s="146"/>
       <c r="G38" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7805,7 +7811,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F39" s="146"/>
       <c r="G39" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7828,7 +7833,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F40" s="146"/>
       <c r="G40" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7851,7 +7855,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F41" s="146"/>
       <c r="G41" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7874,7 +7877,7 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F42" s="147"/>
+      <c r="F42" s="33"/>
       <c r="G42" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7897,7 +7900,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F43" s="146"/>
       <c r="G43" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7920,7 +7922,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F44" s="146"/>
       <c r="G44" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7943,7 +7944,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F45" s="146"/>
       <c r="G45" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7966,7 +7966,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F46" s="146"/>
       <c r="G46" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7989,7 +7988,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F47" s="146"/>
       <c r="G47" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8012,7 +8010,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F48" s="146"/>
       <c r="G48" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8035,7 +8032,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F49" s="146"/>
       <c r="G49" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8058,7 +8054,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F50" s="146"/>
       <c r="G50" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8081,7 +8076,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F51" s="146"/>
       <c r="G51" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8104,7 +8098,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F52" s="146"/>
       <c r="G52" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8127,7 +8120,7 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F53" s="148"/>
+      <c r="F53" s="111"/>
       <c r="G53" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8150,7 +8143,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F54" s="146"/>
       <c r="G54" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8173,7 +8165,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F55" s="146"/>
       <c r="G55" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8196,7 +8187,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F56" s="146"/>
       <c r="G56" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8219,7 +8209,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F57" s="146"/>
       <c r="G57" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8242,7 +8231,7 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F58" s="147"/>
+      <c r="F58" s="33"/>
       <c r="G58" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8265,7 +8254,7 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F59" s="147"/>
+      <c r="F59" s="33"/>
       <c r="G59" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8288,7 +8277,7 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F60" s="147"/>
+      <c r="F60" s="33"/>
       <c r="G60" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8311,7 +8300,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F61" s="146"/>
       <c r="G61" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8334,7 +8322,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F62" s="146"/>
       <c r="G62" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8357,7 +8344,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F63" s="146"/>
       <c r="G63" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8380,7 +8366,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F64" s="146"/>
       <c r="G64" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8403,7 +8388,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F65" s="146"/>
       <c r="G65" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8426,7 +8410,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F66" s="146"/>
       <c r="G66" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8449,7 +8432,6 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F67" s="146"/>
       <c r="G67" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8472,7 +8454,7 @@
         <f t="shared" ref="E68:E84" si="7">MID(B68,C68,D68-C68)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F68" s="148"/>
+      <c r="F68" s="111"/>
       <c r="G68" s="1">
         <f t="shared" ref="G68:G84" si="8">COUNTIF($E$3:$E$100,F68)</f>
         <v>0</v>
@@ -8495,7 +8477,6 @@
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F69" s="146"/>
       <c r="G69" s="1">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -8518,7 +8499,6 @@
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F70" s="146"/>
       <c r="G70" s="1">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -8541,7 +8521,6 @@
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F71" s="146"/>
       <c r="G71" s="1">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -8564,7 +8543,6 @@
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F72" s="146"/>
       <c r="G72" s="1">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -8587,7 +8565,6 @@
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F73" s="146"/>
       <c r="G73" s="1">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -8610,7 +8587,6 @@
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F74" s="146"/>
       <c r="G74" s="1">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -8633,7 +8609,6 @@
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F75" s="146"/>
       <c r="G75" s="1">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -8656,7 +8631,6 @@
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F76" s="146"/>
       <c r="G76" s="1">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -8679,7 +8653,6 @@
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F77" s="146"/>
       <c r="G77" s="1">
         <f t="shared" si="8"/>
         <v>0</v>

--- a/Document/IDD.xlsx
+++ b/Document/IDD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\SoC_Design\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC941B3F-7F6D-47C9-B9E9-D04C64D437AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B9693E-721C-41BD-A898-07F7EED66780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="382">
   <si>
     <t>top_cpu</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -292,11 +292,6 @@
   </si>
   <si>
     <t>u_registers</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_registers
-u_regdst_mux</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -862,10 +857,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>w_id_ctr_regdst</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>w_id_ctr_alusrc</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1351,14 +1342,6 @@
   </si>
   <si>
     <t>w_ex_ctr_regdst</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_ctr_regdst</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_ctr_regdst</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1456,106 +1439,156 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>u_alu_forwarding_unit</t>
+    <t>u_alu_forward_b_mux
+u_ex_mem_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_regwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>u_mem_wb_bridge
-u_alu_forward_mem_regdst_mux</t>
-  </si>
-  <si>
-    <t>u_alu_forward_mem_regdst_mux</t>
-  </si>
-  <si>
-    <t>w_ctr_alu_forward_a</t>
-  </si>
-  <si>
-    <t>w_ctr_alu_forward_b</t>
-  </si>
-  <si>
-    <t>ALU ForwardA Output</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU ForwardB Output</t>
+u_alu_forwarding_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_wdata_forwarding_unit</t>
+  </si>
+  <si>
+    <t>w_ex_alu_forward_mux_data_a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_alu_forward_mux_data_b</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alu_src_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_wdata_forward_mux_data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_wdata_forward_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WDATA Forward MUX Data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_regdst_mux_reg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rt or rd Register (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alu_forwarding_unit
+u_mem_wb_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_ex_mem_bridge
+u_regdst_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_ex_mem_bridge
+u_alu_forwarding_unit
+u_regdst_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_mem_wb_bridge
+u_wdata_forward_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_regdst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_regdst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_regdst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_fw_ctr_alu_1c_forward_a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_fw_ctr_alu_1c_forward_b</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WDATA Forward Output (1 Cycle)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU ForwardB Output (1 Cycle)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU ForwardA Output (1 Cycle)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_fw_ctr_wdata_1c_forward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_fw_ctr_alu_2c_forward_a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_fw_ctr_alu_2c_forward_b</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU ForwardA Output (2 Cycle)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>u_alu_forward_a_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>u_alu_forward_b_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>u_mem_wb_bridge
 o_d_mem_addr
 u_alu_forward_a_mux
 u_alu_forward_b_mux</t>
-  </si>
-  <si>
-    <t>u_ex_mem_bridge
-u_alu_forwarding_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_alu_forward_b_mux
-u_ex_mem_bridge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_regwrite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_mem_wb_bridge
-u_alu_forwarding_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WDATA Forward Output</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_mem_wb_bridge
-u_alu_forward_mem_regdst_mux
-u_wdata_forward_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alu_forwarding_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>u_registers
 u_wdata_forwarding_unit</t>
-  </si>
-  <si>
-    <t>w_ctr_wdata_forward</t>
-  </si>
-  <si>
-    <t>u_wdata_forwarding_unit</t>
-  </si>
-  <si>
-    <t>w_ex_alu_forward_mux_data_a</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_alu_forward_mux_data_b</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_alu_src_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_wdata_forward_mux_data</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_wdata_forward_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WDATA Forward MUX Data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU ForwardB Output (2 Cycle)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>u_memtoreg_mux
-u_wdata_forward_mux</t>
+u_wdata_forward_mux
+u_alu_forward_a_mux
+u_alu_forward_b_mux</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2181,7 +2214,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2533,13 +2566,61 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2551,28 +2632,10 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2583,45 +2646,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2983,32 +3007,32 @@
   <sheetData>
     <row r="1" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="131" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="132"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="132"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="133"/>
-      <c r="I2" s="117" t="s">
-        <v>104</v>
-      </c>
-      <c r="J2" s="119"/>
-      <c r="K2" s="117" t="s">
-        <v>98</v>
-      </c>
-      <c r="L2" s="118"/>
-      <c r="M2" s="119"/>
-      <c r="O2" s="117" t="s">
-        <v>104</v>
-      </c>
-      <c r="P2" s="119"/>
-      <c r="Q2" s="117" t="s">
-        <v>151</v>
-      </c>
-      <c r="R2" s="118"/>
-      <c r="S2" s="119"/>
+      <c r="B2" s="141" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="142"/>
+      <c r="G2" s="143"/>
+      <c r="I2" s="120" t="s">
+        <v>103</v>
+      </c>
+      <c r="J2" s="121"/>
+      <c r="K2" s="120" t="s">
+        <v>97</v>
+      </c>
+      <c r="L2" s="122"/>
+      <c r="M2" s="121"/>
+      <c r="O2" s="120" t="s">
+        <v>103</v>
+      </c>
+      <c r="P2" s="121"/>
+      <c r="Q2" s="120" t="s">
+        <v>150</v>
+      </c>
+      <c r="R2" s="122"/>
+      <c r="S2" s="121"/>
     </row>
     <row r="3" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="34" t="s">
@@ -3029,24 +3053,24 @@
       <c r="G3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="126" t="s">
+      <c r="I3" s="130" t="s">
+        <v>109</v>
+      </c>
+      <c r="J3" s="131"/>
+      <c r="K3" s="132" t="s">
         <v>110</v>
       </c>
-      <c r="J3" s="127"/>
-      <c r="K3" s="128" t="s">
-        <v>111</v>
-      </c>
-      <c r="L3" s="129"/>
-      <c r="M3" s="130"/>
-      <c r="O3" s="126" t="s">
-        <v>110</v>
-      </c>
-      <c r="P3" s="127"/>
-      <c r="Q3" s="128" t="s">
-        <v>239</v>
-      </c>
-      <c r="R3" s="129"/>
-      <c r="S3" s="130"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="134"/>
+      <c r="O3" s="130" t="s">
+        <v>109</v>
+      </c>
+      <c r="P3" s="131"/>
+      <c r="Q3" s="132" t="s">
+        <v>237</v>
+      </c>
+      <c r="R3" s="133"/>
+      <c r="S3" s="134"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B4" s="35">
@@ -3067,24 +3091,24 @@
       <c r="G4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="126" t="s">
-        <v>108</v>
-      </c>
-      <c r="J4" s="127"/>
-      <c r="K4" s="126" t="s">
-        <v>65</v>
-      </c>
-      <c r="L4" s="140"/>
-      <c r="M4" s="127"/>
-      <c r="O4" s="126" t="s">
-        <v>108</v>
-      </c>
-      <c r="P4" s="127"/>
-      <c r="Q4" s="126" t="s">
-        <v>65</v>
-      </c>
-      <c r="R4" s="140"/>
-      <c r="S4" s="127"/>
+      <c r="I4" s="130" t="s">
+        <v>107</v>
+      </c>
+      <c r="J4" s="131"/>
+      <c r="K4" s="130" t="s">
+        <v>64</v>
+      </c>
+      <c r="L4" s="135"/>
+      <c r="M4" s="131"/>
+      <c r="O4" s="130" t="s">
+        <v>107</v>
+      </c>
+      <c r="P4" s="131"/>
+      <c r="Q4" s="130" t="s">
+        <v>64</v>
+      </c>
+      <c r="R4" s="135"/>
+      <c r="S4" s="131"/>
     </row>
     <row r="5" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="54">
@@ -3105,24 +3129,24 @@
       <c r="G5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="120" t="s">
+      <c r="I5" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="121"/>
-      <c r="K5" s="122" t="s">
-        <v>103</v>
-      </c>
-      <c r="L5" s="123"/>
-      <c r="M5" s="124"/>
-      <c r="O5" s="120" t="s">
+      <c r="J5" s="137"/>
+      <c r="K5" s="138" t="s">
+        <v>102</v>
+      </c>
+      <c r="L5" s="119"/>
+      <c r="M5" s="139"/>
+      <c r="O5" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="121"/>
-      <c r="Q5" s="122" t="s">
-        <v>152</v>
-      </c>
-      <c r="R5" s="123"/>
-      <c r="S5" s="124"/>
+      <c r="P5" s="137"/>
+      <c r="Q5" s="138" t="s">
+        <v>151</v>
+      </c>
+      <c r="R5" s="119"/>
+      <c r="S5" s="139"/>
     </row>
     <row r="6" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="55">
@@ -3146,22 +3170,22 @@
       <c r="I6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="125" t="s">
-        <v>99</v>
-      </c>
-      <c r="K6" s="125"/>
-      <c r="L6" s="125"/>
+      <c r="J6" s="128" t="s">
+        <v>98</v>
+      </c>
+      <c r="K6" s="128"/>
+      <c r="L6" s="128"/>
       <c r="M6" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="125" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q6" s="125"/>
-      <c r="R6" s="125"/>
+      <c r="P6" s="128" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q6" s="128"/>
+      <c r="R6" s="128"/>
       <c r="S6" s="69" t="s">
         <v>8</v>
       </c>
@@ -3188,24 +3212,24 @@
       <c r="I7" s="70">
         <v>1</v>
       </c>
-      <c r="J7" s="134" t="s">
+      <c r="J7" s="140" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="134"/>
-      <c r="L7" s="134"/>
+      <c r="K7" s="140"/>
+      <c r="L7" s="140"/>
       <c r="M7" s="71" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O7" s="87">
         <v>1</v>
       </c>
-      <c r="P7" s="141" t="s">
+      <c r="P7" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="Q7" s="141"/>
-      <c r="R7" s="141"/>
+      <c r="Q7" s="129"/>
+      <c r="R7" s="129"/>
       <c r="S7" s="88" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3231,7 +3255,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="68" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K8" s="68" t="s">
         <v>1</v>
@@ -3245,13 +3269,13 @@
       <c r="O8" s="80">
         <v>2</v>
       </c>
-      <c r="P8" s="123" t="s">
+      <c r="P8" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="123"/>
-      <c r="R8" s="123"/>
+      <c r="Q8" s="119"/>
+      <c r="R8" s="119"/>
       <c r="S8" s="82" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3277,22 +3301,22 @@
         <v>1</v>
       </c>
       <c r="J9" s="73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K9" s="73" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L9" s="74" t="s">
         <v>21</v>
       </c>
       <c r="M9" s="75" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O9" s="67" t="s">
         <v>41</v>
       </c>
       <c r="P9" s="68" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q9" s="68" t="s">
         <v>1</v>
@@ -3327,22 +3351,22 @@
         <v>2</v>
       </c>
       <c r="J10" s="77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K10" s="77" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L10" s="78" t="s">
         <v>21</v>
       </c>
       <c r="M10" s="79" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O10" s="72">
         <v>1</v>
       </c>
       <c r="P10" s="73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q10" s="73" t="s">
         <v>5</v>
@@ -3351,7 +3375,7 @@
         <v>1</v>
       </c>
       <c r="S10" s="75" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3377,22 +3401,22 @@
         <v>3</v>
       </c>
       <c r="J11" s="66" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K11" s="66" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L11" s="81" t="s">
         <v>21</v>
       </c>
       <c r="M11" s="82" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O11" s="72">
         <v>2</v>
       </c>
       <c r="P11" s="73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q11" s="73" t="s">
         <v>6</v>
@@ -3401,7 +3425,7 @@
         <v>1</v>
       </c>
       <c r="S11" s="75" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3423,29 +3447,29 @@
       <c r="G12" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="135" t="s">
+      <c r="I12" s="123" t="s">
+        <v>105</v>
+      </c>
+      <c r="J12" s="124"/>
+      <c r="K12" s="125" t="s">
         <v>106</v>
       </c>
-      <c r="J12" s="136"/>
-      <c r="K12" s="137" t="s">
-        <v>107</v>
-      </c>
-      <c r="L12" s="138"/>
-      <c r="M12" s="139"/>
+      <c r="L12" s="126"/>
+      <c r="M12" s="127"/>
       <c r="O12" s="72">
         <v>3</v>
       </c>
       <c r="P12" s="73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q12" s="73" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="R12" s="74" t="s">
         <v>21</v>
       </c>
       <c r="S12" s="75" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3471,7 +3495,7 @@
         <v>4</v>
       </c>
       <c r="P13" s="73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q13" s="73" t="s">
         <v>10</v>
@@ -3506,16 +3530,16 @@
         <v>5</v>
       </c>
       <c r="P14" s="77" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q14" s="73" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="R14" s="74" t="s">
         <v>21</v>
       </c>
       <c r="S14" s="79" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3541,28 +3565,28 @@
         <v>6</v>
       </c>
       <c r="P15" s="66" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q15" s="73" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="R15" s="74" t="s">
         <v>20</v>
       </c>
       <c r="S15" s="82" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="O16" s="135" t="s">
-        <v>106</v>
-      </c>
-      <c r="P16" s="136"/>
-      <c r="Q16" s="137" t="s">
-        <v>242</v>
-      </c>
-      <c r="R16" s="138"/>
-      <c r="S16" s="139"/>
+      <c r="O16" s="123" t="s">
+        <v>105</v>
+      </c>
+      <c r="P16" s="124"/>
+      <c r="Q16" s="125" t="s">
+        <v>240</v>
+      </c>
+      <c r="R16" s="126"/>
+      <c r="S16" s="127"/>
     </row>
     <row r="17" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="90" t="s">
@@ -3584,44 +3608,44 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B18" s="33">
         <f>IF(C18="","",1)</f>
         <v>1</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="D18" s="1">
-        <v>1</v>
+        <v>196</v>
+      </c>
+      <c r="D18" s="90" t="s">
+        <v>21</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="I18" s="117" t="s">
+        <v>238</v>
+      </c>
+      <c r="F18" s="103" t="s">
+        <v>259</v>
+      </c>
+      <c r="G18" s="99" t="s">
+        <v>198</v>
+      </c>
+      <c r="I18" s="120" t="s">
+        <v>103</v>
+      </c>
+      <c r="J18" s="121"/>
+      <c r="K18" s="120" t="s">
         <v>104</v>
       </c>
-      <c r="J18" s="119"/>
-      <c r="K18" s="117" t="s">
-        <v>105</v>
-      </c>
-      <c r="L18" s="118"/>
-      <c r="M18" s="119"/>
-      <c r="O18" s="117" t="s">
-        <v>104</v>
-      </c>
-      <c r="P18" s="119"/>
-      <c r="Q18" s="117" t="s">
-        <v>161</v>
-      </c>
-      <c r="R18" s="118"/>
-      <c r="S18" s="119"/>
+      <c r="L18" s="122"/>
+      <c r="M18" s="121"/>
+      <c r="O18" s="120" t="s">
+        <v>103</v>
+      </c>
+      <c r="P18" s="121"/>
+      <c r="Q18" s="120" t="s">
+        <v>160</v>
+      </c>
+      <c r="R18" s="122"/>
+      <c r="S18" s="121"/>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B19" s="33">
@@ -3629,38 +3653,38 @@
         <v>2</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>355</v>
+        <v>298</v>
       </c>
       <c r="D19" s="1">
         <v>1</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>351</v>
+      <c r="E19" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>359</v>
+        <v>64</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="I19" s="126" t="s">
-        <v>110</v>
-      </c>
-      <c r="J19" s="127"/>
-      <c r="K19" s="128" t="s">
-        <v>112</v>
-      </c>
-      <c r="L19" s="129"/>
-      <c r="M19" s="130"/>
-      <c r="O19" s="126" t="s">
-        <v>110</v>
-      </c>
-      <c r="P19" s="127"/>
-      <c r="Q19" s="128" t="s">
-        <v>239</v>
-      </c>
-      <c r="R19" s="129"/>
-      <c r="S19" s="130"/>
+        <v>84</v>
+      </c>
+      <c r="I19" s="130" t="s">
+        <v>109</v>
+      </c>
+      <c r="J19" s="131"/>
+      <c r="K19" s="132" t="s">
+        <v>111</v>
+      </c>
+      <c r="L19" s="133"/>
+      <c r="M19" s="134"/>
+      <c r="O19" s="130" t="s">
+        <v>109</v>
+      </c>
+      <c r="P19" s="131"/>
+      <c r="Q19" s="132" t="s">
+        <v>237</v>
+      </c>
+      <c r="R19" s="133"/>
+      <c r="S19" s="134"/>
     </row>
     <row r="20" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B20" s="33">
@@ -3668,117 +3692,117 @@
         <v>3</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D20" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>240</v>
+        <v>294</v>
+      </c>
+      <c r="D20" s="1">
+        <v>4</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="F20" s="103" t="s">
-        <v>261</v>
-      </c>
-      <c r="G20" s="99" t="s">
-        <v>199</v>
-      </c>
-      <c r="I20" s="126" t="s">
+        <v>76</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I20" s="130" t="s">
+        <v>107</v>
+      </c>
+      <c r="J20" s="131"/>
+      <c r="K20" s="132" t="s">
         <v>108</v>
       </c>
-      <c r="J20" s="127"/>
-      <c r="K20" s="128" t="s">
-        <v>109</v>
-      </c>
-      <c r="L20" s="129"/>
-      <c r="M20" s="130"/>
-      <c r="O20" s="126" t="s">
-        <v>108</v>
-      </c>
-      <c r="P20" s="127"/>
-      <c r="Q20" s="126" t="s">
-        <v>65</v>
-      </c>
-      <c r="R20" s="140"/>
-      <c r="S20" s="127"/>
-    </row>
-    <row r="21" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L20" s="133"/>
+      <c r="M20" s="134"/>
+      <c r="O20" s="130" t="s">
+        <v>107</v>
+      </c>
+      <c r="P20" s="131"/>
+      <c r="Q20" s="130" t="s">
+        <v>64</v>
+      </c>
+      <c r="R20" s="135"/>
+      <c r="S20" s="131"/>
+    </row>
+    <row r="21" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="33">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="D21" s="1">
-        <v>1</v>
+        <v>351</v>
+      </c>
+      <c r="D21" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>65</v>
+        <v>375</v>
+      </c>
+      <c r="F21" s="103" t="s">
+        <v>76</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="I21" s="120" t="s">
+        <v>345</v>
+      </c>
+      <c r="I21" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="121"/>
-      <c r="K21" s="122" t="s">
-        <v>126</v>
-      </c>
-      <c r="L21" s="123"/>
-      <c r="M21" s="124"/>
-      <c r="O21" s="120" t="s">
+      <c r="J21" s="137"/>
+      <c r="K21" s="138" t="s">
+        <v>125</v>
+      </c>
+      <c r="L21" s="119"/>
+      <c r="M21" s="139"/>
+      <c r="O21" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="121"/>
-      <c r="Q21" s="122" t="s">
-        <v>162</v>
-      </c>
-      <c r="R21" s="123"/>
-      <c r="S21" s="124"/>
-    </row>
-    <row r="22" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P21" s="137"/>
+      <c r="Q21" s="138" t="s">
+        <v>161</v>
+      </c>
+      <c r="R21" s="119"/>
+      <c r="S21" s="139"/>
+    </row>
+    <row r="22" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="33">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="D22" s="1">
-        <v>4</v>
+        <v>352</v>
+      </c>
+      <c r="D22" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>76</v>
+        <v>376</v>
       </c>
       <c r="F22" s="103" t="s">
-        <v>77</v>
+        <v>353</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>78</v>
+        <v>346</v>
       </c>
       <c r="I22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J22" s="125" t="s">
-        <v>99</v>
-      </c>
-      <c r="K22" s="125"/>
-      <c r="L22" s="125"/>
+      <c r="J22" s="128" t="s">
+        <v>98</v>
+      </c>
+      <c r="K22" s="128"/>
+      <c r="L22" s="128"/>
       <c r="M22" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P22" s="125" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q22" s="125"/>
-      <c r="R22" s="125"/>
+      <c r="P22" s="128" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q22" s="128"/>
+      <c r="R22" s="128"/>
       <c r="S22" s="69" t="s">
         <v>8</v>
       </c>
@@ -3789,41 +3813,41 @@
         <v>6</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D23" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F23" s="103" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I23" s="70">
         <v>1</v>
       </c>
-      <c r="J23" s="134" t="s">
+      <c r="J23" s="140" t="s">
         <v>20</v>
       </c>
-      <c r="K23" s="134"/>
-      <c r="L23" s="134"/>
+      <c r="K23" s="140"/>
+      <c r="L23" s="140"/>
       <c r="M23" s="71" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O23" s="87">
         <v>1</v>
       </c>
-      <c r="P23" s="141" t="s">
+      <c r="P23" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="Q23" s="141"/>
-      <c r="R23" s="141"/>
+      <c r="Q23" s="129"/>
+      <c r="R23" s="129"/>
       <c r="S23" s="88" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3832,25 +3856,25 @@
         <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I24" s="67" t="s">
         <v>41</v>
       </c>
       <c r="J24" s="68" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K24" s="68" t="s">
         <v>1</v>
@@ -3864,13 +3888,13 @@
       <c r="O24" s="80">
         <v>2</v>
       </c>
-      <c r="P24" s="123" t="s">
+      <c r="P24" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="Q24" s="123"/>
-      <c r="R24" s="123"/>
+      <c r="Q24" s="119"/>
+      <c r="R24" s="119"/>
       <c r="S24" s="82" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3879,40 +3903,40 @@
         <v>8</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D25" s="1">
         <v>3</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="I25" s="72">
         <v>1</v>
       </c>
       <c r="J25" s="73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K25" s="73" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L25" s="74" t="s">
         <v>20</v>
       </c>
       <c r="M25" s="75" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O25" s="67" t="s">
         <v>41</v>
       </c>
       <c r="P25" s="68" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q25" s="68" t="s">
         <v>1</v>
@@ -3930,40 +3954,40 @@
         <v>9</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D26" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F26" s="103" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I26" s="76">
         <v>2</v>
       </c>
       <c r="J26" s="77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K26" s="77" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L26" s="78" t="s">
         <v>20</v>
       </c>
       <c r="M26" s="79" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O26" s="72">
         <v>1</v>
       </c>
       <c r="P26" s="73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q26" s="73" t="s">
         <v>5</v>
@@ -3972,7 +3996,7 @@
         <v>1</v>
       </c>
       <c r="S26" s="75" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.3">
@@ -3981,40 +4005,40 @@
         <v>10</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D27" s="1">
         <v>1</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I27" s="83">
         <v>3</v>
       </c>
       <c r="J27" s="77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K27" s="84" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L27" s="84">
         <v>1</v>
       </c>
       <c r="M27" s="85" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O27" s="72">
         <v>2</v>
       </c>
       <c r="P27" s="73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q27" s="73" t="s">
         <v>6</v>
@@ -4023,7 +4047,7 @@
         <v>1</v>
       </c>
       <c r="S27" s="75" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="2:19" x14ac:dyDescent="0.3">
@@ -4032,7 +4056,7 @@
         <v>11</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D28" s="90" t="s">
         <v>20</v>
@@ -4044,37 +4068,37 @@
         <v>53</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I28" s="83">
         <v>4</v>
       </c>
       <c r="J28" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K28" s="84" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L28" s="84">
         <v>4</v>
       </c>
       <c r="M28" s="85" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O28" s="83">
         <v>3</v>
       </c>
       <c r="P28" s="73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q28" s="73" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="R28" s="74" t="s">
         <v>21</v>
       </c>
       <c r="S28" s="75" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="2:19" x14ac:dyDescent="0.3">
@@ -4083,7 +4107,7 @@
         <v>12</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D29" s="90" t="s">
         <v>21</v>
@@ -4095,37 +4119,37 @@
         <v>36</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I29" s="83">
         <v>5</v>
       </c>
       <c r="J29" s="84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K29" s="84" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L29" s="86" t="s">
         <v>20</v>
       </c>
       <c r="M29" s="85" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O29" s="83">
         <v>4</v>
       </c>
       <c r="P29" s="77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q29" s="84" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R29" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S29" s="85" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="2:19" x14ac:dyDescent="0.3">
@@ -4134,49 +4158,49 @@
         <v>13</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D30" s="1">
         <v>1</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I30" s="83">
         <v>6</v>
       </c>
       <c r="J30" s="84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K30" s="84" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L30" s="84">
         <v>1</v>
       </c>
       <c r="M30" s="85" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O30" s="83">
         <v>5</v>
       </c>
       <c r="P30" s="77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q30" s="84" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="R30" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S30" s="85" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -4185,49 +4209,49 @@
         <v>14</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D31" s="1">
         <v>1</v>
       </c>
       <c r="E31" s="102" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>53</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I31" s="80">
         <v>7</v>
       </c>
       <c r="J31" s="66" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K31" s="66" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L31" s="66">
         <v>1</v>
       </c>
       <c r="M31" s="82" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O31" s="83">
         <v>6</v>
       </c>
       <c r="P31" s="77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q31" s="84" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R31" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S31" s="85" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4236,79 +4260,79 @@
         <v>15</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>36</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="I32" s="135" t="s">
-        <v>106</v>
-      </c>
-      <c r="J32" s="136"/>
-      <c r="K32" s="137" t="s">
-        <v>80</v>
-      </c>
-      <c r="L32" s="138"/>
-      <c r="M32" s="139"/>
+        <v>269</v>
+      </c>
+      <c r="I32" s="123" t="s">
+        <v>105</v>
+      </c>
+      <c r="J32" s="124"/>
+      <c r="K32" s="125" t="s">
+        <v>79</v>
+      </c>
+      <c r="L32" s="126"/>
+      <c r="M32" s="127"/>
       <c r="O32" s="83">
         <v>7</v>
       </c>
       <c r="P32" s="77" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q32" s="77" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="R32" s="78" t="s">
         <v>21</v>
       </c>
       <c r="S32" s="79" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B33" s="33">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D33" s="1">
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F33" s="103" t="s">
-        <v>244</v>
+        <v>360</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="O33" s="83">
         <v>8</v>
       </c>
       <c r="P33" s="84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q33" s="84" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R33" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S33" s="85" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="2:19" x14ac:dyDescent="0.3">
@@ -4317,70 +4341,70 @@
         <v>17</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D34" s="1">
         <v>6</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O34" s="83">
         <v>9</v>
       </c>
       <c r="P34" s="84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q34" s="84" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R34" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S34" s="85" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="35" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="33">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D35" s="90" t="s">
         <v>56</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F35" s="103" t="s">
-        <v>244</v>
+        <v>360</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="O35" s="80">
         <v>10</v>
       </c>
       <c r="P35" s="66" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q35" s="66" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R35" s="81" t="s">
         <v>20</v>
       </c>
       <c r="S35" s="82" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4389,89 +4413,89 @@
         <v>19</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D36" s="90" t="s">
         <v>56</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>351</v>
+        <v>241</v>
+      </c>
+      <c r="F36" s="103" t="s">
+        <v>378</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="O36" s="135" t="s">
-        <v>106</v>
-      </c>
-      <c r="P36" s="136"/>
-      <c r="Q36" s="137" t="s">
-        <v>243</v>
-      </c>
-      <c r="R36" s="138"/>
-      <c r="S36" s="139"/>
-    </row>
-    <row r="37" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+        <v>337</v>
+      </c>
+      <c r="O36" s="123" t="s">
+        <v>105</v>
+      </c>
+      <c r="P36" s="124"/>
+      <c r="Q36" s="125" t="s">
+        <v>241</v>
+      </c>
+      <c r="R36" s="126"/>
+      <c r="S36" s="127"/>
+    </row>
+    <row r="37" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="33">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D37" s="90" t="s">
         <v>56</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F37" s="103" t="s">
         <v>361</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="38" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="38" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B38" s="33">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>370</v>
+        <v>300</v>
       </c>
       <c r="D38" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="F38" s="103" t="s">
-        <v>77</v>
+        <v>86</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="I38" s="117" t="s">
-        <v>104</v>
-      </c>
-      <c r="J38" s="119"/>
-      <c r="K38" s="117" t="s">
-        <v>124</v>
-      </c>
-      <c r="L38" s="118"/>
-      <c r="M38" s="119"/>
-      <c r="O38" s="117" t="s">
-        <v>104</v>
-      </c>
-      <c r="P38" s="119"/>
-      <c r="Q38" s="117" t="s">
-        <v>175</v>
-      </c>
-      <c r="R38" s="118"/>
-      <c r="S38" s="119"/>
+        <v>87</v>
+      </c>
+      <c r="I38" s="120" t="s">
+        <v>103</v>
+      </c>
+      <c r="J38" s="121"/>
+      <c r="K38" s="120" t="s">
+        <v>123</v>
+      </c>
+      <c r="L38" s="122"/>
+      <c r="M38" s="121"/>
+      <c r="O38" s="120" t="s">
+        <v>103</v>
+      </c>
+      <c r="P38" s="121"/>
+      <c r="Q38" s="120" t="s">
+        <v>174</v>
+      </c>
+      <c r="R38" s="122"/>
+      <c r="S38" s="121"/>
     </row>
     <row r="39" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B39" s="33">
@@ -4479,77 +4503,77 @@
         <v>22</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="D39" s="90" t="s">
+        <v>234</v>
+      </c>
+      <c r="D39" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="F39" s="103" t="s">
-        <v>372</v>
+      <c r="E39" s="102" t="s">
+        <v>238</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="I39" s="126" t="s">
-        <v>110</v>
-      </c>
-      <c r="J39" s="127"/>
-      <c r="K39" s="128" t="s">
-        <v>125</v>
-      </c>
-      <c r="L39" s="129"/>
-      <c r="M39" s="130"/>
-      <c r="O39" s="126" t="s">
-        <v>110</v>
-      </c>
-      <c r="P39" s="127"/>
-      <c r="Q39" s="128" t="s">
-        <v>239</v>
-      </c>
-      <c r="R39" s="129"/>
-      <c r="S39" s="130"/>
+        <v>235</v>
+      </c>
+      <c r="I39" s="130" t="s">
+        <v>109</v>
+      </c>
+      <c r="J39" s="131"/>
+      <c r="K39" s="132" t="s">
+        <v>124</v>
+      </c>
+      <c r="L39" s="133"/>
+      <c r="M39" s="134"/>
+      <c r="O39" s="130" t="s">
+        <v>109</v>
+      </c>
+      <c r="P39" s="131"/>
+      <c r="Q39" s="132" t="s">
+        <v>237</v>
+      </c>
+      <c r="R39" s="133"/>
+      <c r="S39" s="134"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B40" s="33">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>302</v>
+      <c r="C40" s="97" t="s">
+        <v>278</v>
       </c>
       <c r="D40" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="I40" s="126" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="98" t="s">
+        <v>35</v>
+      </c>
+      <c r="G40" s="99" t="s">
+        <v>279</v>
+      </c>
+      <c r="I40" s="130" t="s">
+        <v>107</v>
+      </c>
+      <c r="J40" s="131"/>
+      <c r="K40" s="132" t="s">
         <v>108</v>
       </c>
-      <c r="J40" s="127"/>
-      <c r="K40" s="128" t="s">
-        <v>109</v>
-      </c>
-      <c r="L40" s="129"/>
-      <c r="M40" s="130"/>
-      <c r="O40" s="126" t="s">
-        <v>108</v>
-      </c>
-      <c r="P40" s="127"/>
-      <c r="Q40" s="126" t="s">
-        <v>65</v>
-      </c>
-      <c r="R40" s="140"/>
-      <c r="S40" s="127"/>
+      <c r="L40" s="133"/>
+      <c r="M40" s="134"/>
+      <c r="O40" s="130" t="s">
+        <v>107</v>
+      </c>
+      <c r="P40" s="131"/>
+      <c r="Q40" s="130" t="s">
+        <v>64</v>
+      </c>
+      <c r="R40" s="135"/>
+      <c r="S40" s="131"/>
     </row>
     <row r="41" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="33">
@@ -4557,78 +4581,78 @@
         <v>24</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="D41" s="101" t="s">
+        <v>301</v>
+      </c>
+      <c r="D41" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="E41" s="102" t="s">
-        <v>240</v>
+      <c r="E41" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="I41" s="120" t="s">
+        <v>88</v>
+      </c>
+      <c r="I41" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="121"/>
-      <c r="K41" s="122" t="s">
-        <v>127</v>
-      </c>
-      <c r="L41" s="123"/>
-      <c r="M41" s="124"/>
-      <c r="O41" s="120" t="s">
+      <c r="J41" s="137"/>
+      <c r="K41" s="138" t="s">
+        <v>126</v>
+      </c>
+      <c r="L41" s="119"/>
+      <c r="M41" s="139"/>
+      <c r="O41" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="P41" s="121"/>
-      <c r="Q41" s="122" t="s">
-        <v>176</v>
-      </c>
-      <c r="R41" s="123"/>
-      <c r="S41" s="124"/>
+      <c r="P41" s="137"/>
+      <c r="Q41" s="138" t="s">
+        <v>175</v>
+      </c>
+      <c r="R41" s="119"/>
+      <c r="S41" s="139"/>
     </row>
     <row r="42" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="33">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C42" s="97" t="s">
-        <v>280</v>
-      </c>
-      <c r="D42" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E42" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F42" s="98" t="s">
-        <v>35</v>
-      </c>
-      <c r="G42" s="99" t="s">
-        <v>281</v>
+      <c r="C42" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1</v>
+      </c>
+      <c r="E42" s="114" t="s">
+        <v>241</v>
+      </c>
+      <c r="F42" s="114" t="s">
+        <v>242</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>252</v>
       </c>
       <c r="I42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J42" s="125" t="s">
-        <v>99</v>
-      </c>
-      <c r="K42" s="125"/>
-      <c r="L42" s="125"/>
+      <c r="J42" s="128" t="s">
+        <v>98</v>
+      </c>
+      <c r="K42" s="128"/>
+      <c r="L42" s="128"/>
       <c r="M42" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P42" s="125" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q42" s="125"/>
-      <c r="R42" s="125"/>
+      <c r="P42" s="128" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q42" s="128"/>
+      <c r="R42" s="128"/>
       <c r="S42" s="69" t="s">
         <v>8</v>
       </c>
@@ -4639,41 +4663,41 @@
         <v>26</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="D43" s="90" t="s">
+        <v>270</v>
+      </c>
+      <c r="D43" s="1">
+        <v>1</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F43" s="103" t="s">
+        <v>242</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="I43" s="70">
+        <v>1</v>
+      </c>
+      <c r="J43" s="140" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I43" s="70">
-        <v>1</v>
-      </c>
-      <c r="J43" s="134" t="s">
-        <v>20</v>
-      </c>
-      <c r="K43" s="134"/>
-      <c r="L43" s="134"/>
+      <c r="K43" s="140"/>
+      <c r="L43" s="140"/>
       <c r="M43" s="71" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O43" s="87">
         <v>1</v>
       </c>
-      <c r="P43" s="141" t="s">
+      <c r="P43" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="Q43" s="141"/>
-      <c r="R43" s="141"/>
+      <c r="Q43" s="129"/>
+      <c r="R43" s="129"/>
       <c r="S43" s="88" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="44" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4682,25 +4706,25 @@
         <v>27</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
       </c>
       <c r="E44" s="114" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F44" s="114" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I44" s="67" t="s">
         <v>41</v>
       </c>
       <c r="J44" s="68" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K44" s="68" t="s">
         <v>1</v>
@@ -4714,13 +4738,13 @@
       <c r="O44" s="80">
         <v>2</v>
       </c>
-      <c r="P44" s="123" t="s">
+      <c r="P44" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="Q44" s="123"/>
-      <c r="R44" s="123"/>
+      <c r="Q44" s="119"/>
+      <c r="R44" s="119"/>
       <c r="S44" s="82" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4729,40 +4753,40 @@
         <v>28</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="D45" s="1">
-        <v>1</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>243</v>
+        <v>222</v>
+      </c>
+      <c r="D45" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="F45" s="103" t="s">
-        <v>244</v>
+        <v>375</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>275</v>
+        <v>224</v>
       </c>
       <c r="I45" s="72">
         <v>1</v>
       </c>
       <c r="J45" s="73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K45" s="73" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L45" s="73">
         <v>6</v>
       </c>
       <c r="M45" s="75" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O45" s="67" t="s">
         <v>41</v>
       </c>
       <c r="P45" s="68" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q45" s="68" t="s">
         <v>1</v>
@@ -4774,46 +4798,46 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B46" s="33">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="D46" s="1">
-        <v>1</v>
-      </c>
-      <c r="E46" s="114" t="s">
-        <v>243</v>
-      </c>
-      <c r="F46" s="114" t="s">
-        <v>244</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>255</v>
+      <c r="C46" s="112" t="s">
+        <v>223</v>
+      </c>
+      <c r="D46" s="113" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" s="111" t="s">
+        <v>238</v>
+      </c>
+      <c r="F46" s="115" t="s">
+        <v>347</v>
+      </c>
+      <c r="G46" s="112" t="s">
+        <v>225</v>
       </c>
       <c r="I46" s="76">
         <v>2</v>
       </c>
       <c r="J46" s="77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K46" s="77" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L46" s="77">
         <v>3</v>
       </c>
       <c r="M46" s="79" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O46" s="72">
         <v>1</v>
       </c>
       <c r="P46" s="73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q46" s="73" t="s">
         <v>5</v>
@@ -4822,7 +4846,7 @@
         <v>1</v>
       </c>
       <c r="S46" s="75" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="47" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4831,40 +4855,40 @@
         <v>30</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>224</v>
+        <v>357</v>
       </c>
       <c r="D47" s="90" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="F47" s="103" t="s">
+        <v>63</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="G47" s="5" t="s">
         <v>358</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>226</v>
       </c>
       <c r="I47" s="80">
         <v>3</v>
       </c>
       <c r="J47" s="66" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K47" s="66" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L47" s="66">
         <v>4</v>
       </c>
       <c r="M47" s="82" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O47" s="72">
         <v>2</v>
       </c>
       <c r="P47" s="73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q47" s="73" t="s">
         <v>6</v>
@@ -4873,52 +4897,52 @@
         <v>1</v>
       </c>
       <c r="S47" s="75" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="48" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B48" s="33">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C48" s="112" t="s">
-        <v>225</v>
-      </c>
-      <c r="D48" s="113" t="s">
-        <v>20</v>
-      </c>
-      <c r="E48" s="111" t="s">
-        <v>240</v>
-      </c>
-      <c r="F48" s="115" t="s">
-        <v>362</v>
-      </c>
-      <c r="G48" s="112" t="s">
-        <v>227</v>
-      </c>
-      <c r="I48" s="135" t="s">
-        <v>106</v>
-      </c>
-      <c r="J48" s="136"/>
-      <c r="K48" s="137" t="s">
-        <v>66</v>
-      </c>
-      <c r="L48" s="138"/>
-      <c r="M48" s="139"/>
+      <c r="C48" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="D48" s="1">
+        <v>1</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F48" s="103" t="s">
+        <v>242</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I48" s="123" t="s">
+        <v>105</v>
+      </c>
+      <c r="J48" s="124"/>
+      <c r="K48" s="125" t="s">
+        <v>65</v>
+      </c>
+      <c r="L48" s="126"/>
+      <c r="M48" s="127"/>
       <c r="O48" s="83">
         <v>3</v>
       </c>
       <c r="P48" s="73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q48" s="73" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R48" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S48" s="75" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="49" spans="2:19" x14ac:dyDescent="0.3">
@@ -4927,34 +4951,34 @@
         <v>32</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="D49" s="1">
-        <v>1</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F49" s="103" t="s">
-        <v>244</v>
+        <v>285</v>
+      </c>
+      <c r="D49" s="90" t="s">
+        <v>49</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>286</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>309</v>
+        <v>54</v>
       </c>
       <c r="O49" s="83">
         <v>4</v>
       </c>
       <c r="P49" s="77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q49" s="84" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="R49" s="84">
         <v>1</v>
       </c>
       <c r="S49" s="85" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="50" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4963,124 +4987,124 @@
         <v>33</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D50" s="90" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O50" s="83">
         <v>5</v>
       </c>
       <c r="P50" s="77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q50" s="84" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="R50" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S50" s="85" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="51" spans="2:19" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="51" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B51" s="33">
         <f t="shared" ref="B51:B82" si="1">IF(C51="","",B50+1)</f>
         <v>34</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>288</v>
+        <v>226</v>
       </c>
       <c r="D51" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>40</v>
+        <v>238</v>
+      </c>
+      <c r="F51" s="103" t="s">
+        <v>48</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I51" s="117" t="s">
-        <v>104</v>
-      </c>
-      <c r="J51" s="119"/>
-      <c r="K51" s="117" t="s">
-        <v>131</v>
-      </c>
-      <c r="L51" s="118"/>
-      <c r="M51" s="119"/>
+        <v>228</v>
+      </c>
+      <c r="I51" s="120" t="s">
+        <v>103</v>
+      </c>
+      <c r="J51" s="121"/>
+      <c r="K51" s="120" t="s">
+        <v>130</v>
+      </c>
+      <c r="L51" s="122"/>
+      <c r="M51" s="121"/>
       <c r="O51" s="83">
         <v>6</v>
       </c>
       <c r="P51" s="77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q51" s="84" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="R51" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S51" s="85" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="52" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="52" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B52" s="33">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D52" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="F52" s="103" t="s">
-        <v>48</v>
+        <v>366</v>
+      </c>
+      <c r="D52" s="1">
+        <v>1</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>375</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="I52" s="126" t="s">
-        <v>110</v>
-      </c>
-      <c r="J52" s="127"/>
-      <c r="K52" s="128" t="s">
-        <v>132</v>
-      </c>
-      <c r="L52" s="129"/>
-      <c r="M52" s="130"/>
+        <v>370</v>
+      </c>
+      <c r="I52" s="130" t="s">
+        <v>109</v>
+      </c>
+      <c r="J52" s="131"/>
+      <c r="K52" s="132" t="s">
+        <v>131</v>
+      </c>
+      <c r="L52" s="133"/>
+      <c r="M52" s="134"/>
       <c r="O52" s="83">
         <v>7</v>
       </c>
       <c r="P52" s="77" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q52" s="77" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="R52" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S52" s="79" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="53" spans="2:19" x14ac:dyDescent="0.3">
@@ -5089,82 +5113,82 @@
         <v>36</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="D53" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>241</v>
+        <v>367</v>
+      </c>
+      <c r="D53" s="1">
+        <v>1</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>378</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>65</v>
+        <v>376</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="I53" s="126" t="s">
+        <v>369</v>
+      </c>
+      <c r="I53" s="130" t="s">
+        <v>107</v>
+      </c>
+      <c r="J53" s="131"/>
+      <c r="K53" s="132" t="s">
         <v>108</v>
       </c>
-      <c r="J53" s="127"/>
-      <c r="K53" s="128" t="s">
-        <v>109</v>
-      </c>
-      <c r="L53" s="129"/>
-      <c r="M53" s="130"/>
+      <c r="L53" s="133"/>
+      <c r="M53" s="134"/>
       <c r="O53" s="83">
         <v>8</v>
       </c>
       <c r="P53" s="84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q53" s="84" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R53" s="84">
         <v>1</v>
       </c>
       <c r="S53" s="85" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="54" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="54" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="33">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D54" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="F54" s="103" t="s">
-        <v>260</v>
-      </c>
-      <c r="G54" s="99" t="s">
-        <v>196</v>
-      </c>
-      <c r="I54" s="120" t="s">
+        <v>372</v>
+      </c>
+      <c r="D54" s="1">
+        <v>1</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="I54" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="121"/>
-      <c r="K54" s="122" t="s">
-        <v>133</v>
-      </c>
-      <c r="L54" s="123"/>
-      <c r="M54" s="124"/>
+      <c r="J54" s="137"/>
+      <c r="K54" s="138" t="s">
+        <v>132</v>
+      </c>
+      <c r="L54" s="119"/>
+      <c r="M54" s="139"/>
       <c r="O54" s="83">
         <v>9</v>
       </c>
       <c r="P54" s="84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q54" s="84" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="R54" s="86" t="s">
         <v>20</v>
@@ -5179,28 +5203,28 @@
         <v>38</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>200</v>
+        <v>373</v>
       </c>
       <c r="D55" s="1">
-        <v>3</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>58</v>
+        <v>1</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>378</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>243</v>
+        <v>376</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>214</v>
+        <v>380</v>
       </c>
       <c r="I55" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J55" s="125" t="s">
-        <v>99</v>
-      </c>
-      <c r="K55" s="125"/>
-      <c r="L55" s="125"/>
+      <c r="J55" s="128" t="s">
+        <v>98</v>
+      </c>
+      <c r="K55" s="128"/>
+      <c r="L55" s="128"/>
       <c r="M55" s="69" t="s">
         <v>8</v>
       </c>
@@ -5208,10 +5232,10 @@
         <v>10</v>
       </c>
       <c r="P55" s="66" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q55" s="66" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R55" s="81" t="s">
         <v>20</v>
@@ -5226,40 +5250,40 @@
         <v>39</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D56" s="1">
+        <v>371</v>
+      </c>
+      <c r="D56" s="33">
         <v>1</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>58</v>
+        <v>350</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>243</v>
+        <v>355</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>221</v>
+        <v>368</v>
       </c>
       <c r="I56" s="87">
         <v>1</v>
       </c>
-      <c r="J56" s="141" t="s">
+      <c r="J56" s="129" t="s">
         <v>20</v>
       </c>
-      <c r="K56" s="141"/>
-      <c r="L56" s="141"/>
+      <c r="K56" s="129"/>
+      <c r="L56" s="129"/>
       <c r="M56" s="88" t="s">
-        <v>135</v>
-      </c>
-      <c r="O56" s="135" t="s">
-        <v>106</v>
-      </c>
-      <c r="P56" s="136"/>
-      <c r="Q56" s="137" t="s">
-        <v>244</v>
-      </c>
-      <c r="R56" s="138"/>
-      <c r="S56" s="139"/>
+        <v>134</v>
+      </c>
+      <c r="O56" s="123" t="s">
+        <v>105</v>
+      </c>
+      <c r="P56" s="124"/>
+      <c r="Q56" s="125" t="s">
+        <v>242</v>
+      </c>
+      <c r="R56" s="126"/>
+      <c r="S56" s="127"/>
     </row>
     <row r="57" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="33">
@@ -5267,57 +5291,57 @@
         <v>40</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D57" s="1">
-        <v>1</v>
+        <v>193</v>
+      </c>
+      <c r="D57" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>58</v>
+        <v>239</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>240</v>
+        <v>44</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="I57" s="80">
         <v>2</v>
       </c>
-      <c r="J57" s="123" t="s">
+      <c r="J57" s="119" t="s">
         <v>55</v>
       </c>
-      <c r="K57" s="123"/>
-      <c r="L57" s="123"/>
+      <c r="K57" s="119"/>
+      <c r="L57" s="119"/>
       <c r="M57" s="89" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="58" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="58" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B58" s="33">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D58" s="1">
-        <v>1</v>
+        <v>197</v>
+      </c>
+      <c r="D58" s="90" t="s">
+        <v>21</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>222</v>
+        <v>239</v>
+      </c>
+      <c r="F58" s="103" t="s">
+        <v>258</v>
+      </c>
+      <c r="G58" s="99" t="s">
+        <v>195</v>
       </c>
       <c r="I58" s="67" t="s">
         <v>41</v>
       </c>
       <c r="J58" s="68" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K58" s="68" t="s">
         <v>1</v>
@@ -5328,15 +5352,15 @@
       <c r="M58" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="117" t="s">
-        <v>104</v>
-      </c>
-      <c r="P58" s="119"/>
-      <c r="Q58" s="117" t="s">
-        <v>186</v>
-      </c>
-      <c r="R58" s="118"/>
-      <c r="S58" s="119"/>
+      <c r="O58" s="120" t="s">
+        <v>103</v>
+      </c>
+      <c r="P58" s="121"/>
+      <c r="Q58" s="120" t="s">
+        <v>185</v>
+      </c>
+      <c r="R58" s="122"/>
+      <c r="S58" s="121"/>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B59" s="33">
@@ -5344,28 +5368,28 @@
         <v>42</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D59" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F59" s="1" t="s">
-        <v>243</v>
+      <c r="F59" s="2" t="s">
+        <v>241</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I59" s="72">
         <v>1</v>
       </c>
       <c r="J59" s="73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K59" s="73" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L59" s="74" t="s">
         <v>55</v>
@@ -5373,15 +5397,15 @@
       <c r="M59" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="O59" s="126" t="s">
-        <v>110</v>
-      </c>
-      <c r="P59" s="127"/>
-      <c r="Q59" s="128" t="s">
-        <v>239</v>
-      </c>
-      <c r="R59" s="129"/>
-      <c r="S59" s="130"/>
+      <c r="O59" s="130" t="s">
+        <v>109</v>
+      </c>
+      <c r="P59" s="131"/>
+      <c r="Q59" s="132" t="s">
+        <v>237</v>
+      </c>
+      <c r="R59" s="133"/>
+      <c r="S59" s="134"/>
     </row>
     <row r="60" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B60" s="33">
@@ -5389,44 +5413,44 @@
         <v>43</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="D60" s="90" t="s">
-        <v>57</v>
+        <v>205</v>
+      </c>
+      <c r="D60" s="1">
+        <v>1</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>43</v>
+        <v>241</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>61</v>
+        <v>219</v>
       </c>
       <c r="I60" s="76">
         <v>2</v>
       </c>
       <c r="J60" s="84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K60" s="77" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L60" s="77">
         <v>1</v>
       </c>
       <c r="M60" s="79" t="s">
-        <v>67</v>
-      </c>
-      <c r="O60" s="126" t="s">
-        <v>108</v>
-      </c>
-      <c r="P60" s="127"/>
-      <c r="Q60" s="126" t="s">
-        <v>65</v>
-      </c>
-      <c r="R60" s="140"/>
-      <c r="S60" s="127"/>
+        <v>66</v>
+      </c>
+      <c r="O60" s="130" t="s">
+        <v>107</v>
+      </c>
+      <c r="P60" s="131"/>
+      <c r="Q60" s="130" t="s">
+        <v>64</v>
+      </c>
+      <c r="R60" s="135"/>
+      <c r="S60" s="131"/>
     </row>
     <row r="61" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="33">
@@ -5434,88 +5458,88 @@
         <v>44</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>246</v>
+        <v>200</v>
       </c>
       <c r="D61" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>247</v>
+        <v>214</v>
       </c>
       <c r="I61" s="83">
         <v>3</v>
       </c>
       <c r="J61" s="84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K61" s="84" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L61" s="84">
         <v>1</v>
       </c>
       <c r="M61" s="85" t="s">
-        <v>147</v>
-      </c>
-      <c r="O61" s="120" t="s">
+        <v>146</v>
+      </c>
+      <c r="O61" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="P61" s="121"/>
-      <c r="Q61" s="122" t="s">
-        <v>187</v>
-      </c>
-      <c r="R61" s="123"/>
-      <c r="S61" s="124"/>
-    </row>
-    <row r="62" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P61" s="137"/>
+      <c r="Q61" s="138" t="s">
+        <v>186</v>
+      </c>
+      <c r="R61" s="119"/>
+      <c r="S61" s="139"/>
+    </row>
+    <row r="62" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B62" s="33">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="C62" s="97" t="s">
-        <v>282</v>
-      </c>
-      <c r="D62" s="101" t="s">
-        <v>45</v>
-      </c>
-      <c r="E62" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="F62" s="98" t="s">
-        <v>42</v>
-      </c>
-      <c r="G62" s="99" t="s">
-        <v>50</v>
+      <c r="C62" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D62" s="1">
+        <v>1</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="I62" s="83">
         <v>4</v>
       </c>
       <c r="J62" s="84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K62" s="84" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L62" s="84">
         <v>1</v>
       </c>
       <c r="M62" s="85" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O62" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P62" s="125" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q62" s="125"/>
-      <c r="R62" s="125"/>
+      <c r="P62" s="128" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q62" s="128"/>
+      <c r="R62" s="128"/>
       <c r="S62" s="69" t="s">
         <v>8</v>
       </c>
@@ -5526,45 +5550,45 @@
         <v>46</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D63" s="90" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I63" s="83">
         <v>5</v>
       </c>
       <c r="J63" s="84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K63" s="84" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L63" s="84">
         <v>1</v>
       </c>
       <c r="M63" s="85" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O63" s="87">
         <v>1</v>
       </c>
-      <c r="P63" s="141" t="s">
+      <c r="P63" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="Q63" s="141"/>
-      <c r="R63" s="141"/>
+      <c r="Q63" s="129"/>
+      <c r="R63" s="129"/>
       <c r="S63" s="88" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5573,45 +5597,45 @@
         <v>47</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="D64" s="90" t="s">
-        <v>56</v>
+        <v>244</v>
+      </c>
+      <c r="D64" s="1">
+        <v>6</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>312</v>
+        <v>245</v>
       </c>
       <c r="I64" s="83">
         <v>6</v>
       </c>
       <c r="J64" s="84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K64" s="84" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L64" s="84">
         <v>1</v>
       </c>
       <c r="M64" s="85" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O64" s="80">
         <v>2</v>
       </c>
-      <c r="P64" s="123" t="s">
+      <c r="P64" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="Q64" s="123"/>
-      <c r="R64" s="123"/>
+      <c r="Q64" s="119"/>
+      <c r="R64" s="119"/>
       <c r="S64" s="82" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -5619,41 +5643,41 @@
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D65" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E65" s="1" t="s">
+      <c r="C65" s="97" t="s">
+        <v>280</v>
+      </c>
+      <c r="D65" s="101" t="s">
+        <v>45</v>
+      </c>
+      <c r="E65" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="F65" s="103" t="s">
-        <v>343</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>342</v>
+      <c r="F65" s="98" t="s">
+        <v>42</v>
+      </c>
+      <c r="G65" s="99" t="s">
+        <v>50</v>
       </c>
       <c r="I65" s="83">
         <v>7</v>
       </c>
       <c r="J65" s="84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K65" s="84" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L65" s="84">
         <v>1</v>
       </c>
       <c r="M65" s="85" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O65" s="67" t="s">
         <v>41</v>
       </c>
       <c r="P65" s="68" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q65" s="68" t="s">
         <v>1</v>
@@ -5671,40 +5695,40 @@
         <v>49</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D66" s="90" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>313</v>
+        <v>59</v>
       </c>
       <c r="I66" s="83">
         <v>8</v>
       </c>
       <c r="J66" s="84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K66" s="84" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L66" s="84">
         <v>1</v>
       </c>
       <c r="M66" s="85" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O66" s="72">
         <v>1</v>
       </c>
       <c r="P66" s="73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q66" s="73" t="s">
         <v>5</v>
@@ -5713,7 +5737,7 @@
         <v>1</v>
       </c>
       <c r="S66" s="75" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.3">
@@ -5722,40 +5746,40 @@
         <v>50</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D67" s="1">
-        <v>5</v>
+        <v>291</v>
+      </c>
+      <c r="D67" s="90" t="s">
+        <v>56</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>65</v>
+        <v>241</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>60</v>
+        <v>310</v>
       </c>
       <c r="I67" s="83">
         <v>9</v>
       </c>
       <c r="J67" s="84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K67" s="84" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L67" s="84">
         <v>3</v>
       </c>
       <c r="M67" s="85" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O67" s="72">
         <v>2</v>
       </c>
       <c r="P67" s="73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q67" s="73" t="s">
         <v>6</v>
@@ -5764,7 +5788,7 @@
         <v>1</v>
       </c>
       <c r="S67" s="75" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="68" spans="2:19" ht="33" x14ac:dyDescent="0.3">
@@ -5773,43 +5797,43 @@
         <v>51</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="D68" s="101" t="s">
-        <v>20</v>
-      </c>
-      <c r="E68" s="102" t="s">
-        <v>286</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>243</v>
+        <v>289</v>
+      </c>
+      <c r="D68" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F68" s="103" t="s">
+        <v>339</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>235</v>
+        <v>338</v>
       </c>
       <c r="I68" s="83">
         <v>10</v>
       </c>
       <c r="J68" s="84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K68" s="84" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L68" s="84">
         <v>1</v>
       </c>
       <c r="M68" s="85" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O68" s="83">
         <v>3</v>
       </c>
       <c r="P68" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q68" s="84" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R68" s="86" t="s">
         <v>20</v>
@@ -5824,49 +5848,49 @@
         <v>52</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D69" s="1">
-        <v>1</v>
+        <v>290</v>
+      </c>
+      <c r="D69" s="90" t="s">
+        <v>56</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F69" s="114" t="s">
-        <v>243</v>
+        <v>44</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>219</v>
+        <v>311</v>
       </c>
       <c r="I69" s="83">
         <v>11</v>
       </c>
       <c r="J69" s="84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K69" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L69" s="84">
         <v>1</v>
       </c>
       <c r="M69" s="85" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O69" s="83">
         <v>4</v>
       </c>
       <c r="P69" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q69" s="84" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="R69" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S69" s="85" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.3">
@@ -5875,25 +5899,25 @@
         <v>53</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>203</v>
+        <v>292</v>
       </c>
       <c r="D70" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>240</v>
+        <v>64</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>217</v>
+        <v>60</v>
       </c>
       <c r="I70" s="83">
         <v>12</v>
       </c>
       <c r="J70" s="84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K70" s="84" t="s">
         <v>18</v>
@@ -5902,49 +5926,49 @@
         <v>1</v>
       </c>
       <c r="M70" s="85" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O70" s="83">
         <v>5</v>
       </c>
       <c r="P70" s="84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q70" s="84" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R70" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S70" s="85" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="71" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B71" s="33">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D71" s="1">
-        <v>1</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F71" s="114" t="s">
-        <v>243</v>
+        <v>232</v>
+      </c>
+      <c r="D71" s="101" t="s">
+        <v>20</v>
+      </c>
+      <c r="E71" s="102" t="s">
+        <v>284</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>241</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="I71" s="80">
         <v>13</v>
       </c>
       <c r="J71" s="66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K71" s="66" t="s">
         <v>19</v>
@@ -5953,22 +5977,22 @@
         <v>1</v>
       </c>
       <c r="M71" s="82" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O71" s="83">
         <v>6</v>
       </c>
       <c r="P71" s="84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q71" s="84" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="R71" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S71" s="85" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="72" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5977,58 +6001,58 @@
         <v>55</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D72" s="90" t="s">
-        <v>20</v>
+        <v>203</v>
+      </c>
+      <c r="D72" s="1">
+        <v>1</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F72" s="111" t="s">
-        <v>240</v>
+        <v>58</v>
+      </c>
+      <c r="F72" s="114" t="s">
+        <v>241</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="I72" s="135" t="s">
-        <v>106</v>
-      </c>
-      <c r="J72" s="136"/>
-      <c r="K72" s="137" t="s">
+        <v>217</v>
+      </c>
+      <c r="I72" s="123" t="s">
+        <v>105</v>
+      </c>
+      <c r="J72" s="124"/>
+      <c r="K72" s="125" t="s">
         <v>58</v>
       </c>
-      <c r="L72" s="138"/>
-      <c r="M72" s="139"/>
-      <c r="O72" s="135" t="s">
-        <v>106</v>
-      </c>
-      <c r="P72" s="136"/>
-      <c r="Q72" s="137" t="s">
-        <v>245</v>
-      </c>
-      <c r="R72" s="138"/>
-      <c r="S72" s="139"/>
+      <c r="L72" s="126"/>
+      <c r="M72" s="127"/>
+      <c r="O72" s="123" t="s">
+        <v>105</v>
+      </c>
+      <c r="P72" s="124"/>
+      <c r="Q72" s="125" t="s">
+        <v>243</v>
+      </c>
+      <c r="R72" s="126"/>
+      <c r="S72" s="127"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B73" s="33">
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
-      <c r="C73" s="112" t="s">
-        <v>211</v>
-      </c>
-      <c r="D73" s="113" t="s">
-        <v>20</v>
+      <c r="C73" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D73" s="1">
+        <v>1</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F73" s="111" t="s">
-        <v>240</v>
-      </c>
-      <c r="G73" s="112" t="s">
-        <v>213</v>
+        <v>58</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.3">
@@ -6045,32 +6069,32 @@
       <c r="E74" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F74" s="2" t="s">
-        <v>243</v>
+      <c r="F74" s="114" t="s">
+        <v>241</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="75" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B75" s="33">
         <f t="shared" si="1"/>
         <v>58</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="D75" s="101" t="s">
-        <v>46</v>
+        <v>208</v>
+      </c>
+      <c r="D75" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>234</v>
+        <v>62</v>
+      </c>
+      <c r="F75" s="111" t="s">
+        <v>238</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>51</v>
+        <v>210</v>
       </c>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.3">
@@ -6078,20 +6102,20 @@
         <f t="shared" si="1"/>
         <v>59</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="112" t="s">
         <v>209</v>
       </c>
-      <c r="D76" s="1">
-        <v>1</v>
+      <c r="D76" s="113" t="s">
+        <v>20</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G76" s="5" t="s">
-        <v>223</v>
+        <v>62</v>
+      </c>
+      <c r="F76" s="111" t="s">
+        <v>238</v>
+      </c>
+      <c r="G76" s="112" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.3">
@@ -6100,19 +6124,19 @@
         <v>60</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="D77" s="90" t="s">
-        <v>20</v>
+        <v>363</v>
+      </c>
+      <c r="D77" s="1">
+        <v>1</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F77" s="103" t="s">
-        <v>240</v>
+        <v>58</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.3">
@@ -6120,41 +6144,41 @@
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
-      <c r="C78" s="97" t="s">
-        <v>192</v>
-      </c>
-      <c r="D78" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E78" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="F78" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="G78" s="99" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="79" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+      <c r="C78" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D78" s="1">
+        <v>1</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B79" s="33">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
-      <c r="C79" s="93" t="s">
+      <c r="C79" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="D79" s="94" t="s">
-        <v>21</v>
-      </c>
-      <c r="E79" s="92" t="s">
-        <v>35</v>
-      </c>
-      <c r="F79" s="95" t="s">
-        <v>75</v>
-      </c>
-      <c r="G79" s="96" t="s">
-        <v>37</v>
+      <c r="D79" s="101" t="s">
+        <v>46</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.3">
@@ -6162,20 +6186,20 @@
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
-      <c r="C80" s="93" t="s">
-        <v>284</v>
-      </c>
-      <c r="D80" s="92">
-        <v>1</v>
-      </c>
-      <c r="E80" s="92" t="s">
-        <v>35</v>
-      </c>
-      <c r="F80" s="100" t="s">
-        <v>11</v>
-      </c>
-      <c r="G80" s="96" t="s">
-        <v>38</v>
+      <c r="C80" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D80" s="1">
+        <v>1</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.3">
@@ -6184,40 +6208,40 @@
         <v>64</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>346</v>
+        <v>229</v>
       </c>
       <c r="D81" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F81" s="103" t="s">
+        <v>238</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B82" s="33">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="C82" s="97" t="s">
+        <v>191</v>
+      </c>
+      <c r="D82" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G81" s="5" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="82" spans="2:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="B82" s="33">
-        <f t="shared" si="1"/>
-        <v>65</v>
-      </c>
-      <c r="C82" s="104" t="s">
-        <v>262</v>
-      </c>
-      <c r="D82" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="E82" s="105" t="s">
-        <v>244</v>
-      </c>
-      <c r="F82" s="110" t="s">
-        <v>360</v>
-      </c>
-      <c r="G82" s="107" t="s">
-        <v>265</v>
+      <c r="E82" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="F82" s="98" t="s">
+        <v>240</v>
+      </c>
+      <c r="G82" s="99" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="83" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6225,83 +6249,83 @@
         <f t="shared" ref="B83:B114" si="2">IF(C83="","",B82+1)</f>
         <v>66</v>
       </c>
-      <c r="C83" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="D83" s="1">
-        <v>1</v>
-      </c>
-      <c r="E83" s="103" t="s">
-        <v>244</v>
-      </c>
-      <c r="F83" s="103" t="s">
-        <v>352</v>
-      </c>
-      <c r="G83" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="84" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="C83" s="93" t="s">
+        <v>281</v>
+      </c>
+      <c r="D83" s="94" t="s">
+        <v>21</v>
+      </c>
+      <c r="E83" s="92" t="s">
+        <v>35</v>
+      </c>
+      <c r="F83" s="95" t="s">
+        <v>74</v>
+      </c>
+      <c r="G83" s="96" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B84" s="33">
         <f t="shared" si="2"/>
         <v>67</v>
       </c>
-      <c r="C84" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="D84" s="1">
-        <v>1</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F84" s="103" t="s">
-        <v>364</v>
-      </c>
-      <c r="G84" s="5" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="85" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="C84" s="93" t="s">
+        <v>282</v>
+      </c>
+      <c r="D84" s="92">
+        <v>1</v>
+      </c>
+      <c r="E84" s="92" t="s">
+        <v>35</v>
+      </c>
+      <c r="F84" s="100" t="s">
+        <v>11</v>
+      </c>
+      <c r="G84" s="96" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B85" s="33">
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="D85" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E85" s="103" t="s">
-        <v>244</v>
-      </c>
-      <c r="F85" s="103" t="s">
-        <v>352</v>
+        <v>21</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="86" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7" ht="66" x14ac:dyDescent="0.3">
       <c r="B86" s="33">
         <f t="shared" si="2"/>
         <v>69</v>
       </c>
-      <c r="C86" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="D86" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E86" s="103" t="s">
-        <v>244</v>
-      </c>
-      <c r="F86" s="103" t="s">
-        <v>366</v>
-      </c>
-      <c r="G86" s="5" t="s">
-        <v>321</v>
+      <c r="C86" s="104" t="s">
+        <v>260</v>
+      </c>
+      <c r="D86" s="109" t="s">
+        <v>20</v>
+      </c>
+      <c r="E86" s="105" t="s">
+        <v>242</v>
+      </c>
+      <c r="F86" s="110" t="s">
+        <v>377</v>
+      </c>
+      <c r="G86" s="107" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.3">
@@ -6309,62 +6333,62 @@
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="C87" s="104" t="s">
+      <c r="C87" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D87" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E87" s="103" t="s">
+        <v>242</v>
+      </c>
+      <c r="F87" s="103" t="s">
+        <v>243</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B88" s="33">
+        <f t="shared" si="2"/>
+        <v>71</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D88" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E88" s="103" t="s">
+        <v>242</v>
+      </c>
+      <c r="F88" s="103" t="s">
+        <v>362</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B89" s="33">
+        <f t="shared" si="2"/>
+        <v>72</v>
+      </c>
+      <c r="C89" s="104" t="s">
+        <v>254</v>
+      </c>
+      <c r="D89" s="105">
+        <v>1</v>
+      </c>
+      <c r="E89" s="105" t="s">
+        <v>242</v>
+      </c>
+      <c r="F89" s="106" t="s">
+        <v>14</v>
+      </c>
+      <c r="G89" s="107" t="s">
         <v>256</v>
-      </c>
-      <c r="D87" s="105">
-        <v>1</v>
-      </c>
-      <c r="E87" s="105" t="s">
-        <v>244</v>
-      </c>
-      <c r="F87" s="106" t="s">
-        <v>14</v>
-      </c>
-      <c r="G87" s="107" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B88" s="33">
-        <f t="shared" si="2"/>
-        <v>71</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="D88" s="1">
-        <v>1</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="G88" s="5" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="89" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B89" s="33">
-        <f t="shared" si="2"/>
-        <v>72</v>
-      </c>
-      <c r="C89" s="104" t="s">
-        <v>257</v>
-      </c>
-      <c r="D89" s="105">
-        <v>1</v>
-      </c>
-      <c r="E89" s="105" t="s">
-        <v>244</v>
-      </c>
-      <c r="F89" s="108" t="s">
-        <v>74</v>
-      </c>
-      <c r="G89" s="107" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.3">
@@ -6372,62 +6396,62 @@
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
-      <c r="C90" s="143" t="s">
-        <v>266</v>
-      </c>
-      <c r="D90" s="144" t="s">
+      <c r="C90" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D90" s="1">
+        <v>1</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B91" s="33">
+        <f t="shared" si="2"/>
+        <v>74</v>
+      </c>
+      <c r="C91" s="104" t="s">
+        <v>255</v>
+      </c>
+      <c r="D91" s="105">
+        <v>1</v>
+      </c>
+      <c r="E91" s="105" t="s">
+        <v>242</v>
+      </c>
+      <c r="F91" s="108" t="s">
+        <v>73</v>
+      </c>
+      <c r="G91" s="107" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="92" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B92" s="33">
+        <f t="shared" si="2"/>
+        <v>75</v>
+      </c>
+      <c r="C92" s="112" t="s">
+        <v>264</v>
+      </c>
+      <c r="D92" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="E90" s="145" t="s">
-        <v>244</v>
-      </c>
-      <c r="F90" s="146" t="s">
-        <v>374</v>
-      </c>
-      <c r="G90" s="143" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B91" s="33">
-        <f t="shared" si="2"/>
-        <v>74</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="D91" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="G91" s="5" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="92" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B92" s="33">
-        <f t="shared" si="2"/>
-        <v>75</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="D92" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="F92" s="103" t="s">
-        <v>376</v>
-      </c>
-      <c r="G92" s="5" t="s">
-        <v>279</v>
+      <c r="E92" s="111" t="s">
+        <v>242</v>
+      </c>
+      <c r="F92" s="118" t="s">
+        <v>355</v>
+      </c>
+      <c r="G92" s="112" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.3">
@@ -6436,40 +6460,40 @@
         <v>76</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>327</v>
+        <v>364</v>
       </c>
       <c r="D93" s="1">
         <v>1</v>
       </c>
       <c r="E93" s="103" t="s">
-        <v>245</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>64</v>
+        <v>242</v>
+      </c>
+      <c r="F93" s="103" t="s">
+        <v>243</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="94" spans="2:7" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B94" s="33">
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="D94" s="90" t="s">
         <v>56</v>
       </c>
-      <c r="E94" s="103" t="s">
-        <v>245</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>64</v>
+      <c r="E94" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F94" s="103" t="s">
+        <v>359</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
     </row>
     <row r="95" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6478,19 +6502,19 @@
         <v>78</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="D95" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E95" s="103" t="s">
-        <v>245</v>
+        <v>348</v>
+      </c>
+      <c r="D95" s="1">
+        <v>1</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>242</v>
       </c>
       <c r="F95" s="103" t="s">
-        <v>63</v>
+        <v>349</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.3">
@@ -6498,83 +6522,83 @@
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
-      <c r="C96" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D96" s="1">
-        <v>1</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G96" s="5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C96" s="104" t="s">
+        <v>354</v>
+      </c>
+      <c r="D96" s="109" t="s">
+        <v>20</v>
+      </c>
+      <c r="E96" s="117" t="s">
+        <v>355</v>
+      </c>
+      <c r="F96" s="106" t="s">
+        <v>17</v>
+      </c>
+      <c r="G96" s="107" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" ht="66" x14ac:dyDescent="0.3">
       <c r="B97" s="33">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="D97" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>62</v>
+        <v>243</v>
+      </c>
+      <c r="F97" s="103" t="s">
+        <v>381</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="98" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B98" s="33">
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="D98" s="90" t="s">
         <v>56</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="E98" s="103" t="s">
+        <v>243</v>
+      </c>
+      <c r="F98" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F98" s="103" t="s">
-        <v>367</v>
-      </c>
       <c r="G98" s="5" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="99" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B99" s="33">
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="D99" s="1">
-        <v>1</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>245</v>
+        <v>316</v>
+      </c>
+      <c r="D99" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E99" s="103" t="s">
+        <v>243</v>
       </c>
       <c r="F99" s="103" t="s">
-        <v>367</v>
+        <v>62</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.3">
@@ -6583,19 +6607,19 @@
         <v>83</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="D100" s="33">
-        <v>1</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>369</v>
+        <v>272</v>
+      </c>
+      <c r="D100" s="1">
+        <v>1</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>374</v>
+        <v>81</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>365</v>
+        <v>275</v>
       </c>
     </row>
     <row r="101" spans="2:7" x14ac:dyDescent="0.3">
@@ -6603,38 +6627,83 @@
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
-      <c r="C101" s="104" t="s">
-        <v>373</v>
-      </c>
-      <c r="D101" s="109" t="s">
+      <c r="C101" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D101" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="E101" s="142" t="s">
-        <v>374</v>
-      </c>
-      <c r="F101" s="106" t="s">
-        <v>17</v>
-      </c>
-      <c r="G101" s="107" t="s">
-        <v>375</v>
+      <c r="E101" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B102" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="103" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B103" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B104" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="B102" s="33">
+        <f t="shared" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D102" s="1">
+        <v>1</v>
+      </c>
+      <c r="E102" s="103" t="s">
+        <v>243</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B103" s="33">
+        <f t="shared" si="2"/>
+        <v>86</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D103" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="F103" s="103" t="s">
+        <v>379</v>
+      </c>
+      <c r="G103" s="5" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B104" s="33">
+        <f t="shared" si="2"/>
+        <v>87</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="D104" s="1">
+        <v>1</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F104" s="103" t="s">
+        <v>379</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="105" spans="2:7" x14ac:dyDescent="0.3">
@@ -6642,12 +6711,14 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
+      <c r="E105" s="102"/>
     </row>
     <row r="106" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B106" s="33" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
+      <c r="E106" s="102"/>
     </row>
     <row r="107" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B107" s="33" t="str">
@@ -6860,15 +6931,75 @@
     </sortState>
   </autoFilter>
   <mergeCells count="102">
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="P44:R44"/>
-    <mergeCell ref="O56:P56"/>
-    <mergeCell ref="Q56:S56"/>
-    <mergeCell ref="P62:R62"/>
-    <mergeCell ref="P63:R63"/>
-    <mergeCell ref="P64:R64"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="K72:M72"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="K53:M53"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="K54:M54"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="K48:M48"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="K51:M51"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="K52:M52"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:S18"/>
     <mergeCell ref="O72:P72"/>
     <mergeCell ref="Q72:S72"/>
     <mergeCell ref="P8:R8"/>
@@ -6893,75 +7024,15 @@
     <mergeCell ref="O36:P36"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:S20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="I72:J72"/>
-    <mergeCell ref="K72:M72"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="K53:M53"/>
-    <mergeCell ref="I54:J54"/>
-    <mergeCell ref="K54:M54"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="K48:M48"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="K51:M51"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="K52:M52"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:M40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:M39"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="P44:R44"/>
+    <mergeCell ref="O56:P56"/>
+    <mergeCell ref="Q56:S56"/>
+    <mergeCell ref="P62:R62"/>
+    <mergeCell ref="P63:R63"/>
+    <mergeCell ref="P64:R64"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6983,25 +7054,25 @@
   <sheetData>
     <row r="2" spans="2:8" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="G2" s="102" t="s">
         <v>334</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="H2" s="102" t="s">
         <v>335</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="G2" s="102" t="s">
-        <v>338</v>
-      </c>
-      <c r="H2" s="102" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">

--- a/Document/IDD.xlsx
+++ b/Document/IDD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\SoC_Design\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B9693E-721C-41BD-A898-07F7EED66780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B27CCE0-E8C4-4047-BF55-54CB5B588EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="396">
   <si>
     <t>top_cpu</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1431,19 +1431,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ForwardA MUX Data</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ForwardB MUX Data</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_alu_forward_b_mux
-u_ex_mem_bridge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>w_mem_regwrite</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1453,22 +1440,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>u_wdata_forwarding_unit</t>
-  </si>
-  <si>
-    <t>w_ex_alu_forward_mux_data_a</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_alu_forward_mux_data_b</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>u_alu_src_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_wdata_forward_mux_data</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1504,11 +1476,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>u_mem_wb_bridge
-u_wdata_forward_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>w_id_regdst</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1518,42 +1485,6 @@
   </si>
   <si>
     <t>w_wb_regdst</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_fw_ctr_alu_1c_forward_a</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_fw_ctr_alu_1c_forward_b</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WDATA Forward Output (1 Cycle)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU ForwardB Output (1 Cycle)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU ForwardA Output (1 Cycle)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_fw_ctr_wdata_1c_forward</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_fw_ctr_alu_2c_forward_a</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_fw_ctr_alu_2c_forward_b</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU ForwardA Output (2 Cycle)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1581,14 +1512,130 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ALU ForwardB Output (2 Cycle)</t>
+    <t>w_ex_fw_ctr_wdata_2c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_wdata_forwarding_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_fw_ctr_wdata_2c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_fw_ctr_alu_a_1c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_fw_ctr_alu_b_1c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_fw_ctr_alu_a_2c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_fw_ctr_alu_b_2c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_fw_ctr_wdata_1c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_wdata_fw_mux_data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_alu_fw_mux_data_a</t>
+  </si>
+  <si>
+    <t>fwA MUX Data</t>
+  </si>
+  <si>
+    <t>w_ex_alu_fw_mux_data_b</t>
+  </si>
+  <si>
+    <t>fwB MUX Data</t>
+  </si>
+  <si>
+    <t>ALU fwA Output (1 Cycle)</t>
+  </si>
+  <si>
+    <t>ALU fwB Output (1 Cycle)</t>
+  </si>
+  <si>
+    <t>ALU fwA Output (2 Cycle)</t>
+  </si>
+  <si>
+    <t>ALU fwB Output (2 Cycle)</t>
+  </si>
+  <si>
+    <t>WDATA fw Output (1 Cycle)</t>
+  </si>
+  <si>
+    <t>WDATA fw Output (2 Cycle) (EX)</t>
+  </si>
+  <si>
+    <t>WDATA fw Output (2 Cycle) (MEM)</t>
+  </si>
+  <si>
+    <t>w_mem_wdata_fw_mux_data_2c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alu_forwarding_unit</t>
+  </si>
+  <si>
+    <t>u_alu_forward_a_mux</t>
+  </si>
+  <si>
+    <t>u_alu_forward_b_mux</t>
+  </si>
+  <si>
+    <t>u_mem_wb_bridge
+u_wdata_forwarding_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_wdata_forward_2cycle_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_ex_mem_bridge
+u_wdata_forward_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_ex_mem_bridge
+u_wdata_forward_2cycle_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alu_forward_b_mux
+u_ex_mem_bridge
+u_wdata_forward_2cycle_mux</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>u_memtoreg_mux
 u_wdata_forward_mux
+u_wdata_forward_2cycle_mux
 u_alu_forward_a_mux
 u_alu_forward_b_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_wdata_fw_mux_data_2c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WDATA Forward MUX Data (2 Cylce) (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WDATA Forward MUX Data (2 Cylce) (MEM)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2569,83 +2616,83 @@
     <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3007,32 +3054,32 @@
   <sheetData>
     <row r="1" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="141" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="142"/>
-      <c r="F2" s="142"/>
-      <c r="G2" s="143"/>
-      <c r="I2" s="120" t="s">
+      <c r="B2" s="132" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="134"/>
+      <c r="I2" s="118" t="s">
         <v>103</v>
       </c>
-      <c r="J2" s="121"/>
-      <c r="K2" s="120" t="s">
+      <c r="J2" s="120"/>
+      <c r="K2" s="118" t="s">
         <v>97</v>
       </c>
-      <c r="L2" s="122"/>
-      <c r="M2" s="121"/>
-      <c r="O2" s="120" t="s">
+      <c r="L2" s="119"/>
+      <c r="M2" s="120"/>
+      <c r="O2" s="118" t="s">
         <v>103</v>
       </c>
-      <c r="P2" s="121"/>
-      <c r="Q2" s="120" t="s">
+      <c r="P2" s="120"/>
+      <c r="Q2" s="118" t="s">
         <v>150</v>
       </c>
-      <c r="R2" s="122"/>
-      <c r="S2" s="121"/>
+      <c r="R2" s="119"/>
+      <c r="S2" s="120"/>
     </row>
     <row r="3" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="34" t="s">
@@ -3053,24 +3100,24 @@
       <c r="G3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="130" t="s">
+      <c r="I3" s="127" t="s">
         <v>109</v>
       </c>
-      <c r="J3" s="131"/>
-      <c r="K3" s="132" t="s">
+      <c r="J3" s="128"/>
+      <c r="K3" s="129" t="s">
         <v>110</v>
       </c>
-      <c r="L3" s="133"/>
-      <c r="M3" s="134"/>
-      <c r="O3" s="130" t="s">
+      <c r="L3" s="130"/>
+      <c r="M3" s="131"/>
+      <c r="O3" s="127" t="s">
         <v>109</v>
       </c>
-      <c r="P3" s="131"/>
-      <c r="Q3" s="132" t="s">
+      <c r="P3" s="128"/>
+      <c r="Q3" s="129" t="s">
         <v>237</v>
       </c>
-      <c r="R3" s="133"/>
-      <c r="S3" s="134"/>
+      <c r="R3" s="130"/>
+      <c r="S3" s="131"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B4" s="35">
@@ -3091,24 +3138,24 @@
       <c r="G4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="130" t="s">
+      <c r="I4" s="127" t="s">
         <v>107</v>
       </c>
-      <c r="J4" s="131"/>
-      <c r="K4" s="130" t="s">
+      <c r="J4" s="128"/>
+      <c r="K4" s="127" t="s">
         <v>64</v>
       </c>
-      <c r="L4" s="135"/>
-      <c r="M4" s="131"/>
-      <c r="O4" s="130" t="s">
+      <c r="L4" s="141"/>
+      <c r="M4" s="128"/>
+      <c r="O4" s="127" t="s">
         <v>107</v>
       </c>
-      <c r="P4" s="131"/>
-      <c r="Q4" s="130" t="s">
+      <c r="P4" s="128"/>
+      <c r="Q4" s="127" t="s">
         <v>64</v>
       </c>
-      <c r="R4" s="135"/>
-      <c r="S4" s="131"/>
+      <c r="R4" s="141"/>
+      <c r="S4" s="128"/>
     </row>
     <row r="5" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="54">
@@ -3129,24 +3176,24 @@
       <c r="G5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="136" t="s">
+      <c r="I5" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="137"/>
-      <c r="K5" s="138" t="s">
+      <c r="J5" s="122"/>
+      <c r="K5" s="123" t="s">
         <v>102</v>
       </c>
-      <c r="L5" s="119"/>
-      <c r="M5" s="139"/>
-      <c r="O5" s="136" t="s">
+      <c r="L5" s="124"/>
+      <c r="M5" s="125"/>
+      <c r="O5" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="137"/>
-      <c r="Q5" s="138" t="s">
+      <c r="P5" s="122"/>
+      <c r="Q5" s="123" t="s">
         <v>151</v>
       </c>
-      <c r="R5" s="119"/>
-      <c r="S5" s="139"/>
+      <c r="R5" s="124"/>
+      <c r="S5" s="125"/>
     </row>
     <row r="6" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="55">
@@ -3170,22 +3217,22 @@
       <c r="I6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="128" t="s">
+      <c r="J6" s="126" t="s">
         <v>98</v>
       </c>
-      <c r="K6" s="128"/>
-      <c r="L6" s="128"/>
+      <c r="K6" s="126"/>
+      <c r="L6" s="126"/>
       <c r="M6" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="128" t="s">
+      <c r="P6" s="126" t="s">
         <v>98</v>
       </c>
-      <c r="Q6" s="128"/>
-      <c r="R6" s="128"/>
+      <c r="Q6" s="126"/>
+      <c r="R6" s="126"/>
       <c r="S6" s="69" t="s">
         <v>8</v>
       </c>
@@ -3212,22 +3259,22 @@
       <c r="I7" s="70">
         <v>1</v>
       </c>
-      <c r="J7" s="140" t="s">
+      <c r="J7" s="135" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="140"/>
-      <c r="L7" s="140"/>
+      <c r="K7" s="135"/>
+      <c r="L7" s="135"/>
       <c r="M7" s="71" t="s">
         <v>133</v>
       </c>
       <c r="O7" s="87">
         <v>1</v>
       </c>
-      <c r="P7" s="129" t="s">
+      <c r="P7" s="142" t="s">
         <v>21</v>
       </c>
-      <c r="Q7" s="129"/>
-      <c r="R7" s="129"/>
+      <c r="Q7" s="142"/>
+      <c r="R7" s="142"/>
       <c r="S7" s="88" t="s">
         <v>133</v>
       </c>
@@ -3269,11 +3316,11 @@
       <c r="O8" s="80">
         <v>2</v>
       </c>
-      <c r="P8" s="119" t="s">
+      <c r="P8" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="119"/>
-      <c r="R8" s="119"/>
+      <c r="Q8" s="124"/>
+      <c r="R8" s="124"/>
       <c r="S8" s="82" t="s">
         <v>134</v>
       </c>
@@ -3447,15 +3494,15 @@
       <c r="G12" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="123" t="s">
+      <c r="I12" s="136" t="s">
         <v>105</v>
       </c>
-      <c r="J12" s="124"/>
-      <c r="K12" s="125" t="s">
+      <c r="J12" s="137"/>
+      <c r="K12" s="138" t="s">
         <v>106</v>
       </c>
-      <c r="L12" s="126"/>
-      <c r="M12" s="127"/>
+      <c r="L12" s="139"/>
+      <c r="M12" s="140"/>
       <c r="O12" s="72">
         <v>3</v>
       </c>
@@ -3578,15 +3625,15 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="O16" s="123" t="s">
+      <c r="O16" s="136" t="s">
         <v>105</v>
       </c>
-      <c r="P16" s="124"/>
-      <c r="Q16" s="125" t="s">
+      <c r="P16" s="137"/>
+      <c r="Q16" s="138" t="s">
         <v>240</v>
       </c>
-      <c r="R16" s="126"/>
-      <c r="S16" s="127"/>
+      <c r="R16" s="139"/>
+      <c r="S16" s="140"/>
     </row>
     <row r="17" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="90" t="s">
@@ -3628,24 +3675,24 @@
       <c r="G18" s="99" t="s">
         <v>198</v>
       </c>
-      <c r="I18" s="120" t="s">
+      <c r="I18" s="118" t="s">
         <v>103</v>
       </c>
-      <c r="J18" s="121"/>
-      <c r="K18" s="120" t="s">
+      <c r="J18" s="120"/>
+      <c r="K18" s="118" t="s">
         <v>104</v>
       </c>
-      <c r="L18" s="122"/>
-      <c r="M18" s="121"/>
-      <c r="O18" s="120" t="s">
+      <c r="L18" s="119"/>
+      <c r="M18" s="120"/>
+      <c r="O18" s="118" t="s">
         <v>103</v>
       </c>
-      <c r="P18" s="121"/>
-      <c r="Q18" s="120" t="s">
+      <c r="P18" s="120"/>
+      <c r="Q18" s="118" t="s">
         <v>160</v>
       </c>
-      <c r="R18" s="122"/>
-      <c r="S18" s="121"/>
+      <c r="R18" s="119"/>
+      <c r="S18" s="120"/>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B19" s="33">
@@ -3667,24 +3714,24 @@
       <c r="G19" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="I19" s="130" t="s">
+      <c r="I19" s="127" t="s">
         <v>109</v>
       </c>
-      <c r="J19" s="131"/>
-      <c r="K19" s="132" t="s">
+      <c r="J19" s="128"/>
+      <c r="K19" s="129" t="s">
         <v>111</v>
       </c>
-      <c r="L19" s="133"/>
-      <c r="M19" s="134"/>
-      <c r="O19" s="130" t="s">
+      <c r="L19" s="130"/>
+      <c r="M19" s="131"/>
+      <c r="O19" s="127" t="s">
         <v>109</v>
       </c>
-      <c r="P19" s="131"/>
-      <c r="Q19" s="132" t="s">
+      <c r="P19" s="128"/>
+      <c r="Q19" s="129" t="s">
         <v>237</v>
       </c>
-      <c r="R19" s="133"/>
-      <c r="S19" s="134"/>
+      <c r="R19" s="130"/>
+      <c r="S19" s="131"/>
     </row>
     <row r="20" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B20" s="33">
@@ -3706,24 +3753,24 @@
       <c r="G20" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="I20" s="130" t="s">
+      <c r="I20" s="127" t="s">
         <v>107</v>
       </c>
-      <c r="J20" s="131"/>
-      <c r="K20" s="132" t="s">
+      <c r="J20" s="128"/>
+      <c r="K20" s="129" t="s">
         <v>108</v>
       </c>
-      <c r="L20" s="133"/>
-      <c r="M20" s="134"/>
-      <c r="O20" s="130" t="s">
+      <c r="L20" s="130"/>
+      <c r="M20" s="131"/>
+      <c r="O20" s="127" t="s">
         <v>107</v>
       </c>
-      <c r="P20" s="131"/>
-      <c r="Q20" s="130" t="s">
+      <c r="P20" s="128"/>
+      <c r="Q20" s="127" t="s">
         <v>64</v>
       </c>
-      <c r="R20" s="135"/>
-      <c r="S20" s="131"/>
+      <c r="R20" s="141"/>
+      <c r="S20" s="128"/>
     </row>
     <row r="21" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="33">
@@ -3731,38 +3778,38 @@
         <v>4</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="D21" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="F21" s="103" t="s">
         <v>76</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="I21" s="136" t="s">
+        <v>373</v>
+      </c>
+      <c r="I21" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="137"/>
-      <c r="K21" s="138" t="s">
+      <c r="J21" s="122"/>
+      <c r="K21" s="123" t="s">
         <v>125</v>
       </c>
-      <c r="L21" s="119"/>
-      <c r="M21" s="139"/>
-      <c r="O21" s="136" t="s">
+      <c r="L21" s="124"/>
+      <c r="M21" s="125"/>
+      <c r="O21" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="137"/>
-      <c r="Q21" s="138" t="s">
+      <c r="P21" s="122"/>
+      <c r="Q21" s="123" t="s">
         <v>161</v>
       </c>
-      <c r="R21" s="119"/>
-      <c r="S21" s="139"/>
+      <c r="R21" s="124"/>
+      <c r="S21" s="125"/>
     </row>
     <row r="22" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="33">
@@ -3770,44 +3817,44 @@
         <v>5</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="D22" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="F22" s="103" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>346</v>
+        <v>375</v>
       </c>
       <c r="I22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J22" s="128" t="s">
+      <c r="J22" s="126" t="s">
         <v>98</v>
       </c>
-      <c r="K22" s="128"/>
-      <c r="L22" s="128"/>
+      <c r="K22" s="126"/>
+      <c r="L22" s="126"/>
       <c r="M22" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P22" s="128" t="s">
+      <c r="P22" s="126" t="s">
         <v>98</v>
       </c>
-      <c r="Q22" s="128"/>
-      <c r="R22" s="128"/>
+      <c r="Q22" s="126"/>
+      <c r="R22" s="126"/>
       <c r="S22" s="69" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="33">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -3822,7 +3869,7 @@
         <v>79</v>
       </c>
       <c r="F23" s="103" t="s">
-        <v>242</v>
+        <v>389</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>262</v>
@@ -3830,22 +3877,22 @@
       <c r="I23" s="70">
         <v>1</v>
       </c>
-      <c r="J23" s="140" t="s">
+      <c r="J23" s="135" t="s">
         <v>20</v>
       </c>
-      <c r="K23" s="140"/>
-      <c r="L23" s="140"/>
+      <c r="K23" s="135"/>
+      <c r="L23" s="135"/>
       <c r="M23" s="71" t="s">
         <v>134</v>
       </c>
       <c r="O23" s="87">
         <v>1</v>
       </c>
-      <c r="P23" s="129" t="s">
+      <c r="P23" s="142" t="s">
         <v>21</v>
       </c>
-      <c r="Q23" s="129"/>
-      <c r="R23" s="129"/>
+      <c r="Q23" s="142"/>
+      <c r="R23" s="142"/>
       <c r="S23" s="88" t="s">
         <v>133</v>
       </c>
@@ -3888,11 +3935,11 @@
       <c r="O24" s="80">
         <v>2</v>
       </c>
-      <c r="P24" s="119" t="s">
+      <c r="P24" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="Q24" s="119"/>
-      <c r="R24" s="119"/>
+      <c r="Q24" s="124"/>
+      <c r="R24" s="124"/>
       <c r="S24" s="82" t="s">
         <v>134</v>
       </c>
@@ -4274,15 +4321,15 @@
       <c r="G32" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="I32" s="123" t="s">
+      <c r="I32" s="136" t="s">
         <v>105</v>
       </c>
-      <c r="J32" s="124"/>
-      <c r="K32" s="125" t="s">
+      <c r="J32" s="137"/>
+      <c r="K32" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="L32" s="126"/>
-      <c r="M32" s="127"/>
+      <c r="L32" s="139"/>
+      <c r="M32" s="140"/>
       <c r="O32" s="83">
         <v>7</v>
       </c>
@@ -4314,7 +4361,7 @@
         <v>241</v>
       </c>
       <c r="F33" s="103" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>324</v>
@@ -4386,7 +4433,7 @@
         <v>241</v>
       </c>
       <c r="F35" s="103" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>318</v>
@@ -4422,20 +4469,20 @@
         <v>241</v>
       </c>
       <c r="F36" s="103" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="O36" s="123" t="s">
+      <c r="O36" s="136" t="s">
         <v>105</v>
       </c>
-      <c r="P36" s="124"/>
-      <c r="Q36" s="125" t="s">
+      <c r="P36" s="137"/>
+      <c r="Q36" s="138" t="s">
         <v>241</v>
       </c>
-      <c r="R36" s="126"/>
-      <c r="S36" s="127"/>
+      <c r="R36" s="139"/>
+      <c r="S36" s="140"/>
     </row>
     <row r="37" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="33">
@@ -4452,50 +4499,50 @@
         <v>241</v>
       </c>
       <c r="F37" s="103" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B38" s="33">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="D38" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>64</v>
+        <v>363</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1</v>
+      </c>
+      <c r="E38" s="102" t="s">
+        <v>364</v>
+      </c>
+      <c r="F38" s="103" t="s">
+        <v>390</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="I38" s="120" t="s">
+        <v>381</v>
+      </c>
+      <c r="I38" s="118" t="s">
         <v>103</v>
       </c>
-      <c r="J38" s="121"/>
-      <c r="K38" s="120" t="s">
+      <c r="J38" s="120"/>
+      <c r="K38" s="118" t="s">
         <v>123</v>
       </c>
-      <c r="L38" s="122"/>
-      <c r="M38" s="121"/>
-      <c r="O38" s="120" t="s">
+      <c r="L38" s="119"/>
+      <c r="M38" s="120"/>
+      <c r="O38" s="118" t="s">
         <v>103</v>
       </c>
-      <c r="P38" s="121"/>
-      <c r="Q38" s="120" t="s">
+      <c r="P38" s="120"/>
+      <c r="Q38" s="118" t="s">
         <v>174</v>
       </c>
-      <c r="R38" s="122"/>
-      <c r="S38" s="121"/>
+      <c r="R38" s="119"/>
+      <c r="S38" s="120"/>
     </row>
     <row r="39" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B39" s="33">
@@ -4503,116 +4550,116 @@
         <v>22</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="D39" s="101" t="s">
+        <v>300</v>
+      </c>
+      <c r="D39" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="E39" s="102" t="s">
-        <v>238</v>
+      <c r="E39" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="I39" s="130" t="s">
+        <v>87</v>
+      </c>
+      <c r="I39" s="127" t="s">
         <v>109</v>
       </c>
-      <c r="J39" s="131"/>
-      <c r="K39" s="132" t="s">
+      <c r="J39" s="128"/>
+      <c r="K39" s="129" t="s">
         <v>124</v>
       </c>
-      <c r="L39" s="133"/>
-      <c r="M39" s="134"/>
-      <c r="O39" s="130" t="s">
+      <c r="L39" s="130"/>
+      <c r="M39" s="131"/>
+      <c r="O39" s="127" t="s">
         <v>109</v>
       </c>
-      <c r="P39" s="131"/>
-      <c r="Q39" s="132" t="s">
+      <c r="P39" s="128"/>
+      <c r="Q39" s="129" t="s">
         <v>237</v>
       </c>
-      <c r="R39" s="133"/>
-      <c r="S39" s="134"/>
+      <c r="R39" s="130"/>
+      <c r="S39" s="131"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B40" s="33">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C40" s="97" t="s">
-        <v>278</v>
-      </c>
-      <c r="D40" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="33" t="s">
+      <c r="C40" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D40" s="101" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="102" t="s">
+        <v>238</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F40" s="98" t="s">
-        <v>35</v>
-      </c>
-      <c r="G40" s="99" t="s">
-        <v>279</v>
-      </c>
-      <c r="I40" s="130" t="s">
+      <c r="G40" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="I40" s="127" t="s">
         <v>107</v>
       </c>
-      <c r="J40" s="131"/>
-      <c r="K40" s="132" t="s">
+      <c r="J40" s="128"/>
+      <c r="K40" s="129" t="s">
         <v>108</v>
       </c>
-      <c r="L40" s="133"/>
-      <c r="M40" s="134"/>
-      <c r="O40" s="130" t="s">
+      <c r="L40" s="130"/>
+      <c r="M40" s="131"/>
+      <c r="O40" s="127" t="s">
         <v>107</v>
       </c>
-      <c r="P40" s="131"/>
-      <c r="Q40" s="130" t="s">
+      <c r="P40" s="128"/>
+      <c r="Q40" s="127" t="s">
         <v>64</v>
       </c>
-      <c r="R40" s="135"/>
-      <c r="S40" s="131"/>
+      <c r="R40" s="141"/>
+      <c r="S40" s="128"/>
     </row>
     <row r="41" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="33">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>301</v>
+      <c r="C41" s="97" t="s">
+        <v>278</v>
       </c>
       <c r="D41" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="I41" s="136" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F41" s="98" t="s">
+        <v>35</v>
+      </c>
+      <c r="G41" s="99" t="s">
+        <v>279</v>
+      </c>
+      <c r="I41" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="137"/>
-      <c r="K41" s="138" t="s">
+      <c r="J41" s="122"/>
+      <c r="K41" s="123" t="s">
         <v>126</v>
       </c>
-      <c r="L41" s="119"/>
-      <c r="M41" s="139"/>
-      <c r="O41" s="136" t="s">
+      <c r="L41" s="124"/>
+      <c r="M41" s="125"/>
+      <c r="O41" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="P41" s="137"/>
-      <c r="Q41" s="138" t="s">
+      <c r="P41" s="122"/>
+      <c r="Q41" s="123" t="s">
         <v>175</v>
       </c>
-      <c r="R41" s="119"/>
-      <c r="S41" s="139"/>
+      <c r="R41" s="124"/>
+      <c r="S41" s="125"/>
     </row>
     <row r="42" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="33">
@@ -4620,39 +4667,39 @@
         <v>25</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D42" s="1">
-        <v>1</v>
-      </c>
-      <c r="E42" s="114" t="s">
-        <v>241</v>
-      </c>
-      <c r="F42" s="114" t="s">
-        <v>242</v>
+        <v>301</v>
+      </c>
+      <c r="D42" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>252</v>
+        <v>88</v>
       </c>
       <c r="I42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J42" s="128" t="s">
+      <c r="J42" s="126" t="s">
         <v>98</v>
       </c>
-      <c r="K42" s="128"/>
-      <c r="L42" s="128"/>
+      <c r="K42" s="126"/>
+      <c r="L42" s="126"/>
       <c r="M42" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P42" s="128" t="s">
+      <c r="P42" s="126" t="s">
         <v>98</v>
       </c>
-      <c r="Q42" s="128"/>
-      <c r="R42" s="128"/>
+      <c r="Q42" s="126"/>
+      <c r="R42" s="126"/>
       <c r="S42" s="69" t="s">
         <v>8</v>
       </c>
@@ -4663,39 +4710,39 @@
         <v>26</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="D43" s="1">
         <v>1</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" s="114" t="s">
         <v>241</v>
       </c>
-      <c r="F43" s="103" t="s">
+      <c r="F43" s="114" t="s">
         <v>242</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>273</v>
+        <v>252</v>
       </c>
       <c r="I43" s="70">
         <v>1</v>
       </c>
-      <c r="J43" s="140" t="s">
+      <c r="J43" s="135" t="s">
         <v>20</v>
       </c>
-      <c r="K43" s="140"/>
-      <c r="L43" s="140"/>
+      <c r="K43" s="135"/>
+      <c r="L43" s="135"/>
       <c r="M43" s="71" t="s">
         <v>134</v>
       </c>
       <c r="O43" s="87">
         <v>1</v>
       </c>
-      <c r="P43" s="129" t="s">
+      <c r="P43" s="142" t="s">
         <v>21</v>
       </c>
-      <c r="Q43" s="129"/>
-      <c r="R43" s="129"/>
+      <c r="Q43" s="142"/>
+      <c r="R43" s="142"/>
       <c r="S43" s="88" t="s">
         <v>133</v>
       </c>
@@ -4706,19 +4753,19 @@
         <v>27</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
       </c>
-      <c r="E44" s="114" t="s">
+      <c r="E44" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F44" s="114" t="s">
+      <c r="F44" s="103" t="s">
         <v>242</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="I44" s="67" t="s">
         <v>41</v>
@@ -4738,11 +4785,11 @@
       <c r="O44" s="80">
         <v>2</v>
       </c>
-      <c r="P44" s="119" t="s">
+      <c r="P44" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="Q44" s="119"/>
-      <c r="R44" s="119"/>
+      <c r="Q44" s="124"/>
+      <c r="R44" s="124"/>
       <c r="S44" s="82" t="s">
         <v>134</v>
       </c>
@@ -4753,19 +4800,19 @@
         <v>28</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D45" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F45" s="103" t="s">
-        <v>375</v>
+        <v>251</v>
+      </c>
+      <c r="D45" s="1">
+        <v>1</v>
+      </c>
+      <c r="E45" s="114" t="s">
+        <v>241</v>
+      </c>
+      <c r="F45" s="114" t="s">
+        <v>242</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="I45" s="72">
         <v>1</v>
@@ -4798,25 +4845,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B46" s="33">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C46" s="112" t="s">
-        <v>223</v>
-      </c>
-      <c r="D46" s="113" t="s">
+      <c r="C46" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D46" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="111" t="s">
+      <c r="E46" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F46" s="115" t="s">
-        <v>347</v>
-      </c>
-      <c r="G46" s="112" t="s">
-        <v>225</v>
+      <c r="F46" s="103" t="s">
+        <v>358</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>224</v>
       </c>
       <c r="I46" s="76">
         <v>2</v>
@@ -4849,25 +4896,25 @@
         <v>155</v>
       </c>
     </row>
-    <row r="47" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="33">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="D47" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>358</v>
+      <c r="C47" s="112" t="s">
+        <v>223</v>
+      </c>
+      <c r="D47" s="113" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" s="111" t="s">
+        <v>238</v>
+      </c>
+      <c r="F47" s="115" t="s">
+        <v>391</v>
+      </c>
+      <c r="G47" s="112" t="s">
+        <v>225</v>
       </c>
       <c r="I47" s="80">
         <v>3</v>
@@ -4906,29 +4953,29 @@
         <v>31</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="D48" s="1">
-        <v>1</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="F48" s="103" t="s">
+        <v>350</v>
+      </c>
+      <c r="D48" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F48" s="2" t="s">
         <v>242</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="I48" s="123" t="s">
+        <v>351</v>
+      </c>
+      <c r="I48" s="136" t="s">
         <v>105</v>
       </c>
-      <c r="J48" s="124"/>
-      <c r="K48" s="125" t="s">
+      <c r="J48" s="137"/>
+      <c r="K48" s="138" t="s">
         <v>65</v>
       </c>
-      <c r="L48" s="126"/>
-      <c r="M48" s="127"/>
+      <c r="L48" s="139"/>
+      <c r="M48" s="140"/>
       <c r="O48" s="83">
         <v>3</v>
       </c>
@@ -4951,19 +4998,19 @@
         <v>32</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="D49" s="90" t="s">
-        <v>49</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>286</v>
+        <v>305</v>
+      </c>
+      <c r="D49" s="1">
+        <v>1</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F49" s="103" t="s">
+        <v>242</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>54</v>
+        <v>307</v>
       </c>
       <c r="O49" s="83">
         <v>4</v>
@@ -4987,19 +5034,19 @@
         <v>33</v>
       </c>
       <c r="C50" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D50" s="90" t="s">
+        <v>49</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="D50" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="G50" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O50" s="83">
         <v>5</v>
@@ -5017,35 +5064,35 @@
         <v>182</v>
       </c>
     </row>
-    <row r="51" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B51" s="33">
         <f t="shared" ref="B51:B82" si="1">IF(C51="","",B50+1)</f>
         <v>34</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>226</v>
+        <v>286</v>
       </c>
       <c r="D51" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F51" s="103" t="s">
-        <v>48</v>
+        <v>285</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="I51" s="120" t="s">
+        <v>52</v>
+      </c>
+      <c r="I51" s="118" t="s">
         <v>103</v>
       </c>
-      <c r="J51" s="121"/>
-      <c r="K51" s="120" t="s">
+      <c r="J51" s="120"/>
+      <c r="K51" s="118" t="s">
         <v>130</v>
       </c>
-      <c r="L51" s="122"/>
-      <c r="M51" s="121"/>
+      <c r="L51" s="119"/>
+      <c r="M51" s="120"/>
       <c r="O51" s="83">
         <v>6</v>
       </c>
@@ -5062,35 +5109,35 @@
         <v>169</v>
       </c>
     </row>
-    <row r="52" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B52" s="33">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="D52" s="1">
-        <v>1</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>375</v>
+        <v>226</v>
+      </c>
+      <c r="D52" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F52" s="103" t="s">
+        <v>48</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="I52" s="130" t="s">
+        <v>228</v>
+      </c>
+      <c r="I52" s="127" t="s">
         <v>109</v>
       </c>
-      <c r="J52" s="131"/>
-      <c r="K52" s="132" t="s">
+      <c r="J52" s="128"/>
+      <c r="K52" s="129" t="s">
         <v>131</v>
       </c>
-      <c r="L52" s="133"/>
-      <c r="M52" s="134"/>
+      <c r="L52" s="130"/>
+      <c r="M52" s="131"/>
       <c r="O52" s="83">
         <v>7</v>
       </c>
@@ -5113,29 +5160,29 @@
         <v>36</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="D53" s="1">
-        <v>1</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>376</v>
+        <v>393</v>
+      </c>
+      <c r="D53" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="I53" s="130" t="s">
+        <v>394</v>
+      </c>
+      <c r="I53" s="127" t="s">
         <v>107</v>
       </c>
-      <c r="J53" s="131"/>
-      <c r="K53" s="132" t="s">
+      <c r="J53" s="128"/>
+      <c r="K53" s="129" t="s">
         <v>108</v>
       </c>
-      <c r="L53" s="133"/>
-      <c r="M53" s="134"/>
+      <c r="L53" s="130"/>
+      <c r="M53" s="131"/>
       <c r="O53" s="83">
         <v>8</v>
       </c>
@@ -5158,29 +5205,29 @@
         <v>37</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="D54" s="1">
         <v>1</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="I54" s="136" t="s">
+        <v>376</v>
+      </c>
+      <c r="I54" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="137"/>
-      <c r="K54" s="138" t="s">
+      <c r="J54" s="122"/>
+      <c r="K54" s="123" t="s">
         <v>132</v>
       </c>
-      <c r="L54" s="119"/>
-      <c r="M54" s="139"/>
+      <c r="L54" s="124"/>
+      <c r="M54" s="125"/>
       <c r="O54" s="83">
         <v>9</v>
       </c>
@@ -5203,28 +5250,28 @@
         <v>38</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="D55" s="1">
         <v>1</v>
       </c>
       <c r="E55" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="G55" s="5" t="s">
         <v>378</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>380</v>
       </c>
       <c r="I55" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J55" s="128" t="s">
+      <c r="J55" s="126" t="s">
         <v>98</v>
       </c>
-      <c r="K55" s="128"/>
-      <c r="L55" s="128"/>
+      <c r="K55" s="126"/>
+      <c r="L55" s="126"/>
       <c r="M55" s="69" t="s">
         <v>8</v>
       </c>
@@ -5250,40 +5297,40 @@
         <v>39</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="D56" s="33">
-        <v>1</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>350</v>
+        <v>367</v>
+      </c>
+      <c r="D56" s="1">
+        <v>1</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>384</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>355</v>
+        <v>386</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="I56" s="87">
         <v>1</v>
       </c>
-      <c r="J56" s="129" t="s">
+      <c r="J56" s="142" t="s">
         <v>20</v>
       </c>
-      <c r="K56" s="129"/>
-      <c r="L56" s="129"/>
+      <c r="K56" s="142"/>
+      <c r="L56" s="142"/>
       <c r="M56" s="88" t="s">
         <v>134</v>
       </c>
-      <c r="O56" s="123" t="s">
+      <c r="O56" s="136" t="s">
         <v>105</v>
       </c>
-      <c r="P56" s="124"/>
-      <c r="Q56" s="125" t="s">
+      <c r="P56" s="137"/>
+      <c r="Q56" s="138" t="s">
         <v>242</v>
       </c>
-      <c r="R56" s="126"/>
-      <c r="S56" s="127"/>
+      <c r="R56" s="139"/>
+      <c r="S56" s="140"/>
     </row>
     <row r="57" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="33">
@@ -5291,51 +5338,51 @@
         <v>40</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D57" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>239</v>
+        <v>369</v>
+      </c>
+      <c r="D57" s="1">
+        <v>1</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>384</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>44</v>
+        <v>386</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>194</v>
+        <v>379</v>
       </c>
       <c r="I57" s="80">
         <v>2</v>
       </c>
-      <c r="J57" s="119" t="s">
+      <c r="J57" s="124" t="s">
         <v>55</v>
       </c>
-      <c r="K57" s="119"/>
-      <c r="L57" s="119"/>
+      <c r="K57" s="124"/>
+      <c r="L57" s="124"/>
       <c r="M57" s="89" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="58" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B58" s="33">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D58" s="90" t="s">
-        <v>21</v>
+        <v>370</v>
+      </c>
+      <c r="D58" s="33">
+        <v>1</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F58" s="103" t="s">
-        <v>258</v>
-      </c>
-      <c r="G58" s="99" t="s">
-        <v>195</v>
+        <v>364</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>380</v>
       </c>
       <c r="I58" s="67" t="s">
         <v>41</v>
@@ -5352,15 +5399,15 @@
       <c r="M58" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="120" t="s">
+      <c r="O58" s="118" t="s">
         <v>103</v>
       </c>
-      <c r="P58" s="121"/>
-      <c r="Q58" s="120" t="s">
+      <c r="P58" s="120"/>
+      <c r="Q58" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="R58" s="122"/>
-      <c r="S58" s="121"/>
+      <c r="R58" s="119"/>
+      <c r="S58" s="120"/>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B59" s="33">
@@ -5368,19 +5415,19 @@
         <v>42</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D59" s="1">
-        <v>3</v>
+        <v>193</v>
+      </c>
+      <c r="D59" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>58</v>
+        <v>239</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>241</v>
+        <v>44</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="I59" s="72">
         <v>1</v>
@@ -5397,35 +5444,35 @@
       <c r="M59" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="O59" s="130" t="s">
+      <c r="O59" s="127" t="s">
         <v>109</v>
       </c>
-      <c r="P59" s="131"/>
-      <c r="Q59" s="132" t="s">
+      <c r="P59" s="128"/>
+      <c r="Q59" s="129" t="s">
         <v>237</v>
       </c>
-      <c r="R59" s="133"/>
-      <c r="S59" s="134"/>
-    </row>
-    <row r="60" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="R59" s="130"/>
+      <c r="S59" s="131"/>
+    </row>
+    <row r="60" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B60" s="33">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D60" s="1">
-        <v>1</v>
+        <v>197</v>
+      </c>
+      <c r="D60" s="90" t="s">
+        <v>21</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>219</v>
+        <v>239</v>
+      </c>
+      <c r="F60" s="103" t="s">
+        <v>258</v>
+      </c>
+      <c r="G60" s="99" t="s">
+        <v>195</v>
       </c>
       <c r="I60" s="76">
         <v>2</v>
@@ -5442,15 +5489,15 @@
       <c r="M60" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="O60" s="130" t="s">
+      <c r="O60" s="127" t="s">
         <v>107</v>
       </c>
-      <c r="P60" s="131"/>
-      <c r="Q60" s="130" t="s">
+      <c r="P60" s="128"/>
+      <c r="Q60" s="127" t="s">
         <v>64</v>
       </c>
-      <c r="R60" s="135"/>
-      <c r="S60" s="131"/>
+      <c r="R60" s="141"/>
+      <c r="S60" s="128"/>
     </row>
     <row r="61" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="33">
@@ -5458,19 +5505,19 @@
         <v>44</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D61" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I61" s="83">
         <v>3</v>
@@ -5487,15 +5534,15 @@
       <c r="M61" s="85" t="s">
         <v>146</v>
       </c>
-      <c r="O61" s="136" t="s">
+      <c r="O61" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="P61" s="137"/>
-      <c r="Q61" s="138" t="s">
+      <c r="P61" s="122"/>
+      <c r="Q61" s="123" t="s">
         <v>186</v>
       </c>
-      <c r="R61" s="119"/>
-      <c r="S61" s="139"/>
+      <c r="R61" s="124"/>
+      <c r="S61" s="125"/>
     </row>
     <row r="62" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B62" s="33">
@@ -5503,7 +5550,7 @@
         <v>45</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D62" s="1">
         <v>1</v>
@@ -5515,7 +5562,7 @@
         <v>241</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I62" s="83">
         <v>4</v>
@@ -5535,11 +5582,11 @@
       <c r="O62" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P62" s="128" t="s">
+      <c r="P62" s="126" t="s">
         <v>98</v>
       </c>
-      <c r="Q62" s="128"/>
-      <c r="R62" s="128"/>
+      <c r="Q62" s="126"/>
+      <c r="R62" s="126"/>
       <c r="S62" s="69" t="s">
         <v>8</v>
       </c>
@@ -5550,19 +5597,19 @@
         <v>46</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="D63" s="90" t="s">
-        <v>57</v>
+        <v>200</v>
+      </c>
+      <c r="D63" s="1">
+        <v>1</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>43</v>
+        <v>238</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>61</v>
+        <v>214</v>
       </c>
       <c r="I63" s="83">
         <v>5</v>
@@ -5582,11 +5629,11 @@
       <c r="O63" s="87">
         <v>1</v>
       </c>
-      <c r="P63" s="129" t="s">
+      <c r="P63" s="142" t="s">
         <v>21</v>
       </c>
-      <c r="Q63" s="129"/>
-      <c r="R63" s="129"/>
+      <c r="Q63" s="142"/>
+      <c r="R63" s="142"/>
       <c r="S63" s="88" t="s">
         <v>133</v>
       </c>
@@ -5597,19 +5644,19 @@
         <v>47</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>244</v>
+        <v>206</v>
       </c>
       <c r="D64" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>241</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="I64" s="83">
         <v>6</v>
@@ -5629,34 +5676,34 @@
       <c r="O64" s="80">
         <v>2</v>
       </c>
-      <c r="P64" s="119" t="s">
+      <c r="P64" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="Q64" s="119"/>
-      <c r="R64" s="119"/>
+      <c r="Q64" s="124"/>
+      <c r="R64" s="124"/>
       <c r="S64" s="82" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="65" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="33">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="C65" s="97" t="s">
-        <v>280</v>
-      </c>
-      <c r="D65" s="101" t="s">
-        <v>45</v>
-      </c>
-      <c r="E65" s="33" t="s">
+      <c r="C65" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D65" s="90" t="s">
+        <v>57</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F65" s="98" t="s">
-        <v>42</v>
-      </c>
-      <c r="G65" s="99" t="s">
-        <v>50</v>
+      <c r="F65" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="I65" s="83">
         <v>7</v>
@@ -5695,19 +5742,19 @@
         <v>49</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="D66" s="90" t="s">
-        <v>55</v>
+        <v>244</v>
+      </c>
+      <c r="D66" s="1">
+        <v>6</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>58</v>
+        <v>241</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>59</v>
+        <v>245</v>
       </c>
       <c r="I66" s="83">
         <v>8</v>
@@ -5740,25 +5787,25 @@
         <v>155</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B67" s="33">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D67" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E67" s="1" t="s">
+      <c r="C67" s="97" t="s">
+        <v>280</v>
+      </c>
+      <c r="D67" s="101" t="s">
+        <v>45</v>
+      </c>
+      <c r="E67" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="F67" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>310</v>
+      <c r="F67" s="98" t="s">
+        <v>42</v>
+      </c>
+      <c r="G67" s="99" t="s">
+        <v>50</v>
       </c>
       <c r="I67" s="83">
         <v>9</v>
@@ -5791,25 +5838,25 @@
         <v>156</v>
       </c>
     </row>
-    <row r="68" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B68" s="33">
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D68" s="90" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F68" s="103" t="s">
-        <v>339</v>
+      <c r="F68" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>338</v>
+        <v>59</v>
       </c>
       <c r="I68" s="83">
         <v>10</v>
@@ -5848,7 +5895,7 @@
         <v>52</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D69" s="90" t="s">
         <v>56</v>
@@ -5857,10 +5904,10 @@
         <v>44</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>62</v>
+        <v>241</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I69" s="83">
         <v>11</v>
@@ -5893,25 +5940,25 @@
         <v>182</v>
       </c>
     </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B70" s="33">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="D70" s="1">
-        <v>5</v>
+        <v>289</v>
+      </c>
+      <c r="D70" s="90" t="s">
+        <v>56</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F70" s="2" t="s">
-        <v>64</v>
+      <c r="F70" s="103" t="s">
+        <v>339</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>60</v>
+        <v>338</v>
       </c>
       <c r="I70" s="83">
         <v>12</v>
@@ -5944,25 +5991,25 @@
         <v>189</v>
       </c>
     </row>
-    <row r="71" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B71" s="33">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="D71" s="101" t="s">
-        <v>20</v>
-      </c>
-      <c r="E71" s="102" t="s">
-        <v>284</v>
+        <v>290</v>
+      </c>
+      <c r="D71" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>241</v>
+        <v>62</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>233</v>
+        <v>311</v>
       </c>
       <c r="I71" s="80">
         <v>13</v>
@@ -6001,58 +6048,58 @@
         <v>55</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>203</v>
+        <v>292</v>
       </c>
       <c r="D72" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E72" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I72" s="136" t="s">
+        <v>105</v>
+      </c>
+      <c r="J72" s="137"/>
+      <c r="K72" s="138" t="s">
         <v>58</v>
       </c>
-      <c r="F72" s="114" t="s">
+      <c r="L72" s="139"/>
+      <c r="M72" s="140"/>
+      <c r="O72" s="136" t="s">
+        <v>105</v>
+      </c>
+      <c r="P72" s="137"/>
+      <c r="Q72" s="138" t="s">
+        <v>243</v>
+      </c>
+      <c r="R72" s="139"/>
+      <c r="S72" s="140"/>
+    </row>
+    <row r="73" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+      <c r="B73" s="33">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D73" s="101" t="s">
+        <v>20</v>
+      </c>
+      <c r="E73" s="102" t="s">
+        <v>284</v>
+      </c>
+      <c r="F73" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="G72" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="I72" s="123" t="s">
-        <v>105</v>
-      </c>
-      <c r="J72" s="124"/>
-      <c r="K72" s="125" t="s">
-        <v>58</v>
-      </c>
-      <c r="L72" s="126"/>
-      <c r="M72" s="127"/>
-      <c r="O72" s="123" t="s">
-        <v>105</v>
-      </c>
-      <c r="P72" s="124"/>
-      <c r="Q72" s="125" t="s">
-        <v>243</v>
-      </c>
-      <c r="R72" s="126"/>
-      <c r="S72" s="127"/>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B73" s="33">
-        <f t="shared" si="1"/>
-        <v>56</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D73" s="1">
-        <v>1</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>238</v>
-      </c>
       <c r="G73" s="5" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.3">
@@ -6061,7 +6108,7 @@
         <v>57</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D74" s="1">
         <v>1</v>
@@ -6073,7 +6120,7 @@
         <v>241</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.3">
@@ -6082,19 +6129,19 @@
         <v>58</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D75" s="90" t="s">
-        <v>20</v>
+        <v>201</v>
+      </c>
+      <c r="D75" s="1">
+        <v>1</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F75" s="111" t="s">
+        <v>58</v>
+      </c>
+      <c r="F75" s="2" t="s">
         <v>238</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.3">
@@ -6102,20 +6149,20 @@
         <f t="shared" si="1"/>
         <v>59</v>
       </c>
-      <c r="C76" s="112" t="s">
-        <v>209</v>
-      </c>
-      <c r="D76" s="113" t="s">
-        <v>20</v>
+      <c r="C76" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D76" s="1">
+        <v>1</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F76" s="111" t="s">
-        <v>238</v>
-      </c>
-      <c r="G76" s="112" t="s">
-        <v>211</v>
+        <v>58</v>
+      </c>
+      <c r="F76" s="114" t="s">
+        <v>241</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.3">
@@ -6124,19 +6171,19 @@
         <v>60</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="D77" s="1">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="D77" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>241</v>
+        <v>62</v>
+      </c>
+      <c r="F77" s="111" t="s">
+        <v>238</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.3">
@@ -6144,41 +6191,41 @@
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
-      <c r="C78" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D78" s="1">
-        <v>1</v>
+      <c r="C78" s="112" t="s">
+        <v>209</v>
+      </c>
+      <c r="D78" s="113" t="s">
+        <v>20</v>
       </c>
       <c r="E78" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F78" s="111" t="s">
+        <v>238</v>
+      </c>
+      <c r="G78" s="112" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B79" s="33">
+        <f t="shared" si="1"/>
+        <v>62</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D79" s="1">
+        <v>1</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F78" s="2" t="s">
+      <c r="F79" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="G78" s="5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="79" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B79" s="33">
-        <f t="shared" si="1"/>
-        <v>62</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="D79" s="101" t="s">
-        <v>46</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="G79" s="5" t="s">
-        <v>51</v>
+        <v>213</v>
       </c>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.3">
@@ -6187,7 +6234,7 @@
         <v>63</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D80" s="1">
         <v>1</v>
@@ -6196,31 +6243,31 @@
         <v>58</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>43</v>
+        <v>241</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B81" s="33">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D81" s="90" t="s">
-        <v>20</v>
+        <v>283</v>
+      </c>
+      <c r="D81" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F81" s="103" t="s">
-        <v>238</v>
+        <v>42</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>232</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>227</v>
+        <v>51</v>
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.3">
@@ -6228,41 +6275,41 @@
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
-      <c r="C82" s="97" t="s">
-        <v>191</v>
-      </c>
-      <c r="D82" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E82" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="F82" s="98" t="s">
-        <v>240</v>
-      </c>
-      <c r="G82" s="99" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="83" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="C82" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D82" s="1">
+        <v>1</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B83" s="33">
         <f t="shared" ref="B83:B114" si="2">IF(C83="","",B82+1)</f>
         <v>66</v>
       </c>
-      <c r="C83" s="93" t="s">
-        <v>281</v>
-      </c>
-      <c r="D83" s="94" t="s">
-        <v>21</v>
-      </c>
-      <c r="E83" s="92" t="s">
-        <v>35</v>
-      </c>
-      <c r="F83" s="95" t="s">
-        <v>74</v>
-      </c>
-      <c r="G83" s="96" t="s">
-        <v>37</v>
+      <c r="C83" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D83" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F83" s="103" t="s">
+        <v>238</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.3">
@@ -6270,62 +6317,62 @@
         <f t="shared" si="2"/>
         <v>67</v>
       </c>
-      <c r="C84" s="93" t="s">
+      <c r="C84" s="97" t="s">
+        <v>191</v>
+      </c>
+      <c r="D84" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E84" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="F84" s="98" t="s">
+        <v>240</v>
+      </c>
+      <c r="G84" s="99" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B85" s="33">
+        <f t="shared" si="2"/>
+        <v>68</v>
+      </c>
+      <c r="C85" s="93" t="s">
+        <v>281</v>
+      </c>
+      <c r="D85" s="94" t="s">
+        <v>21</v>
+      </c>
+      <c r="E85" s="92" t="s">
+        <v>35</v>
+      </c>
+      <c r="F85" s="95" t="s">
+        <v>74</v>
+      </c>
+      <c r="G85" s="96" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B86" s="33">
+        <f t="shared" si="2"/>
+        <v>69</v>
+      </c>
+      <c r="C86" s="93" t="s">
         <v>282</v>
       </c>
-      <c r="D84" s="92">
-        <v>1</v>
-      </c>
-      <c r="E84" s="92" t="s">
+      <c r="D86" s="92">
+        <v>1</v>
+      </c>
+      <c r="E86" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="F84" s="100" t="s">
+      <c r="F86" s="100" t="s">
         <v>11</v>
       </c>
-      <c r="G84" s="96" t="s">
+      <c r="G86" s="96" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B85" s="33">
-        <f t="shared" si="2"/>
-        <v>68</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="D85" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G85" s="5" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="86" spans="2:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="B86" s="33">
-        <f t="shared" si="2"/>
-        <v>69</v>
-      </c>
-      <c r="C86" s="104" t="s">
-        <v>260</v>
-      </c>
-      <c r="D86" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="E86" s="105" t="s">
-        <v>242</v>
-      </c>
-      <c r="F86" s="110" t="s">
-        <v>377</v>
-      </c>
-      <c r="G86" s="107" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.3">
@@ -6334,40 +6381,40 @@
         <v>70</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>315</v>
+        <v>342</v>
       </c>
       <c r="D87" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E87" s="103" t="s">
+        <v>21</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+      <c r="B88" s="33">
+        <f t="shared" si="2"/>
+        <v>71</v>
+      </c>
+      <c r="C88" s="104" t="s">
+        <v>260</v>
+      </c>
+      <c r="D88" s="109" t="s">
+        <v>20</v>
+      </c>
+      <c r="E88" s="105" t="s">
         <v>242</v>
       </c>
-      <c r="F87" s="103" t="s">
-        <v>243</v>
-      </c>
-      <c r="G87" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="88" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B88" s="33">
-        <f t="shared" si="2"/>
-        <v>71</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="D88" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E88" s="103" t="s">
-        <v>242</v>
-      </c>
-      <c r="F88" s="103" t="s">
-        <v>362</v>
-      </c>
-      <c r="G88" s="5" t="s">
-        <v>319</v>
+      <c r="F88" s="110" t="s">
+        <v>360</v>
+      </c>
+      <c r="G88" s="107" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.3">
@@ -6375,62 +6422,62 @@
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="C89" s="104" t="s">
-        <v>254</v>
-      </c>
-      <c r="D89" s="105">
-        <v>1</v>
-      </c>
-      <c r="E89" s="105" t="s">
+      <c r="C89" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D89" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E89" s="103" t="s">
         <v>242</v>
       </c>
-      <c r="F89" s="106" t="s">
-        <v>14</v>
-      </c>
-      <c r="G89" s="107" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="90" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F89" s="103" t="s">
+        <v>243</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B90" s="33">
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="D90" s="1">
-        <v>1</v>
-      </c>
-      <c r="E90" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D90" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E90" s="103" t="s">
         <v>242</v>
       </c>
-      <c r="F90" s="2" t="s">
-        <v>243</v>
+      <c r="F90" s="103" t="s">
+        <v>387</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="91" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B91" s="33">
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
-      <c r="C91" s="104" t="s">
-        <v>255</v>
-      </c>
-      <c r="D91" s="105">
-        <v>1</v>
-      </c>
-      <c r="E91" s="105" t="s">
+      <c r="C91" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D91" s="1">
+        <v>1</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="F91" s="108" t="s">
-        <v>73</v>
-      </c>
-      <c r="G91" s="107" t="s">
-        <v>257</v>
+      <c r="F91" s="103" t="s">
+        <v>348</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.3">
@@ -6438,20 +6485,20 @@
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="C92" s="112" t="s">
-        <v>264</v>
-      </c>
-      <c r="D92" s="113" t="s">
-        <v>20</v>
-      </c>
-      <c r="E92" s="111" t="s">
+      <c r="C92" s="104" t="s">
+        <v>254</v>
+      </c>
+      <c r="D92" s="105">
+        <v>1</v>
+      </c>
+      <c r="E92" s="105" t="s">
         <v>242</v>
       </c>
-      <c r="F92" s="118" t="s">
-        <v>355</v>
-      </c>
-      <c r="G92" s="112" t="s">
-        <v>265</v>
+      <c r="F92" s="106" t="s">
+        <v>14</v>
+      </c>
+      <c r="G92" s="107" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.3">
@@ -6460,19 +6507,19 @@
         <v>76</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>364</v>
+        <v>271</v>
       </c>
       <c r="D93" s="1">
         <v>1</v>
       </c>
-      <c r="E93" s="103" t="s">
+      <c r="E93" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="F93" s="103" t="s">
+      <c r="F93" s="2" t="s">
         <v>243</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>325</v>
+        <v>274</v>
       </c>
     </row>
     <row r="94" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6480,41 +6527,41 @@
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
-      <c r="C94" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="D94" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E94" s="1" t="s">
+      <c r="C94" s="104" t="s">
+        <v>255</v>
+      </c>
+      <c r="D94" s="105">
+        <v>1</v>
+      </c>
+      <c r="E94" s="105" t="s">
         <v>242</v>
       </c>
-      <c r="F94" s="103" t="s">
-        <v>359</v>
-      </c>
-      <c r="G94" s="5" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="95" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="F94" s="108" t="s">
+        <v>73</v>
+      </c>
+      <c r="G94" s="107" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B95" s="33">
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C95" s="112" t="s">
+        <v>264</v>
+      </c>
+      <c r="D95" s="113" t="s">
+        <v>20</v>
+      </c>
+      <c r="E95" s="111" t="s">
+        <v>242</v>
+      </c>
+      <c r="F95" s="143" t="s">
         <v>348</v>
       </c>
-      <c r="D95" s="1">
-        <v>1</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="F95" s="103" t="s">
-        <v>349</v>
-      </c>
-      <c r="G95" s="5" t="s">
-        <v>308</v>
+      <c r="G95" s="112" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.3">
@@ -6522,62 +6569,62 @@
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
-      <c r="C96" s="104" t="s">
-        <v>354</v>
-      </c>
-      <c r="D96" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="E96" s="117" t="s">
-        <v>355</v>
-      </c>
-      <c r="F96" s="106" t="s">
-        <v>17</v>
-      </c>
-      <c r="G96" s="107" t="s">
+      <c r="C96" s="3" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="97" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+      <c r="D96" s="1">
+        <v>1</v>
+      </c>
+      <c r="E96" s="103" t="s">
+        <v>242</v>
+      </c>
+      <c r="F96" s="103" t="s">
+        <v>243</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B97" s="33">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>276</v>
+        <v>340</v>
       </c>
       <c r="D97" s="90" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F97" s="103" t="s">
-        <v>381</v>
+        <v>352</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B98" s="33">
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="D98" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E98" s="103" t="s">
-        <v>243</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>64</v>
+        <v>345</v>
+      </c>
+      <c r="D98" s="1">
+        <v>1</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F98" s="103" t="s">
+        <v>346</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.3">
@@ -6585,20 +6632,20 @@
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
-      <c r="C99" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="D99" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E99" s="103" t="s">
-        <v>243</v>
-      </c>
-      <c r="F99" s="103" t="s">
-        <v>62</v>
-      </c>
-      <c r="G99" s="5" t="s">
-        <v>321</v>
+      <c r="C99" s="104" t="s">
+        <v>371</v>
+      </c>
+      <c r="D99" s="109" t="s">
+        <v>20</v>
+      </c>
+      <c r="E99" s="117" t="s">
+        <v>348</v>
+      </c>
+      <c r="F99" s="106" t="s">
+        <v>17</v>
+      </c>
+      <c r="G99" s="107" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.3">
@@ -6607,40 +6654,40 @@
         <v>83</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="D100" s="1">
-        <v>1</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>81</v>
+        <v>383</v>
+      </c>
+      <c r="D100" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>348</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="101" spans="2:7" x14ac:dyDescent="0.3">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B101" s="33">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="D101" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>62</v>
+        <v>243</v>
+      </c>
+      <c r="F101" s="103" t="s">
+        <v>392</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.3">
@@ -6649,10 +6696,10 @@
         <v>85</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="D102" s="1">
-        <v>1</v>
+        <v>317</v>
+      </c>
+      <c r="D102" s="90" t="s">
+        <v>56</v>
       </c>
       <c r="E102" s="103" t="s">
         <v>243</v>
@@ -6661,37 +6708,37 @@
         <v>64</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="103" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B103" s="33">
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="D103" s="90" t="s">
         <v>56</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="E103" s="103" t="s">
         <v>243</v>
       </c>
       <c r="F103" s="103" t="s">
-        <v>379</v>
+        <v>62</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="104" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B104" s="33">
         <f t="shared" si="2"/>
         <v>87</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>306</v>
+        <v>272</v>
       </c>
       <c r="D104" s="1">
         <v>1</v>
@@ -6699,37 +6746,95 @@
       <c r="E104" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F104" s="103" t="s">
-        <v>379</v>
+      <c r="F104" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="G104" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B105" s="33">
+        <f t="shared" si="2"/>
+        <v>88</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D105" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B106" s="33">
+        <f t="shared" si="2"/>
+        <v>89</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="D106" s="1">
+        <v>1</v>
+      </c>
+      <c r="E106" s="103" t="s">
+        <v>243</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G106" s="5" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B107" s="33">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D107" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="F107" s="103" t="s">
+        <v>362</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B108" s="33">
+        <f t="shared" si="2"/>
+        <v>91</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="D108" s="1">
+        <v>1</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F108" s="103" t="s">
+        <v>362</v>
+      </c>
+      <c r="G108" s="5" t="s">
         <v>309</v>
-      </c>
-    </row>
-    <row r="105" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B105" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="E105" s="102"/>
-    </row>
-    <row r="106" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B106" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="E106" s="102"/>
-    </row>
-    <row r="107" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B107" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="108" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B108" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
       </c>
     </row>
     <row r="109" spans="2:7" x14ac:dyDescent="0.3">
@@ -6931,39 +7036,51 @@
     </sortState>
   </autoFilter>
   <mergeCells count="102">
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="P44:R44"/>
+    <mergeCell ref="O56:P56"/>
+    <mergeCell ref="Q56:S56"/>
+    <mergeCell ref="P62:R62"/>
+    <mergeCell ref="P63:R63"/>
+    <mergeCell ref="P64:R64"/>
+    <mergeCell ref="O72:P72"/>
+    <mergeCell ref="Q72:S72"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="O59:P59"/>
+    <mergeCell ref="Q59:S59"/>
+    <mergeCell ref="O60:P60"/>
+    <mergeCell ref="Q60:S60"/>
+    <mergeCell ref="O61:P61"/>
+    <mergeCell ref="Q61:S61"/>
+    <mergeCell ref="P42:R42"/>
+    <mergeCell ref="P43:R43"/>
+    <mergeCell ref="O58:P58"/>
+    <mergeCell ref="Q58:S58"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="P22:R22"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:S18"/>
     <mergeCell ref="I72:J72"/>
     <mergeCell ref="K72:M72"/>
     <mergeCell ref="J57:L57"/>
@@ -6988,51 +7105,39 @@
     <mergeCell ref="K52:M52"/>
     <mergeCell ref="I40:J40"/>
     <mergeCell ref="K40:M40"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:S20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="O72:P72"/>
-    <mergeCell ref="Q72:S72"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="O59:P59"/>
-    <mergeCell ref="Q59:S59"/>
-    <mergeCell ref="O60:P60"/>
-    <mergeCell ref="Q60:S60"/>
-    <mergeCell ref="O61:P61"/>
-    <mergeCell ref="Q61:S61"/>
-    <mergeCell ref="P42:R42"/>
-    <mergeCell ref="P43:R43"/>
-    <mergeCell ref="O58:P58"/>
-    <mergeCell ref="Q58:S58"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="Q39:S39"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="Q41:S41"/>
-    <mergeCell ref="P22:R22"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="Q36:S36"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="P44:R44"/>
-    <mergeCell ref="O56:P56"/>
-    <mergeCell ref="Q56:S56"/>
-    <mergeCell ref="P62:R62"/>
-    <mergeCell ref="P63:R63"/>
-    <mergeCell ref="P64:R64"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Document/IDD.xlsx
+++ b/Document/IDD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\SoC_Design\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B27CCE0-E8C4-4047-BF55-54CB5B588EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC991E40-4640-4764-8153-C0DB49EDCA9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="402">
   <si>
     <t>top_cpu</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -334,6 +334,1268 @@
   <si>
     <t>o_d_mem_en
 o_d_mem_wren</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alu_ctr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alu
+u_mul_div_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALUOpB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALUOpA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alusrc_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_memtoreg_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Registers RDATA2 or Sign-Extend Constant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU Output</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU Carry Out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU Zero Out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_mul_div_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HIGH Register in MUL/DIV Unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOW Register in MUL/DIV Unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC ADDR + 4 or Branch ADDR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Control Input of Branch MUX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Port</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>input</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>output</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i_i0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i_i1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_o</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adder21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parameter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Input 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Input 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Output</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADDR Adder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>module</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_addr_4_adder, u_branch_addr_adder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>include</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>instruction.svh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>file</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adder.sv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alu.sv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i_in0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i_in1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i_carry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i_aluop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_carry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_zero</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU Input 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU Input 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carry In</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carry Out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alu_ctr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alu_ctr.sv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arithmetic Logic Unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU Control Unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i_funct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_aluop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FUNCT CODE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ctr_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ctr_unit.sv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Control Unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADDR WIDTH (1~32 Bit)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DATA_WIDTH {16Bit CPU : 16, 32Bit CPU : 32}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OCPODE_WIDTH 
+{16Bit CPU : 4, 32Bit CPU : 6}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i_opcode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_regdst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_alusrc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_memtoreg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_regwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_memread</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_memwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_branch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_jump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_sign_extend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AluSrc Flag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MemToreg Flag</t>
+  </si>
+  <si>
+    <t>Request to Arbiter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grant from Arbiter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>if_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IF-ID  PipeLine  Register</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i_pc_add4_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_pc_add4_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_i_mem_data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>negative reset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>from PC+4 ADDER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to ID_EX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to I-Decoder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id_ex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID-EX  PipeLine  Register</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>from IF_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i_regs_rdata1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i_regs_rdata2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i_sign_extend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_regs_rdata1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_regs_rdata2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to ?? Adder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>from Registers</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>from Sign-Extend Unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to ALU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to ALUSrc MUX &amp; EX_MEM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to ALUSrc MUX &amp; Branch Shift Left 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ex_mem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EX-MEM  PipeLine  Register</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i_branch_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i_zero</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i_alu_out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_branch_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_alu_out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>from Branch Adder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>from ALU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to Jump MUX ([Warning] Hazard)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Not Used ??</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mem_wb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MEM-WB  PipeLine  Register</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i_d_mem_rdata</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_d_mem_rdata</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to MemtoReg MUX Input (1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to MemtoReg MUX Input (0)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_if_add4_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC ADDR + 4 (IF)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_i_mem_data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I-MEM DATA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC ADDR + 4 (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC ADDR + 4 (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_aluop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_ctr_alusrc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_memtoreg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_regwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_memread</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_memwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_branch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_sign_extend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_reg_rdata1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_reg_rdata2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Registers RDATA1 (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Registers RDATA2 (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALUOpA (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegDst Flag (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALUSrc Flag (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MemtoReg Flag (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegWrite Flag (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MemRead Flag (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MemWrite Flag (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Branch Flag (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jump Flag (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SignExtend Flag (Zero or Sign) (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_reg_rdata1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_reg_rdata2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Registers RDATA1 (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Registers RDATA2 (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_sign_extend_const</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sign-Extend Constant (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sign-Extend Constant (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_sign_extend_const</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_ctr_alusrc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALUSrc Flag (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_jump_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jump ADDR (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_jump_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jump ADDR (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Branch ADDR (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bridge.sv</t>
+  </si>
+  <si>
+    <t>u_id_ex_bridge</t>
+  </si>
+  <si>
+    <t>u_if_id_bridge</t>
+  </si>
+  <si>
+    <t>u_if_id_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_id_ex_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_ex_mem_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_mem_wb_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_dec_funct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded FUNCT CODE (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_dec_funct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded FUNCT CODE (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_aluop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALUOpA (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_memread</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_memwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MemRead Flag (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MemWrite Flag (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_memread</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_memwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MemRead Flag (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MemWrite Flag (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_id_ex_bridge
+w_id_jump_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_branch_addr_adder
+u_branch_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_alu_out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_alu_out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU Output (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU Output (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_reg_rdata2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Registers RDATA2 (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_branch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Branch Flag (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_ctr_jump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jump Flag (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_memtoreg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_memtoreg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_memtoreg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MemtoReg Flag (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MemtoReg Flag (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MemtoReg Flag (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_alu_out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU Output (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_jump_mux_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Branch ADDR or Jump ADDR ([Warning] Hazard)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_dec_jaddr</t>
+  </si>
+  <si>
+    <t>w_if_i_mem_en</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_shift_left2_dec_jaddr</t>
+  </si>
+  <si>
+    <t>w_ex_shift_left2_sign_extend_const</t>
+  </si>
+  <si>
+    <t>w_ex_sign_extend_branch_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_branch_addr</t>
+  </si>
+  <si>
+    <t>w_id_dec_opcode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_dec_rs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_dec_rt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_dec_rd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_dec_shamt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_dec_const</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_alu_ctr</t>
+  </si>
+  <si>
+    <t>w_wb_memtoreg_mux_data</t>
+  </si>
+  <si>
+    <t>ALU Output or D-MEM RDATA ([Warning] Hazard)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_alusrc_mux_data</t>
+  </si>
+  <si>
+    <t>w_ex_alu_carry_out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_alu_zero</t>
+  </si>
+  <si>
+    <t>w_ex_hi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_lo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_branch_mux_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_branch
+w_ex_alu_zero</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_ctr_branch</t>
+  </si>
+  <si>
+    <t>w_ex_regwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_regwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegWrite Flag (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegWrite Flag (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegWrite Flag (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rd Register (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rt Register (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_dec_rt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_dec_rd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_dec_rt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_dec_rd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_dec_rt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_dec_rd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rd Register (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rt Register (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rd Register (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rt Register (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rd Register (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_ctr_regdst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegDst Flag (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegDst Flag (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegDst Flag (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_regdst_mux_reg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rt or rd Register (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>top파일 복붙용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시작위치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>끝위치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>추출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>엑셀 복붙용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름
+바뀐거
+찾기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안적은거
+찾기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_dec_rs</t>
+  </si>
+  <si>
+    <t>Decoded rs Register (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decoded rs Register (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_registers
+u_id_ex_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_regdst_mux_reg</t>
+  </si>
+  <si>
+    <t>rt or rd Register (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_if_pc_mux_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_pc_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I-MEM RADDR (Next)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_regwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_mem_wb_bridge
+u_alu_forwarding_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alu_src_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_wdata_forward_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WDATA Forward MUX Data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_regdst_mux_reg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rt or rd Register (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alu_forwarding_unit
+u_mem_wb_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_ex_mem_bridge
+u_regdst_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_ex_mem_bridge
+u_alu_forwarding_unit
+u_regdst_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_regdst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_regdst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_regdst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alu_forward_a_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alu_forward_b_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_mem_wb_bridge
+o_d_mem_addr
+u_alu_forward_a_mux
+u_alu_forward_b_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alu_forwarding_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_registers
+u_wdata_forwarding_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_fw_ctr_wdata_2c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_wdata_forwarding_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_fw_ctr_wdata_2c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_fw_ctr_alu_a_1c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_fw_ctr_alu_b_1c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_fw_ctr_alu_a_2c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_fw_ctr_alu_b_2c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_fw_ctr_wdata_1c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_wdata_fw_mux_data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_alu_fw_mux_data_a</t>
+  </si>
+  <si>
+    <t>fwA MUX Data</t>
+  </si>
+  <si>
+    <t>w_ex_alu_fw_mux_data_b</t>
+  </si>
+  <si>
+    <t>fwB MUX Data</t>
+  </si>
+  <si>
+    <t>ALU fwA Output (1 Cycle)</t>
+  </si>
+  <si>
+    <t>ALU fwB Output (1 Cycle)</t>
+  </si>
+  <si>
+    <t>ALU fwA Output (2 Cycle)</t>
+  </si>
+  <si>
+    <t>ALU fwB Output (2 Cycle)</t>
+  </si>
+  <si>
+    <t>WDATA fw Output (1 Cycle)</t>
+  </si>
+  <si>
+    <t>WDATA fw Output (2 Cycle) (EX)</t>
+  </si>
+  <si>
+    <t>WDATA fw Output (2 Cycle) (MEM)</t>
+  </si>
+  <si>
+    <t>w_mem_wdata_fw_mux_data_2c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alu_forwarding_unit</t>
+  </si>
+  <si>
+    <t>u_alu_forward_a_mux</t>
+  </si>
+  <si>
+    <t>u_alu_forward_b_mux</t>
+  </si>
+  <si>
+    <t>u_mem_wb_bridge
+u_wdata_forwarding_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_wdata_forward_2cycle_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_ex_mem_bridge
+u_wdata_forward_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_ex_mem_bridge
+u_wdata_forward_2cycle_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alu_forward_b_mux
+u_ex_mem_bridge
+u_wdata_forward_2cycle_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_memtoreg_mux
+u_wdata_forward_mux
+u_wdata_forward_2cycle_mux
+u_alu_forward_a_mux
+u_alu_forward_b_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_wdata_fw_mux_data_2c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WDATA Forward MUX Data (2 Cylce) (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WDATA Forward MUX Data (2 Cylce) (MEM)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -353,1289 +1615,65 @@
       </rPr>
       <t>o_i_mem_addr</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_alu_ctr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_alu
-u_mul_div_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALUOpB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALUOpA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_alu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_alusrc_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_memtoreg_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Registers RDATA2 or Sign-Extend Constant</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU Output</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU Carry Out</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU Zero Out</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_mul_div_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HIGH Register in MUL/DIV Unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LOW Register in MUL/DIV Unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PC ADDR + 4 or Branch ADDR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Control Input of Branch MUX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Port</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>input</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>output</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i_i0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i_i1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_o</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>adder21</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Parameter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Input 0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Input 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Output</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ADDR Adder</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>module</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>alu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Instance</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_addr_4_adder, u_branch_addr_adder</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>include</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>instruction.svh</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>file</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>adder.sv</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>alu.sv</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i_in0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i_in1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i_carry</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i_aluop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_out</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_carry</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_zero</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU Input 0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU Input 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Carry In</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Carry Out</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>alu_ctr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>alu_ctr.sv</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Arithmetic Logic Unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU Control Unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i_funct</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_aluop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FUNCT CODE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ctr_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ctr_unit.sv</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Control Unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ADDR WIDTH (1~32 Bit)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DATA_WIDTH {16Bit CPU : 16, 32Bit CPU : 32}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OCPODE_WIDTH 
-{16Bit CPU : 4, 32Bit CPU : 6}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i_opcode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_regdst</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_alusrc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_memtoreg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_regwrite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_memread</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_memwrite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_branch</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_jump</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_sign_extend</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AluSrc Flag</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MemToreg Flag</t>
-  </si>
-  <si>
-    <t>Request to Arbiter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Grant from Arbiter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>if_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IF-ID  PipeLine  Register</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i_pc_add4_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_pc_add4_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_i_mem_data</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>clock</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>negative reset</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>from PC+4 ADDER</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>to ID_EX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>to I-Decoder</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>id_ex</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID-EX  PipeLine  Register</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>from IF_ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i_regs_rdata1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i_regs_rdata2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i_sign_extend</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_regs_rdata1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_regs_rdata2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>to ?? Adder</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>from Registers</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>from Sign-Extend Unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>to ALU</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>to ALUSrc MUX &amp; EX_MEM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>to ALUSrc MUX &amp; Branch Shift Left 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ex_mem</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EX-MEM  PipeLine  Register</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i_branch_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i_zero</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i_alu_out</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_branch_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_alu_out</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>from Branch Adder</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>from ALU</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>to Jump MUX ([Warning] Hazard)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Not Used ??</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mem_wb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MEM-WB  PipeLine  Register</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i_d_mem_rdata</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_d_mem_rdata</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>to MemtoReg MUX Input (1)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>to MemtoReg MUX Input (0)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_if_add4_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PC ADDR + 4 (IF)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_i_mem_data</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I-MEM DATA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PC ADDR + 4 (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_add4_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_add4_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PC ADDR + 4 (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_aluop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_ctr_alusrc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_memtoreg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_regwrite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_memread</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_memwrite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_branch</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_ctr_jump</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_sign_extend</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_reg_rdata1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_reg_rdata2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Registers RDATA1 (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Registers RDATA2 (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALUOpA (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RegDst Flag (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALUSrc Flag (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MemtoReg Flag (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RegWrite Flag (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MemRead Flag (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MemWrite Flag (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Branch Flag (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Jump Flag (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SignExtend Flag (Zero or Sign) (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_reg_rdata1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_reg_rdata2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Registers RDATA1 (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Registers RDATA2 (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_sign_extend_const</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sign-Extend Constant (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sign-Extend Constant (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_sign_extend_const</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_ctr_alusrc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALUSrc Flag (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_jump_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Jump ADDR (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_jump_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Jump ADDR (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Branch ADDR (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bridge.sv</t>
-  </si>
-  <si>
-    <t>u_id_ex_bridge</t>
-  </si>
-  <si>
-    <t>u_if_id_bridge</t>
-  </si>
-  <si>
-    <t>u_if_id_bridge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_id_ex_bridge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_ex_mem_bridge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_mem_wb_bridge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_dec_funct</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded FUNCT CODE (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_dec_funct</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded FUNCT CODE (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_aluop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALUOpA (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_memread</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_memwrite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MemRead Flag (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MemWrite Flag (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_memread</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_memwrite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MemRead Flag (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MemWrite Flag (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_id_ex_bridge
-w_id_jump_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_branch_addr_adder
-u_branch_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_alu_out</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_alu_out</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU Output (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU Output (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_reg_rdata2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Registers RDATA2 (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_branch</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Branch Flag (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_ctr_jump</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Jump Flag (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_memtoreg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_memtoreg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_memtoreg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MemtoReg Flag (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MemtoReg Flag (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MemtoReg Flag (WB)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_alu_out</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU Output (WB)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_jump_mux_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Branch ADDR or Jump ADDR ([Warning] Hazard)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_dec_jaddr</t>
-  </si>
-  <si>
-    <t>w_if_i_mem_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_if_i_mem_en</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_shift_left2_dec_jaddr</t>
-  </si>
-  <si>
-    <t>w_id_add4_addr
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+u_if_id_bridge</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_jump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_ctr_branch
+w_ex_ctr_jump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instruction Flush Signal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_pc_mux
+u_id_ex_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_pc_addr</t>
+  </si>
+  <si>
+    <t>w_id_pc_addr
 w_id_shift_left2_dec_jaddr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_shift_left2_sign_extend_const</t>
-  </si>
-  <si>
-    <t>w_ex_sign_extend_branch_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_branch_addr</t>
-  </si>
-  <si>
-    <t>w_id_dec_opcode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_dec_rs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_dec_rt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_dec_rd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_dec_shamt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_dec_const</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_alu_ctr</t>
-  </si>
-  <si>
-    <t>w_wb_memtoreg_mux_data</t>
-  </si>
-  <si>
-    <t>ALU Output or D-MEM RDATA ([Warning] Hazard)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_alusrc_mux_data</t>
-  </si>
-  <si>
-    <t>w_ex_alu_carry_out</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_alu_zero</t>
-  </si>
-  <si>
-    <t>w_ex_hi</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_lo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_branch_mux_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_branch
-w_ex_alu_zero</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_ctr_branch</t>
-  </si>
-  <si>
-    <t>w_ex_regwrite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_regwrite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RegWrite Flag (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RegWrite Flag (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RegWrite Flag (WB)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded rd Register (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded rt Register (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_dec_rt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_dec_rd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_dec_rt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_dec_rd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_dec_rt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_dec_rd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded rd Register (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded rt Register (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded rd Register (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded rt Register (WB)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded rd Register (WB)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_ctr_regdst</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RegDst Flag (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RegDst Flag (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RegDst Flag (WB)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_regdst_mux_reg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rt or rd Register (WB)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>top파일 복붙용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>시작위치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>끝위치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>추출</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>엑셀 복붙용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이름
-바뀐거
-찾기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>안적은거
-찾기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_dec_rs</t>
-  </si>
-  <si>
-    <t>Decoded rs Register (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded rs Register (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_registers
-u_id_ex_bridge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_regdst_mux_reg</t>
-  </si>
-  <si>
-    <t>rt or rd Register (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_if_pc_mux_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_pc_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I-MEM RADDR (Next)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_regwrite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_mem_wb_bridge
-u_alu_forwarding_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_alu_src_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_wdata_forward_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WDATA Forward MUX Data</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_regdst_mux_reg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rt or rd Register (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_alu_forwarding_unit
-u_mem_wb_bridge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_ex_mem_bridge
-u_regdst_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_ex_mem_bridge
-u_alu_forwarding_unit
-u_regdst_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_regdst</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_regdst</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_regdst</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_alu_forward_a_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_alu_forward_b_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_mem_wb_bridge
-o_d_mem_addr
-u_alu_forward_a_mux
-u_alu_forward_b_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_alu_forwarding_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_registers
-u_wdata_forwarding_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_fw_ctr_wdata_2c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_wdata_forwarding_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_fw_ctr_wdata_2c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_fw_ctr_alu_a_1c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_fw_ctr_alu_b_1c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_fw_ctr_alu_a_2c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_fw_ctr_alu_b_2c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_fw_ctr_wdata_1c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_wdata_fw_mux_data</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_alu_fw_mux_data_a</t>
-  </si>
-  <si>
-    <t>fwA MUX Data</t>
-  </si>
-  <si>
-    <t>w_ex_alu_fw_mux_data_b</t>
-  </si>
-  <si>
-    <t>fwB MUX Data</t>
-  </si>
-  <si>
-    <t>ALU fwA Output (1 Cycle)</t>
-  </si>
-  <si>
-    <t>ALU fwB Output (1 Cycle)</t>
-  </si>
-  <si>
-    <t>ALU fwA Output (2 Cycle)</t>
-  </si>
-  <si>
-    <t>ALU fwB Output (2 Cycle)</t>
-  </si>
-  <si>
-    <t>WDATA fw Output (1 Cycle)</t>
-  </si>
-  <si>
-    <t>WDATA fw Output (2 Cycle) (EX)</t>
-  </si>
-  <si>
-    <t>WDATA fw Output (2 Cycle) (MEM)</t>
-  </si>
-  <si>
-    <t>w_mem_wdata_fw_mux_data_2c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_alu_forwarding_unit</t>
-  </si>
-  <si>
-    <t>u_alu_forward_a_mux</t>
-  </si>
-  <si>
-    <t>u_alu_forward_b_mux</t>
-  </si>
-  <si>
-    <t>u_mem_wb_bridge
-u_wdata_forwarding_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_wdata_forward_2cycle_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_ex_mem_bridge
-u_wdata_forward_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_ex_mem_bridge
-u_wdata_forward_2cycle_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_alu_forward_b_mux
-u_ex_mem_bridge
-u_wdata_forward_2cycle_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_memtoreg_mux
-u_wdata_forward_mux
-u_wdata_forward_2cycle_mux
-u_alu_forward_a_mux
-u_alu_forward_b_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_wdata_fw_mux_data_2c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WDATA Forward MUX Data (2 Cylce) (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WDATA Forward MUX Data (2 Cylce) (MEM)</t>
+  </si>
+  <si>
+    <t>w_if_i_pc_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_pc_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_branch_mux
+w_ex_flush</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_jump_mux
+w_ex_flush</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_flush</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2616,83 +2654,83 @@
     <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3054,32 +3092,32 @@
   <sheetData>
     <row r="1" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="132" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="133"/>
-      <c r="G2" s="134"/>
-      <c r="I2" s="118" t="s">
-        <v>103</v>
-      </c>
-      <c r="J2" s="120"/>
-      <c r="K2" s="118" t="s">
-        <v>97</v>
-      </c>
-      <c r="L2" s="119"/>
-      <c r="M2" s="120"/>
-      <c r="O2" s="118" t="s">
-        <v>103</v>
-      </c>
-      <c r="P2" s="120"/>
-      <c r="Q2" s="118" t="s">
-        <v>150</v>
-      </c>
-      <c r="R2" s="119"/>
-      <c r="S2" s="120"/>
+      <c r="B2" s="141" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="142"/>
+      <c r="G2" s="143"/>
+      <c r="I2" s="120" t="s">
+        <v>102</v>
+      </c>
+      <c r="J2" s="121"/>
+      <c r="K2" s="120" t="s">
+        <v>96</v>
+      </c>
+      <c r="L2" s="122"/>
+      <c r="M2" s="121"/>
+      <c r="O2" s="120" t="s">
+        <v>102</v>
+      </c>
+      <c r="P2" s="121"/>
+      <c r="Q2" s="120" t="s">
+        <v>149</v>
+      </c>
+      <c r="R2" s="122"/>
+      <c r="S2" s="121"/>
     </row>
     <row r="3" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="34" t="s">
@@ -3100,24 +3138,24 @@
       <c r="G3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="127" t="s">
+      <c r="I3" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="J3" s="131"/>
+      <c r="K3" s="132" t="s">
         <v>109</v>
       </c>
-      <c r="J3" s="128"/>
-      <c r="K3" s="129" t="s">
-        <v>110</v>
-      </c>
-      <c r="L3" s="130"/>
-      <c r="M3" s="131"/>
-      <c r="O3" s="127" t="s">
-        <v>109</v>
-      </c>
-      <c r="P3" s="128"/>
-      <c r="Q3" s="129" t="s">
-        <v>237</v>
-      </c>
-      <c r="R3" s="130"/>
-      <c r="S3" s="131"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="134"/>
+      <c r="O3" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="P3" s="131"/>
+      <c r="Q3" s="132" t="s">
+        <v>233</v>
+      </c>
+      <c r="R3" s="133"/>
+      <c r="S3" s="134"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B4" s="35">
@@ -3138,24 +3176,24 @@
       <c r="G4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="127" t="s">
-        <v>107</v>
-      </c>
-      <c r="J4" s="128"/>
-      <c r="K4" s="127" t="s">
+      <c r="I4" s="130" t="s">
+        <v>106</v>
+      </c>
+      <c r="J4" s="131"/>
+      <c r="K4" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="L4" s="141"/>
-      <c r="M4" s="128"/>
-      <c r="O4" s="127" t="s">
-        <v>107</v>
-      </c>
-      <c r="P4" s="128"/>
-      <c r="Q4" s="127" t="s">
+      <c r="L4" s="135"/>
+      <c r="M4" s="131"/>
+      <c r="O4" s="130" t="s">
+        <v>106</v>
+      </c>
+      <c r="P4" s="131"/>
+      <c r="Q4" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="R4" s="141"/>
-      <c r="S4" s="128"/>
+      <c r="R4" s="135"/>
+      <c r="S4" s="131"/>
     </row>
     <row r="5" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="54">
@@ -3176,24 +3214,24 @@
       <c r="G5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="121" t="s">
+      <c r="I5" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="122"/>
-      <c r="K5" s="123" t="s">
-        <v>102</v>
-      </c>
-      <c r="L5" s="124"/>
-      <c r="M5" s="125"/>
-      <c r="O5" s="121" t="s">
+      <c r="J5" s="137"/>
+      <c r="K5" s="138" t="s">
+        <v>101</v>
+      </c>
+      <c r="L5" s="119"/>
+      <c r="M5" s="139"/>
+      <c r="O5" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="122"/>
-      <c r="Q5" s="123" t="s">
-        <v>151</v>
-      </c>
-      <c r="R5" s="124"/>
-      <c r="S5" s="125"/>
+      <c r="P5" s="137"/>
+      <c r="Q5" s="138" t="s">
+        <v>150</v>
+      </c>
+      <c r="R5" s="119"/>
+      <c r="S5" s="139"/>
     </row>
     <row r="6" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="55">
@@ -3217,22 +3255,22 @@
       <c r="I6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="126" t="s">
-        <v>98</v>
-      </c>
-      <c r="K6" s="126"/>
-      <c r="L6" s="126"/>
+      <c r="J6" s="128" t="s">
+        <v>97</v>
+      </c>
+      <c r="K6" s="128"/>
+      <c r="L6" s="128"/>
       <c r="M6" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="126" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q6" s="126"/>
-      <c r="R6" s="126"/>
+      <c r="P6" s="128" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q6" s="128"/>
+      <c r="R6" s="128"/>
       <c r="S6" s="69" t="s">
         <v>8</v>
       </c>
@@ -3259,24 +3297,24 @@
       <c r="I7" s="70">
         <v>1</v>
       </c>
-      <c r="J7" s="135" t="s">
+      <c r="J7" s="140" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="135"/>
-      <c r="L7" s="135"/>
+      <c r="K7" s="140"/>
+      <c r="L7" s="140"/>
       <c r="M7" s="71" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O7" s="87">
         <v>1</v>
       </c>
-      <c r="P7" s="142" t="s">
+      <c r="P7" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="Q7" s="142"/>
-      <c r="R7" s="142"/>
+      <c r="Q7" s="129"/>
+      <c r="R7" s="129"/>
       <c r="S7" s="88" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3302,7 +3340,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="68" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K8" s="68" t="s">
         <v>1</v>
@@ -3316,13 +3354,13 @@
       <c r="O8" s="80">
         <v>2</v>
       </c>
-      <c r="P8" s="124" t="s">
+      <c r="P8" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="124"/>
-      <c r="R8" s="124"/>
+      <c r="Q8" s="119"/>
+      <c r="R8" s="119"/>
       <c r="S8" s="82" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3348,22 +3386,22 @@
         <v>1</v>
       </c>
       <c r="J9" s="73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K9" s="73" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L9" s="74" t="s">
         <v>21</v>
       </c>
       <c r="M9" s="75" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O9" s="67" t="s">
         <v>41</v>
       </c>
       <c r="P9" s="68" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q9" s="68" t="s">
         <v>1</v>
@@ -3398,22 +3436,22 @@
         <v>2</v>
       </c>
       <c r="J10" s="77" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K10" s="77" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L10" s="78" t="s">
         <v>21</v>
       </c>
       <c r="M10" s="79" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O10" s="72">
         <v>1</v>
       </c>
       <c r="P10" s="73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q10" s="73" t="s">
         <v>5</v>
@@ -3422,7 +3460,7 @@
         <v>1</v>
       </c>
       <c r="S10" s="75" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3448,22 +3486,22 @@
         <v>3</v>
       </c>
       <c r="J11" s="66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K11" s="66" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L11" s="81" t="s">
         <v>21</v>
       </c>
       <c r="M11" s="82" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O11" s="72">
         <v>2</v>
       </c>
       <c r="P11" s="73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q11" s="73" t="s">
         <v>6</v>
@@ -3472,7 +3510,7 @@
         <v>1</v>
       </c>
       <c r="S11" s="75" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3494,29 +3532,29 @@
       <c r="G12" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="136" t="s">
+      <c r="I12" s="123" t="s">
+        <v>104</v>
+      </c>
+      <c r="J12" s="124"/>
+      <c r="K12" s="125" t="s">
         <v>105</v>
       </c>
-      <c r="J12" s="137"/>
-      <c r="K12" s="138" t="s">
-        <v>106</v>
-      </c>
-      <c r="L12" s="139"/>
-      <c r="M12" s="140"/>
+      <c r="L12" s="126"/>
+      <c r="M12" s="127"/>
       <c r="O12" s="72">
         <v>3</v>
       </c>
       <c r="P12" s="73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q12" s="73" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="R12" s="74" t="s">
         <v>21</v>
       </c>
       <c r="S12" s="75" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3542,7 +3580,7 @@
         <v>4</v>
       </c>
       <c r="P13" s="73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q13" s="73" t="s">
         <v>10</v>
@@ -3577,16 +3615,16 @@
         <v>5</v>
       </c>
       <c r="P14" s="77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q14" s="73" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="R14" s="74" t="s">
         <v>21</v>
       </c>
       <c r="S14" s="79" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3612,28 +3650,28 @@
         <v>6</v>
       </c>
       <c r="P15" s="66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q15" s="73" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="R15" s="74" t="s">
         <v>20</v>
       </c>
       <c r="S15" s="82" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="O16" s="136" t="s">
-        <v>105</v>
-      </c>
-      <c r="P16" s="137"/>
-      <c r="Q16" s="138" t="s">
-        <v>240</v>
-      </c>
-      <c r="R16" s="139"/>
-      <c r="S16" s="140"/>
+      <c r="O16" s="123" t="s">
+        <v>104</v>
+      </c>
+      <c r="P16" s="124"/>
+      <c r="Q16" s="125" t="s">
+        <v>236</v>
+      </c>
+      <c r="R16" s="126"/>
+      <c r="S16" s="127"/>
     </row>
     <row r="17" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="90" t="s">
@@ -3661,38 +3699,38 @@
         <v>1</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>196</v>
+        <v>398</v>
       </c>
       <c r="D18" s="90" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F18" s="103" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="G18" s="99" t="s">
-        <v>198</v>
-      </c>
-      <c r="I18" s="118" t="s">
+        <v>195</v>
+      </c>
+      <c r="I18" s="120" t="s">
+        <v>102</v>
+      </c>
+      <c r="J18" s="121"/>
+      <c r="K18" s="120" t="s">
         <v>103</v>
       </c>
-      <c r="J18" s="120"/>
-      <c r="K18" s="118" t="s">
-        <v>104</v>
-      </c>
-      <c r="L18" s="119"/>
-      <c r="M18" s="120"/>
-      <c r="O18" s="118" t="s">
-        <v>103</v>
-      </c>
-      <c r="P18" s="120"/>
-      <c r="Q18" s="118" t="s">
-        <v>160</v>
-      </c>
-      <c r="R18" s="119"/>
-      <c r="S18" s="120"/>
+      <c r="L18" s="122"/>
+      <c r="M18" s="121"/>
+      <c r="O18" s="120" t="s">
+        <v>102</v>
+      </c>
+      <c r="P18" s="121"/>
+      <c r="Q18" s="120" t="s">
+        <v>159</v>
+      </c>
+      <c r="R18" s="122"/>
+      <c r="S18" s="121"/>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B19" s="33">
@@ -3700,38 +3738,38 @@
         <v>2</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="D19" s="1">
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>64</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I19" s="127" t="s">
-        <v>109</v>
-      </c>
-      <c r="J19" s="128"/>
-      <c r="K19" s="129" t="s">
-        <v>111</v>
-      </c>
-      <c r="L19" s="130"/>
-      <c r="M19" s="131"/>
-      <c r="O19" s="127" t="s">
-        <v>109</v>
-      </c>
-      <c r="P19" s="128"/>
-      <c r="Q19" s="129" t="s">
-        <v>237</v>
-      </c>
-      <c r="R19" s="130"/>
-      <c r="S19" s="131"/>
+        <v>83</v>
+      </c>
+      <c r="I19" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="J19" s="131"/>
+      <c r="K19" s="132" t="s">
+        <v>110</v>
+      </c>
+      <c r="L19" s="133"/>
+      <c r="M19" s="134"/>
+      <c r="O19" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="P19" s="131"/>
+      <c r="Q19" s="132" t="s">
+        <v>233</v>
+      </c>
+      <c r="R19" s="133"/>
+      <c r="S19" s="134"/>
     </row>
     <row r="20" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B20" s="33">
@@ -3739,38 +3777,38 @@
         <v>3</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D20" s="1">
         <v>4</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="F20" s="103" t="s">
+      <c r="G20" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I20" s="127" t="s">
+      <c r="I20" s="130" t="s">
+        <v>106</v>
+      </c>
+      <c r="J20" s="131"/>
+      <c r="K20" s="132" t="s">
         <v>107</v>
       </c>
-      <c r="J20" s="128"/>
-      <c r="K20" s="129" t="s">
-        <v>108</v>
-      </c>
-      <c r="L20" s="130"/>
-      <c r="M20" s="131"/>
-      <c r="O20" s="127" t="s">
-        <v>107</v>
-      </c>
-      <c r="P20" s="128"/>
-      <c r="Q20" s="127" t="s">
+      <c r="L20" s="133"/>
+      <c r="M20" s="134"/>
+      <c r="O20" s="130" t="s">
+        <v>106</v>
+      </c>
+      <c r="P20" s="131"/>
+      <c r="Q20" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="R20" s="141"/>
-      <c r="S20" s="128"/>
+      <c r="R20" s="135"/>
+      <c r="S20" s="131"/>
     </row>
     <row r="21" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="33">
@@ -3778,38 +3816,38 @@
         <v>4</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="D21" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="F21" s="103" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="I21" s="121" t="s">
+        <v>367</v>
+      </c>
+      <c r="I21" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="122"/>
-      <c r="K21" s="123" t="s">
-        <v>125</v>
-      </c>
-      <c r="L21" s="124"/>
-      <c r="M21" s="125"/>
-      <c r="O21" s="121" t="s">
+      <c r="J21" s="137"/>
+      <c r="K21" s="138" t="s">
+        <v>124</v>
+      </c>
+      <c r="L21" s="119"/>
+      <c r="M21" s="139"/>
+      <c r="O21" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="122"/>
-      <c r="Q21" s="123" t="s">
-        <v>161</v>
-      </c>
-      <c r="R21" s="124"/>
-      <c r="S21" s="125"/>
+      <c r="P21" s="137"/>
+      <c r="Q21" s="138" t="s">
+        <v>160</v>
+      </c>
+      <c r="R21" s="119"/>
+      <c r="S21" s="139"/>
     </row>
     <row r="22" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="33">
@@ -3817,39 +3855,39 @@
         <v>5</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="D22" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="F22" s="103" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="I22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J22" s="126" t="s">
-        <v>98</v>
-      </c>
-      <c r="K22" s="126"/>
-      <c r="L22" s="126"/>
+      <c r="J22" s="128" t="s">
+        <v>97</v>
+      </c>
+      <c r="K22" s="128"/>
+      <c r="L22" s="128"/>
       <c r="M22" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P22" s="126" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q22" s="126"/>
-      <c r="R22" s="126"/>
+      <c r="P22" s="128" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q22" s="128"/>
+      <c r="R22" s="128"/>
       <c r="S22" s="69" t="s">
         <v>8</v>
       </c>
@@ -3860,41 +3898,41 @@
         <v>6</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D23" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F23" s="103" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I23" s="70">
         <v>1</v>
       </c>
-      <c r="J23" s="135" t="s">
+      <c r="J23" s="140" t="s">
         <v>20</v>
       </c>
-      <c r="K23" s="135"/>
-      <c r="L23" s="135"/>
+      <c r="K23" s="140"/>
+      <c r="L23" s="140"/>
       <c r="M23" s="71" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O23" s="87">
         <v>1</v>
       </c>
-      <c r="P23" s="142" t="s">
+      <c r="P23" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="Q23" s="142"/>
-      <c r="R23" s="142"/>
+      <c r="Q23" s="129"/>
+      <c r="R23" s="129"/>
       <c r="S23" s="88" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3903,25 +3941,25 @@
         <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I24" s="67" t="s">
         <v>41</v>
       </c>
       <c r="J24" s="68" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K24" s="68" t="s">
         <v>1</v>
@@ -3935,13 +3973,13 @@
       <c r="O24" s="80">
         <v>2</v>
       </c>
-      <c r="P24" s="124" t="s">
+      <c r="P24" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="Q24" s="124"/>
-      <c r="R24" s="124"/>
+      <c r="Q24" s="119"/>
+      <c r="R24" s="119"/>
       <c r="S24" s="82" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3950,40 +3988,40 @@
         <v>8</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D25" s="1">
         <v>3</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="I25" s="72">
         <v>1</v>
       </c>
       <c r="J25" s="73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K25" s="73" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L25" s="74" t="s">
         <v>20</v>
       </c>
       <c r="M25" s="75" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O25" s="67" t="s">
         <v>41</v>
       </c>
       <c r="P25" s="68" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q25" s="68" t="s">
         <v>1</v>
@@ -4001,40 +4039,40 @@
         <v>9</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="D26" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F26" s="103" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I26" s="76">
         <v>2</v>
       </c>
       <c r="J26" s="77" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K26" s="77" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L26" s="78" t="s">
         <v>20</v>
       </c>
       <c r="M26" s="79" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O26" s="72">
         <v>1</v>
       </c>
       <c r="P26" s="73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q26" s="73" t="s">
         <v>5</v>
@@ -4043,7 +4081,7 @@
         <v>1</v>
       </c>
       <c r="S26" s="75" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.3">
@@ -4052,40 +4090,40 @@
         <v>10</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D27" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="I27" s="83">
         <v>3</v>
       </c>
       <c r="J27" s="77" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K27" s="84" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L27" s="84">
         <v>1</v>
       </c>
       <c r="M27" s="85" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O27" s="72">
         <v>2</v>
       </c>
       <c r="P27" s="73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q27" s="73" t="s">
         <v>6</v>
@@ -4094,7 +4132,7 @@
         <v>1</v>
       </c>
       <c r="S27" s="75" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="2:19" x14ac:dyDescent="0.3">
@@ -4103,7 +4141,7 @@
         <v>11</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="D28" s="90" t="s">
         <v>20</v>
@@ -4115,37 +4153,37 @@
         <v>53</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="I28" s="83">
         <v>4</v>
       </c>
       <c r="J28" s="84" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K28" s="84" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L28" s="84">
         <v>4</v>
       </c>
       <c r="M28" s="85" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O28" s="83">
         <v>3</v>
       </c>
       <c r="P28" s="73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q28" s="73" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="R28" s="74" t="s">
         <v>21</v>
       </c>
       <c r="S28" s="75" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="2:19" x14ac:dyDescent="0.3">
@@ -4154,7 +4192,7 @@
         <v>12</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="D29" s="90" t="s">
         <v>21</v>
@@ -4166,37 +4204,37 @@
         <v>36</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I29" s="83">
         <v>5</v>
       </c>
       <c r="J29" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K29" s="84" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L29" s="86" t="s">
         <v>20</v>
       </c>
       <c r="M29" s="85" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O29" s="83">
         <v>4</v>
       </c>
       <c r="P29" s="77" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q29" s="84" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R29" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S29" s="85" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="2:19" x14ac:dyDescent="0.3">
@@ -4205,49 +4243,49 @@
         <v>13</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D30" s="1">
         <v>1</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I30" s="83">
         <v>6</v>
       </c>
       <c r="J30" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K30" s="84" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L30" s="84">
         <v>1</v>
       </c>
       <c r="M30" s="85" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O30" s="83">
         <v>5</v>
       </c>
       <c r="P30" s="77" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q30" s="84" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R30" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S30" s="85" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -4256,94 +4294,94 @@
         <v>14</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="D31" s="1">
         <v>1</v>
       </c>
       <c r="E31" s="102" t="s">
-        <v>303</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>53</v>
+        <v>297</v>
+      </c>
+      <c r="F31" s="103" t="s">
+        <v>399</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I31" s="80">
         <v>7</v>
       </c>
       <c r="J31" s="66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K31" s="66" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L31" s="66">
         <v>1</v>
       </c>
       <c r="M31" s="82" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O31" s="83">
         <v>6</v>
       </c>
       <c r="P31" s="77" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q31" s="84" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="R31" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S31" s="85" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="32" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="33">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>36</v>
+        <v>237</v>
+      </c>
+      <c r="F32" s="103" t="s">
+        <v>400</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="I32" s="136" t="s">
-        <v>105</v>
-      </c>
-      <c r="J32" s="137"/>
-      <c r="K32" s="138" t="s">
-        <v>79</v>
-      </c>
-      <c r="L32" s="139"/>
-      <c r="M32" s="140"/>
+        <v>265</v>
+      </c>
+      <c r="I32" s="123" t="s">
+        <v>104</v>
+      </c>
+      <c r="J32" s="124"/>
+      <c r="K32" s="125" t="s">
+        <v>78</v>
+      </c>
+      <c r="L32" s="126"/>
+      <c r="M32" s="127"/>
       <c r="O32" s="83">
         <v>7</v>
       </c>
       <c r="P32" s="77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q32" s="77" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="R32" s="78" t="s">
         <v>21</v>
       </c>
       <c r="S32" s="79" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="2:19" ht="33" x14ac:dyDescent="0.3">
@@ -4352,34 +4390,34 @@
         <v>16</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="D33" s="1">
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F33" s="103" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="O33" s="83">
         <v>8</v>
       </c>
       <c r="P33" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q33" s="84" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R33" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S33" s="85" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34" spans="2:19" x14ac:dyDescent="0.3">
@@ -4388,34 +4426,34 @@
         <v>17</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D34" s="1">
         <v>6</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="O34" s="83">
         <v>9</v>
       </c>
       <c r="P34" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q34" s="84" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R34" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S34" s="85" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -4424,34 +4462,34 @@
         <v>18</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="D35" s="90" t="s">
         <v>56</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F35" s="103" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="O35" s="80">
         <v>10</v>
       </c>
       <c r="P35" s="66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q35" s="66" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="R35" s="81" t="s">
         <v>20</v>
       </c>
       <c r="S35" s="82" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4460,29 +4498,29 @@
         <v>19</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="D36" s="90" t="s">
         <v>56</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F36" s="103" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="O36" s="136" t="s">
-        <v>105</v>
-      </c>
-      <c r="P36" s="137"/>
-      <c r="Q36" s="138" t="s">
-        <v>241</v>
-      </c>
-      <c r="R36" s="139"/>
-      <c r="S36" s="140"/>
+        <v>331</v>
+      </c>
+      <c r="O36" s="123" t="s">
+        <v>104</v>
+      </c>
+      <c r="P36" s="124"/>
+      <c r="Q36" s="125" t="s">
+        <v>237</v>
+      </c>
+      <c r="R36" s="126"/>
+      <c r="S36" s="127"/>
     </row>
     <row r="37" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="33">
@@ -4490,19 +4528,19 @@
         <v>20</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="D37" s="90" t="s">
         <v>56</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F37" s="103" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
     </row>
     <row r="38" spans="2:19" ht="33" x14ac:dyDescent="0.3">
@@ -4511,38 +4549,38 @@
         <v>21</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="D38" s="1">
         <v>1</v>
       </c>
       <c r="E38" s="102" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="F38" s="103" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="I38" s="118" t="s">
-        <v>103</v>
-      </c>
-      <c r="J38" s="120"/>
-      <c r="K38" s="118" t="s">
-        <v>123</v>
-      </c>
-      <c r="L38" s="119"/>
-      <c r="M38" s="120"/>
-      <c r="O38" s="118" t="s">
-        <v>103</v>
-      </c>
-      <c r="P38" s="120"/>
-      <c r="Q38" s="118" t="s">
-        <v>174</v>
-      </c>
-      <c r="R38" s="119"/>
-      <c r="S38" s="120"/>
+        <v>375</v>
+      </c>
+      <c r="I38" s="120" t="s">
+        <v>102</v>
+      </c>
+      <c r="J38" s="121"/>
+      <c r="K38" s="120" t="s">
+        <v>122</v>
+      </c>
+      <c r="L38" s="122"/>
+      <c r="M38" s="121"/>
+      <c r="O38" s="120" t="s">
+        <v>102</v>
+      </c>
+      <c r="P38" s="121"/>
+      <c r="Q38" s="120" t="s">
+        <v>173</v>
+      </c>
+      <c r="R38" s="122"/>
+      <c r="S38" s="121"/>
     </row>
     <row r="39" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B39" s="33">
@@ -4550,38 +4588,38 @@
         <v>22</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D39" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>64</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="I39" s="127" t="s">
-        <v>109</v>
-      </c>
-      <c r="J39" s="128"/>
-      <c r="K39" s="129" t="s">
-        <v>124</v>
-      </c>
-      <c r="L39" s="130"/>
-      <c r="M39" s="131"/>
-      <c r="O39" s="127" t="s">
-        <v>109</v>
-      </c>
-      <c r="P39" s="128"/>
-      <c r="Q39" s="129" t="s">
-        <v>237</v>
-      </c>
-      <c r="R39" s="130"/>
-      <c r="S39" s="131"/>
+        <v>86</v>
+      </c>
+      <c r="I39" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="J39" s="131"/>
+      <c r="K39" s="132" t="s">
+        <v>123</v>
+      </c>
+      <c r="L39" s="133"/>
+      <c r="M39" s="134"/>
+      <c r="O39" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="P39" s="131"/>
+      <c r="Q39" s="132" t="s">
+        <v>233</v>
+      </c>
+      <c r="R39" s="133"/>
+      <c r="S39" s="134"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B40" s="33">
@@ -4589,38 +4627,38 @@
         <v>23</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D40" s="101" t="s">
         <v>20</v>
       </c>
       <c r="E40" s="102" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>36</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="I40" s="127" t="s">
+        <v>231</v>
+      </c>
+      <c r="I40" s="130" t="s">
+        <v>106</v>
+      </c>
+      <c r="J40" s="131"/>
+      <c r="K40" s="132" t="s">
         <v>107</v>
       </c>
-      <c r="J40" s="128"/>
-      <c r="K40" s="129" t="s">
-        <v>108</v>
-      </c>
-      <c r="L40" s="130"/>
-      <c r="M40" s="131"/>
-      <c r="O40" s="127" t="s">
-        <v>107</v>
-      </c>
-      <c r="P40" s="128"/>
-      <c r="Q40" s="127" t="s">
+      <c r="L40" s="133"/>
+      <c r="M40" s="134"/>
+      <c r="O40" s="130" t="s">
+        <v>106</v>
+      </c>
+      <c r="P40" s="131"/>
+      <c r="Q40" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="R40" s="141"/>
-      <c r="S40" s="128"/>
+      <c r="R40" s="135"/>
+      <c r="S40" s="131"/>
     </row>
     <row r="41" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="33">
@@ -4628,7 +4666,7 @@
         <v>24</v>
       </c>
       <c r="C41" s="97" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D41" s="90" t="s">
         <v>21</v>
@@ -4637,29 +4675,29 @@
         <v>36</v>
       </c>
       <c r="F41" s="98" t="s">
-        <v>35</v>
+        <v>337</v>
       </c>
       <c r="G41" s="99" t="s">
-        <v>279</v>
-      </c>
-      <c r="I41" s="121" t="s">
+        <v>275</v>
+      </c>
+      <c r="I41" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="122"/>
-      <c r="K41" s="123" t="s">
-        <v>126</v>
-      </c>
-      <c r="L41" s="124"/>
-      <c r="M41" s="125"/>
-      <c r="O41" s="121" t="s">
+      <c r="J41" s="137"/>
+      <c r="K41" s="138" t="s">
+        <v>125</v>
+      </c>
+      <c r="L41" s="119"/>
+      <c r="M41" s="139"/>
+      <c r="O41" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="P41" s="122"/>
-      <c r="Q41" s="123" t="s">
-        <v>175</v>
-      </c>
-      <c r="R41" s="124"/>
-      <c r="S41" s="125"/>
+      <c r="P41" s="137"/>
+      <c r="Q41" s="138" t="s">
+        <v>174</v>
+      </c>
+      <c r="R41" s="119"/>
+      <c r="S41" s="139"/>
     </row>
     <row r="42" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="33">
@@ -4667,39 +4705,39 @@
         <v>25</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="D42" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>64</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J42" s="126" t="s">
-        <v>98</v>
-      </c>
-      <c r="K42" s="126"/>
-      <c r="L42" s="126"/>
+      <c r="J42" s="128" t="s">
+        <v>97</v>
+      </c>
+      <c r="K42" s="128"/>
+      <c r="L42" s="128"/>
       <c r="M42" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P42" s="126" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q42" s="126"/>
-      <c r="R42" s="126"/>
+      <c r="P42" s="128" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q42" s="128"/>
+      <c r="R42" s="128"/>
       <c r="S42" s="69" t="s">
         <v>8</v>
       </c>
@@ -4710,41 +4748,41 @@
         <v>26</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D43" s="1">
         <v>1</v>
       </c>
       <c r="E43" s="114" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F43" s="114" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I43" s="70">
         <v>1</v>
       </c>
-      <c r="J43" s="135" t="s">
+      <c r="J43" s="140" t="s">
         <v>20</v>
       </c>
-      <c r="K43" s="135"/>
-      <c r="L43" s="135"/>
+      <c r="K43" s="140"/>
+      <c r="L43" s="140"/>
       <c r="M43" s="71" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O43" s="87">
         <v>1</v>
       </c>
-      <c r="P43" s="142" t="s">
+      <c r="P43" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="Q43" s="142"/>
-      <c r="R43" s="142"/>
+      <c r="Q43" s="129"/>
+      <c r="R43" s="129"/>
       <c r="S43" s="88" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="44" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4753,25 +4791,25 @@
         <v>27</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F44" s="103" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="I44" s="67" t="s">
         <v>41</v>
       </c>
       <c r="J44" s="68" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K44" s="68" t="s">
         <v>1</v>
@@ -4785,13 +4823,13 @@
       <c r="O44" s="80">
         <v>2</v>
       </c>
-      <c r="P44" s="124" t="s">
+      <c r="P44" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="Q44" s="124"/>
-      <c r="R44" s="124"/>
+      <c r="Q44" s="119"/>
+      <c r="R44" s="119"/>
       <c r="S44" s="82" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4800,40 +4838,40 @@
         <v>28</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D45" s="1">
         <v>1</v>
       </c>
       <c r="E45" s="114" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F45" s="114" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="I45" s="72">
         <v>1</v>
       </c>
       <c r="J45" s="73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K45" s="73" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L45" s="73">
         <v>6</v>
       </c>
       <c r="M45" s="75" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O45" s="67" t="s">
         <v>41</v>
       </c>
       <c r="P45" s="68" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q45" s="68" t="s">
         <v>1</v>
@@ -4851,40 +4889,40 @@
         <v>29</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D46" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F46" s="103" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="I46" s="76">
         <v>2</v>
       </c>
       <c r="J46" s="77" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K46" s="77" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L46" s="77">
         <v>3</v>
       </c>
       <c r="M46" s="79" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O46" s="72">
         <v>1</v>
       </c>
       <c r="P46" s="73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q46" s="73" t="s">
         <v>5</v>
@@ -4893,7 +4931,7 @@
         <v>1</v>
       </c>
       <c r="S46" s="75" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="47" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4902,40 +4940,40 @@
         <v>30</v>
       </c>
       <c r="C47" s="112" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D47" s="113" t="s">
         <v>20</v>
       </c>
       <c r="E47" s="111" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F47" s="115" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="G47" s="112" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="I47" s="80">
         <v>3</v>
       </c>
       <c r="J47" s="66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K47" s="66" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L47" s="66">
         <v>4</v>
       </c>
       <c r="M47" s="82" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O47" s="72">
         <v>2</v>
       </c>
       <c r="P47" s="73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q47" s="73" t="s">
         <v>6</v>
@@ -4944,7 +4982,7 @@
         <v>1</v>
       </c>
       <c r="S47" s="75" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="48" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4953,7 +4991,7 @@
         <v>31</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D48" s="90" t="s">
         <v>56</v>
@@ -4962,34 +5000,34 @@
         <v>63</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="I48" s="136" t="s">
-        <v>105</v>
-      </c>
-      <c r="J48" s="137"/>
-      <c r="K48" s="138" t="s">
+        <v>345</v>
+      </c>
+      <c r="I48" s="123" t="s">
+        <v>104</v>
+      </c>
+      <c r="J48" s="124"/>
+      <c r="K48" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="L48" s="139"/>
-      <c r="M48" s="140"/>
+      <c r="L48" s="126"/>
+      <c r="M48" s="127"/>
       <c r="O48" s="83">
         <v>3</v>
       </c>
       <c r="P48" s="73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q48" s="73" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="R48" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S48" s="75" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="49" spans="2:19" x14ac:dyDescent="0.3">
@@ -4998,34 +5036,34 @@
         <v>32</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D49" s="1">
         <v>1</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F49" s="103" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="O49" s="83">
         <v>4</v>
       </c>
       <c r="P49" s="77" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q49" s="84" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R49" s="84">
         <v>1</v>
       </c>
       <c r="S49" s="85" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="50" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5034,7 +5072,7 @@
         <v>33</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="D50" s="90" t="s">
         <v>49</v>
@@ -5043,7 +5081,7 @@
         <v>47</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>54</v>
@@ -5052,16 +5090,16 @@
         <v>5</v>
       </c>
       <c r="P50" s="77" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q50" s="84" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="R50" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S50" s="85" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="51" spans="2:19" x14ac:dyDescent="0.3">
@@ -5070,13 +5108,13 @@
         <v>34</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="D51" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>40</v>
@@ -5084,29 +5122,29 @@
       <c r="G51" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I51" s="118" t="s">
-        <v>103</v>
-      </c>
-      <c r="J51" s="120"/>
-      <c r="K51" s="118" t="s">
-        <v>130</v>
-      </c>
-      <c r="L51" s="119"/>
-      <c r="M51" s="120"/>
+      <c r="I51" s="120" t="s">
+        <v>102</v>
+      </c>
+      <c r="J51" s="121"/>
+      <c r="K51" s="120" t="s">
+        <v>129</v>
+      </c>
+      <c r="L51" s="122"/>
+      <c r="M51" s="121"/>
       <c r="O51" s="83">
         <v>6</v>
       </c>
       <c r="P51" s="77" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q51" s="84" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R51" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S51" s="85" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="52" spans="2:19" ht="33" x14ac:dyDescent="0.3">
@@ -5115,43 +5153,43 @@
         <v>35</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D52" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F52" s="103" t="s">
         <v>48</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="I52" s="127" t="s">
-        <v>109</v>
-      </c>
-      <c r="J52" s="128"/>
-      <c r="K52" s="129" t="s">
-        <v>131</v>
-      </c>
-      <c r="L52" s="130"/>
-      <c r="M52" s="131"/>
+        <v>224</v>
+      </c>
+      <c r="I52" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="J52" s="131"/>
+      <c r="K52" s="132" t="s">
+        <v>130</v>
+      </c>
+      <c r="L52" s="133"/>
+      <c r="M52" s="134"/>
       <c r="O52" s="83">
         <v>7</v>
       </c>
       <c r="P52" s="77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q52" s="77" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="R52" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S52" s="79" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="53" spans="2:19" x14ac:dyDescent="0.3">
@@ -5160,43 +5198,43 @@
         <v>36</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="D53" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E53" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="G53" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="I53" s="127" t="s">
+      <c r="I53" s="130" t="s">
+        <v>106</v>
+      </c>
+      <c r="J53" s="131"/>
+      <c r="K53" s="132" t="s">
         <v>107</v>
       </c>
-      <c r="J53" s="128"/>
-      <c r="K53" s="129" t="s">
-        <v>108</v>
-      </c>
-      <c r="L53" s="130"/>
-      <c r="M53" s="131"/>
+      <c r="L53" s="133"/>
+      <c r="M53" s="134"/>
       <c r="O53" s="83">
         <v>8</v>
       </c>
       <c r="P53" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q53" s="84" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R53" s="84">
         <v>1</v>
       </c>
       <c r="S53" s="85" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="54" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5205,37 +5243,37 @@
         <v>37</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="D54" s="1">
         <v>1</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="I54" s="121" t="s">
+        <v>370</v>
+      </c>
+      <c r="I54" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="122"/>
-      <c r="K54" s="123" t="s">
-        <v>132</v>
-      </c>
-      <c r="L54" s="124"/>
-      <c r="M54" s="125"/>
+      <c r="J54" s="137"/>
+      <c r="K54" s="138" t="s">
+        <v>131</v>
+      </c>
+      <c r="L54" s="119"/>
+      <c r="M54" s="139"/>
       <c r="O54" s="83">
         <v>9</v>
       </c>
       <c r="P54" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q54" s="84" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="R54" s="86" t="s">
         <v>20</v>
@@ -5250,28 +5288,28 @@
         <v>38</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="D55" s="1">
         <v>1</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="I55" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J55" s="126" t="s">
-        <v>98</v>
-      </c>
-      <c r="K55" s="126"/>
-      <c r="L55" s="126"/>
+      <c r="J55" s="128" t="s">
+        <v>97</v>
+      </c>
+      <c r="K55" s="128"/>
+      <c r="L55" s="128"/>
       <c r="M55" s="69" t="s">
         <v>8</v>
       </c>
@@ -5279,10 +5317,10 @@
         <v>10</v>
       </c>
       <c r="P55" s="66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q55" s="66" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R55" s="81" t="s">
         <v>20</v>
@@ -5297,40 +5335,40 @@
         <v>39</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="D56" s="1">
         <v>1</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="I56" s="87">
         <v>1</v>
       </c>
-      <c r="J56" s="142" t="s">
+      <c r="J56" s="129" t="s">
         <v>20</v>
       </c>
-      <c r="K56" s="142"/>
-      <c r="L56" s="142"/>
+      <c r="K56" s="129"/>
+      <c r="L56" s="129"/>
       <c r="M56" s="88" t="s">
-        <v>134</v>
-      </c>
-      <c r="O56" s="136" t="s">
-        <v>105</v>
-      </c>
-      <c r="P56" s="137"/>
-      <c r="Q56" s="138" t="s">
-        <v>242</v>
-      </c>
-      <c r="R56" s="139"/>
-      <c r="S56" s="140"/>
+        <v>133</v>
+      </c>
+      <c r="O56" s="123" t="s">
+        <v>104</v>
+      </c>
+      <c r="P56" s="124"/>
+      <c r="Q56" s="125" t="s">
+        <v>238</v>
+      </c>
+      <c r="R56" s="126"/>
+      <c r="S56" s="127"/>
     </row>
     <row r="57" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="33">
@@ -5338,30 +5376,30 @@
         <v>40</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="D57" s="1">
         <v>1</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="I57" s="80">
         <v>2</v>
       </c>
-      <c r="J57" s="124" t="s">
+      <c r="J57" s="119" t="s">
         <v>55</v>
       </c>
-      <c r="K57" s="124"/>
-      <c r="L57" s="124"/>
+      <c r="K57" s="119"/>
+      <c r="L57" s="119"/>
       <c r="M57" s="89" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5370,25 +5408,25 @@
         <v>41</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="D58" s="33">
         <v>1</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="I58" s="67" t="s">
         <v>41</v>
       </c>
       <c r="J58" s="68" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K58" s="68" t="s">
         <v>1</v>
@@ -5399,15 +5437,15 @@
       <c r="M58" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="118" t="s">
-        <v>103</v>
-      </c>
-      <c r="P58" s="120"/>
-      <c r="Q58" s="118" t="s">
-        <v>185</v>
-      </c>
-      <c r="R58" s="119"/>
-      <c r="S58" s="120"/>
+      <c r="O58" s="120" t="s">
+        <v>102</v>
+      </c>
+      <c r="P58" s="121"/>
+      <c r="Q58" s="120" t="s">
+        <v>184</v>
+      </c>
+      <c r="R58" s="122"/>
+      <c r="S58" s="121"/>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B59" s="33">
@@ -5415,28 +5453,28 @@
         <v>42</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D59" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>44</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I59" s="72">
         <v>1</v>
       </c>
       <c r="J59" s="73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K59" s="73" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L59" s="74" t="s">
         <v>55</v>
@@ -5444,15 +5482,15 @@
       <c r="M59" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="O59" s="127" t="s">
-        <v>109</v>
-      </c>
-      <c r="P59" s="128"/>
-      <c r="Q59" s="129" t="s">
-        <v>237</v>
-      </c>
-      <c r="R59" s="130"/>
-      <c r="S59" s="131"/>
+      <c r="O59" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="P59" s="131"/>
+      <c r="Q59" s="132" t="s">
+        <v>233</v>
+      </c>
+      <c r="R59" s="133"/>
+      <c r="S59" s="134"/>
     </row>
     <row r="60" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B60" s="33">
@@ -5460,28 +5498,28 @@
         <v>43</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>197</v>
+        <v>395</v>
       </c>
       <c r="D60" s="90" t="s">
         <v>21</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F60" s="103" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G60" s="99" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I60" s="76">
         <v>2</v>
       </c>
       <c r="J60" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K60" s="77" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L60" s="77">
         <v>1</v>
@@ -5489,15 +5527,15 @@
       <c r="M60" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="O60" s="127" t="s">
-        <v>107</v>
-      </c>
-      <c r="P60" s="128"/>
-      <c r="Q60" s="127" t="s">
+      <c r="O60" s="130" t="s">
+        <v>106</v>
+      </c>
+      <c r="P60" s="131"/>
+      <c r="Q60" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="R60" s="141"/>
-      <c r="S60" s="128"/>
+      <c r="R60" s="135"/>
+      <c r="S60" s="131"/>
     </row>
     <row r="61" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="33">
@@ -5505,7 +5543,7 @@
         <v>44</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D61" s="1">
         <v>3</v>
@@ -5514,35 +5552,35 @@
         <v>58</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="I61" s="83">
         <v>3</v>
       </c>
       <c r="J61" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K61" s="84" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L61" s="84">
         <v>1</v>
       </c>
       <c r="M61" s="85" t="s">
-        <v>146</v>
-      </c>
-      <c r="O61" s="121" t="s">
+        <v>145</v>
+      </c>
+      <c r="O61" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="P61" s="122"/>
-      <c r="Q61" s="123" t="s">
-        <v>186</v>
-      </c>
-      <c r="R61" s="124"/>
-      <c r="S61" s="125"/>
+      <c r="P61" s="137"/>
+      <c r="Q61" s="138" t="s">
+        <v>185</v>
+      </c>
+      <c r="R61" s="119"/>
+      <c r="S61" s="139"/>
     </row>
     <row r="62" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B62" s="33">
@@ -5550,43 +5588,43 @@
         <v>45</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D62" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="I62" s="83">
         <v>4</v>
       </c>
       <c r="J62" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K62" s="84" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L62" s="84">
         <v>1</v>
       </c>
       <c r="M62" s="85" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O62" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P62" s="126" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q62" s="126"/>
-      <c r="R62" s="126"/>
+      <c r="P62" s="128" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q62" s="128"/>
+      <c r="R62" s="128"/>
       <c r="S62" s="69" t="s">
         <v>8</v>
       </c>
@@ -5597,7 +5635,7 @@
         <v>46</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D63" s="1">
         <v>1</v>
@@ -5606,19 +5644,19 @@
         <v>58</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I63" s="83">
         <v>5</v>
       </c>
       <c r="J63" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K63" s="84" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L63" s="84">
         <v>1</v>
@@ -5629,13 +5667,13 @@
       <c r="O63" s="87">
         <v>1</v>
       </c>
-      <c r="P63" s="142" t="s">
+      <c r="P63" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="Q63" s="142"/>
-      <c r="R63" s="142"/>
+      <c r="Q63" s="129"/>
+      <c r="R63" s="129"/>
       <c r="S63" s="88" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="64" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5644,7 +5682,7 @@
         <v>47</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>206</v>
+        <v>391</v>
       </c>
       <c r="D64" s="1">
         <v>1</v>
@@ -5653,19 +5691,19 @@
         <v>58</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="I64" s="83">
         <v>6</v>
       </c>
       <c r="J64" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K64" s="84" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L64" s="84">
         <v>1</v>
@@ -5676,13 +5714,13 @@
       <c r="O64" s="80">
         <v>2</v>
       </c>
-      <c r="P64" s="124" t="s">
+      <c r="P64" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="Q64" s="124"/>
-      <c r="R64" s="124"/>
+      <c r="Q64" s="119"/>
+      <c r="R64" s="119"/>
       <c r="S64" s="82" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="65" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5691,7 +5729,7 @@
         <v>48</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D65" s="90" t="s">
         <v>57</v>
@@ -5709,10 +5747,10 @@
         <v>7</v>
       </c>
       <c r="J65" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K65" s="84" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L65" s="84">
         <v>1</v>
@@ -5724,7 +5762,7 @@
         <v>41</v>
       </c>
       <c r="P65" s="68" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q65" s="68" t="s">
         <v>1</v>
@@ -5742,7 +5780,7 @@
         <v>49</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D66" s="1">
         <v>6</v>
@@ -5751,19 +5789,19 @@
         <v>44</v>
       </c>
       <c r="F66" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G66" s="5" t="s">
         <v>241</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>245</v>
       </c>
       <c r="I66" s="83">
         <v>8</v>
       </c>
       <c r="J66" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K66" s="84" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L66" s="84">
         <v>1</v>
@@ -5775,7 +5813,7 @@
         <v>1</v>
       </c>
       <c r="P66" s="73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q66" s="73" t="s">
         <v>5</v>
@@ -5784,7 +5822,7 @@
         <v>1</v>
       </c>
       <c r="S66" s="75" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="67" spans="2:19" ht="33" x14ac:dyDescent="0.3">
@@ -5793,7 +5831,7 @@
         <v>50</v>
       </c>
       <c r="C67" s="97" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D67" s="101" t="s">
         <v>45</v>
@@ -5811,22 +5849,22 @@
         <v>9</v>
       </c>
       <c r="J67" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K67" s="84" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L67" s="84">
         <v>3</v>
       </c>
       <c r="M67" s="85" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O67" s="72">
         <v>2</v>
       </c>
       <c r="P67" s="73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q67" s="73" t="s">
         <v>6</v>
@@ -5835,7 +5873,7 @@
         <v>1</v>
       </c>
       <c r="S67" s="75" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.3">
@@ -5844,7 +5882,7 @@
         <v>51</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="D68" s="90" t="s">
         <v>55</v>
@@ -5862,10 +5900,10 @@
         <v>10</v>
       </c>
       <c r="J68" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K68" s="84" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L68" s="84">
         <v>1</v>
@@ -5877,10 +5915,10 @@
         <v>3</v>
       </c>
       <c r="P68" s="84" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q68" s="84" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R68" s="86" t="s">
         <v>20</v>
@@ -5895,7 +5933,7 @@
         <v>52</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="D69" s="90" t="s">
         <v>56</v>
@@ -5904,19 +5942,19 @@
         <v>44</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="I69" s="83">
         <v>11</v>
       </c>
       <c r="J69" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K69" s="84" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L69" s="84">
         <v>1</v>
@@ -5928,16 +5966,16 @@
         <v>4</v>
       </c>
       <c r="P69" s="84" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q69" s="84" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="R69" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S69" s="85" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="70" spans="2:19" ht="33" x14ac:dyDescent="0.3">
@@ -5946,7 +5984,7 @@
         <v>53</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="D70" s="90" t="s">
         <v>56</v>
@@ -5955,16 +5993,16 @@
         <v>44</v>
       </c>
       <c r="F70" s="103" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="I70" s="83">
         <v>12</v>
       </c>
       <c r="J70" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K70" s="84" t="s">
         <v>18</v>
@@ -5973,22 +6011,22 @@
         <v>1</v>
       </c>
       <c r="M70" s="85" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O70" s="83">
         <v>5</v>
       </c>
       <c r="P70" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q70" s="84" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R70" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S70" s="85" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="71" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5997,7 +6035,7 @@
         <v>54</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="D71" s="90" t="s">
         <v>56</v>
@@ -6009,13 +6047,13 @@
         <v>62</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="I71" s="80">
         <v>13</v>
       </c>
       <c r="J71" s="66" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K71" s="66" t="s">
         <v>19</v>
@@ -6024,22 +6062,22 @@
         <v>1</v>
       </c>
       <c r="M71" s="82" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O71" s="83">
         <v>6</v>
       </c>
       <c r="P71" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q71" s="84" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="R71" s="86" t="s">
         <v>20</v>
       </c>
       <c r="S71" s="85" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="72" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -6048,7 +6086,7 @@
         <v>55</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="D72" s="1">
         <v>5</v>
@@ -6062,24 +6100,24 @@
       <c r="G72" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="I72" s="136" t="s">
-        <v>105</v>
-      </c>
-      <c r="J72" s="137"/>
-      <c r="K72" s="138" t="s">
+      <c r="I72" s="123" t="s">
+        <v>104</v>
+      </c>
+      <c r="J72" s="124"/>
+      <c r="K72" s="125" t="s">
         <v>58</v>
       </c>
-      <c r="L72" s="139"/>
-      <c r="M72" s="140"/>
-      <c r="O72" s="136" t="s">
-        <v>105</v>
-      </c>
-      <c r="P72" s="137"/>
-      <c r="Q72" s="138" t="s">
-        <v>243</v>
-      </c>
-      <c r="R72" s="139"/>
-      <c r="S72" s="140"/>
+      <c r="L72" s="126"/>
+      <c r="M72" s="127"/>
+      <c r="O72" s="123" t="s">
+        <v>104</v>
+      </c>
+      <c r="P72" s="124"/>
+      <c r="Q72" s="125" t="s">
+        <v>239</v>
+      </c>
+      <c r="R72" s="126"/>
+      <c r="S72" s="127"/>
     </row>
     <row r="73" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B73" s="33">
@@ -6087,19 +6125,19 @@
         <v>56</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D73" s="101" t="s">
         <v>20</v>
       </c>
       <c r="E73" s="102" t="s">
-        <v>284</v>
+        <v>396</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.3">
@@ -6108,7 +6146,7 @@
         <v>57</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D74" s="1">
         <v>1</v>
@@ -6117,10 +6155,10 @@
         <v>58</v>
       </c>
       <c r="F74" s="114" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.3">
@@ -6129,7 +6167,7 @@
         <v>58</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D75" s="1">
         <v>1</v>
@@ -6138,10 +6176,10 @@
         <v>58</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.3">
@@ -6150,7 +6188,7 @@
         <v>59</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D76" s="1">
         <v>1</v>
@@ -6159,10 +6197,10 @@
         <v>58</v>
       </c>
       <c r="F76" s="114" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.3">
@@ -6171,7 +6209,7 @@
         <v>60</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D77" s="90" t="s">
         <v>20</v>
@@ -6180,10 +6218,10 @@
         <v>62</v>
       </c>
       <c r="F77" s="111" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.3">
@@ -6192,7 +6230,7 @@
         <v>61</v>
       </c>
       <c r="C78" s="112" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D78" s="113" t="s">
         <v>20</v>
@@ -6201,10 +6239,10 @@
         <v>62</v>
       </c>
       <c r="F78" s="111" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G78" s="112" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.3">
@@ -6213,7 +6251,7 @@
         <v>62</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="D79" s="1">
         <v>1</v>
@@ -6222,10 +6260,10 @@
         <v>58</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.3">
@@ -6234,7 +6272,7 @@
         <v>63</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D80" s="1">
         <v>1</v>
@@ -6243,10 +6281,10 @@
         <v>58</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="81" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
@@ -6255,7 +6293,7 @@
         <v>64</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="D81" s="101" t="s">
         <v>46</v>
@@ -6264,7 +6302,7 @@
         <v>42</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G81" s="5" t="s">
         <v>51</v>
@@ -6276,7 +6314,7 @@
         <v>65</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D82" s="1">
         <v>1</v>
@@ -6288,7 +6326,7 @@
         <v>43</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.3">
@@ -6297,7 +6335,7 @@
         <v>66</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D83" s="90" t="s">
         <v>20</v>
@@ -6306,10 +6344,10 @@
         <v>43</v>
       </c>
       <c r="F83" s="103" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.3">
@@ -6318,7 +6356,7 @@
         <v>67</v>
       </c>
       <c r="C84" s="97" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D84" s="90" t="s">
         <v>21</v>
@@ -6327,19 +6365,19 @@
         <v>39</v>
       </c>
       <c r="F84" s="98" t="s">
-        <v>240</v>
+        <v>337</v>
       </c>
       <c r="G84" s="99" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="85" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B85" s="33">
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
       <c r="C85" s="93" t="s">
-        <v>281</v>
+        <v>397</v>
       </c>
       <c r="D85" s="94" t="s">
         <v>21</v>
@@ -6348,7 +6386,7 @@
         <v>35</v>
       </c>
       <c r="F85" s="95" t="s">
-        <v>74</v>
+        <v>390</v>
       </c>
       <c r="G85" s="96" t="s">
         <v>37</v>
@@ -6360,7 +6398,7 @@
         <v>69</v>
       </c>
       <c r="C86" s="93" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="D86" s="92">
         <v>1</v>
@@ -6381,19 +6419,19 @@
         <v>70</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="D87" s="90" t="s">
         <v>21</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
     </row>
     <row r="88" spans="2:7" ht="66" x14ac:dyDescent="0.3">
@@ -6402,19 +6440,19 @@
         <v>71</v>
       </c>
       <c r="C88" s="104" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D88" s="109" t="s">
         <v>20</v>
       </c>
       <c r="E88" s="105" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F88" s="110" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="G88" s="107" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.3">
@@ -6423,19 +6461,19 @@
         <v>72</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="D89" s="90" t="s">
         <v>56</v>
       </c>
       <c r="E89" s="103" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F89" s="103" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="90" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6444,19 +6482,19 @@
         <v>73</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="D90" s="90" t="s">
         <v>56</v>
       </c>
       <c r="E90" s="103" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F90" s="103" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.3">
@@ -6465,19 +6503,19 @@
         <v>74</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="D91" s="1">
         <v>1</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F91" s="103" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.3">
@@ -6486,19 +6524,19 @@
         <v>75</v>
       </c>
       <c r="C92" s="104" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D92" s="105">
         <v>1</v>
       </c>
       <c r="E92" s="105" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F92" s="106" t="s">
         <v>14</v>
       </c>
       <c r="G92" s="107" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.3">
@@ -6507,19 +6545,19 @@
         <v>76</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D93" s="1">
         <v>1</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="94" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6528,19 +6566,19 @@
         <v>77</v>
       </c>
       <c r="C94" s="104" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D94" s="105">
         <v>1</v>
       </c>
       <c r="E94" s="105" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F94" s="108" t="s">
         <v>73</v>
       </c>
       <c r="G94" s="107" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.3">
@@ -6549,19 +6587,19 @@
         <v>78</v>
       </c>
       <c r="C95" s="112" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D95" s="113" t="s">
         <v>20</v>
       </c>
       <c r="E95" s="111" t="s">
-        <v>242</v>
-      </c>
-      <c r="F95" s="143" t="s">
-        <v>348</v>
+        <v>238</v>
+      </c>
+      <c r="F95" s="118" t="s">
+        <v>342</v>
       </c>
       <c r="G95" s="112" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.3">
@@ -6570,19 +6608,19 @@
         <v>79</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D96" s="1">
         <v>1</v>
       </c>
       <c r="E96" s="103" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F96" s="103" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="97" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6591,19 +6629,19 @@
         <v>80</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="D97" s="90" t="s">
         <v>56</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F97" s="103" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="98" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6612,19 +6650,19 @@
         <v>81</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="D98" s="1">
         <v>1</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F98" s="103" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.3">
@@ -6633,19 +6671,19 @@
         <v>82</v>
       </c>
       <c r="C99" s="104" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="D99" s="109" t="s">
         <v>20</v>
       </c>
       <c r="E99" s="117" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="F99" s="106" t="s">
         <v>17</v>
       </c>
       <c r="G99" s="107" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.3">
@@ -6654,19 +6692,19 @@
         <v>83</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="D100" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
     </row>
     <row r="101" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
@@ -6675,19 +6713,19 @@
         <v>84</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D101" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F101" s="103" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.3">
@@ -6696,19 +6734,19 @@
         <v>85</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="D102" s="90" t="s">
         <v>56</v>
       </c>
       <c r="E102" s="103" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>64</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.3">
@@ -6717,19 +6755,19 @@
         <v>86</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="D103" s="90" t="s">
         <v>56</v>
       </c>
       <c r="E103" s="103" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F103" s="103" t="s">
         <v>62</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="104" spans="2:7" x14ac:dyDescent="0.3">
@@ -6738,19 +6776,19 @@
         <v>87</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D104" s="1">
         <v>1</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" spans="2:7" x14ac:dyDescent="0.3">
@@ -6759,19 +6797,19 @@
         <v>88</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="D105" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="106" spans="2:7" x14ac:dyDescent="0.3">
@@ -6780,19 +6818,19 @@
         <v>89</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D106" s="1">
         <v>1</v>
       </c>
       <c r="E106" s="103" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>64</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="107" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6801,19 +6839,19 @@
         <v>90</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D107" s="90" t="s">
         <v>56</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F107" s="103" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="108" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6822,25 +6860,40 @@
         <v>91</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="D108" s="1">
         <v>1</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F108" s="103" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="109" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B109" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>303</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B109" s="33">
+        <f t="shared" si="2"/>
+        <v>92</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="D109" s="1">
+        <v>1</v>
+      </c>
+      <c r="E109" s="102" t="s">
+        <v>392</v>
+      </c>
+      <c r="F109" s="103" t="s">
+        <v>394</v>
+      </c>
+      <c r="G109" s="5" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="110" spans="2:7" x14ac:dyDescent="0.3">
@@ -7036,15 +7089,75 @@
     </sortState>
   </autoFilter>
   <mergeCells count="102">
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="P44:R44"/>
-    <mergeCell ref="O56:P56"/>
-    <mergeCell ref="Q56:S56"/>
-    <mergeCell ref="P62:R62"/>
-    <mergeCell ref="P63:R63"/>
-    <mergeCell ref="P64:R64"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="K72:M72"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="K53:M53"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="K54:M54"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="K48:M48"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="K51:M51"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="K52:M52"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:S18"/>
     <mergeCell ref="O72:P72"/>
     <mergeCell ref="Q72:S72"/>
     <mergeCell ref="P8:R8"/>
@@ -7069,75 +7182,15 @@
     <mergeCell ref="O36:P36"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:S20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="I72:J72"/>
-    <mergeCell ref="K72:M72"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="K53:M53"/>
-    <mergeCell ref="I54:J54"/>
-    <mergeCell ref="K54:M54"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="K48:M48"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="K51:M51"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="K52:M52"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:M40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:M39"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="P44:R44"/>
+    <mergeCell ref="O56:P56"/>
+    <mergeCell ref="Q56:S56"/>
+    <mergeCell ref="P62:R62"/>
+    <mergeCell ref="P63:R63"/>
+    <mergeCell ref="P64:R64"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7159,25 +7212,25 @@
   <sheetData>
     <row r="2" spans="2:8" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="G2" s="102" t="s">
+        <v>328</v>
+      </c>
+      <c r="H2" s="102" t="s">
         <v>329</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="G2" s="102" t="s">
-        <v>334</v>
-      </c>
-      <c r="H2" s="102" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">

--- a/Document/IDD.xlsx
+++ b/Document/IDD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\SoC_Design\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC991E40-4640-4764-8153-C0DB49EDCA9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E47090BE-DFE7-4CE4-9182-D31A5AA789FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
+    <workbookView xWindow="17235" yWindow="0" windowWidth="11670" windowHeight="15585" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
   </bookViews>
   <sheets>
     <sheet name="CPU" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="395">
   <si>
     <t>top_cpu</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1269,18 +1269,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>w_mem_dec_rd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_dec_rt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_dec_rd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Decoded rd Register (EX)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1289,31 +1277,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Decoded rd Register (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded rt Register (WB)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decoded rd Register (WB)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>w_ex_ctr_regdst</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>RegDst Flag (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RegDst Flag (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RegDst Flag (WB)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1367,11 +1335,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>u_registers
-u_id_ex_bridge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>w_mem_regdst_mux_reg</t>
   </si>
   <si>
@@ -1422,11 +1385,6 @@
   <si>
     <t>u_alu_forwarding_unit
 u_mem_wb_bridge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_ex_mem_bridge
-u_regdst_mux</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1437,14 +1395,6 @@
   </si>
   <si>
     <t>w_id_regdst</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_regdst</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_regdst</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1552,11 +1502,6 @@
   </si>
   <si>
     <t>u_alu_forward_b_mux</t>
-  </si>
-  <si>
-    <t>u_mem_wb_bridge
-u_wdata_forwarding_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>u_wdata_forward_2cycle_mux</t>
@@ -1643,11 +1588,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>u_pc_mux
-u_id_ex_bridge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>w_id_pc_addr</t>
   </si>
   <si>
@@ -1674,6 +1614,40 @@
   </si>
   <si>
     <t>w_ex_flush</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_ex_mem_bridge
+u_load_stall_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_registers
+u_id_ex_bridge
+u_load_stall_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_load_stall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_load_stall_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Load Stall Flag Signal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_if_id_bridge
+u_id_ex_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_pc_mux
+u_if_id_bridge
+u_id_ex_bridge</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2657,16 +2631,58 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2684,52 +2700,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3092,31 +3066,31 @@
   <sheetData>
     <row r="1" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="141" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="142"/>
-      <c r="F2" s="142"/>
-      <c r="G2" s="143"/>
-      <c r="I2" s="120" t="s">
+      <c r="B2" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="135"/>
+      <c r="I2" s="119" t="s">
         <v>102</v>
       </c>
       <c r="J2" s="121"/>
-      <c r="K2" s="120" t="s">
+      <c r="K2" s="119" t="s">
         <v>96</v>
       </c>
-      <c r="L2" s="122"/>
+      <c r="L2" s="120"/>
       <c r="M2" s="121"/>
-      <c r="O2" s="120" t="s">
+      <c r="O2" s="119" t="s">
         <v>102</v>
       </c>
       <c r="P2" s="121"/>
-      <c r="Q2" s="120" t="s">
+      <c r="Q2" s="119" t="s">
         <v>149</v>
       </c>
-      <c r="R2" s="122"/>
+      <c r="R2" s="120"/>
       <c r="S2" s="121"/>
     </row>
     <row r="3" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3138,24 +3112,24 @@
       <c r="G3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="130" t="s">
+      <c r="I3" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="J3" s="131"/>
-      <c r="K3" s="132" t="s">
+      <c r="J3" s="129"/>
+      <c r="K3" s="130" t="s">
         <v>109</v>
       </c>
-      <c r="L3" s="133"/>
-      <c r="M3" s="134"/>
-      <c r="O3" s="130" t="s">
+      <c r="L3" s="131"/>
+      <c r="M3" s="132"/>
+      <c r="O3" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="P3" s="131"/>
-      <c r="Q3" s="132" t="s">
+      <c r="P3" s="129"/>
+      <c r="Q3" s="130" t="s">
         <v>233</v>
       </c>
-      <c r="R3" s="133"/>
-      <c r="S3" s="134"/>
+      <c r="R3" s="131"/>
+      <c r="S3" s="132"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B4" s="35">
@@ -3176,24 +3150,24 @@
       <c r="G4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="130" t="s">
+      <c r="I4" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="J4" s="131"/>
-      <c r="K4" s="130" t="s">
+      <c r="J4" s="129"/>
+      <c r="K4" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="L4" s="135"/>
-      <c r="M4" s="131"/>
-      <c r="O4" s="130" t="s">
+      <c r="L4" s="142"/>
+      <c r="M4" s="129"/>
+      <c r="O4" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="P4" s="131"/>
-      <c r="Q4" s="130" t="s">
+      <c r="P4" s="129"/>
+      <c r="Q4" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="R4" s="135"/>
-      <c r="S4" s="131"/>
+      <c r="R4" s="142"/>
+      <c r="S4" s="129"/>
     </row>
     <row r="5" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="54">
@@ -3214,24 +3188,24 @@
       <c r="G5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="136" t="s">
+      <c r="I5" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="137"/>
-      <c r="K5" s="138" t="s">
+      <c r="J5" s="123"/>
+      <c r="K5" s="124" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="119"/>
-      <c r="M5" s="139"/>
-      <c r="O5" s="136" t="s">
+      <c r="L5" s="125"/>
+      <c r="M5" s="126"/>
+      <c r="O5" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="137"/>
-      <c r="Q5" s="138" t="s">
+      <c r="P5" s="123"/>
+      <c r="Q5" s="124" t="s">
         <v>150</v>
       </c>
-      <c r="R5" s="119"/>
-      <c r="S5" s="139"/>
+      <c r="R5" s="125"/>
+      <c r="S5" s="126"/>
     </row>
     <row r="6" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="55">
@@ -3255,22 +3229,22 @@
       <c r="I6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="128" t="s">
+      <c r="J6" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="K6" s="128"/>
-      <c r="L6" s="128"/>
+      <c r="K6" s="127"/>
+      <c r="L6" s="127"/>
       <c r="M6" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="128" t="s">
+      <c r="P6" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="Q6" s="128"/>
-      <c r="R6" s="128"/>
+      <c r="Q6" s="127"/>
+      <c r="R6" s="127"/>
       <c r="S6" s="69" t="s">
         <v>8</v>
       </c>
@@ -3297,22 +3271,22 @@
       <c r="I7" s="70">
         <v>1</v>
       </c>
-      <c r="J7" s="140" t="s">
+      <c r="J7" s="136" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="140"/>
-      <c r="L7" s="140"/>
+      <c r="K7" s="136"/>
+      <c r="L7" s="136"/>
       <c r="M7" s="71" t="s">
         <v>132</v>
       </c>
       <c r="O7" s="87">
         <v>1</v>
       </c>
-      <c r="P7" s="129" t="s">
+      <c r="P7" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="Q7" s="129"/>
-      <c r="R7" s="129"/>
+      <c r="Q7" s="143"/>
+      <c r="R7" s="143"/>
       <c r="S7" s="88" t="s">
         <v>132</v>
       </c>
@@ -3354,11 +3328,11 @@
       <c r="O8" s="80">
         <v>2</v>
       </c>
-      <c r="P8" s="119" t="s">
+      <c r="P8" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="119"/>
-      <c r="R8" s="119"/>
+      <c r="Q8" s="125"/>
+      <c r="R8" s="125"/>
       <c r="S8" s="82" t="s">
         <v>133</v>
       </c>
@@ -3532,15 +3506,15 @@
       <c r="G12" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="123" t="s">
+      <c r="I12" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="J12" s="124"/>
-      <c r="K12" s="125" t="s">
+      <c r="J12" s="138"/>
+      <c r="K12" s="139" t="s">
         <v>105</v>
       </c>
-      <c r="L12" s="126"/>
-      <c r="M12" s="127"/>
+      <c r="L12" s="140"/>
+      <c r="M12" s="141"/>
       <c r="O12" s="72">
         <v>3</v>
       </c>
@@ -3663,15 +3637,15 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="O16" s="123" t="s">
+      <c r="O16" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="P16" s="124"/>
-      <c r="Q16" s="125" t="s">
+      <c r="P16" s="138"/>
+      <c r="Q16" s="139" t="s">
         <v>236</v>
       </c>
-      <c r="R16" s="126"/>
-      <c r="S16" s="127"/>
+      <c r="R16" s="140"/>
+      <c r="S16" s="141"/>
     </row>
     <row r="17" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="90" t="s">
@@ -3693,83 +3667,83 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B18" s="33">
         <f>IF(C18="","",1)</f>
         <v>1</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="D18" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="F18" s="103" t="s">
-        <v>255</v>
-      </c>
-      <c r="G18" s="99" t="s">
-        <v>195</v>
-      </c>
-      <c r="I18" s="120" t="s">
+        <v>292</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I18" s="119" t="s">
         <v>102</v>
       </c>
       <c r="J18" s="121"/>
-      <c r="K18" s="120" t="s">
+      <c r="K18" s="119" t="s">
         <v>103</v>
       </c>
-      <c r="L18" s="122"/>
+      <c r="L18" s="120"/>
       <c r="M18" s="121"/>
-      <c r="O18" s="120" t="s">
+      <c r="O18" s="119" t="s">
         <v>102</v>
       </c>
       <c r="P18" s="121"/>
-      <c r="Q18" s="120" t="s">
+      <c r="Q18" s="119" t="s">
         <v>159</v>
       </c>
-      <c r="R18" s="122"/>
+      <c r="R18" s="120"/>
       <c r="S18" s="121"/>
     </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B19" s="33">
         <f t="shared" ref="B19:B50" si="0">IF(C19="","",B18+1)</f>
         <v>2</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D19" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
+      </c>
+      <c r="F19" s="103" t="s">
+        <v>75</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="I19" s="130" t="s">
+        <v>76</v>
+      </c>
+      <c r="I19" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="J19" s="131"/>
-      <c r="K19" s="132" t="s">
+      <c r="J19" s="129"/>
+      <c r="K19" s="130" t="s">
         <v>110</v>
       </c>
-      <c r="L19" s="133"/>
-      <c r="M19" s="134"/>
-      <c r="O19" s="130" t="s">
+      <c r="L19" s="131"/>
+      <c r="M19" s="132"/>
+      <c r="O19" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="P19" s="131"/>
-      <c r="Q19" s="132" t="s">
+      <c r="P19" s="129"/>
+      <c r="Q19" s="130" t="s">
         <v>233</v>
       </c>
-      <c r="R19" s="133"/>
-      <c r="S19" s="134"/>
+      <c r="R19" s="131"/>
+      <c r="S19" s="132"/>
     </row>
     <row r="20" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B20" s="33">
@@ -3777,160 +3751,160 @@
         <v>3</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="D20" s="1">
-        <v>4</v>
+        <v>354</v>
+      </c>
+      <c r="D20" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>74</v>
+        <v>340</v>
       </c>
       <c r="F20" s="103" t="s">
         <v>75</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="I20" s="130" t="s">
+        <v>355</v>
+      </c>
+      <c r="I20" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="J20" s="131"/>
-      <c r="K20" s="132" t="s">
+      <c r="J20" s="129"/>
+      <c r="K20" s="130" t="s">
         <v>107</v>
       </c>
-      <c r="L20" s="133"/>
-      <c r="M20" s="134"/>
-      <c r="O20" s="130" t="s">
+      <c r="L20" s="131"/>
+      <c r="M20" s="132"/>
+      <c r="O20" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="P20" s="131"/>
-      <c r="Q20" s="130" t="s">
+      <c r="P20" s="129"/>
+      <c r="Q20" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="R20" s="135"/>
-      <c r="S20" s="131"/>
-    </row>
-    <row r="21" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R20" s="142"/>
+      <c r="S20" s="129"/>
+    </row>
+    <row r="21" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="33">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="D21" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="F21" s="103" t="s">
-        <v>75</v>
+        <v>332</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="I21" s="136" t="s">
+        <v>357</v>
+      </c>
+      <c r="I21" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="137"/>
-      <c r="K21" s="138" t="s">
+      <c r="J21" s="123"/>
+      <c r="K21" s="124" t="s">
         <v>124</v>
       </c>
-      <c r="L21" s="119"/>
-      <c r="M21" s="139"/>
-      <c r="O21" s="136" t="s">
+      <c r="L21" s="125"/>
+      <c r="M21" s="126"/>
+      <c r="O21" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="137"/>
-      <c r="Q21" s="138" t="s">
+      <c r="P21" s="123"/>
+      <c r="Q21" s="124" t="s">
         <v>160</v>
       </c>
-      <c r="R21" s="119"/>
-      <c r="S21" s="139"/>
-    </row>
-    <row r="22" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R21" s="125"/>
+      <c r="S21" s="126"/>
+    </row>
+    <row r="22" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="33">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>368</v>
+        <v>257</v>
       </c>
       <c r="D22" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>353</v>
+        <v>78</v>
       </c>
       <c r="F22" s="103" t="s">
-        <v>341</v>
+        <v>370</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>369</v>
+        <v>258</v>
       </c>
       <c r="I22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J22" s="128" t="s">
+      <c r="J22" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="K22" s="128"/>
-      <c r="L22" s="128"/>
+      <c r="K22" s="127"/>
+      <c r="L22" s="127"/>
       <c r="M22" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P22" s="128" t="s">
+      <c r="P22" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="Q22" s="128"/>
-      <c r="R22" s="128"/>
+      <c r="Q22" s="127"/>
+      <c r="R22" s="127"/>
       <c r="S22" s="69" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="33">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="D23" s="90" t="s">
-        <v>20</v>
+        <v>293</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F23" s="103" t="s">
-        <v>383</v>
+      <c r="F23" s="2" t="s">
+        <v>298</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>258</v>
+        <v>84</v>
       </c>
       <c r="I23" s="70">
         <v>1</v>
       </c>
-      <c r="J23" s="140" t="s">
+      <c r="J23" s="136" t="s">
         <v>20</v>
       </c>
-      <c r="K23" s="140"/>
-      <c r="L23" s="140"/>
+      <c r="K23" s="136"/>
+      <c r="L23" s="136"/>
       <c r="M23" s="71" t="s">
         <v>133</v>
       </c>
       <c r="O23" s="87">
         <v>1</v>
       </c>
-      <c r="P23" s="129" t="s">
+      <c r="P23" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="Q23" s="129"/>
-      <c r="R23" s="129"/>
+      <c r="Q23" s="143"/>
+      <c r="R23" s="143"/>
       <c r="S23" s="88" t="s">
         <v>132</v>
       </c>
@@ -3941,19 +3915,19 @@
         <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>293</v>
+        <v>244</v>
       </c>
       <c r="D24" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>78</v>
+        <v>237</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>298</v>
+        <v>65</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>84</v>
+        <v>245</v>
       </c>
       <c r="I24" s="67" t="s">
         <v>41</v>
@@ -3973,34 +3947,34 @@
       <c r="O24" s="80">
         <v>2</v>
       </c>
-      <c r="P24" s="119" t="s">
+      <c r="P24" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="Q24" s="119"/>
-      <c r="R24" s="119"/>
+      <c r="Q24" s="125"/>
+      <c r="R24" s="125"/>
       <c r="S24" s="82" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="33">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D25" s="1">
-        <v>3</v>
+        <v>291</v>
+      </c>
+      <c r="D25" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>65</v>
+        <v>79</v>
+      </c>
+      <c r="F25" s="103" t="s">
+        <v>75</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>245</v>
+        <v>81</v>
       </c>
       <c r="I25" s="72">
         <v>1</v>
@@ -4033,25 +4007,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B26" s="33">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D26" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F26" s="103" t="s">
-        <v>75</v>
+        <v>262</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>298</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="I26" s="76">
         <v>2</v>
@@ -4090,19 +4064,19 @@
         <v>10</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="D27" s="1">
-        <v>2</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>237</v>
+        <v>281</v>
+      </c>
+      <c r="D27" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>298</v>
+        <v>53</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="I27" s="83">
         <v>3</v>
@@ -4141,19 +4115,19 @@
         <v>11</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D28" s="90" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>232</v>
+        <v>88</v>
       </c>
       <c r="I28" s="83">
         <v>4</v>
@@ -4192,19 +4166,19 @@
         <v>12</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="D29" s="90" t="s">
-        <v>21</v>
+        <v>226</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>53</v>
+        <v>234</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>88</v>
+        <v>227</v>
       </c>
       <c r="I29" s="83">
         <v>5</v>
@@ -4237,25 +4211,25 @@
         <v>168</v>
       </c>
     </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B30" s="33">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>226</v>
+        <v>298</v>
       </c>
       <c r="D30" s="1">
         <v>1</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>79</v>
+      <c r="E30" s="102" t="s">
+        <v>297</v>
+      </c>
+      <c r="F30" s="103" t="s">
+        <v>385</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>227</v>
+        <v>89</v>
       </c>
       <c r="I30" s="83">
         <v>6</v>
@@ -4294,19 +4268,19 @@
         <v>14</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>298</v>
+        <v>264</v>
       </c>
       <c r="D31" s="1">
         <v>1</v>
       </c>
-      <c r="E31" s="102" t="s">
-        <v>297</v>
+      <c r="E31" s="2" t="s">
+        <v>237</v>
       </c>
       <c r="F31" s="103" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>89</v>
+        <v>265</v>
       </c>
       <c r="I31" s="80">
         <v>7</v>
@@ -4339,35 +4313,35 @@
         <v>169</v>
       </c>
     </row>
-    <row r="32" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="33">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>264</v>
+        <v>311</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F32" s="103" t="s">
-        <v>400</v>
+        <v>63</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="I32" s="123" t="s">
+        <v>312</v>
+      </c>
+      <c r="I32" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="J32" s="124"/>
-      <c r="K32" s="125" t="s">
+      <c r="J32" s="138"/>
+      <c r="K32" s="139" t="s">
         <v>78</v>
       </c>
-      <c r="L32" s="126"/>
-      <c r="M32" s="127"/>
+      <c r="L32" s="140"/>
+      <c r="M32" s="141"/>
       <c r="O32" s="83">
         <v>7</v>
       </c>
@@ -4384,25 +4358,25 @@
         <v>167</v>
       </c>
     </row>
-    <row r="33" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B33" s="33">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>317</v>
+        <v>242</v>
       </c>
       <c r="D33" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="F33" s="103" t="s">
-        <v>347</v>
+        <v>234</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>318</v>
+        <v>243</v>
       </c>
       <c r="O33" s="83">
         <v>8</v>
@@ -4426,19 +4400,19 @@
         <v>17</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D34" s="1">
-        <v>6</v>
+        <v>307</v>
+      </c>
+      <c r="D34" s="90" t="s">
+        <v>56</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>65</v>
+        <v>237</v>
+      </c>
+      <c r="F34" s="103" t="s">
+        <v>63</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>243</v>
+        <v>309</v>
       </c>
       <c r="O34" s="83">
         <v>9</v>
@@ -4456,13 +4430,13 @@
         <v>171</v>
       </c>
     </row>
-    <row r="35" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="33">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="D35" s="90" t="s">
         <v>56</v>
@@ -4471,10 +4445,10 @@
         <v>237</v>
       </c>
       <c r="F35" s="103" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="O35" s="80">
         <v>10</v>
@@ -4492,13 +4466,13 @@
         <v>172</v>
       </c>
     </row>
-    <row r="36" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="33">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="D36" s="90" t="s">
         <v>56</v>
@@ -4507,20 +4481,20 @@
         <v>237</v>
       </c>
       <c r="F36" s="103" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="O36" s="123" t="s">
+        <v>305</v>
+      </c>
+      <c r="O36" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="P36" s="124"/>
-      <c r="Q36" s="125" t="s">
+      <c r="P36" s="138"/>
+      <c r="Q36" s="139" t="s">
         <v>237</v>
       </c>
-      <c r="R36" s="126"/>
-      <c r="S36" s="127"/>
+      <c r="R36" s="140"/>
+      <c r="S36" s="141"/>
     </row>
     <row r="37" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="33">
@@ -4528,19 +4502,19 @@
         <v>20</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="D37" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>237</v>
+        <v>387</v>
+      </c>
+      <c r="D37" s="1">
+        <v>1</v>
+      </c>
+      <c r="E37" s="102" t="s">
+        <v>379</v>
       </c>
       <c r="F37" s="103" t="s">
-        <v>348</v>
+        <v>394</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>305</v>
+        <v>380</v>
       </c>
     </row>
     <row r="38" spans="2:19" ht="33" x14ac:dyDescent="0.3">
@@ -4549,37 +4523,37 @@
         <v>21</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="D38" s="1">
         <v>1</v>
       </c>
       <c r="E38" s="102" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="F38" s="103" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="I38" s="120" t="s">
+        <v>363</v>
+      </c>
+      <c r="I38" s="119" t="s">
         <v>102</v>
       </c>
       <c r="J38" s="121"/>
-      <c r="K38" s="120" t="s">
+      <c r="K38" s="119" t="s">
         <v>122</v>
       </c>
-      <c r="L38" s="122"/>
+      <c r="L38" s="120"/>
       <c r="M38" s="121"/>
-      <c r="O38" s="120" t="s">
+      <c r="O38" s="119" t="s">
         <v>102</v>
       </c>
       <c r="P38" s="121"/>
-      <c r="Q38" s="120" t="s">
+      <c r="Q38" s="119" t="s">
         <v>173</v>
       </c>
-      <c r="R38" s="122"/>
+      <c r="R38" s="120"/>
       <c r="S38" s="121"/>
     </row>
     <row r="39" spans="2:19" x14ac:dyDescent="0.3">
@@ -4602,24 +4576,24 @@
       <c r="G39" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="I39" s="130" t="s">
+      <c r="I39" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="J39" s="131"/>
-      <c r="K39" s="132" t="s">
+      <c r="J39" s="129"/>
+      <c r="K39" s="130" t="s">
         <v>123</v>
       </c>
-      <c r="L39" s="133"/>
-      <c r="M39" s="134"/>
-      <c r="O39" s="130" t="s">
+      <c r="L39" s="131"/>
+      <c r="M39" s="132"/>
+      <c r="O39" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="P39" s="131"/>
-      <c r="Q39" s="132" t="s">
+      <c r="P39" s="129"/>
+      <c r="Q39" s="130" t="s">
         <v>233</v>
       </c>
-      <c r="R39" s="133"/>
-      <c r="S39" s="134"/>
+      <c r="R39" s="131"/>
+      <c r="S39" s="132"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B40" s="33">
@@ -4641,24 +4615,24 @@
       <c r="G40" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="I40" s="130" t="s">
+      <c r="I40" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="J40" s="131"/>
-      <c r="K40" s="132" t="s">
+      <c r="J40" s="129"/>
+      <c r="K40" s="130" t="s">
         <v>107</v>
       </c>
-      <c r="L40" s="133"/>
-      <c r="M40" s="134"/>
-      <c r="O40" s="130" t="s">
+      <c r="L40" s="131"/>
+      <c r="M40" s="132"/>
+      <c r="O40" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="P40" s="131"/>
-      <c r="Q40" s="130" t="s">
+      <c r="P40" s="129"/>
+      <c r="Q40" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="R40" s="135"/>
-      <c r="S40" s="131"/>
+      <c r="R40" s="142"/>
+      <c r="S40" s="129"/>
     </row>
     <row r="41" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="33">
@@ -4675,29 +4649,29 @@
         <v>36</v>
       </c>
       <c r="F41" s="98" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="G41" s="99" t="s">
         <v>275</v>
       </c>
-      <c r="I41" s="136" t="s">
+      <c r="I41" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="137"/>
-      <c r="K41" s="138" t="s">
+      <c r="J41" s="123"/>
+      <c r="K41" s="124" t="s">
         <v>125</v>
       </c>
-      <c r="L41" s="119"/>
-      <c r="M41" s="139"/>
-      <c r="O41" s="136" t="s">
+      <c r="L41" s="125"/>
+      <c r="M41" s="126"/>
+      <c r="O41" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="P41" s="137"/>
-      <c r="Q41" s="138" t="s">
+      <c r="P41" s="123"/>
+      <c r="Q41" s="124" t="s">
         <v>174</v>
       </c>
-      <c r="R41" s="119"/>
-      <c r="S41" s="139"/>
+      <c r="R41" s="125"/>
+      <c r="S41" s="126"/>
     </row>
     <row r="42" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="33">
@@ -4722,27 +4696,27 @@
       <c r="I42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J42" s="128" t="s">
+      <c r="J42" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="K42" s="128"/>
-      <c r="L42" s="128"/>
+      <c r="K42" s="127"/>
+      <c r="L42" s="127"/>
       <c r="M42" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P42" s="128" t="s">
+      <c r="P42" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="Q42" s="128"/>
-      <c r="R42" s="128"/>
+      <c r="Q42" s="127"/>
+      <c r="R42" s="127"/>
       <c r="S42" s="69" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="33">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -4756,8 +4730,8 @@
       <c r="E43" s="114" t="s">
         <v>237</v>
       </c>
-      <c r="F43" s="114" t="s">
-        <v>238</v>
+      <c r="F43" s="98" t="s">
+        <v>388</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>248</v>
@@ -4765,22 +4739,22 @@
       <c r="I43" s="70">
         <v>1</v>
       </c>
-      <c r="J43" s="140" t="s">
+      <c r="J43" s="136" t="s">
         <v>20</v>
       </c>
-      <c r="K43" s="140"/>
-      <c r="L43" s="140"/>
+      <c r="K43" s="136"/>
+      <c r="L43" s="136"/>
       <c r="M43" s="71" t="s">
         <v>133</v>
       </c>
       <c r="O43" s="87">
         <v>1</v>
       </c>
-      <c r="P43" s="129" t="s">
+      <c r="P43" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="Q43" s="129"/>
-      <c r="R43" s="129"/>
+      <c r="Q43" s="143"/>
+      <c r="R43" s="143"/>
       <c r="S43" s="88" t="s">
         <v>132</v>
       </c>
@@ -4823,11 +4797,11 @@
       <c r="O44" s="80">
         <v>2</v>
       </c>
-      <c r="P44" s="119" t="s">
+      <c r="P44" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="Q44" s="119"/>
-      <c r="R44" s="119"/>
+      <c r="Q44" s="125"/>
+      <c r="R44" s="125"/>
       <c r="S44" s="82" t="s">
         <v>133</v>
       </c>
@@ -4883,25 +4857,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B46" s="33">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>218</v>
+        <v>384</v>
       </c>
       <c r="D46" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E46" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>234</v>
       </c>
       <c r="F46" s="103" t="s">
-        <v>352</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>220</v>
+        <v>255</v>
+      </c>
+      <c r="G46" s="99" t="s">
+        <v>195</v>
       </c>
       <c r="I46" s="76">
         <v>2</v>
@@ -4934,25 +4908,25 @@
         <v>154</v>
       </c>
     </row>
-    <row r="47" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="33">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C47" s="112" t="s">
-        <v>219</v>
-      </c>
-      <c r="D47" s="113" t="s">
+      <c r="C47" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D47" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="111" t="s">
+      <c r="E47" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="F47" s="115" t="s">
-        <v>385</v>
-      </c>
-      <c r="G47" s="112" t="s">
-        <v>221</v>
+      <c r="F47" s="103" t="s">
+        <v>340</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="I47" s="80">
         <v>3</v>
@@ -4985,35 +4959,35 @@
         <v>155</v>
       </c>
     </row>
-    <row r="48" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B48" s="33">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="D48" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="I48" s="123" t="s">
+      <c r="C48" s="112" t="s">
+        <v>219</v>
+      </c>
+      <c r="D48" s="113" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" s="111" t="s">
+        <v>234</v>
+      </c>
+      <c r="F48" s="115" t="s">
+        <v>372</v>
+      </c>
+      <c r="G48" s="112" t="s">
+        <v>221</v>
+      </c>
+      <c r="I48" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="J48" s="124"/>
-      <c r="K48" s="125" t="s">
+      <c r="J48" s="138"/>
+      <c r="K48" s="139" t="s">
         <v>65</v>
       </c>
-      <c r="L48" s="126"/>
-      <c r="M48" s="127"/>
+      <c r="L48" s="140"/>
+      <c r="M48" s="141"/>
       <c r="O48" s="83">
         <v>3</v>
       </c>
@@ -5030,25 +5004,25 @@
         <v>180</v>
       </c>
     </row>
-    <row r="49" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B49" s="33">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="D49" s="1">
-        <v>1</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>237</v>
+        <v>335</v>
+      </c>
+      <c r="D49" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="F49" s="103" t="s">
-        <v>238</v>
+        <v>388</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>301</v>
+        <v>336</v>
       </c>
       <c r="O49" s="83">
         <v>4</v>
@@ -5072,19 +5046,19 @@
         <v>33</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="D50" s="90" t="s">
-        <v>49</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>280</v>
+        <v>299</v>
+      </c>
+      <c r="D50" s="1">
+        <v>1</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F50" s="103" t="s">
+        <v>238</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>54</v>
+        <v>301</v>
       </c>
       <c r="O50" s="83">
         <v>5</v>
@@ -5108,28 +5082,28 @@
         <v>34</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D51" s="90" t="s">
+        <v>49</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D51" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="G51" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I51" s="120" t="s">
+        <v>54</v>
+      </c>
+      <c r="I51" s="119" t="s">
         <v>102</v>
       </c>
       <c r="J51" s="121"/>
-      <c r="K51" s="120" t="s">
+      <c r="K51" s="119" t="s">
         <v>129</v>
       </c>
-      <c r="L51" s="122"/>
+      <c r="L51" s="120"/>
       <c r="M51" s="121"/>
       <c r="O51" s="83">
         <v>6</v>
@@ -5147,35 +5121,35 @@
         <v>168</v>
       </c>
     </row>
-    <row r="52" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B52" s="33">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>222</v>
+        <v>280</v>
       </c>
       <c r="D52" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="F52" s="103" t="s">
-        <v>48</v>
+        <v>279</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="I52" s="130" t="s">
+        <v>52</v>
+      </c>
+      <c r="I52" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="J52" s="131"/>
-      <c r="K52" s="132" t="s">
+      <c r="J52" s="129"/>
+      <c r="K52" s="130" t="s">
         <v>130</v>
       </c>
-      <c r="L52" s="133"/>
-      <c r="M52" s="134"/>
+      <c r="L52" s="131"/>
+      <c r="M52" s="132"/>
       <c r="O52" s="83">
         <v>7</v>
       </c>
@@ -5192,35 +5166,35 @@
         <v>182</v>
       </c>
     </row>
-    <row r="53" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B53" s="33">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>387</v>
+        <v>222</v>
       </c>
       <c r="D53" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
+      </c>
+      <c r="F53" s="103" t="s">
+        <v>48</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="I53" s="130" t="s">
+        <v>224</v>
+      </c>
+      <c r="I53" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="J53" s="131"/>
-      <c r="K53" s="132" t="s">
+      <c r="J53" s="129"/>
+      <c r="K53" s="130" t="s">
         <v>107</v>
       </c>
-      <c r="L53" s="133"/>
-      <c r="M53" s="134"/>
+      <c r="L53" s="131"/>
+      <c r="M53" s="132"/>
       <c r="O53" s="83">
         <v>8</v>
       </c>
@@ -5243,29 +5217,29 @@
         <v>37</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="D54" s="1">
-        <v>1</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
+      </c>
+      <c r="D54" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="I54" s="136" t="s">
+        <v>375</v>
+      </c>
+      <c r="I54" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="137"/>
-      <c r="K54" s="138" t="s">
+      <c r="J54" s="123"/>
+      <c r="K54" s="124" t="s">
         <v>131</v>
       </c>
-      <c r="L54" s="119"/>
-      <c r="M54" s="139"/>
+      <c r="L54" s="125"/>
+      <c r="M54" s="126"/>
       <c r="O54" s="83">
         <v>9</v>
       </c>
@@ -5288,28 +5262,28 @@
         <v>38</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="D55" s="1">
         <v>1</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="I55" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J55" s="128" t="s">
+      <c r="J55" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="K55" s="128"/>
-      <c r="L55" s="128"/>
+      <c r="K55" s="127"/>
+      <c r="L55" s="127"/>
       <c r="M55" s="69" t="s">
         <v>8</v>
       </c>
@@ -5335,40 +5309,40 @@
         <v>39</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="D56" s="1">
         <v>1</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="I56" s="87">
         <v>1</v>
       </c>
-      <c r="J56" s="129" t="s">
+      <c r="J56" s="143" t="s">
         <v>20</v>
       </c>
-      <c r="K56" s="129"/>
-      <c r="L56" s="129"/>
+      <c r="K56" s="143"/>
+      <c r="L56" s="143"/>
       <c r="M56" s="88" t="s">
         <v>133</v>
       </c>
-      <c r="O56" s="123" t="s">
+      <c r="O56" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="P56" s="124"/>
-      <c r="Q56" s="125" t="s">
+      <c r="P56" s="138"/>
+      <c r="Q56" s="139" t="s">
         <v>238</v>
       </c>
-      <c r="R56" s="126"/>
-      <c r="S56" s="127"/>
+      <c r="R56" s="140"/>
+      <c r="S56" s="141"/>
     </row>
     <row r="57" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="33">
@@ -5376,28 +5350,28 @@
         <v>40</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="D57" s="1">
         <v>1</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="I57" s="80">
         <v>2</v>
       </c>
-      <c r="J57" s="119" t="s">
+      <c r="J57" s="125" t="s">
         <v>55</v>
       </c>
-      <c r="K57" s="119"/>
-      <c r="L57" s="119"/>
+      <c r="K57" s="125"/>
+      <c r="L57" s="125"/>
       <c r="M57" s="89" t="s">
         <v>134</v>
       </c>
@@ -5408,19 +5382,19 @@
         <v>41</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="D58" s="33">
-        <v>1</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>358</v>
+        <v>351</v>
+      </c>
+      <c r="D58" s="1">
+        <v>1</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>366</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="I58" s="67" t="s">
         <v>41</v>
@@ -5437,14 +5411,14 @@
       <c r="M58" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="120" t="s">
+      <c r="O58" s="119" t="s">
         <v>102</v>
       </c>
       <c r="P58" s="121"/>
-      <c r="Q58" s="120" t="s">
+      <c r="Q58" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="R58" s="122"/>
+      <c r="R58" s="120"/>
       <c r="S58" s="121"/>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
@@ -5453,19 +5427,19 @@
         <v>42</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D59" s="90" t="s">
-        <v>20</v>
+        <v>352</v>
+      </c>
+      <c r="D59" s="33">
+        <v>1</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>235</v>
+        <v>346</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>44</v>
+        <v>333</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>193</v>
+        <v>362</v>
       </c>
       <c r="I59" s="72">
         <v>1</v>
@@ -5482,35 +5456,35 @@
       <c r="M59" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="O59" s="130" t="s">
+      <c r="O59" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="P59" s="131"/>
-      <c r="Q59" s="132" t="s">
+      <c r="P59" s="129"/>
+      <c r="Q59" s="130" t="s">
         <v>233</v>
       </c>
-      <c r="R59" s="133"/>
-      <c r="S59" s="134"/>
-    </row>
-    <row r="60" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+      <c r="R59" s="131"/>
+      <c r="S59" s="132"/>
+    </row>
+    <row r="60" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B60" s="33">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>395</v>
+        <v>192</v>
       </c>
       <c r="D60" s="90" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="F60" s="103" t="s">
-        <v>254</v>
-      </c>
-      <c r="G60" s="99" t="s">
-        <v>194</v>
+      <c r="F60" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>193</v>
       </c>
       <c r="I60" s="76">
         <v>2</v>
@@ -5527,15 +5501,15 @@
       <c r="M60" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="O60" s="130" t="s">
+      <c r="O60" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="P60" s="131"/>
-      <c r="Q60" s="130" t="s">
+      <c r="P60" s="129"/>
+      <c r="Q60" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="R60" s="135"/>
-      <c r="S60" s="131"/>
+      <c r="R60" s="142"/>
+      <c r="S60" s="129"/>
     </row>
     <row r="61" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="33">
@@ -5572,15 +5546,15 @@
       <c r="M61" s="85" t="s">
         <v>145</v>
       </c>
-      <c r="O61" s="136" t="s">
+      <c r="O61" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="P61" s="137"/>
-      <c r="Q61" s="138" t="s">
+      <c r="P61" s="123"/>
+      <c r="Q61" s="124" t="s">
         <v>185</v>
       </c>
-      <c r="R61" s="119"/>
-      <c r="S61" s="139"/>
+      <c r="R61" s="125"/>
+      <c r="S61" s="126"/>
     </row>
     <row r="62" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B62" s="33">
@@ -5620,11 +5594,11 @@
       <c r="O62" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P62" s="128" t="s">
+      <c r="P62" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="Q62" s="128"/>
-      <c r="R62" s="128"/>
+      <c r="Q62" s="127"/>
+      <c r="R62" s="127"/>
       <c r="S62" s="69" t="s">
         <v>8</v>
       </c>
@@ -5667,11 +5641,11 @@
       <c r="O63" s="87">
         <v>1</v>
       </c>
-      <c r="P63" s="129" t="s">
+      <c r="P63" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="Q63" s="129"/>
-      <c r="R63" s="129"/>
+      <c r="Q63" s="143"/>
+      <c r="R63" s="143"/>
       <c r="S63" s="88" t="s">
         <v>132</v>
       </c>
@@ -5682,19 +5656,19 @@
         <v>47</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="D64" s="1">
-        <v>1</v>
+        <v>287</v>
+      </c>
+      <c r="D64" s="90" t="s">
+        <v>57</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>237</v>
+        <v>43</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>216</v>
+        <v>61</v>
       </c>
       <c r="I64" s="83">
         <v>6</v>
@@ -5714,11 +5688,11 @@
       <c r="O64" s="80">
         <v>2</v>
       </c>
-      <c r="P64" s="119" t="s">
+      <c r="P64" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="Q64" s="119"/>
-      <c r="R64" s="119"/>
+      <c r="Q64" s="125"/>
+      <c r="R64" s="125"/>
       <c r="S64" s="82" t="s">
         <v>133</v>
       </c>
@@ -5729,19 +5703,19 @@
         <v>48</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="D65" s="90" t="s">
-        <v>57</v>
+        <v>240</v>
+      </c>
+      <c r="D65" s="1">
+        <v>6</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>43</v>
+        <v>237</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>61</v>
+        <v>241</v>
       </c>
       <c r="I65" s="83">
         <v>7</v>
@@ -5774,25 +5748,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B66" s="33">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="D66" s="1">
-        <v>6</v>
-      </c>
-      <c r="E66" s="1" t="s">
+      <c r="C66" s="97" t="s">
+        <v>276</v>
+      </c>
+      <c r="D66" s="101" t="s">
+        <v>45</v>
+      </c>
+      <c r="E66" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="F66" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>241</v>
+      <c r="F66" s="98" t="s">
+        <v>42</v>
+      </c>
+      <c r="G66" s="99" t="s">
+        <v>50</v>
       </c>
       <c r="I66" s="83">
         <v>8</v>
@@ -5825,25 +5799,25 @@
         <v>154</v>
       </c>
     </row>
-    <row r="67" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B67" s="33">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="C67" s="97" t="s">
-        <v>276</v>
-      </c>
-      <c r="D67" s="101" t="s">
-        <v>45</v>
-      </c>
-      <c r="E67" s="33" t="s">
+      <c r="C67" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D67" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F67" s="98" t="s">
-        <v>42</v>
-      </c>
-      <c r="G67" s="99" t="s">
-        <v>50</v>
+      <c r="F67" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="I67" s="83">
         <v>9</v>
@@ -5882,19 +5856,19 @@
         <v>51</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D68" s="90" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>58</v>
+        <v>237</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>59</v>
+        <v>304</v>
       </c>
       <c r="I68" s="83">
         <v>10</v>
@@ -5927,13 +5901,13 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B69" s="33">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D69" s="90" t="s">
         <v>56</v>
@@ -5941,11 +5915,11 @@
       <c r="E69" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F69" s="2" t="s">
-        <v>237</v>
+      <c r="F69" s="103" t="s">
+        <v>389</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="I69" s="83">
         <v>11</v>
@@ -5978,13 +5952,13 @@
         <v>181</v>
       </c>
     </row>
-    <row r="70" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B70" s="33">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D70" s="90" t="s">
         <v>56</v>
@@ -5993,10 +5967,10 @@
         <v>44</v>
       </c>
       <c r="F70" s="103" t="s">
-        <v>333</v>
+        <v>389</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>332</v>
+        <v>305</v>
       </c>
       <c r="I70" s="83">
         <v>12</v>
@@ -6035,19 +6009,19 @@
         <v>54</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="D71" s="90" t="s">
-        <v>56</v>
+        <v>286</v>
+      </c>
+      <c r="D71" s="1">
+        <v>5</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>305</v>
+        <v>60</v>
       </c>
       <c r="I71" s="80">
         <v>13</v>
@@ -6086,38 +6060,38 @@
         <v>55</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>286</v>
+        <v>378</v>
       </c>
       <c r="D72" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>64</v>
+        <v>237</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="I72" s="123" t="s">
+        <v>216</v>
+      </c>
+      <c r="I72" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="J72" s="124"/>
-      <c r="K72" s="125" t="s">
+      <c r="J72" s="138"/>
+      <c r="K72" s="139" t="s">
         <v>58</v>
       </c>
-      <c r="L72" s="126"/>
-      <c r="M72" s="127"/>
-      <c r="O72" s="123" t="s">
+      <c r="L72" s="140"/>
+      <c r="M72" s="141"/>
+      <c r="O72" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="P72" s="124"/>
-      <c r="Q72" s="125" t="s">
+      <c r="P72" s="138"/>
+      <c r="Q72" s="139" t="s">
         <v>239</v>
       </c>
-      <c r="R72" s="126"/>
-      <c r="S72" s="127"/>
+      <c r="R72" s="140"/>
+      <c r="S72" s="141"/>
     </row>
     <row r="73" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B73" s="33">
@@ -6131,7 +6105,7 @@
         <v>20</v>
       </c>
       <c r="E73" s="102" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>237</v>
@@ -6203,25 +6177,25 @@
         <v>214</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B77" s="33">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>204</v>
+        <v>381</v>
       </c>
       <c r="D77" s="90" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F77" s="111" t="s">
-        <v>234</v>
-      </c>
-      <c r="G77" s="5" t="s">
-        <v>206</v>
+        <v>235</v>
+      </c>
+      <c r="F77" s="103" t="s">
+        <v>254</v>
+      </c>
+      <c r="G77" s="99" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.3">
@@ -6229,10 +6203,10 @@
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
-      <c r="C78" s="112" t="s">
-        <v>205</v>
-      </c>
-      <c r="D78" s="113" t="s">
+      <c r="C78" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D78" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E78" s="1" t="s">
@@ -6241,8 +6215,8 @@
       <c r="F78" s="111" t="s">
         <v>234</v>
       </c>
-      <c r="G78" s="112" t="s">
-        <v>207</v>
+      <c r="G78" s="5" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.3">
@@ -6250,20 +6224,20 @@
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D79" s="1">
-        <v>1</v>
+      <c r="C79" s="112" t="s">
+        <v>205</v>
+      </c>
+      <c r="D79" s="113" t="s">
+        <v>20</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="G79" s="5" t="s">
-        <v>209</v>
+        <v>62</v>
+      </c>
+      <c r="F79" s="111" t="s">
+        <v>234</v>
+      </c>
+      <c r="G79" s="112" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.3">
@@ -6272,7 +6246,7 @@
         <v>63</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>199</v>
+        <v>339</v>
       </c>
       <c r="D80" s="1">
         <v>1</v>
@@ -6280,53 +6254,53 @@
       <c r="E80" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F80" s="2" t="s">
+      <c r="F80" s="1" t="s">
         <v>237</v>
       </c>
       <c r="G80" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B81" s="33">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D81" s="1">
+        <v>1</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G81" s="5" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="81" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B81" s="33">
-        <f t="shared" si="1"/>
-        <v>64</v>
-      </c>
-      <c r="C81" s="3" t="s">
+    <row r="82" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B82" s="33">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="D81" s="101" t="s">
+      <c r="D82" s="101" t="s">
         <v>46</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="E82" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F81" s="2" t="s">
+      <c r="F82" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="G81" s="5" t="s">
+      <c r="G82" s="5" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B82" s="33">
-        <f t="shared" si="1"/>
-        <v>65</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D82" s="1">
-        <v>1</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G82" s="5" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.3">
@@ -6335,19 +6309,19 @@
         <v>66</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D83" s="90" t="s">
-        <v>20</v>
+        <v>203</v>
+      </c>
+      <c r="D83" s="1">
+        <v>1</v>
       </c>
       <c r="E83" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F83" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F83" s="103" t="s">
-        <v>234</v>
-      </c>
       <c r="G83" s="5" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.3">
@@ -6355,41 +6329,41 @@
         <f t="shared" si="2"/>
         <v>67</v>
       </c>
-      <c r="C84" s="97" t="s">
+      <c r="C84" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D84" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F84" s="103" t="s">
+        <v>234</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B85" s="33">
+        <f t="shared" si="2"/>
+        <v>68</v>
+      </c>
+      <c r="C85" s="97" t="s">
         <v>190</v>
       </c>
-      <c r="D84" s="90" t="s">
+      <c r="D85" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="E84" s="33" t="s">
+      <c r="E85" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="F84" s="98" t="s">
-        <v>337</v>
-      </c>
-      <c r="G84" s="99" t="s">
+      <c r="F85" s="98" t="s">
+        <v>328</v>
+      </c>
+      <c r="G85" s="99" t="s">
         <v>191</v>
-      </c>
-    </row>
-    <row r="85" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B85" s="33">
-        <f t="shared" si="2"/>
-        <v>68</v>
-      </c>
-      <c r="C85" s="93" t="s">
-        <v>397</v>
-      </c>
-      <c r="D85" s="94" t="s">
-        <v>21</v>
-      </c>
-      <c r="E85" s="92" t="s">
-        <v>35</v>
-      </c>
-      <c r="F85" s="95" t="s">
-        <v>390</v>
-      </c>
-      <c r="G85" s="96" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.3">
@@ -6413,88 +6387,88 @@
         <v>38</v>
       </c>
     </row>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B87" s="33">
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="C87" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="D87" s="90" t="s">
+      <c r="C87" s="93" t="s">
+        <v>383</v>
+      </c>
+      <c r="D87" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="F87" s="2" t="s">
+      <c r="E87" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="G87" s="5" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="88" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+      <c r="F87" s="95" t="s">
+        <v>377</v>
+      </c>
+      <c r="G87" s="96" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B88" s="33">
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
-      <c r="C88" s="104" t="s">
+      <c r="C88" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D88" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B89" s="33">
+        <f t="shared" si="2"/>
+        <v>72</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="D89" s="1">
+        <v>1</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="F89" s="103" t="s">
+        <v>393</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+      <c r="B90" s="33">
+        <f t="shared" si="2"/>
+        <v>73</v>
+      </c>
+      <c r="C90" s="104" t="s">
         <v>256</v>
       </c>
-      <c r="D88" s="109" t="s">
+      <c r="D90" s="109" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="105" t="s">
+      <c r="E90" s="105" t="s">
         <v>238</v>
       </c>
-      <c r="F88" s="110" t="s">
-        <v>354</v>
-      </c>
-      <c r="G88" s="107" t="s">
+      <c r="F90" s="110" t="s">
+        <v>342</v>
+      </c>
+      <c r="G90" s="107" t="s">
         <v>259</v>
-      </c>
-    </row>
-    <row r="89" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B89" s="33">
-        <f t="shared" si="2"/>
-        <v>72</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="D89" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E89" s="103" t="s">
-        <v>238</v>
-      </c>
-      <c r="F89" s="103" t="s">
-        <v>239</v>
-      </c>
-      <c r="G89" s="5" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="90" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B90" s="33">
-        <f t="shared" si="2"/>
-        <v>73</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="D90" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E90" s="103" t="s">
-        <v>238</v>
-      </c>
-      <c r="F90" s="103" t="s">
-        <v>381</v>
-      </c>
-      <c r="G90" s="5" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.3">
@@ -6503,19 +6477,19 @@
         <v>74</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="D91" s="1">
-        <v>1</v>
-      </c>
-      <c r="E91" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D91" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E91" s="103" t="s">
         <v>238</v>
       </c>
       <c r="F91" s="103" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>376</v>
+        <v>310</v>
       </c>
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.3">
@@ -6523,20 +6497,20 @@
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="C92" s="104" t="s">
-        <v>250</v>
-      </c>
-      <c r="D92" s="105">
-        <v>1</v>
-      </c>
-      <c r="E92" s="105" t="s">
+      <c r="C92" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D92" s="1">
+        <v>1</v>
+      </c>
+      <c r="E92" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="F92" s="106" t="s">
-        <v>14</v>
-      </c>
-      <c r="G92" s="107" t="s">
-        <v>252</v>
+      <c r="F92" s="103" t="s">
+        <v>333</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.3">
@@ -6544,62 +6518,62 @@
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C93" s="104" t="s">
+        <v>250</v>
+      </c>
+      <c r="D93" s="105">
+        <v>1</v>
+      </c>
+      <c r="E93" s="105" t="s">
+        <v>238</v>
+      </c>
+      <c r="F93" s="106" t="s">
+        <v>14</v>
+      </c>
+      <c r="G93" s="107" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B94" s="33">
+        <f t="shared" si="2"/>
+        <v>77</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="D93" s="1">
-        <v>1</v>
-      </c>
-      <c r="E93" s="2" t="s">
+      <c r="D94" s="1">
+        <v>1</v>
+      </c>
+      <c r="E94" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="F93" s="2" t="s">
+      <c r="F94" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="G93" s="5" t="s">
+      <c r="G94" s="5" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="94" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B94" s="33">
-        <f t="shared" si="2"/>
-        <v>77</v>
-      </c>
-      <c r="C94" s="104" t="s">
+    <row r="95" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B95" s="33">
+        <f t="shared" si="2"/>
+        <v>78</v>
+      </c>
+      <c r="C95" s="104" t="s">
         <v>251</v>
       </c>
-      <c r="D94" s="105">
-        <v>1</v>
-      </c>
-      <c r="E94" s="105" t="s">
+      <c r="D95" s="105">
+        <v>1</v>
+      </c>
+      <c r="E95" s="105" t="s">
         <v>238</v>
       </c>
-      <c r="F94" s="108" t="s">
+      <c r="F95" s="108" t="s">
         <v>73</v>
       </c>
-      <c r="G94" s="107" t="s">
+      <c r="G95" s="107" t="s">
         <v>253</v>
-      </c>
-    </row>
-    <row r="95" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B95" s="33">
-        <f t="shared" si="2"/>
-        <v>78</v>
-      </c>
-      <c r="C95" s="112" t="s">
-        <v>260</v>
-      </c>
-      <c r="D95" s="113" t="s">
-        <v>20</v>
-      </c>
-      <c r="E95" s="111" t="s">
-        <v>238</v>
-      </c>
-      <c r="F95" s="118" t="s">
-        <v>342</v>
-      </c>
-      <c r="G95" s="112" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.3">
@@ -6607,20 +6581,20 @@
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
-      <c r="C96" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="D96" s="1">
-        <v>1</v>
-      </c>
-      <c r="E96" s="103" t="s">
+      <c r="C96" s="112" t="s">
+        <v>260</v>
+      </c>
+      <c r="D96" s="113" t="s">
+        <v>20</v>
+      </c>
+      <c r="E96" s="111" t="s">
         <v>238</v>
       </c>
-      <c r="F96" s="103" t="s">
-        <v>239</v>
-      </c>
-      <c r="G96" s="5" t="s">
-        <v>319</v>
+      <c r="F96" s="118" t="s">
+        <v>333</v>
+      </c>
+      <c r="G96" s="112" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="97" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6629,7 +6603,7 @@
         <v>80</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="D97" s="90" t="s">
         <v>56</v>
@@ -6638,10 +6612,10 @@
         <v>238</v>
       </c>
       <c r="F97" s="103" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
     </row>
     <row r="98" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6650,7 +6624,7 @@
         <v>81</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="D98" s="1">
         <v>1</v>
@@ -6659,7 +6633,7 @@
         <v>238</v>
       </c>
       <c r="F98" s="103" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="G98" s="5" t="s">
         <v>302</v>
@@ -6671,19 +6645,19 @@
         <v>82</v>
       </c>
       <c r="C99" s="104" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="D99" s="109" t="s">
         <v>20</v>
       </c>
       <c r="E99" s="117" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="F99" s="106" t="s">
         <v>17</v>
       </c>
       <c r="G99" s="107" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.3">
@@ -6692,7 +6666,7 @@
         <v>83</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="D100" s="90" t="s">
         <v>20</v>
@@ -6701,10 +6675,10 @@
         <v>238</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
     </row>
     <row r="101" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
@@ -6722,7 +6696,7 @@
         <v>239</v>
       </c>
       <c r="F101" s="103" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="G101" s="5" t="s">
         <v>273</v>
@@ -6734,19 +6708,19 @@
         <v>85</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="D102" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E102" s="103" t="s">
+        <v>268</v>
+      </c>
+      <c r="D102" s="1">
+        <v>1</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>239</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>316</v>
+        <v>271</v>
       </c>
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.3">
@@ -6755,152 +6729,98 @@
         <v>86</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="D103" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G103" s="5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B104" s="33">
+        <f t="shared" si="2"/>
+        <v>87</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D104" s="90" t="s">
         <v>56</v>
       </c>
-      <c r="E103" s="103" t="s">
+      <c r="E104" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F103" s="103" t="s">
-        <v>62</v>
-      </c>
-      <c r="G103" s="5" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="104" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B104" s="33">
-        <f t="shared" si="2"/>
-        <v>87</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="D104" s="1">
-        <v>1</v>
-      </c>
-      <c r="E104" s="2" t="s">
+      <c r="F104" s="103" t="s">
+        <v>344</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B105" s="33">
+        <f t="shared" si="2"/>
+        <v>88</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D105" s="1">
+        <v>1</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="F104" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G104" s="5" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="105" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B105" s="33">
-        <f t="shared" si="2"/>
-        <v>88</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="D105" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>62</v>
+      <c r="F105" s="103" t="s">
+        <v>344</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
     </row>
     <row r="106" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B106" s="33">
-        <f t="shared" si="2"/>
-        <v>89</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="D106" s="1">
-        <v>1</v>
-      </c>
-      <c r="E106" s="103" t="s">
-        <v>239</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G106" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="107" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B107" s="33">
-        <f t="shared" si="2"/>
-        <v>90</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="D107" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F107" s="103" t="s">
-        <v>356</v>
-      </c>
-      <c r="G107" s="5" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="108" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B108" s="33">
-        <f t="shared" si="2"/>
-        <v>91</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="D108" s="1">
-        <v>1</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="F108" s="103" t="s">
-        <v>356</v>
-      </c>
-      <c r="G108" s="5" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="109" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B109" s="33">
-        <f t="shared" si="2"/>
-        <v>92</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D109" s="1">
-        <v>1</v>
-      </c>
-      <c r="E109" s="102" t="s">
-        <v>392</v>
-      </c>
-      <c r="F109" s="103" t="s">
-        <v>394</v>
-      </c>
-      <c r="G109" s="5" t="s">
-        <v>393</v>
-      </c>
+      <c r="B106" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F106" s="103"/>
+    </row>
+    <row r="107" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B107" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F107" s="103"/>
+    </row>
+    <row r="108" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B108" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" s="103"/>
+    </row>
+    <row r="109" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B109" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F109" s="103"/>
     </row>
     <row r="110" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B110" s="33" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
+      <c r="F110" s="103"/>
     </row>
     <row r="111" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B111" s="33" t="str">
@@ -7089,39 +7009,51 @@
     </sortState>
   </autoFilter>
   <mergeCells count="102">
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="P44:R44"/>
+    <mergeCell ref="O56:P56"/>
+    <mergeCell ref="Q56:S56"/>
+    <mergeCell ref="P62:R62"/>
+    <mergeCell ref="P63:R63"/>
+    <mergeCell ref="P64:R64"/>
+    <mergeCell ref="O72:P72"/>
+    <mergeCell ref="Q72:S72"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="O59:P59"/>
+    <mergeCell ref="Q59:S59"/>
+    <mergeCell ref="O60:P60"/>
+    <mergeCell ref="Q60:S60"/>
+    <mergeCell ref="O61:P61"/>
+    <mergeCell ref="Q61:S61"/>
+    <mergeCell ref="P42:R42"/>
+    <mergeCell ref="P43:R43"/>
+    <mergeCell ref="O58:P58"/>
+    <mergeCell ref="Q58:S58"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="P22:R22"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:S18"/>
     <mergeCell ref="I72:J72"/>
     <mergeCell ref="K72:M72"/>
     <mergeCell ref="J57:L57"/>
@@ -7146,51 +7078,39 @@
     <mergeCell ref="K52:M52"/>
     <mergeCell ref="I40:J40"/>
     <mergeCell ref="K40:M40"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:S20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="O72:P72"/>
-    <mergeCell ref="Q72:S72"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="O59:P59"/>
-    <mergeCell ref="Q59:S59"/>
-    <mergeCell ref="O60:P60"/>
-    <mergeCell ref="Q60:S60"/>
-    <mergeCell ref="O61:P61"/>
-    <mergeCell ref="Q61:S61"/>
-    <mergeCell ref="P42:R42"/>
-    <mergeCell ref="P43:R43"/>
-    <mergeCell ref="O58:P58"/>
-    <mergeCell ref="Q58:S58"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="Q39:S39"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="Q41:S41"/>
-    <mergeCell ref="P22:R22"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="Q36:S36"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="P44:R44"/>
-    <mergeCell ref="O56:P56"/>
-    <mergeCell ref="Q56:S56"/>
-    <mergeCell ref="P62:R62"/>
-    <mergeCell ref="P63:R63"/>
-    <mergeCell ref="P64:R64"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7212,25 +7132,25 @@
   <sheetData>
     <row r="2" spans="2:8" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="G2" s="102" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="H2" s="102" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
